--- a/Stat Reviews/OT24_StatReview/scotusblog_replication/data/term_index.xlsx
+++ b/Stat Reviews/OT24_StatReview/scotusblog_replication/data/term_index.xlsx
@@ -1561,12 +1561,24 @@
       <c r="E3" t="n">
         <v>0</v>
       </c>
-      <c r="F3" s="1"/>
-      <c r="G3" s="1"/>
-      <c r="H3"/>
-      <c r="I3"/>
-      <c r="J3"/>
-      <c r="K3"/>
+      <c r="F3" s="1" t="n">
+        <v>45601</v>
+      </c>
+      <c r="G3" s="1" t="n">
+        <v>45776</v>
+      </c>
+      <c r="H3" t="n">
+        <v>176</v>
+      </c>
+      <c r="I3" t="s">
+        <v>39</v>
+      </c>
+      <c r="J3" t="s">
+        <v>20</v>
+      </c>
+      <c r="K3" t="s">
+        <v>59</v>
+      </c>
     </row>
     <row r="4">
       <c r="A4" t="s">
@@ -1956,12 +1968,24 @@
       <c r="E7" t="n">
         <v>0</v>
       </c>
-      <c r="F7" s="1"/>
-      <c r="G7" s="1"/>
-      <c r="H7"/>
-      <c r="I7"/>
-      <c r="J7"/>
-      <c r="K7"/>
+      <c r="F7" s="1" t="n">
+        <v>45635</v>
+      </c>
+      <c r="G7" s="1" t="n">
+        <v>45777</v>
+      </c>
+      <c r="H7" t="n">
+        <v>143</v>
+      </c>
+      <c r="I7" t="s">
+        <v>34</v>
+      </c>
+      <c r="J7" t="s">
+        <v>25</v>
+      </c>
+      <c r="K7" t="s">
+        <v>45</v>
+      </c>
     </row>
     <row r="8">
       <c r="A8" t="s">

--- a/Stat Reviews/OT24_StatReview/scotusblog_replication/data/term_index.xlsx
+++ b/Stat Reviews/OT24_StatReview/scotusblog_replication/data/term_index.xlsx
@@ -2292,12 +2292,24 @@
       <c r="E9" t="n">
         <v>0</v>
       </c>
-      <c r="F9" s="1"/>
-      <c r="G9" s="1"/>
-      <c r="H9"/>
-      <c r="I9"/>
-      <c r="J9"/>
-      <c r="K9"/>
+      <c r="F9" s="1" t="n">
+        <v>45679</v>
+      </c>
+      <c r="G9" s="1" t="n">
+        <v>45792</v>
+      </c>
+      <c r="H9" t="n">
+        <v>114</v>
+      </c>
+      <c r="I9" t="s">
+        <v>15</v>
+      </c>
+      <c r="J9" t="s">
+        <v>40</v>
+      </c>
+      <c r="K9" t="s">
+        <v>41</v>
+      </c>
     </row>
     <row r="10">
       <c r="A10" t="s">

--- a/Stat Reviews/OT24_StatReview/scotusblog_replication/data/term_index.xlsx
+++ b/Stat Reviews/OT24_StatReview/scotusblog_replication/data/term_index.xlsx
@@ -20,7 +20,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="196" uniqueCount="196">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="199" uniqueCount="199">
   <si>
     <t xml:space="preserve">sitting</t>
   </si>
@@ -110,6 +110,15 @@
   </si>
   <si>
     <t xml:space="preserve">(5-4)*</t>
+  </si>
+  <si>
+    <t xml:space="preserve">24A1007</t>
+  </si>
+  <si>
+    <t xml:space="preserve">A.A.R.P v. Trump</t>
+  </si>
+  <si>
+    <t xml:space="preserve">NDTX</t>
   </si>
   <si>
     <t xml:space="preserve">October</t>
@@ -1103,6 +1112,37 @@
         <v>16</v>
       </c>
     </row>
+    <row r="6">
+      <c r="A6" t="s">
+        <v>11</v>
+      </c>
+      <c r="B6" t="s">
+        <v>30</v>
+      </c>
+      <c r="C6" t="s">
+        <v>31</v>
+      </c>
+      <c r="D6" t="s">
+        <v>32</v>
+      </c>
+      <c r="E6" t="n">
+        <v>0</v>
+      </c>
+      <c r="F6" s="1"/>
+      <c r="G6" s="1" t="n">
+        <v>45793</v>
+      </c>
+      <c r="H6"/>
+      <c r="I6" t="s">
+        <v>24</v>
+      </c>
+      <c r="J6" t="s">
+        <v>20</v>
+      </c>
+      <c r="K6" t="s">
+        <v>16</v>
+      </c>
+    </row>
   </sheetData>
   <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
   <pageSetup paperSize="9" orientation="portrait" horizontalDpi="300" verticalDpi="300" r:id="rId2"/>
@@ -1151,16 +1191,16 @@
     </row>
     <row r="2">
       <c r="A2" t="s">
-        <v>30</v>
+        <v>33</v>
       </c>
       <c r="B2" t="s">
-        <v>31</v>
+        <v>34</v>
       </c>
       <c r="C2" t="s">
-        <v>32</v>
+        <v>35</v>
       </c>
       <c r="D2" t="s">
-        <v>33</v>
+        <v>36</v>
       </c>
       <c r="E2" t="n">
         <v>0</v>
@@ -1175,27 +1215,27 @@
         <v>138</v>
       </c>
       <c r="I2" t="s">
-        <v>34</v>
+        <v>37</v>
       </c>
       <c r="J2" t="s">
         <v>25</v>
       </c>
       <c r="K2" t="s">
-        <v>35</v>
+        <v>38</v>
       </c>
     </row>
     <row r="3">
       <c r="A3" t="s">
-        <v>30</v>
+        <v>33</v>
       </c>
       <c r="B3" t="s">
-        <v>36</v>
+        <v>39</v>
       </c>
       <c r="C3" t="s">
-        <v>37</v>
+        <v>40</v>
       </c>
       <c r="D3" t="s">
-        <v>38</v>
+        <v>41</v>
       </c>
       <c r="E3" t="n">
         <v>0</v>
@@ -1210,27 +1250,27 @@
         <v>101</v>
       </c>
       <c r="I3" t="s">
-        <v>39</v>
+        <v>42</v>
       </c>
       <c r="J3" t="s">
-        <v>40</v>
+        <v>43</v>
       </c>
       <c r="K3" t="s">
-        <v>41</v>
+        <v>44</v>
       </c>
     </row>
     <row r="4">
       <c r="A4" t="s">
-        <v>30</v>
+        <v>33</v>
       </c>
       <c r="B4" t="s">
-        <v>42</v>
+        <v>45</v>
       </c>
       <c r="C4" t="s">
-        <v>43</v>
+        <v>46</v>
       </c>
       <c r="D4" t="s">
-        <v>44</v>
+        <v>47</v>
       </c>
       <c r="E4" t="n">
         <v>0</v>
@@ -1245,27 +1285,27 @@
         <v>170</v>
       </c>
       <c r="I4" t="s">
-        <v>34</v>
+        <v>37</v>
       </c>
       <c r="J4" t="s">
         <v>20</v>
       </c>
       <c r="K4" t="s">
-        <v>45</v>
+        <v>48</v>
       </c>
     </row>
     <row r="5">
       <c r="A5" t="s">
-        <v>30</v>
+        <v>33</v>
       </c>
       <c r="B5" t="s">
-        <v>46</v>
+        <v>49</v>
       </c>
       <c r="C5" t="s">
-        <v>47</v>
+        <v>50</v>
       </c>
       <c r="D5" t="s">
-        <v>48</v>
+        <v>51</v>
       </c>
       <c r="E5" t="n">
         <v>0</v>
@@ -1280,27 +1320,27 @@
         <v>141</v>
       </c>
       <c r="I5" t="s">
-        <v>34</v>
+        <v>37</v>
       </c>
       <c r="J5" t="s">
         <v>20</v>
       </c>
       <c r="K5" t="s">
-        <v>49</v>
+        <v>52</v>
       </c>
     </row>
     <row r="6">
       <c r="A6" t="s">
-        <v>30</v>
+        <v>33</v>
       </c>
       <c r="B6" t="s">
-        <v>50</v>
+        <v>53</v>
       </c>
       <c r="C6" t="s">
-        <v>51</v>
+        <v>54</v>
       </c>
       <c r="D6" t="s">
-        <v>52</v>
+        <v>55</v>
       </c>
       <c r="E6" t="n">
         <v>1</v>
@@ -1315,27 +1355,27 @@
         <v>140</v>
       </c>
       <c r="I6" t="s">
-        <v>34</v>
+        <v>37</v>
       </c>
       <c r="J6" t="s">
-        <v>53</v>
+        <v>56</v>
       </c>
       <c r="K6" t="s">
-        <v>54</v>
+        <v>57</v>
       </c>
     </row>
     <row r="7">
       <c r="A7" t="s">
-        <v>30</v>
+        <v>33</v>
       </c>
       <c r="B7" t="s">
-        <v>55</v>
+        <v>58</v>
       </c>
       <c r="C7" t="s">
-        <v>56</v>
+        <v>59</v>
       </c>
       <c r="D7" t="s">
-        <v>57</v>
+        <v>60</v>
       </c>
       <c r="E7" t="n">
         <v>0</v>
@@ -1350,24 +1390,24 @@
         <v>170</v>
       </c>
       <c r="I7" t="s">
-        <v>58</v>
+        <v>61</v>
       </c>
       <c r="J7" t="s">
         <v>25</v>
       </c>
       <c r="K7" t="s">
-        <v>59</v>
+        <v>62</v>
       </c>
     </row>
     <row r="8">
       <c r="A8" t="s">
-        <v>30</v>
+        <v>33</v>
       </c>
       <c r="B8" t="s">
-        <v>60</v>
+        <v>63</v>
       </c>
       <c r="C8" t="s">
-        <v>61</v>
+        <v>64</v>
       </c>
       <c r="D8" t="s">
         <v>14</v>
@@ -1385,27 +1425,27 @@
         <v>57</v>
       </c>
       <c r="I8" t="s">
-        <v>39</v>
+        <v>42</v>
       </c>
       <c r="J8" t="s">
-        <v>40</v>
+        <v>43</v>
       </c>
       <c r="K8" t="s">
-        <v>62</v>
+        <v>65</v>
       </c>
     </row>
     <row r="9">
       <c r="A9" t="s">
-        <v>30</v>
+        <v>33</v>
       </c>
       <c r="B9" t="s">
-        <v>63</v>
+        <v>66</v>
       </c>
       <c r="C9" t="s">
-        <v>64</v>
+        <v>67</v>
       </c>
       <c r="D9" t="s">
-        <v>65</v>
+        <v>68</v>
       </c>
       <c r="E9" t="n">
         <v>0</v>
@@ -1420,27 +1460,27 @@
         <v>141</v>
       </c>
       <c r="I9" t="s">
-        <v>39</v>
+        <v>42</v>
       </c>
       <c r="J9" t="s">
         <v>20</v>
       </c>
       <c r="K9" t="s">
-        <v>66</v>
+        <v>69</v>
       </c>
     </row>
     <row r="10">
       <c r="A10" t="s">
-        <v>30</v>
+        <v>33</v>
       </c>
       <c r="B10" t="s">
-        <v>67</v>
+        <v>70</v>
       </c>
       <c r="C10" t="s">
-        <v>68</v>
+        <v>71</v>
       </c>
       <c r="D10" t="s">
-        <v>69</v>
+        <v>72</v>
       </c>
       <c r="E10" t="n">
         <v>0</v>
@@ -1455,13 +1495,13 @@
         <v>140</v>
       </c>
       <c r="I10" t="s">
-        <v>34</v>
+        <v>37</v>
       </c>
       <c r="J10" t="s">
-        <v>40</v>
+        <v>43</v>
       </c>
       <c r="K10" t="s">
-        <v>70</v>
+        <v>73</v>
       </c>
     </row>
   </sheetData>
@@ -1512,16 +1552,16 @@
     </row>
     <row r="2">
       <c r="A2" t="s">
-        <v>71</v>
+        <v>74</v>
       </c>
       <c r="B2" t="s">
-        <v>72</v>
+        <v>75</v>
       </c>
       <c r="C2" t="s">
-        <v>73</v>
+        <v>76</v>
       </c>
       <c r="D2" t="s">
-        <v>74</v>
+        <v>77</v>
       </c>
       <c r="E2" t="n">
         <v>0</v>
@@ -1536,27 +1576,27 @@
         <v>110</v>
       </c>
       <c r="I2" t="s">
-        <v>58</v>
+        <v>61</v>
       </c>
       <c r="J2" t="s">
-        <v>40</v>
+        <v>43</v>
       </c>
       <c r="K2" t="s">
-        <v>41</v>
+        <v>44</v>
       </c>
     </row>
     <row r="3">
       <c r="A3" t="s">
-        <v>71</v>
+        <v>74</v>
       </c>
       <c r="B3" t="s">
-        <v>75</v>
+        <v>78</v>
       </c>
       <c r="C3" t="s">
-        <v>76</v>
+        <v>79</v>
       </c>
       <c r="D3" t="s">
-        <v>77</v>
+        <v>80</v>
       </c>
       <c r="E3" t="n">
         <v>0</v>
@@ -1571,27 +1611,27 @@
         <v>176</v>
       </c>
       <c r="I3" t="s">
-        <v>39</v>
+        <v>42</v>
       </c>
       <c r="J3" t="s">
         <v>20</v>
       </c>
       <c r="K3" t="s">
-        <v>59</v>
+        <v>62</v>
       </c>
     </row>
     <row r="4">
       <c r="A4" t="s">
-        <v>71</v>
+        <v>74</v>
       </c>
       <c r="B4" t="s">
-        <v>78</v>
+        <v>81</v>
       </c>
       <c r="C4" t="s">
-        <v>79</v>
+        <v>82</v>
       </c>
       <c r="D4" t="s">
-        <v>48</v>
+        <v>51</v>
       </c>
       <c r="E4" t="n">
         <v>0</v>
@@ -1606,27 +1646,27 @@
         <v>72</v>
       </c>
       <c r="I4" t="s">
-        <v>34</v>
+        <v>37</v>
       </c>
       <c r="J4" t="s">
-        <v>40</v>
+        <v>43</v>
       </c>
       <c r="K4" t="s">
-        <v>35</v>
+        <v>38</v>
       </c>
     </row>
     <row r="5">
       <c r="A5" t="s">
-        <v>71</v>
+        <v>74</v>
       </c>
       <c r="B5" t="s">
-        <v>80</v>
+        <v>83</v>
       </c>
       <c r="C5" t="s">
-        <v>81</v>
+        <v>84</v>
       </c>
       <c r="D5" t="s">
-        <v>69</v>
+        <v>72</v>
       </c>
       <c r="E5" t="n">
         <v>0</v>
@@ -1641,7 +1681,7 @@
         <v>17</v>
       </c>
       <c r="I5" t="s">
-        <v>82</v>
+        <v>85</v>
       </c>
       <c r="J5" t="s">
         <v>16</v>
@@ -1652,16 +1692,16 @@
     </row>
     <row r="6">
       <c r="A6" t="s">
-        <v>71</v>
+        <v>74</v>
       </c>
       <c r="B6" t="s">
-        <v>83</v>
+        <v>86</v>
       </c>
       <c r="C6" t="s">
-        <v>84</v>
+        <v>87</v>
       </c>
       <c r="D6" t="s">
-        <v>57</v>
+        <v>60</v>
       </c>
       <c r="E6" t="n">
         <v>0</v>
@@ -1676,27 +1716,27 @@
         <v>162</v>
       </c>
       <c r="I6" t="s">
-        <v>34</v>
+        <v>37</v>
       </c>
       <c r="J6" t="s">
-        <v>85</v>
+        <v>88</v>
       </c>
       <c r="K6" t="s">
-        <v>45</v>
+        <v>48</v>
       </c>
     </row>
     <row r="7">
       <c r="A7" t="s">
-        <v>71</v>
+        <v>74</v>
       </c>
       <c r="B7" t="s">
-        <v>86</v>
+        <v>89</v>
       </c>
       <c r="C7" t="s">
-        <v>87</v>
+        <v>90</v>
       </c>
       <c r="D7" t="s">
-        <v>57</v>
+        <v>60</v>
       </c>
       <c r="E7" t="n">
         <v>0</v>
@@ -1711,27 +1751,27 @@
         <v>130</v>
       </c>
       <c r="I7" t="s">
-        <v>39</v>
+        <v>42</v>
       </c>
       <c r="J7" t="s">
         <v>20</v>
       </c>
       <c r="K7" t="s">
-        <v>66</v>
+        <v>69</v>
       </c>
     </row>
     <row r="8">
       <c r="A8" t="s">
-        <v>71</v>
+        <v>74</v>
       </c>
       <c r="B8" t="s">
-        <v>88</v>
+        <v>91</v>
       </c>
       <c r="C8" t="s">
-        <v>89</v>
+        <v>92</v>
       </c>
       <c r="D8" t="s">
-        <v>69</v>
+        <v>72</v>
       </c>
       <c r="E8" t="n">
         <v>0</v>
@@ -1746,7 +1786,7 @@
         <v>29</v>
       </c>
       <c r="I8" t="s">
-        <v>82</v>
+        <v>85</v>
       </c>
       <c r="J8" t="s">
         <v>16</v>
@@ -1803,16 +1843,16 @@
     </row>
     <row r="2">
       <c r="A2" t="s">
-        <v>90</v>
+        <v>93</v>
       </c>
       <c r="B2" t="s">
-        <v>91</v>
+        <v>94</v>
       </c>
       <c r="C2" t="s">
-        <v>92</v>
+        <v>95</v>
       </c>
       <c r="D2" t="s">
-        <v>44</v>
+        <v>47</v>
       </c>
       <c r="E2" t="n">
         <v>0</v>
@@ -1830,21 +1870,21 @@
         <v>15</v>
       </c>
       <c r="J2" t="s">
-        <v>40</v>
+        <v>43</v>
       </c>
       <c r="K2" t="s">
-        <v>70</v>
+        <v>73</v>
       </c>
     </row>
     <row r="3">
       <c r="A3" t="s">
-        <v>90</v>
+        <v>93</v>
       </c>
       <c r="B3" t="s">
-        <v>93</v>
+        <v>96</v>
       </c>
       <c r="C3" t="s">
-        <v>94</v>
+        <v>97</v>
       </c>
       <c r="D3" t="s">
         <v>19</v>
@@ -1862,27 +1902,27 @@
         <v>115</v>
       </c>
       <c r="I3" t="s">
-        <v>95</v>
+        <v>98</v>
       </c>
       <c r="J3" t="s">
-        <v>96</v>
+        <v>99</v>
       </c>
       <c r="K3" t="s">
-        <v>62</v>
+        <v>65</v>
       </c>
     </row>
     <row r="4">
       <c r="A4" t="s">
-        <v>90</v>
+        <v>93</v>
       </c>
       <c r="B4" t="s">
-        <v>97</v>
+        <v>100</v>
       </c>
       <c r="C4" t="s">
-        <v>98</v>
+        <v>101</v>
       </c>
       <c r="D4" t="s">
-        <v>77</v>
+        <v>80</v>
       </c>
       <c r="E4" t="n">
         <v>0</v>
@@ -1900,24 +1940,24 @@
         <v>15</v>
       </c>
       <c r="J4" t="s">
-        <v>40</v>
+        <v>43</v>
       </c>
       <c r="K4" t="s">
-        <v>54</v>
+        <v>57</v>
       </c>
     </row>
     <row r="5">
       <c r="A5" t="s">
-        <v>90</v>
+        <v>93</v>
       </c>
       <c r="B5" t="s">
-        <v>99</v>
+        <v>102</v>
       </c>
       <c r="C5" t="s">
-        <v>100</v>
+        <v>103</v>
       </c>
       <c r="D5" t="s">
-        <v>101</v>
+        <v>104</v>
       </c>
       <c r="E5" t="n">
         <v>1</v>
@@ -1931,16 +1971,16 @@
     </row>
     <row r="6">
       <c r="A6" t="s">
-        <v>90</v>
+        <v>93</v>
       </c>
       <c r="B6" t="s">
-        <v>102</v>
+        <v>105</v>
       </c>
       <c r="C6" t="s">
-        <v>103</v>
+        <v>106</v>
       </c>
       <c r="D6" t="s">
-        <v>104</v>
+        <v>107</v>
       </c>
       <c r="E6" t="n">
         <v>0</v>
@@ -1954,16 +1994,16 @@
     </row>
     <row r="7">
       <c r="A7" t="s">
-        <v>90</v>
+        <v>93</v>
       </c>
       <c r="B7" t="s">
-        <v>105</v>
+        <v>108</v>
       </c>
       <c r="C7" t="s">
-        <v>106</v>
+        <v>109</v>
       </c>
       <c r="D7" t="s">
-        <v>65</v>
+        <v>68</v>
       </c>
       <c r="E7" t="n">
         <v>0</v>
@@ -1978,27 +2018,27 @@
         <v>143</v>
       </c>
       <c r="I7" t="s">
-        <v>34</v>
+        <v>37</v>
       </c>
       <c r="J7" t="s">
         <v>25</v>
       </c>
       <c r="K7" t="s">
-        <v>45</v>
+        <v>48</v>
       </c>
     </row>
     <row r="8">
       <c r="A8" t="s">
-        <v>90</v>
+        <v>93</v>
       </c>
       <c r="B8" t="s">
-        <v>107</v>
+        <v>110</v>
       </c>
       <c r="C8" t="s">
-        <v>108</v>
+        <v>111</v>
       </c>
       <c r="D8" t="s">
-        <v>77</v>
+        <v>80</v>
       </c>
       <c r="E8" t="n">
         <v>0</v>
@@ -2012,16 +2052,16 @@
     </row>
     <row r="9">
       <c r="A9" t="s">
-        <v>90</v>
+        <v>93</v>
       </c>
       <c r="B9" t="s">
-        <v>109</v>
+        <v>112</v>
       </c>
       <c r="C9" t="s">
-        <v>110</v>
+        <v>113</v>
       </c>
       <c r="D9" t="s">
-        <v>48</v>
+        <v>51</v>
       </c>
       <c r="E9" t="n">
         <v>0</v>
@@ -2039,10 +2079,10 @@
         <v>15</v>
       </c>
       <c r="J9" t="s">
-        <v>40</v>
+        <v>43</v>
       </c>
       <c r="K9" t="s">
-        <v>41</v>
+        <v>44</v>
       </c>
     </row>
   </sheetData>
@@ -2093,16 +2133,16 @@
     </row>
     <row r="2">
       <c r="A2" t="s">
-        <v>111</v>
+        <v>114</v>
       </c>
       <c r="B2" t="s">
-        <v>112</v>
+        <v>115</v>
       </c>
       <c r="C2" t="s">
-        <v>113</v>
+        <v>116</v>
       </c>
       <c r="D2" t="s">
-        <v>44</v>
+        <v>47</v>
       </c>
       <c r="E2" t="n">
         <v>0</v>
@@ -2116,13 +2156,13 @@
     </row>
     <row r="3">
       <c r="A3" t="s">
-        <v>111</v>
+        <v>114</v>
       </c>
       <c r="B3" t="s">
-        <v>114</v>
+        <v>117</v>
       </c>
       <c r="C3" t="s">
-        <v>115</v>
+        <v>118</v>
       </c>
       <c r="D3" t="s">
         <v>14</v>
@@ -2139,16 +2179,16 @@
     </row>
     <row r="4">
       <c r="A4" t="s">
-        <v>111</v>
+        <v>114</v>
       </c>
       <c r="B4" t="s">
-        <v>116</v>
+        <v>119</v>
       </c>
       <c r="C4" t="s">
-        <v>117</v>
+        <v>120</v>
       </c>
       <c r="D4" t="s">
-        <v>74</v>
+        <v>77</v>
       </c>
       <c r="E4" t="n">
         <v>0</v>
@@ -2166,21 +2206,21 @@
         <v>15</v>
       </c>
       <c r="J4" t="s">
-        <v>40</v>
+        <v>43</v>
       </c>
       <c r="K4" t="s">
-        <v>49</v>
+        <v>52</v>
       </c>
     </row>
     <row r="5">
       <c r="A5" t="s">
-        <v>111</v>
+        <v>114</v>
       </c>
       <c r="B5" t="s">
-        <v>118</v>
+        <v>121</v>
       </c>
       <c r="C5" t="s">
-        <v>119</v>
+        <v>122</v>
       </c>
       <c r="D5" t="s">
         <v>19</v>
@@ -2198,27 +2238,27 @@
         <v>44</v>
       </c>
       <c r="I5" t="s">
-        <v>34</v>
+        <v>37</v>
       </c>
       <c r="J5" t="s">
-        <v>40</v>
+        <v>43</v>
       </c>
       <c r="K5" t="s">
-        <v>70</v>
+        <v>73</v>
       </c>
     </row>
     <row r="6">
       <c r="A6" t="s">
-        <v>111</v>
+        <v>114</v>
       </c>
       <c r="B6" t="s">
-        <v>120</v>
+        <v>123</v>
       </c>
       <c r="C6" t="s">
-        <v>121</v>
+        <v>124</v>
       </c>
       <c r="D6" t="s">
-        <v>44</v>
+        <v>47</v>
       </c>
       <c r="E6" t="n">
         <v>0</v>
@@ -2232,16 +2272,16 @@
     </row>
     <row r="7">
       <c r="A7" t="s">
-        <v>111</v>
+        <v>114</v>
       </c>
       <c r="B7" t="s">
-        <v>122</v>
+        <v>125</v>
       </c>
       <c r="C7" t="s">
-        <v>123</v>
+        <v>126</v>
       </c>
       <c r="D7" t="s">
-        <v>44</v>
+        <v>47</v>
       </c>
       <c r="E7" t="n">
         <v>0</v>
@@ -2255,16 +2295,16 @@
     </row>
     <row r="8">
       <c r="A8" t="s">
-        <v>111</v>
+        <v>114</v>
       </c>
       <c r="B8" t="s">
-        <v>124</v>
+        <v>127</v>
       </c>
       <c r="C8" t="s">
-        <v>125</v>
+        <v>128</v>
       </c>
       <c r="D8" t="s">
-        <v>69</v>
+        <v>72</v>
       </c>
       <c r="E8" t="n">
         <v>0</v>
@@ -2278,16 +2318,16 @@
     </row>
     <row r="9">
       <c r="A9" t="s">
-        <v>111</v>
+        <v>114</v>
       </c>
       <c r="B9" t="s">
-        <v>126</v>
+        <v>129</v>
       </c>
       <c r="C9" t="s">
-        <v>127</v>
+        <v>130</v>
       </c>
       <c r="D9" t="s">
-        <v>44</v>
+        <v>47</v>
       </c>
       <c r="E9" t="n">
         <v>0</v>
@@ -2305,24 +2345,24 @@
         <v>15</v>
       </c>
       <c r="J9" t="s">
-        <v>40</v>
+        <v>43</v>
       </c>
       <c r="K9" t="s">
-        <v>41</v>
+        <v>44</v>
       </c>
     </row>
     <row r="10">
       <c r="A10" t="s">
-        <v>111</v>
+        <v>114</v>
       </c>
       <c r="B10" t="s">
-        <v>128</v>
+        <v>131</v>
       </c>
       <c r="C10" t="s">
-        <v>129</v>
+        <v>132</v>
       </c>
       <c r="D10" t="s">
-        <v>57</v>
+        <v>60</v>
       </c>
       <c r="E10" t="n">
         <v>0</v>
@@ -2337,27 +2377,27 @@
         <v>86</v>
       </c>
       <c r="I10" t="s">
-        <v>34</v>
+        <v>37</v>
       </c>
       <c r="J10" t="s">
-        <v>40</v>
+        <v>43</v>
       </c>
       <c r="K10" t="s">
-        <v>54</v>
+        <v>57</v>
       </c>
     </row>
     <row r="11">
       <c r="A11" t="s">
-        <v>111</v>
+        <v>114</v>
       </c>
       <c r="B11" t="s">
-        <v>130</v>
+        <v>133</v>
       </c>
       <c r="C11" t="s">
-        <v>131</v>
+        <v>134</v>
       </c>
       <c r="D11" t="s">
-        <v>77</v>
+        <v>80</v>
       </c>
       <c r="E11" t="n">
         <v>1</v>
@@ -2372,10 +2412,10 @@
         <v>8</v>
       </c>
       <c r="I11" t="s">
-        <v>39</v>
+        <v>42</v>
       </c>
       <c r="J11" t="s">
-        <v>40</v>
+        <v>43</v>
       </c>
       <c r="K11" t="s">
         <v>16</v>
@@ -2429,16 +2469,16 @@
     </row>
     <row r="2">
       <c r="A2" t="s">
-        <v>132</v>
+        <v>135</v>
       </c>
       <c r="B2" t="s">
-        <v>133</v>
+        <v>136</v>
       </c>
       <c r="C2" t="s">
-        <v>134</v>
+        <v>137</v>
       </c>
       <c r="D2" t="s">
-        <v>44</v>
+        <v>47</v>
       </c>
       <c r="E2" t="n">
         <v>0</v>
@@ -2452,16 +2492,16 @@
     </row>
     <row r="3">
       <c r="A3" t="s">
-        <v>132</v>
+        <v>135</v>
       </c>
       <c r="B3" t="s">
-        <v>135</v>
+        <v>138</v>
       </c>
       <c r="C3" t="s">
-        <v>136</v>
+        <v>139</v>
       </c>
       <c r="D3" t="s">
-        <v>101</v>
+        <v>104</v>
       </c>
       <c r="E3" t="n">
         <v>0</v>
@@ -2475,16 +2515,16 @@
     </row>
     <row r="4">
       <c r="A4" t="s">
-        <v>132</v>
+        <v>135</v>
       </c>
       <c r="B4" t="s">
-        <v>137</v>
+        <v>140</v>
       </c>
       <c r="C4" t="s">
-        <v>138</v>
+        <v>141</v>
       </c>
       <c r="D4" t="s">
-        <v>101</v>
+        <v>104</v>
       </c>
       <c r="E4" t="n">
         <v>0</v>
@@ -2498,16 +2538,16 @@
     </row>
     <row r="5">
       <c r="A5" t="s">
-        <v>132</v>
+        <v>135</v>
       </c>
       <c r="B5" t="s">
-        <v>139</v>
+        <v>142</v>
       </c>
       <c r="C5" t="s">
-        <v>140</v>
+        <v>143</v>
       </c>
       <c r="D5" t="s">
-        <v>101</v>
+        <v>104</v>
       </c>
       <c r="E5" t="n">
         <v>0</v>
@@ -2521,16 +2561,16 @@
     </row>
     <row r="6">
       <c r="A6" t="s">
-        <v>132</v>
+        <v>135</v>
       </c>
       <c r="B6" t="s">
-        <v>141</v>
+        <v>144</v>
       </c>
       <c r="C6" t="s">
-        <v>142</v>
+        <v>145</v>
       </c>
       <c r="D6" t="s">
-        <v>69</v>
+        <v>72</v>
       </c>
       <c r="E6" t="n">
         <v>0</v>
@@ -2544,16 +2584,16 @@
     </row>
     <row r="7">
       <c r="A7" t="s">
-        <v>132</v>
+        <v>135</v>
       </c>
       <c r="B7" t="s">
-        <v>143</v>
+        <v>146</v>
       </c>
       <c r="C7" t="s">
-        <v>144</v>
+        <v>147</v>
       </c>
       <c r="D7" t="s">
-        <v>57</v>
+        <v>60</v>
       </c>
       <c r="E7" t="n">
         <v>0</v>
@@ -2567,16 +2607,16 @@
     </row>
     <row r="8">
       <c r="A8" t="s">
-        <v>132</v>
+        <v>135</v>
       </c>
       <c r="B8" t="s">
-        <v>145</v>
+        <v>148</v>
       </c>
       <c r="C8" t="s">
-        <v>146</v>
+        <v>149</v>
       </c>
       <c r="D8" t="s">
-        <v>147</v>
+        <v>150</v>
       </c>
       <c r="E8" t="n">
         <v>0</v>
@@ -2590,16 +2630,16 @@
     </row>
     <row r="9">
       <c r="A9" t="s">
-        <v>132</v>
+        <v>135</v>
       </c>
       <c r="B9" t="s">
-        <v>148</v>
+        <v>151</v>
       </c>
       <c r="C9" t="s">
-        <v>149</v>
+        <v>152</v>
       </c>
       <c r="D9" t="s">
-        <v>44</v>
+        <v>47</v>
       </c>
       <c r="E9" t="n">
         <v>0</v>
@@ -2659,16 +2699,16 @@
     </row>
     <row r="2">
       <c r="A2" t="s">
-        <v>150</v>
+        <v>153</v>
       </c>
       <c r="B2" t="s">
-        <v>151</v>
+        <v>154</v>
       </c>
       <c r="C2" t="s">
-        <v>152</v>
+        <v>155</v>
       </c>
       <c r="D2" t="s">
-        <v>153</v>
+        <v>156</v>
       </c>
       <c r="E2" t="n">
         <v>0</v>
@@ -2682,16 +2722,16 @@
     </row>
     <row r="3">
       <c r="A3" t="s">
-        <v>150</v>
+        <v>153</v>
       </c>
       <c r="B3" t="s">
-        <v>154</v>
+        <v>157</v>
       </c>
       <c r="C3" t="s">
-        <v>155</v>
+        <v>158</v>
       </c>
       <c r="D3" t="s">
-        <v>48</v>
+        <v>51</v>
       </c>
       <c r="E3" t="n">
         <v>0</v>
@@ -2705,16 +2745,16 @@
     </row>
     <row r="4">
       <c r="A4" t="s">
-        <v>150</v>
+        <v>153</v>
       </c>
       <c r="B4" t="s">
-        <v>156</v>
+        <v>159</v>
       </c>
       <c r="C4" t="s">
-        <v>157</v>
+        <v>160</v>
       </c>
       <c r="D4" t="s">
-        <v>44</v>
+        <v>47</v>
       </c>
       <c r="E4" t="n">
         <v>0</v>
@@ -2728,13 +2768,13 @@
     </row>
     <row r="5">
       <c r="A5" t="s">
-        <v>150</v>
+        <v>153</v>
       </c>
       <c r="B5" t="s">
-        <v>158</v>
+        <v>161</v>
       </c>
       <c r="C5" t="s">
-        <v>159</v>
+        <v>162</v>
       </c>
       <c r="D5" t="s">
         <v>19</v>
@@ -2751,16 +2791,16 @@
     </row>
     <row r="6">
       <c r="A6" t="s">
-        <v>150</v>
+        <v>153</v>
       </c>
       <c r="B6" t="s">
-        <v>160</v>
+        <v>163</v>
       </c>
       <c r="C6" t="s">
-        <v>161</v>
+        <v>164</v>
       </c>
       <c r="D6" t="s">
-        <v>44</v>
+        <v>47</v>
       </c>
       <c r="E6" t="n">
         <v>0</v>
@@ -2774,16 +2814,16 @@
     </row>
     <row r="7">
       <c r="A7" t="s">
-        <v>150</v>
+        <v>153</v>
       </c>
       <c r="B7" t="s">
-        <v>162</v>
+        <v>165</v>
       </c>
       <c r="C7" t="s">
-        <v>163</v>
+        <v>166</v>
       </c>
       <c r="D7" t="s">
-        <v>164</v>
+        <v>167</v>
       </c>
       <c r="E7" t="n">
         <v>0</v>
@@ -2797,16 +2837,16 @@
     </row>
     <row r="8">
       <c r="A8" t="s">
-        <v>150</v>
+        <v>153</v>
       </c>
       <c r="B8" t="s">
-        <v>165</v>
+        <v>168</v>
       </c>
       <c r="C8" t="s">
-        <v>166</v>
+        <v>169</v>
       </c>
       <c r="D8" t="s">
-        <v>44</v>
+        <v>47</v>
       </c>
       <c r="E8" t="n">
         <v>0</v>
@@ -2820,16 +2860,16 @@
     </row>
     <row r="9">
       <c r="A9" t="s">
-        <v>150</v>
+        <v>153</v>
       </c>
       <c r="B9" t="s">
-        <v>167</v>
+        <v>170</v>
       </c>
       <c r="C9" t="s">
-        <v>168</v>
+        <v>171</v>
       </c>
       <c r="D9" t="s">
-        <v>57</v>
+        <v>60</v>
       </c>
       <c r="E9" t="n">
         <v>0</v>
@@ -2843,16 +2883,16 @@
     </row>
     <row r="10">
       <c r="A10" t="s">
-        <v>150</v>
+        <v>153</v>
       </c>
       <c r="B10" t="s">
-        <v>169</v>
+        <v>172</v>
       </c>
       <c r="C10" t="s">
-        <v>170</v>
+        <v>173</v>
       </c>
       <c r="D10" t="s">
-        <v>48</v>
+        <v>51</v>
       </c>
       <c r="E10" t="n">
         <v>0</v>
@@ -2912,16 +2952,16 @@
     </row>
     <row r="2">
       <c r="A2" t="s">
-        <v>171</v>
+        <v>174</v>
       </c>
       <c r="B2" t="s">
-        <v>172</v>
+        <v>175</v>
       </c>
       <c r="C2" t="s">
-        <v>173</v>
+        <v>176</v>
       </c>
       <c r="D2" t="s">
-        <v>44</v>
+        <v>47</v>
       </c>
       <c r="E2" t="n">
         <v>0</v>
@@ -2935,16 +2975,16 @@
     </row>
     <row r="3">
       <c r="A3" t="s">
-        <v>171</v>
+        <v>174</v>
       </c>
       <c r="B3" t="s">
-        <v>174</v>
+        <v>177</v>
       </c>
       <c r="C3" t="s">
-        <v>175</v>
+        <v>178</v>
       </c>
       <c r="D3" t="s">
-        <v>48</v>
+        <v>51</v>
       </c>
       <c r="E3" t="n">
         <v>0</v>
@@ -2958,16 +2998,16 @@
     </row>
     <row r="4">
       <c r="A4" t="s">
-        <v>171</v>
+        <v>174</v>
       </c>
       <c r="B4" t="s">
-        <v>176</v>
+        <v>179</v>
       </c>
       <c r="C4" t="s">
-        <v>177</v>
+        <v>180</v>
       </c>
       <c r="D4" t="s">
-        <v>48</v>
+        <v>51</v>
       </c>
       <c r="E4" t="n">
         <v>0</v>
@@ -2981,16 +3021,16 @@
     </row>
     <row r="5">
       <c r="A5" t="s">
-        <v>171</v>
+        <v>174</v>
       </c>
       <c r="B5" t="s">
-        <v>178</v>
+        <v>181</v>
       </c>
       <c r="C5" t="s">
-        <v>179</v>
+        <v>182</v>
       </c>
       <c r="D5" t="s">
-        <v>104</v>
+        <v>107</v>
       </c>
       <c r="E5" t="n">
         <v>0</v>
@@ -3004,16 +3044,16 @@
     </row>
     <row r="6">
       <c r="A6" t="s">
-        <v>171</v>
+        <v>174</v>
       </c>
       <c r="B6" t="s">
-        <v>180</v>
+        <v>183</v>
       </c>
       <c r="C6" t="s">
-        <v>181</v>
+        <v>184</v>
       </c>
       <c r="D6" t="s">
-        <v>77</v>
+        <v>80</v>
       </c>
       <c r="E6" t="n">
         <v>0</v>
@@ -3027,16 +3067,16 @@
     </row>
     <row r="7">
       <c r="A7" t="s">
-        <v>171</v>
+        <v>174</v>
       </c>
       <c r="B7" t="s">
-        <v>182</v>
+        <v>185</v>
       </c>
       <c r="C7" t="s">
-        <v>183</v>
+        <v>186</v>
       </c>
       <c r="D7" t="s">
-        <v>38</v>
+        <v>41</v>
       </c>
       <c r="E7" t="n">
         <v>0</v>
@@ -3050,16 +3090,16 @@
     </row>
     <row r="8">
       <c r="A8" t="s">
-        <v>171</v>
+        <v>174</v>
       </c>
       <c r="B8" t="s">
-        <v>184</v>
+        <v>187</v>
       </c>
       <c r="C8" t="s">
-        <v>185</v>
+        <v>188</v>
       </c>
       <c r="D8" t="s">
-        <v>65</v>
+        <v>68</v>
       </c>
       <c r="E8" t="n">
         <v>0</v>
@@ -3073,13 +3113,13 @@
     </row>
     <row r="9">
       <c r="A9" t="s">
-        <v>171</v>
+        <v>174</v>
       </c>
       <c r="B9" t="s">
-        <v>186</v>
+        <v>189</v>
       </c>
       <c r="C9" t="s">
-        <v>187</v>
+        <v>190</v>
       </c>
       <c r="D9" t="s">
         <v>14</v>
@@ -3096,16 +3136,16 @@
     </row>
     <row r="10">
       <c r="A10" t="s">
-        <v>171</v>
+        <v>174</v>
       </c>
       <c r="B10" t="s">
-        <v>188</v>
+        <v>191</v>
       </c>
       <c r="C10" t="s">
-        <v>189</v>
+        <v>192</v>
       </c>
       <c r="D10" t="s">
-        <v>69</v>
+        <v>72</v>
       </c>
       <c r="E10" t="n">
         <v>0</v>
@@ -3119,16 +3159,16 @@
     </row>
     <row r="11">
       <c r="A11" t="s">
-        <v>171</v>
+        <v>174</v>
       </c>
       <c r="B11" t="s">
-        <v>190</v>
+        <v>193</v>
       </c>
       <c r="C11" t="s">
-        <v>191</v>
+        <v>194</v>
       </c>
       <c r="D11" t="s">
-        <v>192</v>
+        <v>195</v>
       </c>
       <c r="E11" t="n">
         <v>1</v>
@@ -3188,16 +3228,16 @@
     </row>
     <row r="2">
       <c r="A2" t="s">
-        <v>193</v>
+        <v>196</v>
       </c>
       <c r="B2" t="s">
-        <v>194</v>
+        <v>197</v>
       </c>
       <c r="C2" t="s">
-        <v>195</v>
+        <v>198</v>
       </c>
       <c r="D2" t="s">
-        <v>48</v>
+        <v>51</v>
       </c>
       <c r="E2" t="n">
         <v>1</v>

--- a/Stat Reviews/OT24_StatReview/scotusblog_replication/data/term_index.xlsx
+++ b/Stat Reviews/OT24_StatReview/scotusblog_replication/data/term_index.xlsx
@@ -20,7 +20,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="199" uniqueCount="199">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="200" uniqueCount="200">
   <si>
     <t xml:space="preserve">sitting</t>
   </si>
@@ -118,7 +118,7 @@
     <t xml:space="preserve">A.A.R.P v. Trump</t>
   </si>
   <si>
-    <t xml:space="preserve">NDTX</t>
+    <t xml:space="preserve">CA5</t>
   </si>
   <si>
     <t xml:space="preserve">October</t>
@@ -163,9 +163,6 @@
     <t xml:space="preserve">Vanderstok</t>
   </si>
   <si>
-    <t xml:space="preserve">CA5</t>
-  </si>
-  <si>
     <t xml:space="preserve">Gorsuch</t>
   </si>
   <si>
@@ -358,6 +355,9 @@
     <t xml:space="preserve">Seven County</t>
   </si>
   <si>
+    <t xml:space="preserve">(8-0)</t>
+  </si>
+  <si>
     <t xml:space="preserve">23-900</t>
   </si>
   <si>
@@ -608,6 +608,9 @@
   </si>
   <si>
     <t xml:space="preserve">SCOK</t>
+  </si>
+  <si>
+    <t xml:space="preserve">(4-4)*</t>
   </si>
   <si>
     <t xml:space="preserve">May</t>
@@ -1270,7 +1273,7 @@
         <v>46</v>
       </c>
       <c r="D4" t="s">
-        <v>47</v>
+        <v>32</v>
       </c>
       <c r="E4" t="n">
         <v>0</v>
@@ -1291,7 +1294,7 @@
         <v>20</v>
       </c>
       <c r="K4" t="s">
-        <v>48</v>
+        <v>47</v>
       </c>
     </row>
     <row r="5">
@@ -1299,13 +1302,13 @@
         <v>33</v>
       </c>
       <c r="B5" t="s">
+        <v>48</v>
+      </c>
+      <c r="C5" t="s">
         <v>49</v>
       </c>
-      <c r="C5" t="s">
+      <c r="D5" t="s">
         <v>50</v>
-      </c>
-      <c r="D5" t="s">
-        <v>51</v>
       </c>
       <c r="E5" t="n">
         <v>0</v>
@@ -1326,7 +1329,7 @@
         <v>20</v>
       </c>
       <c r="K5" t="s">
-        <v>52</v>
+        <v>51</v>
       </c>
     </row>
     <row r="6">
@@ -1334,13 +1337,13 @@
         <v>33</v>
       </c>
       <c r="B6" t="s">
+        <v>52</v>
+      </c>
+      <c r="C6" t="s">
         <v>53</v>
       </c>
-      <c r="C6" t="s">
+      <c r="D6" t="s">
         <v>54</v>
-      </c>
-      <c r="D6" t="s">
-        <v>55</v>
       </c>
       <c r="E6" t="n">
         <v>1</v>
@@ -1358,10 +1361,10 @@
         <v>37</v>
       </c>
       <c r="J6" t="s">
+        <v>55</v>
+      </c>
+      <c r="K6" t="s">
         <v>56</v>
-      </c>
-      <c r="K6" t="s">
-        <v>57</v>
       </c>
     </row>
     <row r="7">
@@ -1369,13 +1372,13 @@
         <v>33</v>
       </c>
       <c r="B7" t="s">
+        <v>57</v>
+      </c>
+      <c r="C7" t="s">
         <v>58</v>
       </c>
-      <c r="C7" t="s">
+      <c r="D7" t="s">
         <v>59</v>
-      </c>
-      <c r="D7" t="s">
-        <v>60</v>
       </c>
       <c r="E7" t="n">
         <v>0</v>
@@ -1390,13 +1393,13 @@
         <v>170</v>
       </c>
       <c r="I7" t="s">
-        <v>61</v>
+        <v>60</v>
       </c>
       <c r="J7" t="s">
         <v>25</v>
       </c>
       <c r="K7" t="s">
-        <v>62</v>
+        <v>61</v>
       </c>
     </row>
     <row r="8">
@@ -1404,10 +1407,10 @@
         <v>33</v>
       </c>
       <c r="B8" t="s">
+        <v>62</v>
+      </c>
+      <c r="C8" t="s">
         <v>63</v>
-      </c>
-      <c r="C8" t="s">
-        <v>64</v>
       </c>
       <c r="D8" t="s">
         <v>14</v>
@@ -1431,7 +1434,7 @@
         <v>43</v>
       </c>
       <c r="K8" t="s">
-        <v>65</v>
+        <v>64</v>
       </c>
     </row>
     <row r="9">
@@ -1439,13 +1442,13 @@
         <v>33</v>
       </c>
       <c r="B9" t="s">
+        <v>65</v>
+      </c>
+      <c r="C9" t="s">
         <v>66</v>
       </c>
-      <c r="C9" t="s">
+      <c r="D9" t="s">
         <v>67</v>
-      </c>
-      <c r="D9" t="s">
-        <v>68</v>
       </c>
       <c r="E9" t="n">
         <v>0</v>
@@ -1466,7 +1469,7 @@
         <v>20</v>
       </c>
       <c r="K9" t="s">
-        <v>69</v>
+        <v>68</v>
       </c>
     </row>
     <row r="10">
@@ -1474,13 +1477,13 @@
         <v>33</v>
       </c>
       <c r="B10" t="s">
+        <v>69</v>
+      </c>
+      <c r="C10" t="s">
         <v>70</v>
       </c>
-      <c r="C10" t="s">
+      <c r="D10" t="s">
         <v>71</v>
-      </c>
-      <c r="D10" t="s">
-        <v>72</v>
       </c>
       <c r="E10" t="n">
         <v>0</v>
@@ -1501,7 +1504,7 @@
         <v>43</v>
       </c>
       <c r="K10" t="s">
-        <v>73</v>
+        <v>72</v>
       </c>
     </row>
   </sheetData>
@@ -1552,16 +1555,16 @@
     </row>
     <row r="2">
       <c r="A2" t="s">
+        <v>73</v>
+      </c>
+      <c r="B2" t="s">
         <v>74</v>
       </c>
-      <c r="B2" t="s">
+      <c r="C2" t="s">
         <v>75</v>
       </c>
-      <c r="C2" t="s">
+      <c r="D2" t="s">
         <v>76</v>
-      </c>
-      <c r="D2" t="s">
-        <v>77</v>
       </c>
       <c r="E2" t="n">
         <v>0</v>
@@ -1576,7 +1579,7 @@
         <v>110</v>
       </c>
       <c r="I2" t="s">
-        <v>61</v>
+        <v>60</v>
       </c>
       <c r="J2" t="s">
         <v>43</v>
@@ -1587,16 +1590,16 @@
     </row>
     <row r="3">
       <c r="A3" t="s">
-        <v>74</v>
+        <v>73</v>
       </c>
       <c r="B3" t="s">
+        <v>77</v>
+      </c>
+      <c r="C3" t="s">
         <v>78</v>
       </c>
-      <c r="C3" t="s">
+      <c r="D3" t="s">
         <v>79</v>
-      </c>
-      <c r="D3" t="s">
-        <v>80</v>
       </c>
       <c r="E3" t="n">
         <v>0</v>
@@ -1617,21 +1620,21 @@
         <v>20</v>
       </c>
       <c r="K3" t="s">
-        <v>62</v>
+        <v>61</v>
       </c>
     </row>
     <row r="4">
       <c r="A4" t="s">
-        <v>74</v>
+        <v>73</v>
       </c>
       <c r="B4" t="s">
+        <v>80</v>
+      </c>
+      <c r="C4" t="s">
         <v>81</v>
       </c>
-      <c r="C4" t="s">
-        <v>82</v>
-      </c>
       <c r="D4" t="s">
-        <v>51</v>
+        <v>50</v>
       </c>
       <c r="E4" t="n">
         <v>0</v>
@@ -1657,16 +1660,16 @@
     </row>
     <row r="5">
       <c r="A5" t="s">
-        <v>74</v>
+        <v>73</v>
       </c>
       <c r="B5" t="s">
+        <v>82</v>
+      </c>
+      <c r="C5" t="s">
         <v>83</v>
       </c>
-      <c r="C5" t="s">
-        <v>84</v>
-      </c>
       <c r="D5" t="s">
-        <v>72</v>
+        <v>71</v>
       </c>
       <c r="E5" t="n">
         <v>0</v>
@@ -1681,7 +1684,7 @@
         <v>17</v>
       </c>
       <c r="I5" t="s">
-        <v>85</v>
+        <v>84</v>
       </c>
       <c r="J5" t="s">
         <v>16</v>
@@ -1692,16 +1695,16 @@
     </row>
     <row r="6">
       <c r="A6" t="s">
-        <v>74</v>
+        <v>73</v>
       </c>
       <c r="B6" t="s">
+        <v>85</v>
+      </c>
+      <c r="C6" t="s">
         <v>86</v>
       </c>
-      <c r="C6" t="s">
-        <v>87</v>
-      </c>
       <c r="D6" t="s">
-        <v>60</v>
+        <v>59</v>
       </c>
       <c r="E6" t="n">
         <v>0</v>
@@ -1719,24 +1722,24 @@
         <v>37</v>
       </c>
       <c r="J6" t="s">
-        <v>88</v>
+        <v>87</v>
       </c>
       <c r="K6" t="s">
-        <v>48</v>
+        <v>47</v>
       </c>
     </row>
     <row r="7">
       <c r="A7" t="s">
-        <v>74</v>
+        <v>73</v>
       </c>
       <c r="B7" t="s">
+        <v>88</v>
+      </c>
+      <c r="C7" t="s">
         <v>89</v>
       </c>
-      <c r="C7" t="s">
-        <v>90</v>
-      </c>
       <c r="D7" t="s">
-        <v>60</v>
+        <v>59</v>
       </c>
       <c r="E7" t="n">
         <v>0</v>
@@ -1757,21 +1760,21 @@
         <v>20</v>
       </c>
       <c r="K7" t="s">
-        <v>69</v>
+        <v>68</v>
       </c>
     </row>
     <row r="8">
       <c r="A8" t="s">
-        <v>74</v>
+        <v>73</v>
       </c>
       <c r="B8" t="s">
+        <v>90</v>
+      </c>
+      <c r="C8" t="s">
         <v>91</v>
       </c>
-      <c r="C8" t="s">
-        <v>92</v>
-      </c>
       <c r="D8" t="s">
-        <v>72</v>
+        <v>71</v>
       </c>
       <c r="E8" t="n">
         <v>0</v>
@@ -1786,7 +1789,7 @@
         <v>29</v>
       </c>
       <c r="I8" t="s">
-        <v>85</v>
+        <v>84</v>
       </c>
       <c r="J8" t="s">
         <v>16</v>
@@ -1843,16 +1846,16 @@
     </row>
     <row r="2">
       <c r="A2" t="s">
+        <v>92</v>
+      </c>
+      <c r="B2" t="s">
         <v>93</v>
       </c>
-      <c r="B2" t="s">
+      <c r="C2" t="s">
         <v>94</v>
       </c>
-      <c r="C2" t="s">
-        <v>95</v>
-      </c>
       <c r="D2" t="s">
-        <v>47</v>
+        <v>32</v>
       </c>
       <c r="E2" t="n">
         <v>0</v>
@@ -1873,18 +1876,18 @@
         <v>43</v>
       </c>
       <c r="K2" t="s">
-        <v>73</v>
+        <v>72</v>
       </c>
     </row>
     <row r="3">
       <c r="A3" t="s">
-        <v>93</v>
+        <v>92</v>
       </c>
       <c r="B3" t="s">
+        <v>95</v>
+      </c>
+      <c r="C3" t="s">
         <v>96</v>
-      </c>
-      <c r="C3" t="s">
-        <v>97</v>
       </c>
       <c r="D3" t="s">
         <v>19</v>
@@ -1902,27 +1905,27 @@
         <v>115</v>
       </c>
       <c r="I3" t="s">
+        <v>97</v>
+      </c>
+      <c r="J3" t="s">
         <v>98</v>
       </c>
-      <c r="J3" t="s">
-        <v>99</v>
-      </c>
       <c r="K3" t="s">
-        <v>65</v>
+        <v>64</v>
       </c>
     </row>
     <row r="4">
       <c r="A4" t="s">
-        <v>93</v>
+        <v>92</v>
       </c>
       <c r="B4" t="s">
+        <v>99</v>
+      </c>
+      <c r="C4" t="s">
         <v>100</v>
       </c>
-      <c r="C4" t="s">
-        <v>101</v>
-      </c>
       <c r="D4" t="s">
-        <v>80</v>
+        <v>79</v>
       </c>
       <c r="E4" t="n">
         <v>0</v>
@@ -1943,21 +1946,21 @@
         <v>43</v>
       </c>
       <c r="K4" t="s">
-        <v>57</v>
+        <v>56</v>
       </c>
     </row>
     <row r="5">
       <c r="A5" t="s">
-        <v>93</v>
+        <v>92</v>
       </c>
       <c r="B5" t="s">
+        <v>101</v>
+      </c>
+      <c r="C5" t="s">
         <v>102</v>
       </c>
-      <c r="C5" t="s">
+      <c r="D5" t="s">
         <v>103</v>
-      </c>
-      <c r="D5" t="s">
-        <v>104</v>
       </c>
       <c r="E5" t="n">
         <v>1</v>
@@ -1971,39 +1974,51 @@
     </row>
     <row r="6">
       <c r="A6" t="s">
-        <v>93</v>
+        <v>92</v>
       </c>
       <c r="B6" t="s">
+        <v>104</v>
+      </c>
+      <c r="C6" t="s">
         <v>105</v>
       </c>
-      <c r="C6" t="s">
+      <c r="D6" t="s">
         <v>106</v>
       </c>
-      <c r="D6" t="s">
-        <v>107</v>
-      </c>
       <c r="E6" t="n">
         <v>0</v>
       </c>
-      <c r="F6" s="1"/>
-      <c r="G6" s="1"/>
-      <c r="H6"/>
-      <c r="I6"/>
-      <c r="J6"/>
-      <c r="K6"/>
+      <c r="F6" s="1" t="n">
+        <v>45635</v>
+      </c>
+      <c r="G6" s="1" t="n">
+        <v>45799</v>
+      </c>
+      <c r="H6" t="n">
+        <v>165</v>
+      </c>
+      <c r="I6" t="s">
+        <v>42</v>
+      </c>
+      <c r="J6" t="s">
+        <v>43</v>
+      </c>
+      <c r="K6" t="s">
+        <v>61</v>
+      </c>
     </row>
     <row r="7">
       <c r="A7" t="s">
-        <v>93</v>
+        <v>92</v>
       </c>
       <c r="B7" t="s">
+        <v>107</v>
+      </c>
+      <c r="C7" t="s">
         <v>108</v>
       </c>
-      <c r="C7" t="s">
-        <v>109</v>
-      </c>
       <c r="D7" t="s">
-        <v>68</v>
+        <v>67</v>
       </c>
       <c r="E7" t="n">
         <v>0</v>
@@ -2024,35 +2039,47 @@
         <v>25</v>
       </c>
       <c r="K7" t="s">
-        <v>48</v>
+        <v>47</v>
       </c>
     </row>
     <row r="8">
       <c r="A8" t="s">
-        <v>93</v>
+        <v>92</v>
       </c>
       <c r="B8" t="s">
+        <v>109</v>
+      </c>
+      <c r="C8" t="s">
         <v>110</v>
       </c>
-      <c r="C8" t="s">
+      <c r="D8" t="s">
+        <v>79</v>
+      </c>
+      <c r="E8" t="n">
+        <v>0</v>
+      </c>
+      <c r="F8" s="1" t="n">
+        <v>45636</v>
+      </c>
+      <c r="G8" s="1" t="n">
+        <v>45806</v>
+      </c>
+      <c r="H8" t="n">
+        <v>171</v>
+      </c>
+      <c r="I8" t="s">
+        <v>37</v>
+      </c>
+      <c r="J8" t="s">
         <v>111</v>
       </c>
-      <c r="D8" t="s">
-        <v>80</v>
-      </c>
-      <c r="E8" t="n">
-        <v>0</v>
-      </c>
-      <c r="F8" s="1"/>
-      <c r="G8" s="1"/>
-      <c r="H8"/>
-      <c r="I8"/>
-      <c r="J8"/>
-      <c r="K8"/>
+      <c r="K8" t="s">
+        <v>38</v>
+      </c>
     </row>
     <row r="9">
       <c r="A9" t="s">
-        <v>93</v>
+        <v>92</v>
       </c>
       <c r="B9" t="s">
         <v>112</v>
@@ -2061,7 +2088,7 @@
         <v>113</v>
       </c>
       <c r="D9" t="s">
-        <v>51</v>
+        <v>50</v>
       </c>
       <c r="E9" t="n">
         <v>0</v>
@@ -2142,7 +2169,7 @@
         <v>116</v>
       </c>
       <c r="D2" t="s">
-        <v>47</v>
+        <v>32</v>
       </c>
       <c r="E2" t="n">
         <v>0</v>
@@ -2188,7 +2215,7 @@
         <v>120</v>
       </c>
       <c r="D4" t="s">
-        <v>77</v>
+        <v>76</v>
       </c>
       <c r="E4" t="n">
         <v>0</v>
@@ -2209,7 +2236,7 @@
         <v>43</v>
       </c>
       <c r="K4" t="s">
-        <v>52</v>
+        <v>51</v>
       </c>
     </row>
     <row r="5">
@@ -2244,7 +2271,7 @@
         <v>43</v>
       </c>
       <c r="K5" t="s">
-        <v>73</v>
+        <v>72</v>
       </c>
     </row>
     <row r="6">
@@ -2258,7 +2285,7 @@
         <v>124</v>
       </c>
       <c r="D6" t="s">
-        <v>47</v>
+        <v>32</v>
       </c>
       <c r="E6" t="n">
         <v>0</v>
@@ -2281,7 +2308,7 @@
         <v>126</v>
       </c>
       <c r="D7" t="s">
-        <v>47</v>
+        <v>32</v>
       </c>
       <c r="E7" t="n">
         <v>0</v>
@@ -2304,7 +2331,7 @@
         <v>128</v>
       </c>
       <c r="D8" t="s">
-        <v>72</v>
+        <v>71</v>
       </c>
       <c r="E8" t="n">
         <v>0</v>
@@ -2327,7 +2354,7 @@
         <v>130</v>
       </c>
       <c r="D9" t="s">
-        <v>47</v>
+        <v>32</v>
       </c>
       <c r="E9" t="n">
         <v>0</v>
@@ -2362,7 +2389,7 @@
         <v>132</v>
       </c>
       <c r="D10" t="s">
-        <v>60</v>
+        <v>59</v>
       </c>
       <c r="E10" t="n">
         <v>0</v>
@@ -2383,7 +2410,7 @@
         <v>43</v>
       </c>
       <c r="K10" t="s">
-        <v>57</v>
+        <v>56</v>
       </c>
     </row>
     <row r="11">
@@ -2397,7 +2424,7 @@
         <v>134</v>
       </c>
       <c r="D11" t="s">
-        <v>80</v>
+        <v>79</v>
       </c>
       <c r="E11" t="n">
         <v>1</v>
@@ -2478,7 +2505,7 @@
         <v>137</v>
       </c>
       <c r="D2" t="s">
-        <v>47</v>
+        <v>32</v>
       </c>
       <c r="E2" t="n">
         <v>0</v>
@@ -2501,7 +2528,7 @@
         <v>139</v>
       </c>
       <c r="D3" t="s">
-        <v>104</v>
+        <v>103</v>
       </c>
       <c r="E3" t="n">
         <v>0</v>
@@ -2524,7 +2551,7 @@
         <v>141</v>
       </c>
       <c r="D4" t="s">
-        <v>104</v>
+        <v>103</v>
       </c>
       <c r="E4" t="n">
         <v>0</v>
@@ -2547,7 +2574,7 @@
         <v>143</v>
       </c>
       <c r="D5" t="s">
-        <v>104</v>
+        <v>103</v>
       </c>
       <c r="E5" t="n">
         <v>0</v>
@@ -2570,7 +2597,7 @@
         <v>145</v>
       </c>
       <c r="D6" t="s">
-        <v>72</v>
+        <v>71</v>
       </c>
       <c r="E6" t="n">
         <v>0</v>
@@ -2593,7 +2620,7 @@
         <v>147</v>
       </c>
       <c r="D7" t="s">
-        <v>60</v>
+        <v>59</v>
       </c>
       <c r="E7" t="n">
         <v>0</v>
@@ -2639,7 +2666,7 @@
         <v>152</v>
       </c>
       <c r="D9" t="s">
-        <v>47</v>
+        <v>32</v>
       </c>
       <c r="E9" t="n">
         <v>0</v>
@@ -2731,7 +2758,7 @@
         <v>158</v>
       </c>
       <c r="D3" t="s">
-        <v>51</v>
+        <v>50</v>
       </c>
       <c r="E3" t="n">
         <v>0</v>
@@ -2754,7 +2781,7 @@
         <v>160</v>
       </c>
       <c r="D4" t="s">
-        <v>47</v>
+        <v>32</v>
       </c>
       <c r="E4" t="n">
         <v>0</v>
@@ -2800,7 +2827,7 @@
         <v>164</v>
       </c>
       <c r="D6" t="s">
-        <v>47</v>
+        <v>32</v>
       </c>
       <c r="E6" t="n">
         <v>0</v>
@@ -2846,7 +2873,7 @@
         <v>169</v>
       </c>
       <c r="D8" t="s">
-        <v>47</v>
+        <v>32</v>
       </c>
       <c r="E8" t="n">
         <v>0</v>
@@ -2869,7 +2896,7 @@
         <v>171</v>
       </c>
       <c r="D9" t="s">
-        <v>60</v>
+        <v>59</v>
       </c>
       <c r="E9" t="n">
         <v>0</v>
@@ -2892,7 +2919,7 @@
         <v>173</v>
       </c>
       <c r="D10" t="s">
-        <v>51</v>
+        <v>50</v>
       </c>
       <c r="E10" t="n">
         <v>0</v>
@@ -2961,7 +2988,7 @@
         <v>176</v>
       </c>
       <c r="D2" t="s">
-        <v>47</v>
+        <v>32</v>
       </c>
       <c r="E2" t="n">
         <v>0</v>
@@ -2984,7 +3011,7 @@
         <v>178</v>
       </c>
       <c r="D3" t="s">
-        <v>51</v>
+        <v>50</v>
       </c>
       <c r="E3" t="n">
         <v>0</v>
@@ -3007,7 +3034,7 @@
         <v>180</v>
       </c>
       <c r="D4" t="s">
-        <v>51</v>
+        <v>50</v>
       </c>
       <c r="E4" t="n">
         <v>0</v>
@@ -3030,7 +3057,7 @@
         <v>182</v>
       </c>
       <c r="D5" t="s">
-        <v>107</v>
+        <v>106</v>
       </c>
       <c r="E5" t="n">
         <v>0</v>
@@ -3053,7 +3080,7 @@
         <v>184</v>
       </c>
       <c r="D6" t="s">
-        <v>80</v>
+        <v>79</v>
       </c>
       <c r="E6" t="n">
         <v>0</v>
@@ -3099,7 +3126,7 @@
         <v>188</v>
       </c>
       <c r="D8" t="s">
-        <v>68</v>
+        <v>67</v>
       </c>
       <c r="E8" t="n">
         <v>0</v>
@@ -3145,7 +3172,7 @@
         <v>192</v>
       </c>
       <c r="D10" t="s">
-        <v>72</v>
+        <v>71</v>
       </c>
       <c r="E10" t="n">
         <v>0</v>
@@ -3173,12 +3200,24 @@
       <c r="E11" t="n">
         <v>1</v>
       </c>
-      <c r="F11" s="1"/>
-      <c r="G11" s="1"/>
-      <c r="H11"/>
-      <c r="I11"/>
-      <c r="J11"/>
-      <c r="K11"/>
+      <c r="F11" s="1" t="n">
+        <v>45777</v>
+      </c>
+      <c r="G11" s="1" t="n">
+        <v>45799</v>
+      </c>
+      <c r="H11" t="n">
+        <v>23</v>
+      </c>
+      <c r="I11" t="s">
+        <v>42</v>
+      </c>
+      <c r="J11" t="s">
+        <v>196</v>
+      </c>
+      <c r="K11" t="s">
+        <v>16</v>
+      </c>
     </row>
   </sheetData>
   <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
@@ -3228,16 +3267,16 @@
     </row>
     <row r="2">
       <c r="A2" t="s">
-        <v>196</v>
+        <v>197</v>
       </c>
       <c r="B2" t="s">
-        <v>197</v>
+        <v>198</v>
       </c>
       <c r="C2" t="s">
-        <v>198</v>
+        <v>199</v>
       </c>
       <c r="D2" t="s">
-        <v>51</v>
+        <v>50</v>
       </c>
       <c r="E2" t="n">
         <v>1</v>

--- a/Stat Reviews/OT24_StatReview/scotusblog_replication/data/term_index.xlsx
+++ b/Stat Reviews/OT24_StatReview/scotusblog_replication/data/term_index.xlsx
@@ -1,625 +1,633 @@
 
 <file path=xl/workbook.xml><?xml version="1.0" encoding="utf-8"?>
 <workbook xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x15="http://schemas.microsoft.com/office/spreadsheetml/2010/11/main" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr6="http://schemas.microsoft.com/office/spreadsheetml/2016/revision6" xmlns:xr10="http://schemas.microsoft.com/office/spreadsheetml/2016/revision10" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" mc:Ignorable="x15 xr xr6 xr10 xr2">
-  <workbookPr date1904="false"/>
+  <fileVersion appName="xl" lastEdited="7" lowestEdited="7" rupBuild="28827"/>
+  <workbookPr/>
+  <mc:AlternateContent xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006">
+    <mc:Choice Requires="x15">
+      <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\Users\jaketruscott\Github\scotuswatch\Stat Reviews\OT24_StatReview\scotusblog_replication\data\"/>
+    </mc:Choice>
+  </mc:AlternateContent>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{7BFFBEBD-B4A6-4A60-8728-154472C9C7FF}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
-    <workbookView xWindow="0" yWindow="0" windowWidth="13125" windowHeight="6105" firstSheet="0" activeTab="0"/>
+    <workbookView xWindow="28680" yWindow="-120" windowWidth="29040" windowHeight="15720" activeTab="7" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
   <sheets>
-    <sheet name="No_Argument" sheetId="1" state="visible" r:id="rId1"/>
-    <sheet name="October" sheetId="2" state="visible" r:id="rId2"/>
-    <sheet name="November" sheetId="3" state="visible" r:id="rId3"/>
-    <sheet name="December" sheetId="4" state="visible" r:id="rId4"/>
-    <sheet name="January" sheetId="5" state="visible" r:id="rId5"/>
-    <sheet name="February" sheetId="6" state="visible" r:id="rId6"/>
-    <sheet name="March" sheetId="7" state="visible" r:id="rId7"/>
-    <sheet name="April" sheetId="8" state="visible" r:id="rId8"/>
-    <sheet name="May" sheetId="9" state="visible" r:id="rId9"/>
+    <sheet name="No_Argument" sheetId="1" r:id="rId1"/>
+    <sheet name="October" sheetId="2" r:id="rId2"/>
+    <sheet name="November" sheetId="3" r:id="rId3"/>
+    <sheet name="December" sheetId="4" r:id="rId4"/>
+    <sheet name="January" sheetId="5" r:id="rId5"/>
+    <sheet name="February" sheetId="6" r:id="rId6"/>
+    <sheet name="March" sheetId="7" r:id="rId7"/>
+    <sheet name="April" sheetId="8" r:id="rId8"/>
+    <sheet name="May" sheetId="9" r:id="rId9"/>
   </sheets>
+  <calcPr calcId="0"/>
 </workbook>
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="200" uniqueCount="200">
-  <si>
-    <t xml:space="preserve">sitting</t>
-  </si>
-  <si>
-    <t xml:space="preserve">docket</t>
-  </si>
-  <si>
-    <t xml:space="preserve">short_hand</t>
-  </si>
-  <si>
-    <t xml:space="preserve">lower_court</t>
-  </si>
-  <si>
-    <t xml:space="preserve">major_case</t>
-  </si>
-  <si>
-    <t xml:space="preserve">date_argued</t>
-  </si>
-  <si>
-    <t xml:space="preserve">date_decided</t>
-  </si>
-  <si>
-    <t xml:space="preserve">days_elapsed</t>
-  </si>
-  <si>
-    <t xml:space="preserve">decision</t>
-  </si>
-  <si>
-    <t xml:space="preserve">coalition</t>
-  </si>
-  <si>
-    <t xml:space="preserve">author</t>
-  </si>
-  <si>
-    <t xml:space="preserve">No Argument</t>
-  </si>
-  <si>
-    <t xml:space="preserve">23-167</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Hamm</t>
-  </si>
-  <si>
-    <t xml:space="preserve">CA11</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Vacate and Remand</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Per Curiam</t>
-  </si>
-  <si>
-    <t xml:space="preserve">23-6573</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Andrew</t>
-  </si>
-  <si>
-    <t xml:space="preserve">CA10</t>
-  </si>
-  <si>
-    <t xml:space="preserve">(7-2)</t>
-  </si>
-  <si>
-    <t xml:space="preserve">24A910</t>
-  </si>
-  <si>
-    <t xml:space="preserve">DOE v. CA</t>
-  </si>
-  <si>
-    <t xml:space="preserve">DCMA</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Granted</t>
-  </si>
-  <si>
-    <t xml:space="preserve">(5-4)</t>
-  </si>
-  <si>
-    <t xml:space="preserve">24A931</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Trump v. J.G.G.</t>
-  </si>
-  <si>
-    <t xml:space="preserve">DCDC</t>
-  </si>
-  <si>
-    <t xml:space="preserve">(5-4)*</t>
-  </si>
-  <si>
-    <t xml:space="preserve">24A1007</t>
-  </si>
-  <si>
-    <t xml:space="preserve">A.A.R.P v. Trump</t>
-  </si>
-  <si>
-    <t xml:space="preserve">CA5</t>
-  </si>
-  <si>
-    <t xml:space="preserve">October</t>
-  </si>
-  <si>
-    <t xml:space="preserve">23-191</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Willaims</t>
-  </si>
-  <si>
-    <t xml:space="preserve">SCAL</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Reverse and Remand</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Kavanaugh</t>
-  </si>
-  <si>
-    <t xml:space="preserve">23-677</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Royal Canin</t>
-  </si>
-  <si>
-    <t xml:space="preserve">CA8</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Affirm</t>
-  </si>
-  <si>
-    <t xml:space="preserve">(9-0)</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Kagan</t>
-  </si>
-  <si>
-    <t xml:space="preserve">23-852</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Vanderstok</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Gorsuch</t>
-  </si>
-  <si>
-    <t xml:space="preserve">23-621</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Lackey</t>
-  </si>
-  <si>
-    <t xml:space="preserve">CA4</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Roberts</t>
-  </si>
-  <si>
-    <t xml:space="preserve">22-7466</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Glossip</t>
-  </si>
-  <si>
-    <t xml:space="preserve">CCAOK</t>
-  </si>
-  <si>
-    <t xml:space="preserve">(6-2)</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Sotomayor</t>
-  </si>
-  <si>
-    <t xml:space="preserve">23-365</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Medical Marijuana</t>
-  </si>
-  <si>
-    <t xml:space="preserve">CA2</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Affirm and Remand</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Barrett</t>
-  </si>
-  <si>
-    <t xml:space="preserve">23-583</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Bouarafa</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Jackson</t>
-  </si>
-  <si>
-    <t xml:space="preserve">23-713</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Bufkin</t>
-  </si>
-  <si>
-    <t xml:space="preserve">CAFED</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Thomas</t>
-  </si>
-  <si>
-    <t xml:space="preserve">23-753</t>
-  </si>
-  <si>
-    <t xml:space="preserve">SF v. EPA</t>
-  </si>
-  <si>
-    <t xml:space="preserve">CA9</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Alito</t>
-  </si>
-  <si>
-    <t xml:space="preserve">November</t>
-  </si>
-  <si>
-    <t xml:space="preserve">23-1127</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Wisconsin Bell</t>
-  </si>
-  <si>
-    <t xml:space="preserve">CA7</t>
-  </si>
-  <si>
-    <t xml:space="preserve">23-715</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Advocate Christ Medical</t>
-  </si>
-  <si>
-    <t xml:space="preserve">CADC</t>
-  </si>
-  <si>
-    <t xml:space="preserve">23-217</t>
-  </si>
-  <si>
-    <t xml:space="preserve">E.M.D. Sales</t>
-  </si>
-  <si>
-    <t xml:space="preserve">23-980</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Facebook</t>
-  </si>
-  <si>
-    <t xml:space="preserve">DIG</t>
-  </si>
-  <si>
-    <t xml:space="preserve">23-929</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Velazquez</t>
-  </si>
-  <si>
-    <t xml:space="preserve">(6-3)</t>
-  </si>
-  <si>
-    <t xml:space="preserve">23-825</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Delligatti</t>
-  </si>
-  <si>
-    <t xml:space="preserve">23-970</t>
-  </si>
-  <si>
-    <t xml:space="preserve">NVIDIA</t>
-  </si>
-  <si>
-    <t xml:space="preserve">December</t>
-  </si>
-  <si>
-    <t xml:space="preserve">23-1038</t>
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="487" uniqueCount="200">
+  <si>
+    <t>sitting</t>
+  </si>
+  <si>
+    <t>docket</t>
+  </si>
+  <si>
+    <t>short_hand</t>
+  </si>
+  <si>
+    <t>lower_court</t>
+  </si>
+  <si>
+    <t>major_case</t>
+  </si>
+  <si>
+    <t>date_argued</t>
+  </si>
+  <si>
+    <t>date_decided</t>
+  </si>
+  <si>
+    <t>days_elapsed</t>
+  </si>
+  <si>
+    <t>decision</t>
+  </si>
+  <si>
+    <t>coalition</t>
+  </si>
+  <si>
+    <t>author</t>
+  </si>
+  <si>
+    <t>No Argument</t>
+  </si>
+  <si>
+    <t>23-167</t>
+  </si>
+  <si>
+    <t>Hamm</t>
+  </si>
+  <si>
+    <t>CA11</t>
+  </si>
+  <si>
+    <t>Vacate and Remand</t>
+  </si>
+  <si>
+    <t>Per Curiam</t>
+  </si>
+  <si>
+    <t>23-6573</t>
+  </si>
+  <si>
+    <t>Andrew</t>
+  </si>
+  <si>
+    <t>CA10</t>
+  </si>
+  <si>
+    <t>(7-2)</t>
+  </si>
+  <si>
+    <t>24A910</t>
+  </si>
+  <si>
+    <t>DOE v. CA</t>
+  </si>
+  <si>
+    <t>DCMA</t>
+  </si>
+  <si>
+    <t>Granted</t>
+  </si>
+  <si>
+    <t>(5-4)</t>
+  </si>
+  <si>
+    <t>24A931</t>
+  </si>
+  <si>
+    <t>Trump v. J.G.G.</t>
+  </si>
+  <si>
+    <t>DCDC</t>
+  </si>
+  <si>
+    <t>(5-4)*</t>
+  </si>
+  <si>
+    <t>24A1007</t>
+  </si>
+  <si>
+    <t>A.A.R.P v. Trump</t>
+  </si>
+  <si>
+    <t>CA5</t>
+  </si>
+  <si>
+    <t>October</t>
+  </si>
+  <si>
+    <t>23-191</t>
+  </si>
+  <si>
+    <t>Willaims</t>
+  </si>
+  <si>
+    <t>SCAL</t>
+  </si>
+  <si>
+    <t>Reverse and Remand</t>
+  </si>
+  <si>
+    <t>Kavanaugh</t>
+  </si>
+  <si>
+    <t>23-677</t>
+  </si>
+  <si>
+    <t>Royal Canin</t>
+  </si>
+  <si>
+    <t>CA8</t>
+  </si>
+  <si>
+    <t>Affirm</t>
+  </si>
+  <si>
+    <t>(9-0)</t>
+  </si>
+  <si>
+    <t>Kagan</t>
+  </si>
+  <si>
+    <t>23-852</t>
+  </si>
+  <si>
+    <t>Vanderstok</t>
+  </si>
+  <si>
+    <t>Gorsuch</t>
+  </si>
+  <si>
+    <t>23-621</t>
+  </si>
+  <si>
+    <t>Lackey</t>
+  </si>
+  <si>
+    <t>CA4</t>
+  </si>
+  <si>
+    <t>Roberts</t>
+  </si>
+  <si>
+    <t>22-7466</t>
+  </si>
+  <si>
+    <t>Glossip</t>
+  </si>
+  <si>
+    <t>CCAOK</t>
+  </si>
+  <si>
+    <t>(6-2)</t>
+  </si>
+  <si>
+    <t>Sotomayor</t>
+  </si>
+  <si>
+    <t>23-365</t>
+  </si>
+  <si>
+    <t>Medical Marijuana</t>
+  </si>
+  <si>
+    <t>CA2</t>
+  </si>
+  <si>
+    <t>Affirm and Remand</t>
+  </si>
+  <si>
+    <t>Barrett</t>
+  </si>
+  <si>
+    <t>23-583</t>
+  </si>
+  <si>
+    <t>Bouarafa</t>
+  </si>
+  <si>
+    <t>Jackson</t>
+  </si>
+  <si>
+    <t>23-713</t>
+  </si>
+  <si>
+    <t>Bufkin</t>
+  </si>
+  <si>
+    <t>CAFED</t>
+  </si>
+  <si>
+    <t>Thomas</t>
+  </si>
+  <si>
+    <t>23-753</t>
+  </si>
+  <si>
+    <t>SF v. EPA</t>
+  </si>
+  <si>
+    <t>CA9</t>
+  </si>
+  <si>
+    <t>Alito</t>
+  </si>
+  <si>
+    <t>November</t>
+  </si>
+  <si>
+    <t>23-1127</t>
+  </si>
+  <si>
+    <t>Wisconsin Bell</t>
+  </si>
+  <si>
+    <t>CA7</t>
+  </si>
+  <si>
+    <t>23-715</t>
+  </si>
+  <si>
+    <t>Advocate Christ Medical</t>
+  </si>
+  <si>
+    <t>CADC</t>
+  </si>
+  <si>
+    <t>23-217</t>
+  </si>
+  <si>
+    <t>E.M.D. Sales</t>
+  </si>
+  <si>
+    <t>23-980</t>
+  </si>
+  <si>
+    <t>Facebook</t>
+  </si>
+  <si>
+    <t>DIG</t>
+  </si>
+  <si>
+    <t>23-929</t>
+  </si>
+  <si>
+    <t>Velazquez</t>
+  </si>
+  <si>
+    <t>(6-3)</t>
+  </si>
+  <si>
+    <t>23-825</t>
+  </si>
+  <si>
+    <t>Delligatti</t>
+  </si>
+  <si>
+    <t>23-970</t>
+  </si>
+  <si>
+    <t>NVIDIA</t>
+  </si>
+  <si>
+    <t>December</t>
+  </si>
+  <si>
+    <t>23-1038</t>
   </si>
   <si>
     <t xml:space="preserve">Wages and White Lion </t>
   </si>
   <si>
-    <t xml:space="preserve">23-824</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Miller</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Reverse</t>
-  </si>
-  <si>
-    <t xml:space="preserve">(8-1)</t>
-  </si>
-  <si>
-    <t xml:space="preserve">23-867</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Hungary</t>
-  </si>
-  <si>
-    <t xml:space="preserve">23-477</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Skrmetti</t>
-  </si>
-  <si>
-    <t xml:space="preserve">CA6</t>
-  </si>
-  <si>
-    <t xml:space="preserve">23-909</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Kouisisis</t>
-  </si>
-  <si>
-    <t xml:space="preserve">CA3</t>
-  </si>
-  <si>
-    <t xml:space="preserve">23-861</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Feliciano</t>
-  </si>
-  <si>
-    <t xml:space="preserve">23-975</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Seven County</t>
-  </si>
-  <si>
-    <t xml:space="preserve">(8-0)</t>
-  </si>
-  <si>
-    <t xml:space="preserve">23-900</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Dewberry</t>
-  </si>
-  <si>
-    <t xml:space="preserve">January</t>
-  </si>
-  <si>
-    <t xml:space="preserve">23-1002</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Hewitt</t>
-  </si>
-  <si>
-    <t xml:space="preserve">23-997</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Stanley</t>
-  </si>
-  <si>
-    <t xml:space="preserve">23-1095</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Thompson</t>
-  </si>
-  <si>
-    <t xml:space="preserve">23-971</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Waetzig</t>
-  </si>
-  <si>
-    <t xml:space="preserve">23-1122</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Free Speech</t>
-  </si>
-  <si>
-    <t xml:space="preserve">23-1187</t>
+    <t>23-824</t>
+  </si>
+  <si>
+    <t>Miller</t>
+  </si>
+  <si>
+    <t>Reverse</t>
+  </si>
+  <si>
+    <t>(8-1)</t>
+  </si>
+  <si>
+    <t>23-867</t>
+  </si>
+  <si>
+    <t>Hungary</t>
+  </si>
+  <si>
+    <t>23-477</t>
+  </si>
+  <si>
+    <t>Skrmetti</t>
+  </si>
+  <si>
+    <t>CA6</t>
+  </si>
+  <si>
+    <t>23-909</t>
+  </si>
+  <si>
+    <t>Kouisisis</t>
+  </si>
+  <si>
+    <t>CA3</t>
+  </si>
+  <si>
+    <t>23-861</t>
+  </si>
+  <si>
+    <t>Feliciano</t>
+  </si>
+  <si>
+    <t>23-975</t>
+  </si>
+  <si>
+    <t>Seven County</t>
+  </si>
+  <si>
+    <t>(8-0)</t>
+  </si>
+  <si>
+    <t>23-900</t>
+  </si>
+  <si>
+    <t>Dewberry</t>
+  </si>
+  <si>
+    <t>January</t>
+  </si>
+  <si>
+    <t>23-1002</t>
+  </si>
+  <si>
+    <t>Hewitt</t>
+  </si>
+  <si>
+    <t>23-997</t>
+  </si>
+  <si>
+    <t>Stanley</t>
+  </si>
+  <si>
+    <t>23-1095</t>
+  </si>
+  <si>
+    <t>Thompson</t>
+  </si>
+  <si>
+    <t>23-971</t>
+  </si>
+  <si>
+    <t>Waetzig</t>
+  </si>
+  <si>
+    <t>23-1122</t>
+  </si>
+  <si>
+    <t>Free Speech</t>
+  </si>
+  <si>
+    <t>23-1187</t>
   </si>
   <si>
     <t xml:space="preserve"> R.J. Reynolds </t>
   </si>
   <si>
-    <t xml:space="preserve">23-1226</t>
-  </si>
-  <si>
-    <t xml:space="preserve">McLaughlin</t>
-  </si>
-  <si>
-    <t xml:space="preserve">23-1239</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Barnes</t>
-  </si>
-  <si>
-    <t xml:space="preserve">23-1007</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Cunningham</t>
-  </si>
-  <si>
-    <t xml:space="preserve">24-656</t>
-  </si>
-  <si>
-    <t xml:space="preserve">TikTok</t>
-  </si>
-  <si>
-    <t xml:space="preserve">February</t>
-  </si>
-  <si>
-    <t xml:space="preserve">23-7809</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Guitierrez</t>
-  </si>
-  <si>
-    <t xml:space="preserve">23-7483</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Esteras</t>
-  </si>
-  <si>
-    <t xml:space="preserve">23-1324</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Perttu</t>
-  </si>
-  <si>
-    <t xml:space="preserve">23-1039</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Ames</t>
-  </si>
-  <si>
-    <t xml:space="preserve">23-1201</t>
-  </si>
-  <si>
-    <t xml:space="preserve">CC/Devas</t>
-  </si>
-  <si>
-    <t xml:space="preserve">23-1259</t>
-  </si>
-  <si>
-    <t xml:space="preserve">BLOM Bank</t>
-  </si>
-  <si>
-    <t xml:space="preserve">23-1141</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Smith and Wesson</t>
-  </si>
-  <si>
-    <t xml:space="preserve">CA1</t>
-  </si>
-  <si>
-    <t xml:space="preserve">23-1300</t>
-  </si>
-  <si>
-    <t xml:space="preserve">NRC</t>
-  </si>
-  <si>
-    <t xml:space="preserve">March</t>
-  </si>
-  <si>
-    <t xml:space="preserve">24-109</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Lousiana</t>
-  </si>
-  <si>
-    <t xml:space="preserve">WDLA</t>
-  </si>
-  <si>
-    <t xml:space="preserve">23-1270</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Riley</t>
-  </si>
-  <si>
-    <t xml:space="preserve">23-1229</t>
+    <t>23-1226</t>
+  </si>
+  <si>
+    <t>McLaughlin</t>
+  </si>
+  <si>
+    <t>23-1239</t>
+  </si>
+  <si>
+    <t>Barnes</t>
+  </si>
+  <si>
+    <t>23-1007</t>
+  </si>
+  <si>
+    <t>Cunningham</t>
+  </si>
+  <si>
+    <t>24-656</t>
+  </si>
+  <si>
+    <t>TikTok</t>
+  </si>
+  <si>
+    <t>February</t>
+  </si>
+  <si>
+    <t>23-7809</t>
+  </si>
+  <si>
+    <t>Guitierrez</t>
+  </si>
+  <si>
+    <t>23-7483</t>
+  </si>
+  <si>
+    <t>Esteras</t>
+  </si>
+  <si>
+    <t>23-1324</t>
+  </si>
+  <si>
+    <t>Perttu</t>
+  </si>
+  <si>
+    <t>23-1039</t>
+  </si>
+  <si>
+    <t>Ames</t>
+  </si>
+  <si>
+    <t>23-1201</t>
+  </si>
+  <si>
+    <t>CC/Devas</t>
+  </si>
+  <si>
+    <t>23-1259</t>
+  </si>
+  <si>
+    <t>BLOM Bank</t>
+  </si>
+  <si>
+    <t>23-1141</t>
+  </si>
+  <si>
+    <t>Smith and Wesson</t>
+  </si>
+  <si>
+    <t>CA1</t>
+  </si>
+  <si>
+    <t>23-1300</t>
+  </si>
+  <si>
+    <t>NRC</t>
+  </si>
+  <si>
+    <t>March</t>
+  </si>
+  <si>
+    <t>24-109</t>
+  </si>
+  <si>
+    <t>Lousiana</t>
+  </si>
+  <si>
+    <t>WDLA</t>
+  </si>
+  <si>
+    <t>23-1270</t>
+  </si>
+  <si>
+    <t>Riley</t>
+  </si>
+  <si>
+    <t>23-1229</t>
   </si>
   <si>
     <t xml:space="preserve">Calumet </t>
   </si>
   <si>
-    <t xml:space="preserve">23-1067</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Oklahoma</t>
-  </si>
-  <si>
-    <t xml:space="preserve">24-354</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Consumers' Research</t>
-  </si>
-  <si>
-    <t xml:space="preserve">24-154</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Catholic Charities</t>
-  </si>
-  <si>
-    <t xml:space="preserve">SCWI</t>
-  </si>
-  <si>
-    <t xml:space="preserve">23-1345</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Rivers</t>
-  </si>
-  <si>
-    <t xml:space="preserve">24-20</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Fuld</t>
-  </si>
-  <si>
-    <t xml:space="preserve">23-1275</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Medina</t>
-  </si>
-  <si>
-    <t xml:space="preserve">April</t>
-  </si>
-  <si>
-    <t xml:space="preserve">24-316</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Kennedy</t>
-  </si>
-  <si>
-    <t xml:space="preserve">24-275</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Parrish</t>
-  </si>
-  <si>
-    <t xml:space="preserve">24-297</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Mahmoud</t>
-  </si>
-  <si>
-    <t xml:space="preserve">24-416</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Cir</t>
-  </si>
-  <si>
-    <t xml:space="preserve">24-7</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Diamond</t>
-  </si>
-  <si>
-    <t xml:space="preserve">24-249</t>
-  </si>
-  <si>
-    <t xml:space="preserve">A.J.T.</t>
-  </si>
-  <si>
-    <t xml:space="preserve">24-320</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Soto</t>
-  </si>
-  <si>
-    <t xml:space="preserve">24-362</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Martin</t>
-  </si>
-  <si>
-    <t xml:space="preserve">24-304</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Laboratory Corp.</t>
-  </si>
-  <si>
-    <t xml:space="preserve">24-394</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Drummond</t>
-  </si>
-  <si>
-    <t xml:space="preserve">SCOK</t>
-  </si>
-  <si>
-    <t xml:space="preserve">(4-4)*</t>
-  </si>
-  <si>
-    <t xml:space="preserve">May</t>
-  </si>
-  <si>
-    <t xml:space="preserve">24A884</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Trump v. CASA</t>
+    <t>23-1067</t>
+  </si>
+  <si>
+    <t>Oklahoma</t>
+  </si>
+  <si>
+    <t>24-354</t>
+  </si>
+  <si>
+    <t>Consumers' Research</t>
+  </si>
+  <si>
+    <t>24-154</t>
+  </si>
+  <si>
+    <t>Catholic Charities</t>
+  </si>
+  <si>
+    <t>SCWI</t>
+  </si>
+  <si>
+    <t>23-1345</t>
+  </si>
+  <si>
+    <t>Rivers</t>
+  </si>
+  <si>
+    <t>24-20</t>
+  </si>
+  <si>
+    <t>Fuld</t>
+  </si>
+  <si>
+    <t>23-1275</t>
+  </si>
+  <si>
+    <t>Medina</t>
+  </si>
+  <si>
+    <t>April</t>
+  </si>
+  <si>
+    <t>24-316</t>
+  </si>
+  <si>
+    <t>Kennedy</t>
+  </si>
+  <si>
+    <t>24-275</t>
+  </si>
+  <si>
+    <t>Parrish</t>
+  </si>
+  <si>
+    <t>24-297</t>
+  </si>
+  <si>
+    <t>Mahmoud</t>
+  </si>
+  <si>
+    <t>24-416</t>
+  </si>
+  <si>
+    <t>Cir</t>
+  </si>
+  <si>
+    <t>24-7</t>
+  </si>
+  <si>
+    <t>Diamond</t>
+  </si>
+  <si>
+    <t>24-249</t>
+  </si>
+  <si>
+    <t>A.J.T.</t>
+  </si>
+  <si>
+    <t>24-320</t>
+  </si>
+  <si>
+    <t>Soto</t>
+  </si>
+  <si>
+    <t>24-362</t>
+  </si>
+  <si>
+    <t>Martin</t>
+  </si>
+  <si>
+    <t>24-304</t>
+  </si>
+  <si>
+    <t>Laboratory Corp.</t>
+  </si>
+  <si>
+    <t>24-394</t>
+  </si>
+  <si>
+    <t>Drummond</t>
+  </si>
+  <si>
+    <t>SCOK</t>
+  </si>
+  <si>
+    <t>(4-4)*</t>
+  </si>
+  <si>
+    <t>May</t>
+  </si>
+  <si>
+    <t>24A884</t>
+  </si>
+  <si>
+    <t>Trump v. CASA</t>
   </si>
 </sst>
 </file>
@@ -627,9 +635,9 @@
 <file path=xl/styles.xml><?xml version="1.0" encoding="utf-8"?>
 <styleSheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:x16r2="http://schemas.microsoft.com/office/spreadsheetml/2015/02/main" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" mc:Ignorable="x14ac x16r2 xr">
   <numFmts count="1">
-    <numFmt numFmtId="165" formatCode="mm/dd/yyyy"/>
+    <numFmt numFmtId="164" formatCode="mm/dd/yyyy"/>
   </numFmts>
-  <fonts count="2">
+  <fonts count="2" x14ac:knownFonts="1">
     <font>
       <sz val="11"/>
       <color rgb="FF000000"/>
@@ -665,12 +673,21 @@
   </cellStyleXfs>
   <cellXfs count="2">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0"/>
-    <xf numFmtId="165" fontId="1" fillId="0" borderId="0" xfId="0" applyFont="1" applyNumberFormat="1"/>
+    <xf numFmtId="164" fontId="1" fillId="0" borderId="0" xfId="0" applyNumberFormat="1" applyFont="1"/>
   </cellXfs>
   <cellStyles count="1">
     <cellStyle name="Normal" xfId="0" builtinId="0"/>
   </cellStyles>
   <dxfs count="0"/>
+  <tableStyles count="0" defaultTableStyle="TableStyleMedium2" defaultPivotStyle="PivotStyleLight16"/>
+  <extLst>
+    <ext xmlns:x14="http://schemas.microsoft.com/office/spreadsheetml/2009/9/main" uri="{EB79DEF2-80B8-43e5-95BD-54CBDDF9020C}">
+      <x14:slicerStyles defaultSlicerStyle="SlicerStyleLight1"/>
+    </ext>
+    <ext xmlns:x15="http://schemas.microsoft.com/office/spreadsheetml/2010/11/main" uri="{9260A510-F301-46a8-8635-F512D64BE5F5}">
+      <x15:timelineStyles defaultTimelineStyle="TimeSlicerStyleLight1"/>
+    </ext>
+  </extLst>
 </styleSheet>
 </file>
 
@@ -952,11 +969,11 @@
 </file>
 
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
-<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:xdr="http://schemas.openxmlformats.org/drawingml/2006/spreadsheetDrawing" xmlns:x14="http://schemas.microsoft.com/office/spreadsheetml/2009/9/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3">
-  <dimension ref="A1"/>
-  <sheetFormatPr defaultRowHeight="15.0" baseColWidth="10"/>
+<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{00000000-0001-0000-0000-000000000000}">
+  <dimension ref="A1:K6"/>
+  <sheetFormatPr defaultColWidth="11.42578125" defaultRowHeight="15" x14ac:dyDescent="0.25"/>
   <sheetData>
-    <row r="1">
+    <row r="1" spans="1:11" x14ac:dyDescent="0.25">
       <c r="A1" t="s">
         <v>0</v>
       </c>
@@ -991,7 +1008,7 @@
         <v>10</v>
       </c>
     </row>
-    <row r="2">
+    <row r="2" spans="1:11" x14ac:dyDescent="0.25">
       <c r="A2" t="s">
         <v>11</v>
       </c>
@@ -1004,14 +1021,13 @@
       <c r="D2" t="s">
         <v>14</v>
       </c>
-      <c r="E2" t="n">
+      <c r="E2">
         <v>0</v>
       </c>
       <c r="F2" s="1"/>
-      <c r="G2" s="1" t="n">
+      <c r="G2" s="1">
         <v>45600</v>
       </c>
-      <c r="H2"/>
       <c r="I2" t="s">
         <v>15</v>
       </c>
@@ -1022,7 +1038,7 @@
         <v>16</v>
       </c>
     </row>
-    <row r="3">
+    <row r="3" spans="1:11" x14ac:dyDescent="0.25">
       <c r="A3" t="s">
         <v>11</v>
       </c>
@@ -1035,14 +1051,13 @@
       <c r="D3" t="s">
         <v>19</v>
       </c>
-      <c r="E3" t="n">
+      <c r="E3">
         <v>0</v>
       </c>
       <c r="F3" s="1"/>
-      <c r="G3" s="1" t="n">
+      <c r="G3" s="1">
         <v>45678</v>
       </c>
-      <c r="H3"/>
       <c r="I3" t="s">
         <v>15</v>
       </c>
@@ -1053,7 +1068,7 @@
         <v>16</v>
       </c>
     </row>
-    <row r="4">
+    <row r="4" spans="1:11" x14ac:dyDescent="0.25">
       <c r="A4" t="s">
         <v>11</v>
       </c>
@@ -1066,14 +1081,13 @@
       <c r="D4" t="s">
         <v>23</v>
       </c>
-      <c r="E4" t="n">
+      <c r="E4">
         <v>0</v>
       </c>
       <c r="F4" s="1"/>
-      <c r="G4" s="1" t="n">
+      <c r="G4" s="1">
         <v>45751</v>
       </c>
-      <c r="H4"/>
       <c r="I4" t="s">
         <v>24</v>
       </c>
@@ -1084,7 +1098,7 @@
         <v>16</v>
       </c>
     </row>
-    <row r="5">
+    <row r="5" spans="1:11" x14ac:dyDescent="0.25">
       <c r="A5" t="s">
         <v>11</v>
       </c>
@@ -1097,14 +1111,13 @@
       <c r="D5" t="s">
         <v>28</v>
       </c>
-      <c r="E5" t="n">
+      <c r="E5">
         <v>0</v>
       </c>
       <c r="F5" s="1"/>
-      <c r="G5" s="1" t="n">
+      <c r="G5" s="1">
         <v>45754</v>
       </c>
-      <c r="H5"/>
       <c r="I5" t="s">
         <v>24</v>
       </c>
@@ -1115,7 +1128,7 @@
         <v>16</v>
       </c>
     </row>
-    <row r="6">
+    <row r="6" spans="1:11" x14ac:dyDescent="0.25">
       <c r="A6" t="s">
         <v>11</v>
       </c>
@@ -1128,14 +1141,13 @@
       <c r="D6" t="s">
         <v>32</v>
       </c>
-      <c r="E6" t="n">
+      <c r="E6">
         <v>0</v>
       </c>
       <c r="F6" s="1"/>
-      <c r="G6" s="1" t="n">
+      <c r="G6" s="1">
         <v>45793</v>
       </c>
-      <c r="H6"/>
       <c r="I6" t="s">
         <v>24</v>
       </c>
@@ -1148,16 +1160,16 @@
     </row>
   </sheetData>
   <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
-  <pageSetup paperSize="9" orientation="portrait" horizontalDpi="300" verticalDpi="300" r:id="rId2"/>
+  <pageSetup paperSize="9" orientation="portrait" horizontalDpi="300" verticalDpi="300"/>
 </worksheet>
 </file>
 
 <file path=xl/worksheets/sheet2.xml><?xml version="1.0" encoding="utf-8"?>
-<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:xdr="http://schemas.openxmlformats.org/drawingml/2006/spreadsheetDrawing" xmlns:x14="http://schemas.microsoft.com/office/spreadsheetml/2009/9/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3">
-  <dimension ref="A1"/>
-  <sheetFormatPr defaultRowHeight="15.0" baseColWidth="10"/>
+<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{00000000-0001-0000-0100-000000000000}">
+  <dimension ref="A1:K10"/>
+  <sheetFormatPr defaultColWidth="11.42578125" defaultRowHeight="15" x14ac:dyDescent="0.25"/>
   <sheetData>
-    <row r="1">
+    <row r="1" spans="1:11" x14ac:dyDescent="0.25">
       <c r="A1" t="s">
         <v>0</v>
       </c>
@@ -1192,7 +1204,7 @@
         <v>10</v>
       </c>
     </row>
-    <row r="2">
+    <row r="2" spans="1:11" x14ac:dyDescent="0.25">
       <c r="A2" t="s">
         <v>33</v>
       </c>
@@ -1205,16 +1217,16 @@
       <c r="D2" t="s">
         <v>36</v>
       </c>
-      <c r="E2" t="n">
-        <v>0</v>
-      </c>
-      <c r="F2" s="1" t="n">
+      <c r="E2">
+        <v>0</v>
+      </c>
+      <c r="F2" s="1">
         <v>45572</v>
       </c>
-      <c r="G2" s="1" t="n">
+      <c r="G2" s="1">
         <v>45709</v>
       </c>
-      <c r="H2" t="n">
+      <c r="H2">
         <v>138</v>
       </c>
       <c r="I2" t="s">
@@ -1227,7 +1239,7 @@
         <v>38</v>
       </c>
     </row>
-    <row r="3">
+    <row r="3" spans="1:11" x14ac:dyDescent="0.25">
       <c r="A3" t="s">
         <v>33</v>
       </c>
@@ -1240,16 +1252,16 @@
       <c r="D3" t="s">
         <v>41</v>
       </c>
-      <c r="E3" t="n">
-        <v>0</v>
-      </c>
-      <c r="F3" s="1" t="n">
+      <c r="E3">
+        <v>0</v>
+      </c>
+      <c r="F3" s="1">
         <v>45572</v>
       </c>
-      <c r="G3" s="1" t="n">
+      <c r="G3" s="1">
         <v>45672</v>
       </c>
-      <c r="H3" t="n">
+      <c r="H3">
         <v>101</v>
       </c>
       <c r="I3" t="s">
@@ -1262,7 +1274,7 @@
         <v>44</v>
       </c>
     </row>
-    <row r="4">
+    <row r="4" spans="1:11" x14ac:dyDescent="0.25">
       <c r="A4" t="s">
         <v>33</v>
       </c>
@@ -1275,16 +1287,16 @@
       <c r="D4" t="s">
         <v>32</v>
       </c>
-      <c r="E4" t="n">
-        <v>0</v>
-      </c>
-      <c r="F4" s="1" t="n">
+      <c r="E4">
+        <v>0</v>
+      </c>
+      <c r="F4" s="1">
         <v>45573</v>
       </c>
-      <c r="G4" s="1" t="n">
+      <c r="G4" s="1">
         <v>45742</v>
       </c>
-      <c r="H4" t="n">
+      <c r="H4">
         <v>170</v>
       </c>
       <c r="I4" t="s">
@@ -1297,7 +1309,7 @@
         <v>47</v>
       </c>
     </row>
-    <row r="5">
+    <row r="5" spans="1:11" x14ac:dyDescent="0.25">
       <c r="A5" t="s">
         <v>33</v>
       </c>
@@ -1310,16 +1322,16 @@
       <c r="D5" t="s">
         <v>50</v>
       </c>
-      <c r="E5" t="n">
-        <v>0</v>
-      </c>
-      <c r="F5" s="1" t="n">
+      <c r="E5">
+        <v>0</v>
+      </c>
+      <c r="F5" s="1">
         <v>45573</v>
       </c>
-      <c r="G5" s="1" t="n">
+      <c r="G5" s="1">
         <v>45713</v>
       </c>
-      <c r="H5" t="n">
+      <c r="H5">
         <v>141</v>
       </c>
       <c r="I5" t="s">
@@ -1332,7 +1344,7 @@
         <v>51</v>
       </c>
     </row>
-    <row r="6">
+    <row r="6" spans="1:11" x14ac:dyDescent="0.25">
       <c r="A6" t="s">
         <v>33</v>
       </c>
@@ -1345,16 +1357,16 @@
       <c r="D6" t="s">
         <v>54</v>
       </c>
-      <c r="E6" t="n">
+      <c r="E6">
         <v>1</v>
       </c>
-      <c r="F6" s="1" t="n">
+      <c r="F6" s="1">
         <v>45574</v>
       </c>
-      <c r="G6" s="1" t="n">
+      <c r="G6" s="1">
         <v>45713</v>
       </c>
-      <c r="H6" t="n">
+      <c r="H6">
         <v>140</v>
       </c>
       <c r="I6" t="s">
@@ -1367,7 +1379,7 @@
         <v>56</v>
       </c>
     </row>
-    <row r="7">
+    <row r="7" spans="1:11" x14ac:dyDescent="0.25">
       <c r="A7" t="s">
         <v>33</v>
       </c>
@@ -1380,16 +1392,16 @@
       <c r="D7" t="s">
         <v>59</v>
       </c>
-      <c r="E7" t="n">
-        <v>0</v>
-      </c>
-      <c r="F7" s="1" t="n">
+      <c r="E7">
+        <v>0</v>
+      </c>
+      <c r="F7" s="1">
         <v>45580</v>
       </c>
-      <c r="G7" s="1" t="n">
+      <c r="G7" s="1">
         <v>45749</v>
       </c>
-      <c r="H7" t="n">
+      <c r="H7">
         <v>170</v>
       </c>
       <c r="I7" t="s">
@@ -1402,7 +1414,7 @@
         <v>61</v>
       </c>
     </row>
-    <row r="8">
+    <row r="8" spans="1:11" x14ac:dyDescent="0.25">
       <c r="A8" t="s">
         <v>33</v>
       </c>
@@ -1415,16 +1427,16 @@
       <c r="D8" t="s">
         <v>14</v>
       </c>
-      <c r="E8" t="n">
-        <v>0</v>
-      </c>
-      <c r="F8" s="1" t="n">
+      <c r="E8">
+        <v>0</v>
+      </c>
+      <c r="F8" s="1">
         <v>45580</v>
       </c>
-      <c r="G8" s="1" t="n">
+      <c r="G8" s="1">
         <v>45636</v>
       </c>
-      <c r="H8" t="n">
+      <c r="H8">
         <v>57</v>
       </c>
       <c r="I8" t="s">
@@ -1437,7 +1449,7 @@
         <v>64</v>
       </c>
     </row>
-    <row r="9">
+    <row r="9" spans="1:11" x14ac:dyDescent="0.25">
       <c r="A9" t="s">
         <v>33</v>
       </c>
@@ -1450,16 +1462,16 @@
       <c r="D9" t="s">
         <v>67</v>
       </c>
-      <c r="E9" t="n">
-        <v>0</v>
-      </c>
-      <c r="F9" s="1" t="n">
+      <c r="E9">
+        <v>0</v>
+      </c>
+      <c r="F9" s="1">
         <v>45581</v>
       </c>
-      <c r="G9" s="1" t="n">
+      <c r="G9" s="1">
         <v>45721</v>
       </c>
-      <c r="H9" t="n">
+      <c r="H9">
         <v>141</v>
       </c>
       <c r="I9" t="s">
@@ -1472,7 +1484,7 @@
         <v>68</v>
       </c>
     </row>
-    <row r="10">
+    <row r="10" spans="1:11" x14ac:dyDescent="0.25">
       <c r="A10" t="s">
         <v>33</v>
       </c>
@@ -1485,16 +1497,16 @@
       <c r="D10" t="s">
         <v>71</v>
       </c>
-      <c r="E10" t="n">
-        <v>0</v>
-      </c>
-      <c r="F10" s="1" t="n">
+      <c r="E10">
+        <v>0</v>
+      </c>
+      <c r="F10" s="1">
         <v>45581</v>
       </c>
-      <c r="G10" s="1" t="n">
+      <c r="G10" s="1">
         <v>45720</v>
       </c>
-      <c r="H10" t="n">
+      <c r="H10">
         <v>140</v>
       </c>
       <c r="I10" t="s">
@@ -1509,16 +1521,16 @@
     </row>
   </sheetData>
   <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
-  <pageSetup paperSize="9" orientation="portrait" horizontalDpi="300" verticalDpi="300" r:id="rId2"/>
+  <pageSetup paperSize="9" orientation="portrait" horizontalDpi="300" verticalDpi="300"/>
 </worksheet>
 </file>
 
 <file path=xl/worksheets/sheet3.xml><?xml version="1.0" encoding="utf-8"?>
-<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:xdr="http://schemas.openxmlformats.org/drawingml/2006/spreadsheetDrawing" xmlns:x14="http://schemas.microsoft.com/office/spreadsheetml/2009/9/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3">
-  <dimension ref="A1"/>
-  <sheetFormatPr defaultRowHeight="15.0" baseColWidth="10"/>
+<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{00000000-0001-0000-0200-000000000000}">
+  <dimension ref="A1:K8"/>
+  <sheetFormatPr defaultColWidth="11.42578125" defaultRowHeight="15" x14ac:dyDescent="0.25"/>
   <sheetData>
-    <row r="1">
+    <row r="1" spans="1:11" x14ac:dyDescent="0.25">
       <c r="A1" t="s">
         <v>0</v>
       </c>
@@ -1553,7 +1565,7 @@
         <v>10</v>
       </c>
     </row>
-    <row r="2">
+    <row r="2" spans="1:11" x14ac:dyDescent="0.25">
       <c r="A2" t="s">
         <v>73</v>
       </c>
@@ -1566,16 +1578,16 @@
       <c r="D2" t="s">
         <v>76</v>
       </c>
-      <c r="E2" t="n">
-        <v>0</v>
-      </c>
-      <c r="F2" s="1" t="n">
+      <c r="E2">
+        <v>0</v>
+      </c>
+      <c r="F2" s="1">
         <v>45600</v>
       </c>
-      <c r="G2" s="1" t="n">
+      <c r="G2" s="1">
         <v>45709</v>
       </c>
-      <c r="H2" t="n">
+      <c r="H2">
         <v>110</v>
       </c>
       <c r="I2" t="s">
@@ -1588,7 +1600,7 @@
         <v>44</v>
       </c>
     </row>
-    <row r="3">
+    <row r="3" spans="1:11" x14ac:dyDescent="0.25">
       <c r="A3" t="s">
         <v>73</v>
       </c>
@@ -1601,16 +1613,16 @@
       <c r="D3" t="s">
         <v>79</v>
       </c>
-      <c r="E3" t="n">
-        <v>0</v>
-      </c>
-      <c r="F3" s="1" t="n">
+      <c r="E3">
+        <v>0</v>
+      </c>
+      <c r="F3" s="1">
         <v>45601</v>
       </c>
-      <c r="G3" s="1" t="n">
+      <c r="G3" s="1">
         <v>45776</v>
       </c>
-      <c r="H3" t="n">
+      <c r="H3">
         <v>176</v>
       </c>
       <c r="I3" t="s">
@@ -1623,7 +1635,7 @@
         <v>61</v>
       </c>
     </row>
-    <row r="4">
+    <row r="4" spans="1:11" x14ac:dyDescent="0.25">
       <c r="A4" t="s">
         <v>73</v>
       </c>
@@ -1636,16 +1648,16 @@
       <c r="D4" t="s">
         <v>50</v>
       </c>
-      <c r="E4" t="n">
-        <v>0</v>
-      </c>
-      <c r="F4" s="1" t="n">
+      <c r="E4">
+        <v>0</v>
+      </c>
+      <c r="F4" s="1">
         <v>45601</v>
       </c>
-      <c r="G4" s="1" t="n">
+      <c r="G4" s="1">
         <v>45672</v>
       </c>
-      <c r="H4" t="n">
+      <c r="H4">
         <v>72</v>
       </c>
       <c r="I4" t="s">
@@ -1658,7 +1670,7 @@
         <v>38</v>
       </c>
     </row>
-    <row r="5">
+    <row r="5" spans="1:11" x14ac:dyDescent="0.25">
       <c r="A5" t="s">
         <v>73</v>
       </c>
@@ -1671,16 +1683,16 @@
       <c r="D5" t="s">
         <v>71</v>
       </c>
-      <c r="E5" t="n">
-        <v>0</v>
-      </c>
-      <c r="F5" s="1" t="n">
+      <c r="E5">
+        <v>0</v>
+      </c>
+      <c r="F5" s="1">
         <v>45602</v>
       </c>
-      <c r="G5" s="1" t="n">
+      <c r="G5" s="1">
         <v>45618</v>
       </c>
-      <c r="H5" t="n">
+      <c r="H5">
         <v>17</v>
       </c>
       <c r="I5" t="s">
@@ -1693,7 +1705,7 @@
         <v>16</v>
       </c>
     </row>
-    <row r="6">
+    <row r="6" spans="1:11" x14ac:dyDescent="0.25">
       <c r="A6" t="s">
         <v>73</v>
       </c>
@@ -1706,16 +1718,16 @@
       <c r="D6" t="s">
         <v>59</v>
       </c>
-      <c r="E6" t="n">
-        <v>0</v>
-      </c>
-      <c r="F6" s="1" t="n">
+      <c r="E6">
+        <v>0</v>
+      </c>
+      <c r="F6" s="1">
         <v>45608</v>
       </c>
-      <c r="G6" s="1" t="n">
+      <c r="G6" s="1">
         <v>45769</v>
       </c>
-      <c r="H6" t="n">
+      <c r="H6">
         <v>162</v>
       </c>
       <c r="I6" t="s">
@@ -1728,7 +1740,7 @@
         <v>47</v>
       </c>
     </row>
-    <row r="7">
+    <row r="7" spans="1:11" x14ac:dyDescent="0.25">
       <c r="A7" t="s">
         <v>73</v>
       </c>
@@ -1741,16 +1753,16 @@
       <c r="D7" t="s">
         <v>59</v>
       </c>
-      <c r="E7" t="n">
-        <v>0</v>
-      </c>
-      <c r="F7" s="1" t="n">
+      <c r="E7">
+        <v>0</v>
+      </c>
+      <c r="F7" s="1">
         <v>45608</v>
       </c>
-      <c r="G7" s="1" t="n">
+      <c r="G7" s="1">
         <v>45737</v>
       </c>
-      <c r="H7" t="n">
+      <c r="H7">
         <v>130</v>
       </c>
       <c r="I7" t="s">
@@ -1763,7 +1775,7 @@
         <v>68</v>
       </c>
     </row>
-    <row r="8">
+    <row r="8" spans="1:11" x14ac:dyDescent="0.25">
       <c r="A8" t="s">
         <v>73</v>
       </c>
@@ -1776,16 +1788,16 @@
       <c r="D8" t="s">
         <v>71</v>
       </c>
-      <c r="E8" t="n">
-        <v>0</v>
-      </c>
-      <c r="F8" s="1" t="n">
+      <c r="E8">
+        <v>0</v>
+      </c>
+      <c r="F8" s="1">
         <v>45609</v>
       </c>
-      <c r="G8" s="1" t="n">
+      <c r="G8" s="1">
         <v>45637</v>
       </c>
-      <c r="H8" t="n">
+      <c r="H8">
         <v>29</v>
       </c>
       <c r="I8" t="s">
@@ -1800,16 +1812,16 @@
     </row>
   </sheetData>
   <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
-  <pageSetup paperSize="9" orientation="portrait" horizontalDpi="300" verticalDpi="300" r:id="rId2"/>
+  <pageSetup paperSize="9" orientation="portrait" horizontalDpi="300" verticalDpi="300"/>
 </worksheet>
 </file>
 
 <file path=xl/worksheets/sheet4.xml><?xml version="1.0" encoding="utf-8"?>
-<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:xdr="http://schemas.openxmlformats.org/drawingml/2006/spreadsheetDrawing" xmlns:x14="http://schemas.microsoft.com/office/spreadsheetml/2009/9/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3">
-  <dimension ref="A1"/>
-  <sheetFormatPr defaultRowHeight="15.0" baseColWidth="10"/>
+<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{00000000-0001-0000-0300-000000000000}">
+  <dimension ref="A1:K9"/>
+  <sheetFormatPr defaultColWidth="11.42578125" defaultRowHeight="15" x14ac:dyDescent="0.25"/>
   <sheetData>
-    <row r="1">
+    <row r="1" spans="1:11" x14ac:dyDescent="0.25">
       <c r="A1" t="s">
         <v>0</v>
       </c>
@@ -1844,7 +1856,7 @@
         <v>10</v>
       </c>
     </row>
-    <row r="2">
+    <row r="2" spans="1:11" x14ac:dyDescent="0.25">
       <c r="A2" t="s">
         <v>92</v>
       </c>
@@ -1857,16 +1869,16 @@
       <c r="D2" t="s">
         <v>32</v>
       </c>
-      <c r="E2" t="n">
-        <v>0</v>
-      </c>
-      <c r="F2" s="1" t="n">
+      <c r="E2">
+        <v>0</v>
+      </c>
+      <c r="F2" s="1">
         <v>45628</v>
       </c>
-      <c r="G2" s="1" t="n">
+      <c r="G2" s="1">
         <v>45749</v>
       </c>
-      <c r="H2" t="n">
+      <c r="H2">
         <v>122</v>
       </c>
       <c r="I2" t="s">
@@ -1879,7 +1891,7 @@
         <v>72</v>
       </c>
     </row>
-    <row r="3">
+    <row r="3" spans="1:11" x14ac:dyDescent="0.25">
       <c r="A3" t="s">
         <v>92</v>
       </c>
@@ -1892,16 +1904,16 @@
       <c r="D3" t="s">
         <v>19</v>
       </c>
-      <c r="E3" t="n">
-        <v>0</v>
-      </c>
-      <c r="F3" s="1" t="n">
+      <c r="E3">
+        <v>0</v>
+      </c>
+      <c r="F3" s="1">
         <v>45628</v>
       </c>
-      <c r="G3" s="1" t="n">
+      <c r="G3" s="1">
         <v>45742</v>
       </c>
-      <c r="H3" t="n">
+      <c r="H3">
         <v>115</v>
       </c>
       <c r="I3" t="s">
@@ -1914,7 +1926,7 @@
         <v>64</v>
       </c>
     </row>
-    <row r="4">
+    <row r="4" spans="1:11" x14ac:dyDescent="0.25">
       <c r="A4" t="s">
         <v>92</v>
       </c>
@@ -1927,16 +1939,16 @@
       <c r="D4" t="s">
         <v>79</v>
       </c>
-      <c r="E4" t="n">
-        <v>0</v>
-      </c>
-      <c r="F4" s="1" t="n">
+      <c r="E4">
+        <v>0</v>
+      </c>
+      <c r="F4" s="1">
         <v>45629</v>
       </c>
-      <c r="G4" s="1" t="n">
+      <c r="G4" s="1">
         <v>45709</v>
       </c>
-      <c r="H4" t="n">
+      <c r="H4">
         <v>81</v>
       </c>
       <c r="I4" t="s">
@@ -1949,7 +1961,7 @@
         <v>56</v>
       </c>
     </row>
-    <row r="5">
+    <row r="5" spans="1:11" x14ac:dyDescent="0.25">
       <c r="A5" t="s">
         <v>92</v>
       </c>
@@ -1962,17 +1974,13 @@
       <c r="D5" t="s">
         <v>103</v>
       </c>
-      <c r="E5" t="n">
+      <c r="E5">
         <v>1</v>
       </c>
       <c r="F5" s="1"/>
       <c r="G5" s="1"/>
-      <c r="H5"/>
-      <c r="I5"/>
-      <c r="J5"/>
-      <c r="K5"/>
-    </row>
-    <row r="6">
+    </row>
+    <row r="6" spans="1:11" x14ac:dyDescent="0.25">
       <c r="A6" t="s">
         <v>92</v>
       </c>
@@ -1985,16 +1993,16 @@
       <c r="D6" t="s">
         <v>106</v>
       </c>
-      <c r="E6" t="n">
-        <v>0</v>
-      </c>
-      <c r="F6" s="1" t="n">
+      <c r="E6">
+        <v>0</v>
+      </c>
+      <c r="F6" s="1">
         <v>45635</v>
       </c>
-      <c r="G6" s="1" t="n">
+      <c r="G6" s="1">
         <v>45799</v>
       </c>
-      <c r="H6" t="n">
+      <c r="H6">
         <v>165</v>
       </c>
       <c r="I6" t="s">
@@ -2007,7 +2015,7 @@
         <v>61</v>
       </c>
     </row>
-    <row r="7">
+    <row r="7" spans="1:11" x14ac:dyDescent="0.25">
       <c r="A7" t="s">
         <v>92</v>
       </c>
@@ -2020,16 +2028,16 @@
       <c r="D7" t="s">
         <v>67</v>
       </c>
-      <c r="E7" t="n">
-        <v>0</v>
-      </c>
-      <c r="F7" s="1" t="n">
+      <c r="E7">
+        <v>0</v>
+      </c>
+      <c r="F7" s="1">
         <v>45635</v>
       </c>
-      <c r="G7" s="1" t="n">
+      <c r="G7" s="1">
         <v>45777</v>
       </c>
-      <c r="H7" t="n">
+      <c r="H7">
         <v>143</v>
       </c>
       <c r="I7" t="s">
@@ -2042,7 +2050,7 @@
         <v>47</v>
       </c>
     </row>
-    <row r="8">
+    <row r="8" spans="1:11" x14ac:dyDescent="0.25">
       <c r="A8" t="s">
         <v>92</v>
       </c>
@@ -2055,16 +2063,16 @@
       <c r="D8" t="s">
         <v>79</v>
       </c>
-      <c r="E8" t="n">
-        <v>0</v>
-      </c>
-      <c r="F8" s="1" t="n">
+      <c r="E8">
+        <v>0</v>
+      </c>
+      <c r="F8" s="1">
         <v>45636</v>
       </c>
-      <c r="G8" s="1" t="n">
+      <c r="G8" s="1">
         <v>45806</v>
       </c>
-      <c r="H8" t="n">
+      <c r="H8">
         <v>171</v>
       </c>
       <c r="I8" t="s">
@@ -2077,7 +2085,7 @@
         <v>38</v>
       </c>
     </row>
-    <row r="9">
+    <row r="9" spans="1:11" x14ac:dyDescent="0.25">
       <c r="A9" t="s">
         <v>92</v>
       </c>
@@ -2090,16 +2098,16 @@
       <c r="D9" t="s">
         <v>50</v>
       </c>
-      <c r="E9" t="n">
-        <v>0</v>
-      </c>
-      <c r="F9" s="1" t="n">
+      <c r="E9">
+        <v>0</v>
+      </c>
+      <c r="F9" s="1">
         <v>45637</v>
       </c>
-      <c r="G9" s="1" t="n">
+      <c r="G9" s="1">
         <v>45714</v>
       </c>
-      <c r="H9" t="n">
+      <c r="H9">
         <v>78</v>
       </c>
       <c r="I9" t="s">
@@ -2114,16 +2122,16 @@
     </row>
   </sheetData>
   <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
-  <pageSetup paperSize="9" orientation="portrait" horizontalDpi="300" verticalDpi="300" r:id="rId2"/>
+  <pageSetup paperSize="9" orientation="portrait" horizontalDpi="300" verticalDpi="300"/>
 </worksheet>
 </file>
 
 <file path=xl/worksheets/sheet5.xml><?xml version="1.0" encoding="utf-8"?>
-<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:xdr="http://schemas.openxmlformats.org/drawingml/2006/spreadsheetDrawing" xmlns:x14="http://schemas.microsoft.com/office/spreadsheetml/2009/9/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3">
-  <dimension ref="A1"/>
-  <sheetFormatPr defaultRowHeight="15.0" baseColWidth="10"/>
+<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{00000000-0001-0000-0400-000000000000}">
+  <dimension ref="A1:K11"/>
+  <sheetFormatPr defaultColWidth="11.42578125" defaultRowHeight="15" x14ac:dyDescent="0.25"/>
   <sheetData>
-    <row r="1">
+    <row r="1" spans="1:11" x14ac:dyDescent="0.25">
       <c r="A1" t="s">
         <v>0</v>
       </c>
@@ -2158,7 +2166,7 @@
         <v>10</v>
       </c>
     </row>
-    <row r="2">
+    <row r="2" spans="1:11" x14ac:dyDescent="0.25">
       <c r="A2" t="s">
         <v>114</v>
       </c>
@@ -2171,17 +2179,13 @@
       <c r="D2" t="s">
         <v>32</v>
       </c>
-      <c r="E2" t="n">
+      <c r="E2">
         <v>0</v>
       </c>
       <c r="F2" s="1"/>
       <c r="G2" s="1"/>
-      <c r="H2"/>
-      <c r="I2"/>
-      <c r="J2"/>
-      <c r="K2"/>
-    </row>
-    <row r="3">
+    </row>
+    <row r="3" spans="1:11" x14ac:dyDescent="0.25">
       <c r="A3" t="s">
         <v>114</v>
       </c>
@@ -2194,17 +2198,13 @@
       <c r="D3" t="s">
         <v>14</v>
       </c>
-      <c r="E3" t="n">
+      <c r="E3">
         <v>0</v>
       </c>
       <c r="F3" s="1"/>
       <c r="G3" s="1"/>
-      <c r="H3"/>
-      <c r="I3"/>
-      <c r="J3"/>
-      <c r="K3"/>
-    </row>
-    <row r="4">
+    </row>
+    <row r="4" spans="1:11" x14ac:dyDescent="0.25">
       <c r="A4" t="s">
         <v>114</v>
       </c>
@@ -2217,16 +2217,16 @@
       <c r="D4" t="s">
         <v>76</v>
       </c>
-      <c r="E4" t="n">
-        <v>0</v>
-      </c>
-      <c r="F4" s="1" t="n">
+      <c r="E4">
+        <v>0</v>
+      </c>
+      <c r="F4" s="1">
         <v>45671</v>
       </c>
-      <c r="G4" s="1" t="n">
+      <c r="G4" s="1">
         <v>45737</v>
       </c>
-      <c r="H4" t="n">
+      <c r="H4">
         <v>67</v>
       </c>
       <c r="I4" t="s">
@@ -2239,7 +2239,7 @@
         <v>51</v>
       </c>
     </row>
-    <row r="5">
+    <row r="5" spans="1:11" x14ac:dyDescent="0.25">
       <c r="A5" t="s">
         <v>114</v>
       </c>
@@ -2252,16 +2252,16 @@
       <c r="D5" t="s">
         <v>19</v>
       </c>
-      <c r="E5" t="n">
-        <v>0</v>
-      </c>
-      <c r="F5" s="1" t="n">
+      <c r="E5">
+        <v>0</v>
+      </c>
+      <c r="F5" s="1">
         <v>45671</v>
       </c>
-      <c r="G5" s="1" t="n">
+      <c r="G5" s="1">
         <v>45714</v>
       </c>
-      <c r="H5" t="n">
+      <c r="H5">
         <v>44</v>
       </c>
       <c r="I5" t="s">
@@ -2274,7 +2274,7 @@
         <v>72</v>
       </c>
     </row>
-    <row r="6">
+    <row r="6" spans="1:11" x14ac:dyDescent="0.25">
       <c r="A6" t="s">
         <v>114</v>
       </c>
@@ -2287,17 +2287,13 @@
       <c r="D6" t="s">
         <v>32</v>
       </c>
-      <c r="E6" t="n">
+      <c r="E6">
         <v>0</v>
       </c>
       <c r="F6" s="1"/>
       <c r="G6" s="1"/>
-      <c r="H6"/>
-      <c r="I6"/>
-      <c r="J6"/>
-      <c r="K6"/>
-    </row>
-    <row r="7">
+    </row>
+    <row r="7" spans="1:11" x14ac:dyDescent="0.25">
       <c r="A7" t="s">
         <v>114</v>
       </c>
@@ -2310,17 +2306,13 @@
       <c r="D7" t="s">
         <v>32</v>
       </c>
-      <c r="E7" t="n">
+      <c r="E7">
         <v>0</v>
       </c>
       <c r="F7" s="1"/>
       <c r="G7" s="1"/>
-      <c r="H7"/>
-      <c r="I7"/>
-      <c r="J7"/>
-      <c r="K7"/>
-    </row>
-    <row r="8">
+    </row>
+    <row r="8" spans="1:11" x14ac:dyDescent="0.25">
       <c r="A8" t="s">
         <v>114</v>
       </c>
@@ -2333,17 +2325,13 @@
       <c r="D8" t="s">
         <v>71</v>
       </c>
-      <c r="E8" t="n">
+      <c r="E8">
         <v>0</v>
       </c>
       <c r="F8" s="1"/>
       <c r="G8" s="1"/>
-      <c r="H8"/>
-      <c r="I8"/>
-      <c r="J8"/>
-      <c r="K8"/>
-    </row>
-    <row r="9">
+    </row>
+    <row r="9" spans="1:11" x14ac:dyDescent="0.25">
       <c r="A9" t="s">
         <v>114</v>
       </c>
@@ -2356,16 +2344,16 @@
       <c r="D9" t="s">
         <v>32</v>
       </c>
-      <c r="E9" t="n">
-        <v>0</v>
-      </c>
-      <c r="F9" s="1" t="n">
+      <c r="E9">
+        <v>0</v>
+      </c>
+      <c r="F9" s="1">
         <v>45679</v>
       </c>
-      <c r="G9" s="1" t="n">
+      <c r="G9" s="1">
         <v>45792</v>
       </c>
-      <c r="H9" t="n">
+      <c r="H9">
         <v>114</v>
       </c>
       <c r="I9" t="s">
@@ -2378,7 +2366,7 @@
         <v>44</v>
       </c>
     </row>
-    <row r="10">
+    <row r="10" spans="1:11" x14ac:dyDescent="0.25">
       <c r="A10" t="s">
         <v>114</v>
       </c>
@@ -2391,16 +2379,16 @@
       <c r="D10" t="s">
         <v>59</v>
       </c>
-      <c r="E10" t="n">
-        <v>0</v>
-      </c>
-      <c r="F10" s="1" t="n">
+      <c r="E10">
+        <v>0</v>
+      </c>
+      <c r="F10" s="1">
         <v>45679</v>
       </c>
-      <c r="G10" s="1" t="n">
+      <c r="G10" s="1">
         <v>45764</v>
       </c>
-      <c r="H10" t="n">
+      <c r="H10">
         <v>86</v>
       </c>
       <c r="I10" t="s">
@@ -2413,7 +2401,7 @@
         <v>56</v>
       </c>
     </row>
-    <row r="11">
+    <row r="11" spans="1:11" x14ac:dyDescent="0.25">
       <c r="A11" t="s">
         <v>114</v>
       </c>
@@ -2426,16 +2414,16 @@
       <c r="D11" t="s">
         <v>79</v>
       </c>
-      <c r="E11" t="n">
+      <c r="E11">
         <v>1</v>
       </c>
-      <c r="F11" s="1" t="n">
+      <c r="F11" s="1">
         <v>45667</v>
       </c>
-      <c r="G11" s="1" t="n">
+      <c r="G11" s="1">
         <v>45674</v>
       </c>
-      <c r="H11" t="n">
+      <c r="H11">
         <v>8</v>
       </c>
       <c r="I11" t="s">
@@ -2450,16 +2438,16 @@
     </row>
   </sheetData>
   <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
-  <pageSetup paperSize="9" orientation="portrait" horizontalDpi="300" verticalDpi="300" r:id="rId2"/>
+  <pageSetup paperSize="9" orientation="portrait" horizontalDpi="300" verticalDpi="300"/>
 </worksheet>
 </file>
 
 <file path=xl/worksheets/sheet6.xml><?xml version="1.0" encoding="utf-8"?>
-<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:xdr="http://schemas.openxmlformats.org/drawingml/2006/spreadsheetDrawing" xmlns:x14="http://schemas.microsoft.com/office/spreadsheetml/2009/9/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3">
-  <dimension ref="A1"/>
-  <sheetFormatPr defaultRowHeight="15.0" baseColWidth="10"/>
+<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{00000000-0001-0000-0500-000000000000}">
+  <dimension ref="A1:K9"/>
+  <sheetFormatPr defaultColWidth="11.42578125" defaultRowHeight="15" x14ac:dyDescent="0.25"/>
   <sheetData>
-    <row r="1">
+    <row r="1" spans="1:11" x14ac:dyDescent="0.25">
       <c r="A1" t="s">
         <v>0</v>
       </c>
@@ -2494,7 +2482,7 @@
         <v>10</v>
       </c>
     </row>
-    <row r="2">
+    <row r="2" spans="1:11" x14ac:dyDescent="0.25">
       <c r="A2" t="s">
         <v>135</v>
       </c>
@@ -2507,17 +2495,13 @@
       <c r="D2" t="s">
         <v>32</v>
       </c>
-      <c r="E2" t="n">
+      <c r="E2">
         <v>0</v>
       </c>
       <c r="F2" s="1"/>
       <c r="G2" s="1"/>
-      <c r="H2"/>
-      <c r="I2"/>
-      <c r="J2"/>
-      <c r="K2"/>
-    </row>
-    <row r="3">
+    </row>
+    <row r="3" spans="1:11" x14ac:dyDescent="0.25">
       <c r="A3" t="s">
         <v>135</v>
       </c>
@@ -2530,17 +2514,13 @@
       <c r="D3" t="s">
         <v>103</v>
       </c>
-      <c r="E3" t="n">
+      <c r="E3">
         <v>0</v>
       </c>
       <c r="F3" s="1"/>
       <c r="G3" s="1"/>
-      <c r="H3"/>
-      <c r="I3"/>
-      <c r="J3"/>
-      <c r="K3"/>
-    </row>
-    <row r="4">
+    </row>
+    <row r="4" spans="1:11" x14ac:dyDescent="0.25">
       <c r="A4" t="s">
         <v>135</v>
       </c>
@@ -2553,17 +2533,13 @@
       <c r="D4" t="s">
         <v>103</v>
       </c>
-      <c r="E4" t="n">
+      <c r="E4">
         <v>0</v>
       </c>
       <c r="F4" s="1"/>
       <c r="G4" s="1"/>
-      <c r="H4"/>
-      <c r="I4"/>
-      <c r="J4"/>
-      <c r="K4"/>
-    </row>
-    <row r="5">
+    </row>
+    <row r="5" spans="1:11" x14ac:dyDescent="0.25">
       <c r="A5" t="s">
         <v>135</v>
       </c>
@@ -2576,17 +2552,29 @@
       <c r="D5" t="s">
         <v>103</v>
       </c>
-      <c r="E5" t="n">
-        <v>0</v>
-      </c>
-      <c r="F5" s="1"/>
-      <c r="G5" s="1"/>
-      <c r="H5"/>
-      <c r="I5"/>
-      <c r="J5"/>
-      <c r="K5"/>
-    </row>
-    <row r="6">
+      <c r="E5">
+        <v>0</v>
+      </c>
+      <c r="F5" s="1">
+        <v>45714</v>
+      </c>
+      <c r="G5" s="1">
+        <v>45813</v>
+      </c>
+      <c r="H5">
+        <v>100</v>
+      </c>
+      <c r="I5" t="s">
+        <v>15</v>
+      </c>
+      <c r="J5" t="s">
+        <v>43</v>
+      </c>
+      <c r="K5" t="s">
+        <v>64</v>
+      </c>
+    </row>
+    <row r="6" spans="1:11" x14ac:dyDescent="0.25">
       <c r="A6" t="s">
         <v>135</v>
       </c>
@@ -2599,17 +2587,29 @@
       <c r="D6" t="s">
         <v>71</v>
       </c>
-      <c r="E6" t="n">
-        <v>0</v>
-      </c>
-      <c r="F6" s="1"/>
-      <c r="G6" s="1"/>
-      <c r="H6"/>
-      <c r="I6"/>
-      <c r="J6"/>
-      <c r="K6"/>
-    </row>
-    <row r="7">
+      <c r="E6">
+        <v>0</v>
+      </c>
+      <c r="F6" s="1">
+        <v>45719</v>
+      </c>
+      <c r="G6" s="1">
+        <v>45813</v>
+      </c>
+      <c r="H6">
+        <v>95</v>
+      </c>
+      <c r="I6" t="s">
+        <v>37</v>
+      </c>
+      <c r="J6" t="s">
+        <v>43</v>
+      </c>
+      <c r="K6" t="s">
+        <v>72</v>
+      </c>
+    </row>
+    <row r="7" spans="1:11" x14ac:dyDescent="0.25">
       <c r="A7" t="s">
         <v>135</v>
       </c>
@@ -2622,17 +2622,29 @@
       <c r="D7" t="s">
         <v>59</v>
       </c>
-      <c r="E7" t="n">
-        <v>0</v>
-      </c>
-      <c r="F7" s="1"/>
-      <c r="G7" s="1"/>
-      <c r="H7"/>
-      <c r="I7"/>
-      <c r="J7"/>
-      <c r="K7"/>
-    </row>
-    <row r="8">
+      <c r="E7">
+        <v>0</v>
+      </c>
+      <c r="F7" s="1">
+        <v>45719</v>
+      </c>
+      <c r="G7" s="1">
+        <v>45813</v>
+      </c>
+      <c r="H7">
+        <v>95</v>
+      </c>
+      <c r="I7" t="s">
+        <v>37</v>
+      </c>
+      <c r="J7" t="s">
+        <v>43</v>
+      </c>
+      <c r="K7" t="s">
+        <v>68</v>
+      </c>
+    </row>
+    <row r="8" spans="1:11" x14ac:dyDescent="0.25">
       <c r="A8" t="s">
         <v>135</v>
       </c>
@@ -2645,17 +2657,29 @@
       <c r="D8" t="s">
         <v>150</v>
       </c>
-      <c r="E8" t="n">
-        <v>0</v>
-      </c>
-      <c r="F8" s="1"/>
-      <c r="G8" s="1"/>
-      <c r="H8"/>
-      <c r="I8"/>
-      <c r="J8"/>
-      <c r="K8"/>
-    </row>
-    <row r="9">
+      <c r="E8">
+        <v>0</v>
+      </c>
+      <c r="F8" s="1">
+        <v>45720</v>
+      </c>
+      <c r="G8" s="1">
+        <v>45813</v>
+      </c>
+      <c r="H8">
+        <v>94</v>
+      </c>
+      <c r="I8" t="s">
+        <v>37</v>
+      </c>
+      <c r="J8" t="s">
+        <v>43</v>
+      </c>
+      <c r="K8" t="s">
+        <v>44</v>
+      </c>
+    </row>
+    <row r="9" spans="1:11" x14ac:dyDescent="0.25">
       <c r="A9" t="s">
         <v>135</v>
       </c>
@@ -2668,28 +2692,24 @@
       <c r="D9" t="s">
         <v>32</v>
       </c>
-      <c r="E9" t="n">
+      <c r="E9">
         <v>0</v>
       </c>
       <c r="F9" s="1"/>
       <c r="G9" s="1"/>
-      <c r="H9"/>
-      <c r="I9"/>
-      <c r="J9"/>
-      <c r="K9"/>
     </row>
   </sheetData>
   <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
-  <pageSetup paperSize="9" orientation="portrait" horizontalDpi="300" verticalDpi="300" r:id="rId2"/>
+  <pageSetup paperSize="9" orientation="portrait" horizontalDpi="300" verticalDpi="300"/>
 </worksheet>
 </file>
 
 <file path=xl/worksheets/sheet7.xml><?xml version="1.0" encoding="utf-8"?>
-<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:xdr="http://schemas.openxmlformats.org/drawingml/2006/spreadsheetDrawing" xmlns:x14="http://schemas.microsoft.com/office/spreadsheetml/2009/9/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3">
-  <dimension ref="A1"/>
-  <sheetFormatPr defaultRowHeight="15.0" baseColWidth="10"/>
+<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{00000000-0001-0000-0600-000000000000}">
+  <dimension ref="A1:K10"/>
+  <sheetFormatPr defaultColWidth="11.42578125" defaultRowHeight="15" x14ac:dyDescent="0.25"/>
   <sheetData>
-    <row r="1">
+    <row r="1" spans="1:11" x14ac:dyDescent="0.25">
       <c r="A1" t="s">
         <v>0</v>
       </c>
@@ -2724,7 +2744,7 @@
         <v>10</v>
       </c>
     </row>
-    <row r="2">
+    <row r="2" spans="1:11" x14ac:dyDescent="0.25">
       <c r="A2" t="s">
         <v>153</v>
       </c>
@@ -2737,17 +2757,13 @@
       <c r="D2" t="s">
         <v>156</v>
       </c>
-      <c r="E2" t="n">
+      <c r="E2">
         <v>0</v>
       </c>
       <c r="F2" s="1"/>
       <c r="G2" s="1"/>
-      <c r="H2"/>
-      <c r="I2"/>
-      <c r="J2"/>
-      <c r="K2"/>
-    </row>
-    <row r="3">
+    </row>
+    <row r="3" spans="1:11" x14ac:dyDescent="0.25">
       <c r="A3" t="s">
         <v>153</v>
       </c>
@@ -2760,17 +2776,13 @@
       <c r="D3" t="s">
         <v>50</v>
       </c>
-      <c r="E3" t="n">
+      <c r="E3">
         <v>0</v>
       </c>
       <c r="F3" s="1"/>
       <c r="G3" s="1"/>
-      <c r="H3"/>
-      <c r="I3"/>
-      <c r="J3"/>
-      <c r="K3"/>
-    </row>
-    <row r="4">
+    </row>
+    <row r="4" spans="1:11" x14ac:dyDescent="0.25">
       <c r="A4" t="s">
         <v>153</v>
       </c>
@@ -2783,17 +2795,13 @@
       <c r="D4" t="s">
         <v>32</v>
       </c>
-      <c r="E4" t="n">
+      <c r="E4">
         <v>0</v>
       </c>
       <c r="F4" s="1"/>
       <c r="G4" s="1"/>
-      <c r="H4"/>
-      <c r="I4"/>
-      <c r="J4"/>
-      <c r="K4"/>
-    </row>
-    <row r="5">
+    </row>
+    <row r="5" spans="1:11" x14ac:dyDescent="0.25">
       <c r="A5" t="s">
         <v>153</v>
       </c>
@@ -2806,17 +2814,13 @@
       <c r="D5" t="s">
         <v>19</v>
       </c>
-      <c r="E5" t="n">
+      <c r="E5">
         <v>0</v>
       </c>
       <c r="F5" s="1"/>
       <c r="G5" s="1"/>
-      <c r="H5"/>
-      <c r="I5"/>
-      <c r="J5"/>
-      <c r="K5"/>
-    </row>
-    <row r="6">
+    </row>
+    <row r="6" spans="1:11" x14ac:dyDescent="0.25">
       <c r="A6" t="s">
         <v>153</v>
       </c>
@@ -2829,17 +2833,13 @@
       <c r="D6" t="s">
         <v>32</v>
       </c>
-      <c r="E6" t="n">
+      <c r="E6">
         <v>0</v>
       </c>
       <c r="F6" s="1"/>
       <c r="G6" s="1"/>
-      <c r="H6"/>
-      <c r="I6"/>
-      <c r="J6"/>
-      <c r="K6"/>
-    </row>
-    <row r="7">
+    </row>
+    <row r="7" spans="1:11" x14ac:dyDescent="0.25">
       <c r="A7" t="s">
         <v>153</v>
       </c>
@@ -2852,17 +2852,29 @@
       <c r="D7" t="s">
         <v>167</v>
       </c>
-      <c r="E7" t="n">
-        <v>0</v>
-      </c>
-      <c r="F7" s="1"/>
-      <c r="G7" s="1"/>
-      <c r="H7"/>
-      <c r="I7"/>
-      <c r="J7"/>
-      <c r="K7"/>
-    </row>
-    <row r="8">
+      <c r="E7">
+        <v>0</v>
+      </c>
+      <c r="F7" s="1">
+        <v>45747</v>
+      </c>
+      <c r="G7" s="1">
+        <v>45813</v>
+      </c>
+      <c r="H7">
+        <v>67</v>
+      </c>
+      <c r="I7" t="s">
+        <v>37</v>
+      </c>
+      <c r="J7" t="s">
+        <v>43</v>
+      </c>
+      <c r="K7" t="s">
+        <v>56</v>
+      </c>
+    </row>
+    <row r="8" spans="1:11" x14ac:dyDescent="0.25">
       <c r="A8" t="s">
         <v>153</v>
       </c>
@@ -2875,17 +2887,13 @@
       <c r="D8" t="s">
         <v>32</v>
       </c>
-      <c r="E8" t="n">
+      <c r="E8">
         <v>0</v>
       </c>
       <c r="F8" s="1"/>
       <c r="G8" s="1"/>
-      <c r="H8"/>
-      <c r="I8"/>
-      <c r="J8"/>
-      <c r="K8"/>
-    </row>
-    <row r="9">
+    </row>
+    <row r="9" spans="1:11" x14ac:dyDescent="0.25">
       <c r="A9" t="s">
         <v>153</v>
       </c>
@@ -2898,17 +2906,13 @@
       <c r="D9" t="s">
         <v>59</v>
       </c>
-      <c r="E9" t="n">
+      <c r="E9">
         <v>0</v>
       </c>
       <c r="F9" s="1"/>
       <c r="G9" s="1"/>
-      <c r="H9"/>
-      <c r="I9"/>
-      <c r="J9"/>
-      <c r="K9"/>
-    </row>
-    <row r="10">
+    </row>
+    <row r="10" spans="1:11" x14ac:dyDescent="0.25">
       <c r="A10" t="s">
         <v>153</v>
       </c>
@@ -2921,28 +2925,24 @@
       <c r="D10" t="s">
         <v>50</v>
       </c>
-      <c r="E10" t="n">
+      <c r="E10">
         <v>0</v>
       </c>
       <c r="F10" s="1"/>
       <c r="G10" s="1"/>
-      <c r="H10"/>
-      <c r="I10"/>
-      <c r="J10"/>
-      <c r="K10"/>
     </row>
   </sheetData>
   <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
-  <pageSetup paperSize="9" orientation="portrait" horizontalDpi="300" verticalDpi="300" r:id="rId2"/>
+  <pageSetup paperSize="9" orientation="portrait" horizontalDpi="300" verticalDpi="300"/>
 </worksheet>
 </file>
 
 <file path=xl/worksheets/sheet8.xml><?xml version="1.0" encoding="utf-8"?>
-<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:xdr="http://schemas.openxmlformats.org/drawingml/2006/spreadsheetDrawing" xmlns:x14="http://schemas.microsoft.com/office/spreadsheetml/2009/9/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3">
-  <dimension ref="A1"/>
-  <sheetFormatPr defaultRowHeight="15.0" baseColWidth="10"/>
+<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{00000000-0001-0000-0700-000000000000}">
+  <dimension ref="A1:K11"/>
+  <sheetFormatPr defaultColWidth="11.42578125" defaultRowHeight="15" x14ac:dyDescent="0.25"/>
   <sheetData>
-    <row r="1">
+    <row r="1" spans="1:11" x14ac:dyDescent="0.25">
       <c r="A1" t="s">
         <v>0</v>
       </c>
@@ -2977,7 +2977,7 @@
         <v>10</v>
       </c>
     </row>
-    <row r="2">
+    <row r="2" spans="1:11" x14ac:dyDescent="0.25">
       <c r="A2" t="s">
         <v>174</v>
       </c>
@@ -2990,17 +2990,13 @@
       <c r="D2" t="s">
         <v>32</v>
       </c>
-      <c r="E2" t="n">
+      <c r="E2">
         <v>0</v>
       </c>
       <c r="F2" s="1"/>
       <c r="G2" s="1"/>
-      <c r="H2"/>
-      <c r="I2"/>
-      <c r="J2"/>
-      <c r="K2"/>
-    </row>
-    <row r="3">
+    </row>
+    <row r="3" spans="1:11" x14ac:dyDescent="0.25">
       <c r="A3" t="s">
         <v>174</v>
       </c>
@@ -3013,17 +3009,13 @@
       <c r="D3" t="s">
         <v>50</v>
       </c>
-      <c r="E3" t="n">
+      <c r="E3">
         <v>0</v>
       </c>
       <c r="F3" s="1"/>
       <c r="G3" s="1"/>
-      <c r="H3"/>
-      <c r="I3"/>
-      <c r="J3"/>
-      <c r="K3"/>
-    </row>
-    <row r="4">
+    </row>
+    <row r="4" spans="1:11" x14ac:dyDescent="0.25">
       <c r="A4" t="s">
         <v>174</v>
       </c>
@@ -3036,17 +3028,13 @@
       <c r="D4" t="s">
         <v>50</v>
       </c>
-      <c r="E4" t="n">
+      <c r="E4">
         <v>0</v>
       </c>
       <c r="F4" s="1"/>
       <c r="G4" s="1"/>
-      <c r="H4"/>
-      <c r="I4"/>
-      <c r="J4"/>
-      <c r="K4"/>
-    </row>
-    <row r="5">
+    </row>
+    <row r="5" spans="1:11" x14ac:dyDescent="0.25">
       <c r="A5" t="s">
         <v>174</v>
       </c>
@@ -3059,17 +3047,13 @@
       <c r="D5" t="s">
         <v>106</v>
       </c>
-      <c r="E5" t="n">
+      <c r="E5">
         <v>0</v>
       </c>
       <c r="F5" s="1"/>
       <c r="G5" s="1"/>
-      <c r="H5"/>
-      <c r="I5"/>
-      <c r="J5"/>
-      <c r="K5"/>
-    </row>
-    <row r="6">
+    </row>
+    <row r="6" spans="1:11" x14ac:dyDescent="0.25">
       <c r="A6" t="s">
         <v>174</v>
       </c>
@@ -3082,17 +3066,13 @@
       <c r="D6" t="s">
         <v>79</v>
       </c>
-      <c r="E6" t="n">
+      <c r="E6">
         <v>0</v>
       </c>
       <c r="F6" s="1"/>
       <c r="G6" s="1"/>
-      <c r="H6"/>
-      <c r="I6"/>
-      <c r="J6"/>
-      <c r="K6"/>
-    </row>
-    <row r="7">
+    </row>
+    <row r="7" spans="1:11" x14ac:dyDescent="0.25">
       <c r="A7" t="s">
         <v>174</v>
       </c>
@@ -3105,17 +3085,13 @@
       <c r="D7" t="s">
         <v>41</v>
       </c>
-      <c r="E7" t="n">
+      <c r="E7">
         <v>0</v>
       </c>
       <c r="F7" s="1"/>
       <c r="G7" s="1"/>
-      <c r="H7"/>
-      <c r="I7"/>
-      <c r="J7"/>
-      <c r="K7"/>
-    </row>
-    <row r="8">
+    </row>
+    <row r="8" spans="1:11" x14ac:dyDescent="0.25">
       <c r="A8" t="s">
         <v>174</v>
       </c>
@@ -3128,17 +3104,13 @@
       <c r="D8" t="s">
         <v>67</v>
       </c>
-      <c r="E8" t="n">
+      <c r="E8">
         <v>0</v>
       </c>
       <c r="F8" s="1"/>
       <c r="G8" s="1"/>
-      <c r="H8"/>
-      <c r="I8"/>
-      <c r="J8"/>
-      <c r="K8"/>
-    </row>
-    <row r="9">
+    </row>
+    <row r="9" spans="1:11" x14ac:dyDescent="0.25">
       <c r="A9" t="s">
         <v>174</v>
       </c>
@@ -3151,17 +3123,13 @@
       <c r="D9" t="s">
         <v>14</v>
       </c>
-      <c r="E9" t="n">
+      <c r="E9">
         <v>0</v>
       </c>
       <c r="F9" s="1"/>
       <c r="G9" s="1"/>
-      <c r="H9"/>
-      <c r="I9"/>
-      <c r="J9"/>
-      <c r="K9"/>
-    </row>
-    <row r="10">
+    </row>
+    <row r="10" spans="1:11" x14ac:dyDescent="0.25">
       <c r="A10" t="s">
         <v>174</v>
       </c>
@@ -3174,17 +3142,29 @@
       <c r="D10" t="s">
         <v>71</v>
       </c>
-      <c r="E10" t="n">
-        <v>0</v>
-      </c>
-      <c r="F10" s="1"/>
-      <c r="G10" s="1"/>
-      <c r="H10"/>
-      <c r="I10"/>
-      <c r="J10"/>
-      <c r="K10"/>
-    </row>
-    <row r="11">
+      <c r="E10">
+        <v>0</v>
+      </c>
+      <c r="F10" s="1">
+        <v>45776</v>
+      </c>
+      <c r="G10" s="1">
+        <v>45813</v>
+      </c>
+      <c r="H10">
+        <v>38</v>
+      </c>
+      <c r="I10" t="s">
+        <v>84</v>
+      </c>
+      <c r="J10" t="s">
+        <v>43</v>
+      </c>
+      <c r="K10" t="s">
+        <v>16</v>
+      </c>
+    </row>
+    <row r="11" spans="1:11" x14ac:dyDescent="0.25">
       <c r="A11" t="s">
         <v>174</v>
       </c>
@@ -3197,16 +3177,16 @@
       <c r="D11" t="s">
         <v>195</v>
       </c>
-      <c r="E11" t="n">
+      <c r="E11">
         <v>1</v>
       </c>
-      <c r="F11" s="1" t="n">
+      <c r="F11" s="1">
         <v>45777</v>
       </c>
-      <c r="G11" s="1" t="n">
+      <c r="G11" s="1">
         <v>45799</v>
       </c>
-      <c r="H11" t="n">
+      <c r="H11">
         <v>23</v>
       </c>
       <c r="I11" t="s">
@@ -3221,16 +3201,16 @@
     </row>
   </sheetData>
   <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
-  <pageSetup paperSize="9" orientation="portrait" horizontalDpi="300" verticalDpi="300" r:id="rId2"/>
+  <pageSetup paperSize="9" orientation="portrait" horizontalDpi="300" verticalDpi="300"/>
 </worksheet>
 </file>
 
 <file path=xl/worksheets/sheet9.xml><?xml version="1.0" encoding="utf-8"?>
-<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:xdr="http://schemas.openxmlformats.org/drawingml/2006/spreadsheetDrawing" xmlns:x14="http://schemas.microsoft.com/office/spreadsheetml/2009/9/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3">
-  <dimension ref="A1"/>
-  <sheetFormatPr defaultRowHeight="15.0" baseColWidth="10"/>
+<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{00000000-0001-0000-0800-000000000000}">
+  <dimension ref="A1:K2"/>
+  <sheetFormatPr defaultColWidth="11.42578125" defaultRowHeight="15" x14ac:dyDescent="0.25"/>
   <sheetData>
-    <row r="1">
+    <row r="1" spans="1:11" x14ac:dyDescent="0.25">
       <c r="A1" t="s">
         <v>0</v>
       </c>
@@ -3265,7 +3245,7 @@
         <v>10</v>
       </c>
     </row>
-    <row r="2">
+    <row r="2" spans="1:11" x14ac:dyDescent="0.25">
       <c r="A2" t="s">
         <v>197</v>
       </c>
@@ -3278,18 +3258,14 @@
       <c r="D2" t="s">
         <v>50</v>
       </c>
-      <c r="E2" t="n">
+      <c r="E2">
         <v>1</v>
       </c>
       <c r="F2" s="1"/>
       <c r="G2" s="1"/>
-      <c r="H2"/>
-      <c r="I2"/>
-      <c r="J2"/>
-      <c r="K2"/>
     </row>
   </sheetData>
   <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
-  <pageSetup paperSize="9" orientation="portrait" horizontalDpi="300" verticalDpi="300" r:id="rId2"/>
+  <pageSetup paperSize="9" orientation="portrait" horizontalDpi="300" verticalDpi="300"/>
 </worksheet>
 </file>
--- a/Stat Reviews/OT24_StatReview/scotusblog_replication/data/term_index.xlsx
+++ b/Stat Reviews/OT24_StatReview/scotusblog_replication/data/term_index.xlsx
@@ -1,633 +1,625 @@
 
 <file path=xl/workbook.xml><?xml version="1.0" encoding="utf-8"?>
 <workbook xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x15="http://schemas.microsoft.com/office/spreadsheetml/2010/11/main" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr6="http://schemas.microsoft.com/office/spreadsheetml/2016/revision6" xmlns:xr10="http://schemas.microsoft.com/office/spreadsheetml/2016/revision10" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" mc:Ignorable="x15 xr xr6 xr10 xr2">
-  <fileVersion appName="xl" lastEdited="7" lowestEdited="7" rupBuild="28827"/>
-  <workbookPr/>
-  <mc:AlternateContent xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006">
-    <mc:Choice Requires="x15">
-      <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\Users\jaketruscott\Github\scotuswatch\Stat Reviews\OT24_StatReview\scotusblog_replication\data\"/>
-    </mc:Choice>
-  </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{7BFFBEBD-B4A6-4A60-8728-154472C9C7FF}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <workbookPr date1904="false"/>
   <bookViews>
-    <workbookView xWindow="28680" yWindow="-120" windowWidth="29040" windowHeight="15720" activeTab="7" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
+    <workbookView xWindow="0" yWindow="0" windowWidth="13125" windowHeight="6105" firstSheet="0" activeTab="0"/>
   </bookViews>
   <sheets>
-    <sheet name="No_Argument" sheetId="1" r:id="rId1"/>
-    <sheet name="October" sheetId="2" r:id="rId2"/>
-    <sheet name="November" sheetId="3" r:id="rId3"/>
-    <sheet name="December" sheetId="4" r:id="rId4"/>
-    <sheet name="January" sheetId="5" r:id="rId5"/>
-    <sheet name="February" sheetId="6" r:id="rId6"/>
-    <sheet name="March" sheetId="7" r:id="rId7"/>
-    <sheet name="April" sheetId="8" r:id="rId8"/>
-    <sheet name="May" sheetId="9" r:id="rId9"/>
+    <sheet name="No_Argument" sheetId="1" state="visible" r:id="rId1"/>
+    <sheet name="October" sheetId="2" state="visible" r:id="rId2"/>
+    <sheet name="November" sheetId="3" state="visible" r:id="rId3"/>
+    <sheet name="December" sheetId="4" state="visible" r:id="rId4"/>
+    <sheet name="January" sheetId="5" state="visible" r:id="rId5"/>
+    <sheet name="February" sheetId="6" state="visible" r:id="rId6"/>
+    <sheet name="March" sheetId="7" state="visible" r:id="rId7"/>
+    <sheet name="April" sheetId="8" state="visible" r:id="rId8"/>
+    <sheet name="May" sheetId="9" state="visible" r:id="rId9"/>
   </sheets>
-  <calcPr calcId="0"/>
 </workbook>
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="487" uniqueCount="200">
-  <si>
-    <t>sitting</t>
-  </si>
-  <si>
-    <t>docket</t>
-  </si>
-  <si>
-    <t>short_hand</t>
-  </si>
-  <si>
-    <t>lower_court</t>
-  </si>
-  <si>
-    <t>major_case</t>
-  </si>
-  <si>
-    <t>date_argued</t>
-  </si>
-  <si>
-    <t>date_decided</t>
-  </si>
-  <si>
-    <t>days_elapsed</t>
-  </si>
-  <si>
-    <t>decision</t>
-  </si>
-  <si>
-    <t>coalition</t>
-  </si>
-  <si>
-    <t>author</t>
-  </si>
-  <si>
-    <t>No Argument</t>
-  </si>
-  <si>
-    <t>23-167</t>
-  </si>
-  <si>
-    <t>Hamm</t>
-  </si>
-  <si>
-    <t>CA11</t>
-  </si>
-  <si>
-    <t>Vacate and Remand</t>
-  </si>
-  <si>
-    <t>Per Curiam</t>
-  </si>
-  <si>
-    <t>23-6573</t>
-  </si>
-  <si>
-    <t>Andrew</t>
-  </si>
-  <si>
-    <t>CA10</t>
-  </si>
-  <si>
-    <t>(7-2)</t>
-  </si>
-  <si>
-    <t>24A910</t>
-  </si>
-  <si>
-    <t>DOE v. CA</t>
-  </si>
-  <si>
-    <t>DCMA</t>
-  </si>
-  <si>
-    <t>Granted</t>
-  </si>
-  <si>
-    <t>(5-4)</t>
-  </si>
-  <si>
-    <t>24A931</t>
-  </si>
-  <si>
-    <t>Trump v. J.G.G.</t>
-  </si>
-  <si>
-    <t>DCDC</t>
-  </si>
-  <si>
-    <t>(5-4)*</t>
-  </si>
-  <si>
-    <t>24A1007</t>
-  </si>
-  <si>
-    <t>A.A.R.P v. Trump</t>
-  </si>
-  <si>
-    <t>CA5</t>
-  </si>
-  <si>
-    <t>October</t>
-  </si>
-  <si>
-    <t>23-191</t>
-  </si>
-  <si>
-    <t>Willaims</t>
-  </si>
-  <si>
-    <t>SCAL</t>
-  </si>
-  <si>
-    <t>Reverse and Remand</t>
-  </si>
-  <si>
-    <t>Kavanaugh</t>
-  </si>
-  <si>
-    <t>23-677</t>
-  </si>
-  <si>
-    <t>Royal Canin</t>
-  </si>
-  <si>
-    <t>CA8</t>
-  </si>
-  <si>
-    <t>Affirm</t>
-  </si>
-  <si>
-    <t>(9-0)</t>
-  </si>
-  <si>
-    <t>Kagan</t>
-  </si>
-  <si>
-    <t>23-852</t>
-  </si>
-  <si>
-    <t>Vanderstok</t>
-  </si>
-  <si>
-    <t>Gorsuch</t>
-  </si>
-  <si>
-    <t>23-621</t>
-  </si>
-  <si>
-    <t>Lackey</t>
-  </si>
-  <si>
-    <t>CA4</t>
-  </si>
-  <si>
-    <t>Roberts</t>
-  </si>
-  <si>
-    <t>22-7466</t>
-  </si>
-  <si>
-    <t>Glossip</t>
-  </si>
-  <si>
-    <t>CCAOK</t>
-  </si>
-  <si>
-    <t>(6-2)</t>
-  </si>
-  <si>
-    <t>Sotomayor</t>
-  </si>
-  <si>
-    <t>23-365</t>
-  </si>
-  <si>
-    <t>Medical Marijuana</t>
-  </si>
-  <si>
-    <t>CA2</t>
-  </si>
-  <si>
-    <t>Affirm and Remand</t>
-  </si>
-  <si>
-    <t>Barrett</t>
-  </si>
-  <si>
-    <t>23-583</t>
-  </si>
-  <si>
-    <t>Bouarafa</t>
-  </si>
-  <si>
-    <t>Jackson</t>
-  </si>
-  <si>
-    <t>23-713</t>
-  </si>
-  <si>
-    <t>Bufkin</t>
-  </si>
-  <si>
-    <t>CAFED</t>
-  </si>
-  <si>
-    <t>Thomas</t>
-  </si>
-  <si>
-    <t>23-753</t>
-  </si>
-  <si>
-    <t>SF v. EPA</t>
-  </si>
-  <si>
-    <t>CA9</t>
-  </si>
-  <si>
-    <t>Alito</t>
-  </si>
-  <si>
-    <t>November</t>
-  </si>
-  <si>
-    <t>23-1127</t>
-  </si>
-  <si>
-    <t>Wisconsin Bell</t>
-  </si>
-  <si>
-    <t>CA7</t>
-  </si>
-  <si>
-    <t>23-715</t>
-  </si>
-  <si>
-    <t>Advocate Christ Medical</t>
-  </si>
-  <si>
-    <t>CADC</t>
-  </si>
-  <si>
-    <t>23-217</t>
-  </si>
-  <si>
-    <t>E.M.D. Sales</t>
-  </si>
-  <si>
-    <t>23-980</t>
-  </si>
-  <si>
-    <t>Facebook</t>
-  </si>
-  <si>
-    <t>DIG</t>
-  </si>
-  <si>
-    <t>23-929</t>
-  </si>
-  <si>
-    <t>Velazquez</t>
-  </si>
-  <si>
-    <t>(6-3)</t>
-  </si>
-  <si>
-    <t>23-825</t>
-  </si>
-  <si>
-    <t>Delligatti</t>
-  </si>
-  <si>
-    <t>23-970</t>
-  </si>
-  <si>
-    <t>NVIDIA</t>
-  </si>
-  <si>
-    <t>December</t>
-  </si>
-  <si>
-    <t>23-1038</t>
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="200" uniqueCount="200">
+  <si>
+    <t xml:space="preserve">sitting</t>
+  </si>
+  <si>
+    <t xml:space="preserve">docket</t>
+  </si>
+  <si>
+    <t xml:space="preserve">short_hand</t>
+  </si>
+  <si>
+    <t xml:space="preserve">lower_court</t>
+  </si>
+  <si>
+    <t xml:space="preserve">major_case</t>
+  </si>
+  <si>
+    <t xml:space="preserve">date_argued</t>
+  </si>
+  <si>
+    <t xml:space="preserve">date_decided</t>
+  </si>
+  <si>
+    <t xml:space="preserve">days_elapsed</t>
+  </si>
+  <si>
+    <t xml:space="preserve">decision</t>
+  </si>
+  <si>
+    <t xml:space="preserve">coalition</t>
+  </si>
+  <si>
+    <t xml:space="preserve">author</t>
+  </si>
+  <si>
+    <t xml:space="preserve">No Argument</t>
+  </si>
+  <si>
+    <t xml:space="preserve">23-167</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Hamm</t>
+  </si>
+  <si>
+    <t xml:space="preserve">CA11</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Vacate and Remand</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Per Curiam</t>
+  </si>
+  <si>
+    <t xml:space="preserve">23-6573</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Andrew</t>
+  </si>
+  <si>
+    <t xml:space="preserve">CA10</t>
+  </si>
+  <si>
+    <t xml:space="preserve">(7-2)</t>
+  </si>
+  <si>
+    <t xml:space="preserve">24A910</t>
+  </si>
+  <si>
+    <t xml:space="preserve">DOE v. CA</t>
+  </si>
+  <si>
+    <t xml:space="preserve">DCMA</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Granted</t>
+  </si>
+  <si>
+    <t xml:space="preserve">(5-4)</t>
+  </si>
+  <si>
+    <t xml:space="preserve">24A931</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Trump v. J.G.G.</t>
+  </si>
+  <si>
+    <t xml:space="preserve">DCDC</t>
+  </si>
+  <si>
+    <t xml:space="preserve">(5-4)*</t>
+  </si>
+  <si>
+    <t xml:space="preserve">24A1007</t>
+  </si>
+  <si>
+    <t xml:space="preserve">A.A.R.P v. Trump</t>
+  </si>
+  <si>
+    <t xml:space="preserve">CA5</t>
+  </si>
+  <si>
+    <t xml:space="preserve">October</t>
+  </si>
+  <si>
+    <t xml:space="preserve">23-191</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Willaims</t>
+  </si>
+  <si>
+    <t xml:space="preserve">SCAL</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Reverse and Remand</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Kavanaugh</t>
+  </si>
+  <si>
+    <t xml:space="preserve">23-677</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Royal Canin</t>
+  </si>
+  <si>
+    <t xml:space="preserve">CA8</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Affirm</t>
+  </si>
+  <si>
+    <t xml:space="preserve">(9-0)</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Kagan</t>
+  </si>
+  <si>
+    <t xml:space="preserve">23-852</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Vanderstok</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Gorsuch</t>
+  </si>
+  <si>
+    <t xml:space="preserve">23-621</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Lackey</t>
+  </si>
+  <si>
+    <t xml:space="preserve">CA4</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Roberts</t>
+  </si>
+  <si>
+    <t xml:space="preserve">22-7466</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Glossip</t>
+  </si>
+  <si>
+    <t xml:space="preserve">CCAOK</t>
+  </si>
+  <si>
+    <t xml:space="preserve">(6-2)</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Sotomayor</t>
+  </si>
+  <si>
+    <t xml:space="preserve">23-365</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Medical Marijuana</t>
+  </si>
+  <si>
+    <t xml:space="preserve">CA2</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Affirm and Remand</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Barrett</t>
+  </si>
+  <si>
+    <t xml:space="preserve">23-583</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Bouarafa</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Jackson</t>
+  </si>
+  <si>
+    <t xml:space="preserve">23-713</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Bufkin</t>
+  </si>
+  <si>
+    <t xml:space="preserve">CAFED</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Thomas</t>
+  </si>
+  <si>
+    <t xml:space="preserve">23-753</t>
+  </si>
+  <si>
+    <t xml:space="preserve">SF v. EPA</t>
+  </si>
+  <si>
+    <t xml:space="preserve">CA9</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Alito</t>
+  </si>
+  <si>
+    <t xml:space="preserve">November</t>
+  </si>
+  <si>
+    <t xml:space="preserve">23-1127</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Wisconsin Bell</t>
+  </si>
+  <si>
+    <t xml:space="preserve">CA7</t>
+  </si>
+  <si>
+    <t xml:space="preserve">23-715</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Advocate Christ Medical</t>
+  </si>
+  <si>
+    <t xml:space="preserve">CADC</t>
+  </si>
+  <si>
+    <t xml:space="preserve">23-217</t>
+  </si>
+  <si>
+    <t xml:space="preserve">E.M.D. Sales</t>
+  </si>
+  <si>
+    <t xml:space="preserve">23-980</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Facebook</t>
+  </si>
+  <si>
+    <t xml:space="preserve">DIG</t>
+  </si>
+  <si>
+    <t xml:space="preserve">23-929</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Velazquez</t>
+  </si>
+  <si>
+    <t xml:space="preserve">(6-3)</t>
+  </si>
+  <si>
+    <t xml:space="preserve">23-825</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Delligatti</t>
+  </si>
+  <si>
+    <t xml:space="preserve">23-970</t>
+  </si>
+  <si>
+    <t xml:space="preserve">NVIDIA</t>
+  </si>
+  <si>
+    <t xml:space="preserve">December</t>
+  </si>
+  <si>
+    <t xml:space="preserve">23-1038</t>
   </si>
   <si>
     <t xml:space="preserve">Wages and White Lion </t>
   </si>
   <si>
-    <t>23-824</t>
-  </si>
-  <si>
-    <t>Miller</t>
-  </si>
-  <si>
-    <t>Reverse</t>
-  </si>
-  <si>
-    <t>(8-1)</t>
-  </si>
-  <si>
-    <t>23-867</t>
-  </si>
-  <si>
-    <t>Hungary</t>
-  </si>
-  <si>
-    <t>23-477</t>
-  </si>
-  <si>
-    <t>Skrmetti</t>
-  </si>
-  <si>
-    <t>CA6</t>
-  </si>
-  <si>
-    <t>23-909</t>
-  </si>
-  <si>
-    <t>Kouisisis</t>
-  </si>
-  <si>
-    <t>CA3</t>
-  </si>
-  <si>
-    <t>23-861</t>
-  </si>
-  <si>
-    <t>Feliciano</t>
-  </si>
-  <si>
-    <t>23-975</t>
-  </si>
-  <si>
-    <t>Seven County</t>
-  </si>
-  <si>
-    <t>(8-0)</t>
-  </si>
-  <si>
-    <t>23-900</t>
-  </si>
-  <si>
-    <t>Dewberry</t>
-  </si>
-  <si>
-    <t>January</t>
-  </si>
-  <si>
-    <t>23-1002</t>
-  </si>
-  <si>
-    <t>Hewitt</t>
-  </si>
-  <si>
-    <t>23-997</t>
-  </si>
-  <si>
-    <t>Stanley</t>
-  </si>
-  <si>
-    <t>23-1095</t>
-  </si>
-  <si>
-    <t>Thompson</t>
-  </si>
-  <si>
-    <t>23-971</t>
-  </si>
-  <si>
-    <t>Waetzig</t>
-  </si>
-  <si>
-    <t>23-1122</t>
-  </si>
-  <si>
-    <t>Free Speech</t>
-  </si>
-  <si>
-    <t>23-1187</t>
+    <t xml:space="preserve">23-824</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Miller</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Reverse</t>
+  </si>
+  <si>
+    <t xml:space="preserve">(8-1)</t>
+  </si>
+  <si>
+    <t xml:space="preserve">23-867</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Hungary</t>
+  </si>
+  <si>
+    <t xml:space="preserve">23-477</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Skrmetti</t>
+  </si>
+  <si>
+    <t xml:space="preserve">CA6</t>
+  </si>
+  <si>
+    <t xml:space="preserve">23-909</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Kouisisis</t>
+  </si>
+  <si>
+    <t xml:space="preserve">CA3</t>
+  </si>
+  <si>
+    <t xml:space="preserve">23-861</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Feliciano</t>
+  </si>
+  <si>
+    <t xml:space="preserve">23-975</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Seven County</t>
+  </si>
+  <si>
+    <t xml:space="preserve">(8-0)</t>
+  </si>
+  <si>
+    <t xml:space="preserve">23-900</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Dewberry</t>
+  </si>
+  <si>
+    <t xml:space="preserve">January</t>
+  </si>
+  <si>
+    <t xml:space="preserve">23-1002</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Hewitt</t>
+  </si>
+  <si>
+    <t xml:space="preserve">23-997</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Stanley</t>
+  </si>
+  <si>
+    <t xml:space="preserve">23-1095</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Thompson</t>
+  </si>
+  <si>
+    <t xml:space="preserve">23-971</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Waetzig</t>
+  </si>
+  <si>
+    <t xml:space="preserve">23-1122</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Free Speech</t>
+  </si>
+  <si>
+    <t xml:space="preserve">23-1187</t>
   </si>
   <si>
     <t xml:space="preserve"> R.J. Reynolds </t>
   </si>
   <si>
-    <t>23-1226</t>
-  </si>
-  <si>
-    <t>McLaughlin</t>
-  </si>
-  <si>
-    <t>23-1239</t>
-  </si>
-  <si>
-    <t>Barnes</t>
-  </si>
-  <si>
-    <t>23-1007</t>
-  </si>
-  <si>
-    <t>Cunningham</t>
-  </si>
-  <si>
-    <t>24-656</t>
-  </si>
-  <si>
-    <t>TikTok</t>
-  </si>
-  <si>
-    <t>February</t>
-  </si>
-  <si>
-    <t>23-7809</t>
-  </si>
-  <si>
-    <t>Guitierrez</t>
-  </si>
-  <si>
-    <t>23-7483</t>
-  </si>
-  <si>
-    <t>Esteras</t>
-  </si>
-  <si>
-    <t>23-1324</t>
-  </si>
-  <si>
-    <t>Perttu</t>
-  </si>
-  <si>
-    <t>23-1039</t>
-  </si>
-  <si>
-    <t>Ames</t>
-  </si>
-  <si>
-    <t>23-1201</t>
-  </si>
-  <si>
-    <t>CC/Devas</t>
-  </si>
-  <si>
-    <t>23-1259</t>
-  </si>
-  <si>
-    <t>BLOM Bank</t>
-  </si>
-  <si>
-    <t>23-1141</t>
-  </si>
-  <si>
-    <t>Smith and Wesson</t>
-  </si>
-  <si>
-    <t>CA1</t>
-  </si>
-  <si>
-    <t>23-1300</t>
-  </si>
-  <si>
-    <t>NRC</t>
-  </si>
-  <si>
-    <t>March</t>
-  </si>
-  <si>
-    <t>24-109</t>
-  </si>
-  <si>
-    <t>Lousiana</t>
-  </si>
-  <si>
-    <t>WDLA</t>
-  </si>
-  <si>
-    <t>23-1270</t>
-  </si>
-  <si>
-    <t>Riley</t>
-  </si>
-  <si>
-    <t>23-1229</t>
+    <t xml:space="preserve">23-1226</t>
+  </si>
+  <si>
+    <t xml:space="preserve">McLaughlin</t>
+  </si>
+  <si>
+    <t xml:space="preserve">23-1239</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Barnes</t>
+  </si>
+  <si>
+    <t xml:space="preserve">23-1007</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Cunningham</t>
+  </si>
+  <si>
+    <t xml:space="preserve">24-656</t>
+  </si>
+  <si>
+    <t xml:space="preserve">TikTok</t>
+  </si>
+  <si>
+    <t xml:space="preserve">February</t>
+  </si>
+  <si>
+    <t xml:space="preserve">23-7809</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Guitierrez</t>
+  </si>
+  <si>
+    <t xml:space="preserve">23-7483</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Esteras</t>
+  </si>
+  <si>
+    <t xml:space="preserve">23-1324</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Perttu</t>
+  </si>
+  <si>
+    <t xml:space="preserve">23-1039</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Ames</t>
+  </si>
+  <si>
+    <t xml:space="preserve">23-1201</t>
+  </si>
+  <si>
+    <t xml:space="preserve">CC/Devas</t>
+  </si>
+  <si>
+    <t xml:space="preserve">23-1259</t>
+  </si>
+  <si>
+    <t xml:space="preserve">BLOM Bank</t>
+  </si>
+  <si>
+    <t xml:space="preserve">23-1141</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Smith and Wesson</t>
+  </si>
+  <si>
+    <t xml:space="preserve">CA1</t>
+  </si>
+  <si>
+    <t xml:space="preserve">23-1300</t>
+  </si>
+  <si>
+    <t xml:space="preserve">NRC</t>
+  </si>
+  <si>
+    <t xml:space="preserve">March</t>
+  </si>
+  <si>
+    <t xml:space="preserve">24-109</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Lousiana</t>
+  </si>
+  <si>
+    <t xml:space="preserve">WDLA</t>
+  </si>
+  <si>
+    <t xml:space="preserve">23-1270</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Riley</t>
+  </si>
+  <si>
+    <t xml:space="preserve">23-1229</t>
   </si>
   <si>
     <t xml:space="preserve">Calumet </t>
   </si>
   <si>
-    <t>23-1067</t>
-  </si>
-  <si>
-    <t>Oklahoma</t>
-  </si>
-  <si>
-    <t>24-354</t>
-  </si>
-  <si>
-    <t>Consumers' Research</t>
-  </si>
-  <si>
-    <t>24-154</t>
-  </si>
-  <si>
-    <t>Catholic Charities</t>
-  </si>
-  <si>
-    <t>SCWI</t>
-  </si>
-  <si>
-    <t>23-1345</t>
-  </si>
-  <si>
-    <t>Rivers</t>
-  </si>
-  <si>
-    <t>24-20</t>
-  </si>
-  <si>
-    <t>Fuld</t>
-  </si>
-  <si>
-    <t>23-1275</t>
-  </si>
-  <si>
-    <t>Medina</t>
-  </si>
-  <si>
-    <t>April</t>
-  </si>
-  <si>
-    <t>24-316</t>
-  </si>
-  <si>
-    <t>Kennedy</t>
-  </si>
-  <si>
-    <t>24-275</t>
-  </si>
-  <si>
-    <t>Parrish</t>
-  </si>
-  <si>
-    <t>24-297</t>
-  </si>
-  <si>
-    <t>Mahmoud</t>
-  </si>
-  <si>
-    <t>24-416</t>
-  </si>
-  <si>
-    <t>Cir</t>
-  </si>
-  <si>
-    <t>24-7</t>
-  </si>
-  <si>
-    <t>Diamond</t>
-  </si>
-  <si>
-    <t>24-249</t>
-  </si>
-  <si>
-    <t>A.J.T.</t>
-  </si>
-  <si>
-    <t>24-320</t>
-  </si>
-  <si>
-    <t>Soto</t>
-  </si>
-  <si>
-    <t>24-362</t>
-  </si>
-  <si>
-    <t>Martin</t>
-  </si>
-  <si>
-    <t>24-304</t>
-  </si>
-  <si>
-    <t>Laboratory Corp.</t>
-  </si>
-  <si>
-    <t>24-394</t>
-  </si>
-  <si>
-    <t>Drummond</t>
-  </si>
-  <si>
-    <t>SCOK</t>
-  </si>
-  <si>
-    <t>(4-4)*</t>
-  </si>
-  <si>
-    <t>May</t>
-  </si>
-  <si>
-    <t>24A884</t>
-  </si>
-  <si>
-    <t>Trump v. CASA</t>
+    <t xml:space="preserve">23-1067</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Oklahoma</t>
+  </si>
+  <si>
+    <t xml:space="preserve">24-354</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Consumers' Research</t>
+  </si>
+  <si>
+    <t xml:space="preserve">24-154</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Catholic Charities</t>
+  </si>
+  <si>
+    <t xml:space="preserve">SCWI</t>
+  </si>
+  <si>
+    <t xml:space="preserve">23-1345</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Rivers</t>
+  </si>
+  <si>
+    <t xml:space="preserve">24-20</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Fuld</t>
+  </si>
+  <si>
+    <t xml:space="preserve">23-1275</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Medina</t>
+  </si>
+  <si>
+    <t xml:space="preserve">April</t>
+  </si>
+  <si>
+    <t xml:space="preserve">24-316</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Kennedy</t>
+  </si>
+  <si>
+    <t xml:space="preserve">24-275</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Parrish</t>
+  </si>
+  <si>
+    <t xml:space="preserve">24-297</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Mahmoud</t>
+  </si>
+  <si>
+    <t xml:space="preserve">24-416</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Zuch</t>
+  </si>
+  <si>
+    <t xml:space="preserve">24-7</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Diamond</t>
+  </si>
+  <si>
+    <t xml:space="preserve">24-249</t>
+  </si>
+  <si>
+    <t xml:space="preserve">A.J.T.</t>
+  </si>
+  <si>
+    <t xml:space="preserve">24-320</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Soto</t>
+  </si>
+  <si>
+    <t xml:space="preserve">24-362</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Martin</t>
+  </si>
+  <si>
+    <t xml:space="preserve">24-304</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Laboratory Corp.</t>
+  </si>
+  <si>
+    <t xml:space="preserve">24-394</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Drummond</t>
+  </si>
+  <si>
+    <t xml:space="preserve">SCOK</t>
+  </si>
+  <si>
+    <t xml:space="preserve">(4-4)*</t>
+  </si>
+  <si>
+    <t xml:space="preserve">May</t>
+  </si>
+  <si>
+    <t xml:space="preserve">24A884</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Trump v. CASA</t>
   </si>
 </sst>
 </file>
@@ -635,9 +627,9 @@
 <file path=xl/styles.xml><?xml version="1.0" encoding="utf-8"?>
 <styleSheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:x16r2="http://schemas.microsoft.com/office/spreadsheetml/2015/02/main" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" mc:Ignorable="x14ac x16r2 xr">
   <numFmts count="1">
-    <numFmt numFmtId="164" formatCode="mm/dd/yyyy"/>
+    <numFmt numFmtId="165" formatCode="mm/dd/yyyy"/>
   </numFmts>
-  <fonts count="2" x14ac:knownFonts="1">
+  <fonts count="2">
     <font>
       <sz val="11"/>
       <color rgb="FF000000"/>
@@ -673,21 +665,12 @@
   </cellStyleXfs>
   <cellXfs count="2">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0"/>
-    <xf numFmtId="164" fontId="1" fillId="0" borderId="0" xfId="0" applyNumberFormat="1" applyFont="1"/>
+    <xf numFmtId="165" fontId="1" fillId="0" borderId="0" xfId="0" applyFont="1" applyNumberFormat="1"/>
   </cellXfs>
   <cellStyles count="1">
     <cellStyle name="Normal" xfId="0" builtinId="0"/>
   </cellStyles>
   <dxfs count="0"/>
-  <tableStyles count="0" defaultTableStyle="TableStyleMedium2" defaultPivotStyle="PivotStyleLight16"/>
-  <extLst>
-    <ext xmlns:x14="http://schemas.microsoft.com/office/spreadsheetml/2009/9/main" uri="{EB79DEF2-80B8-43e5-95BD-54CBDDF9020C}">
-      <x14:slicerStyles defaultSlicerStyle="SlicerStyleLight1"/>
-    </ext>
-    <ext xmlns:x15="http://schemas.microsoft.com/office/spreadsheetml/2010/11/main" uri="{9260A510-F301-46a8-8635-F512D64BE5F5}">
-      <x15:timelineStyles defaultTimelineStyle="TimeSlicerStyleLight1"/>
-    </ext>
-  </extLst>
 </styleSheet>
 </file>
 
@@ -969,11 +952,11 @@
 </file>
 
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
-<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{00000000-0001-0000-0000-000000000000}">
-  <dimension ref="A1:K6"/>
-  <sheetFormatPr defaultColWidth="11.42578125" defaultRowHeight="15" x14ac:dyDescent="0.25"/>
+<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:xdr="http://schemas.openxmlformats.org/drawingml/2006/spreadsheetDrawing" xmlns:x14="http://schemas.microsoft.com/office/spreadsheetml/2009/9/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3">
+  <dimension ref="A1"/>
+  <sheetFormatPr defaultRowHeight="15.0" baseColWidth="10"/>
   <sheetData>
-    <row r="1" spans="1:11" x14ac:dyDescent="0.25">
+    <row r="1">
       <c r="A1" t="s">
         <v>0</v>
       </c>
@@ -1008,7 +991,7 @@
         <v>10</v>
       </c>
     </row>
-    <row r="2" spans="1:11" x14ac:dyDescent="0.25">
+    <row r="2">
       <c r="A2" t="s">
         <v>11</v>
       </c>
@@ -1021,13 +1004,14 @@
       <c r="D2" t="s">
         <v>14</v>
       </c>
-      <c r="E2">
+      <c r="E2" t="n">
         <v>0</v>
       </c>
       <c r="F2" s="1"/>
-      <c r="G2" s="1">
+      <c r="G2" s="1" t="n">
         <v>45600</v>
       </c>
+      <c r="H2"/>
       <c r="I2" t="s">
         <v>15</v>
       </c>
@@ -1038,7 +1022,7 @@
         <v>16</v>
       </c>
     </row>
-    <row r="3" spans="1:11" x14ac:dyDescent="0.25">
+    <row r="3">
       <c r="A3" t="s">
         <v>11</v>
       </c>
@@ -1051,13 +1035,14 @@
       <c r="D3" t="s">
         <v>19</v>
       </c>
-      <c r="E3">
+      <c r="E3" t="n">
         <v>0</v>
       </c>
       <c r="F3" s="1"/>
-      <c r="G3" s="1">
+      <c r="G3" s="1" t="n">
         <v>45678</v>
       </c>
+      <c r="H3"/>
       <c r="I3" t="s">
         <v>15</v>
       </c>
@@ -1068,7 +1053,7 @@
         <v>16</v>
       </c>
     </row>
-    <row r="4" spans="1:11" x14ac:dyDescent="0.25">
+    <row r="4">
       <c r="A4" t="s">
         <v>11</v>
       </c>
@@ -1081,13 +1066,14 @@
       <c r="D4" t="s">
         <v>23</v>
       </c>
-      <c r="E4">
+      <c r="E4" t="n">
         <v>0</v>
       </c>
       <c r="F4" s="1"/>
-      <c r="G4" s="1">
+      <c r="G4" s="1" t="n">
         <v>45751</v>
       </c>
+      <c r="H4"/>
       <c r="I4" t="s">
         <v>24</v>
       </c>
@@ -1098,7 +1084,7 @@
         <v>16</v>
       </c>
     </row>
-    <row r="5" spans="1:11" x14ac:dyDescent="0.25">
+    <row r="5">
       <c r="A5" t="s">
         <v>11</v>
       </c>
@@ -1111,13 +1097,14 @@
       <c r="D5" t="s">
         <v>28</v>
       </c>
-      <c r="E5">
+      <c r="E5" t="n">
         <v>0</v>
       </c>
       <c r="F5" s="1"/>
-      <c r="G5" s="1">
+      <c r="G5" s="1" t="n">
         <v>45754</v>
       </c>
+      <c r="H5"/>
       <c r="I5" t="s">
         <v>24</v>
       </c>
@@ -1128,7 +1115,7 @@
         <v>16</v>
       </c>
     </row>
-    <row r="6" spans="1:11" x14ac:dyDescent="0.25">
+    <row r="6">
       <c r="A6" t="s">
         <v>11</v>
       </c>
@@ -1141,13 +1128,14 @@
       <c r="D6" t="s">
         <v>32</v>
       </c>
-      <c r="E6">
+      <c r="E6" t="n">
         <v>0</v>
       </c>
       <c r="F6" s="1"/>
-      <c r="G6" s="1">
+      <c r="G6" s="1" t="n">
         <v>45793</v>
       </c>
+      <c r="H6"/>
       <c r="I6" t="s">
         <v>24</v>
       </c>
@@ -1160,16 +1148,16 @@
     </row>
   </sheetData>
   <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
-  <pageSetup paperSize="9" orientation="portrait" horizontalDpi="300" verticalDpi="300"/>
+  <pageSetup paperSize="9" orientation="portrait" horizontalDpi="300" verticalDpi="300" r:id="rId2"/>
 </worksheet>
 </file>
 
 <file path=xl/worksheets/sheet2.xml><?xml version="1.0" encoding="utf-8"?>
-<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{00000000-0001-0000-0100-000000000000}">
-  <dimension ref="A1:K10"/>
-  <sheetFormatPr defaultColWidth="11.42578125" defaultRowHeight="15" x14ac:dyDescent="0.25"/>
+<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:xdr="http://schemas.openxmlformats.org/drawingml/2006/spreadsheetDrawing" xmlns:x14="http://schemas.microsoft.com/office/spreadsheetml/2009/9/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3">
+  <dimension ref="A1"/>
+  <sheetFormatPr defaultRowHeight="15.0" baseColWidth="10"/>
   <sheetData>
-    <row r="1" spans="1:11" x14ac:dyDescent="0.25">
+    <row r="1">
       <c r="A1" t="s">
         <v>0</v>
       </c>
@@ -1204,7 +1192,7 @@
         <v>10</v>
       </c>
     </row>
-    <row r="2" spans="1:11" x14ac:dyDescent="0.25">
+    <row r="2">
       <c r="A2" t="s">
         <v>33</v>
       </c>
@@ -1217,16 +1205,16 @@
       <c r="D2" t="s">
         <v>36</v>
       </c>
-      <c r="E2">
-        <v>0</v>
-      </c>
-      <c r="F2" s="1">
+      <c r="E2" t="n">
+        <v>0</v>
+      </c>
+      <c r="F2" s="1" t="n">
         <v>45572</v>
       </c>
-      <c r="G2" s="1">
+      <c r="G2" s="1" t="n">
         <v>45709</v>
       </c>
-      <c r="H2">
+      <c r="H2" t="n">
         <v>138</v>
       </c>
       <c r="I2" t="s">
@@ -1239,7 +1227,7 @@
         <v>38</v>
       </c>
     </row>
-    <row r="3" spans="1:11" x14ac:dyDescent="0.25">
+    <row r="3">
       <c r="A3" t="s">
         <v>33</v>
       </c>
@@ -1252,16 +1240,16 @@
       <c r="D3" t="s">
         <v>41</v>
       </c>
-      <c r="E3">
-        <v>0</v>
-      </c>
-      <c r="F3" s="1">
+      <c r="E3" t="n">
+        <v>0</v>
+      </c>
+      <c r="F3" s="1" t="n">
         <v>45572</v>
       </c>
-      <c r="G3" s="1">
+      <c r="G3" s="1" t="n">
         <v>45672</v>
       </c>
-      <c r="H3">
+      <c r="H3" t="n">
         <v>101</v>
       </c>
       <c r="I3" t="s">
@@ -1274,7 +1262,7 @@
         <v>44</v>
       </c>
     </row>
-    <row r="4" spans="1:11" x14ac:dyDescent="0.25">
+    <row r="4">
       <c r="A4" t="s">
         <v>33</v>
       </c>
@@ -1287,16 +1275,16 @@
       <c r="D4" t="s">
         <v>32</v>
       </c>
-      <c r="E4">
-        <v>0</v>
-      </c>
-      <c r="F4" s="1">
+      <c r="E4" t="n">
+        <v>0</v>
+      </c>
+      <c r="F4" s="1" t="n">
         <v>45573</v>
       </c>
-      <c r="G4" s="1">
+      <c r="G4" s="1" t="n">
         <v>45742</v>
       </c>
-      <c r="H4">
+      <c r="H4" t="n">
         <v>170</v>
       </c>
       <c r="I4" t="s">
@@ -1309,7 +1297,7 @@
         <v>47</v>
       </c>
     </row>
-    <row r="5" spans="1:11" x14ac:dyDescent="0.25">
+    <row r="5">
       <c r="A5" t="s">
         <v>33</v>
       </c>
@@ -1322,16 +1310,16 @@
       <c r="D5" t="s">
         <v>50</v>
       </c>
-      <c r="E5">
-        <v>0</v>
-      </c>
-      <c r="F5" s="1">
+      <c r="E5" t="n">
+        <v>0</v>
+      </c>
+      <c r="F5" s="1" t="n">
         <v>45573</v>
       </c>
-      <c r="G5" s="1">
+      <c r="G5" s="1" t="n">
         <v>45713</v>
       </c>
-      <c r="H5">
+      <c r="H5" t="n">
         <v>141</v>
       </c>
       <c r="I5" t="s">
@@ -1344,7 +1332,7 @@
         <v>51</v>
       </c>
     </row>
-    <row r="6" spans="1:11" x14ac:dyDescent="0.25">
+    <row r="6">
       <c r="A6" t="s">
         <v>33</v>
       </c>
@@ -1357,16 +1345,16 @@
       <c r="D6" t="s">
         <v>54</v>
       </c>
-      <c r="E6">
+      <c r="E6" t="n">
         <v>1</v>
       </c>
-      <c r="F6" s="1">
+      <c r="F6" s="1" t="n">
         <v>45574</v>
       </c>
-      <c r="G6" s="1">
+      <c r="G6" s="1" t="n">
         <v>45713</v>
       </c>
-      <c r="H6">
+      <c r="H6" t="n">
         <v>140</v>
       </c>
       <c r="I6" t="s">
@@ -1379,7 +1367,7 @@
         <v>56</v>
       </c>
     </row>
-    <row r="7" spans="1:11" x14ac:dyDescent="0.25">
+    <row r="7">
       <c r="A7" t="s">
         <v>33</v>
       </c>
@@ -1392,16 +1380,16 @@
       <c r="D7" t="s">
         <v>59</v>
       </c>
-      <c r="E7">
-        <v>0</v>
-      </c>
-      <c r="F7" s="1">
+      <c r="E7" t="n">
+        <v>0</v>
+      </c>
+      <c r="F7" s="1" t="n">
         <v>45580</v>
       </c>
-      <c r="G7" s="1">
+      <c r="G7" s="1" t="n">
         <v>45749</v>
       </c>
-      <c r="H7">
+      <c r="H7" t="n">
         <v>170</v>
       </c>
       <c r="I7" t="s">
@@ -1414,7 +1402,7 @@
         <v>61</v>
       </c>
     </row>
-    <row r="8" spans="1:11" x14ac:dyDescent="0.25">
+    <row r="8">
       <c r="A8" t="s">
         <v>33</v>
       </c>
@@ -1427,16 +1415,16 @@
       <c r="D8" t="s">
         <v>14</v>
       </c>
-      <c r="E8">
-        <v>0</v>
-      </c>
-      <c r="F8" s="1">
+      <c r="E8" t="n">
+        <v>0</v>
+      </c>
+      <c r="F8" s="1" t="n">
         <v>45580</v>
       </c>
-      <c r="G8" s="1">
+      <c r="G8" s="1" t="n">
         <v>45636</v>
       </c>
-      <c r="H8">
+      <c r="H8" t="n">
         <v>57</v>
       </c>
       <c r="I8" t="s">
@@ -1449,7 +1437,7 @@
         <v>64</v>
       </c>
     </row>
-    <row r="9" spans="1:11" x14ac:dyDescent="0.25">
+    <row r="9">
       <c r="A9" t="s">
         <v>33</v>
       </c>
@@ -1462,16 +1450,16 @@
       <c r="D9" t="s">
         <v>67</v>
       </c>
-      <c r="E9">
-        <v>0</v>
-      </c>
-      <c r="F9" s="1">
+      <c r="E9" t="n">
+        <v>0</v>
+      </c>
+      <c r="F9" s="1" t="n">
         <v>45581</v>
       </c>
-      <c r="G9" s="1">
+      <c r="G9" s="1" t="n">
         <v>45721</v>
       </c>
-      <c r="H9">
+      <c r="H9" t="n">
         <v>141</v>
       </c>
       <c r="I9" t="s">
@@ -1484,7 +1472,7 @@
         <v>68</v>
       </c>
     </row>
-    <row r="10" spans="1:11" x14ac:dyDescent="0.25">
+    <row r="10">
       <c r="A10" t="s">
         <v>33</v>
       </c>
@@ -1497,16 +1485,16 @@
       <c r="D10" t="s">
         <v>71</v>
       </c>
-      <c r="E10">
-        <v>0</v>
-      </c>
-      <c r="F10" s="1">
+      <c r="E10" t="n">
+        <v>0</v>
+      </c>
+      <c r="F10" s="1" t="n">
         <v>45581</v>
       </c>
-      <c r="G10" s="1">
+      <c r="G10" s="1" t="n">
         <v>45720</v>
       </c>
-      <c r="H10">
+      <c r="H10" t="n">
         <v>140</v>
       </c>
       <c r="I10" t="s">
@@ -1521,16 +1509,16 @@
     </row>
   </sheetData>
   <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
-  <pageSetup paperSize="9" orientation="portrait" horizontalDpi="300" verticalDpi="300"/>
+  <pageSetup paperSize="9" orientation="portrait" horizontalDpi="300" verticalDpi="300" r:id="rId2"/>
 </worksheet>
 </file>
 
 <file path=xl/worksheets/sheet3.xml><?xml version="1.0" encoding="utf-8"?>
-<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{00000000-0001-0000-0200-000000000000}">
-  <dimension ref="A1:K8"/>
-  <sheetFormatPr defaultColWidth="11.42578125" defaultRowHeight="15" x14ac:dyDescent="0.25"/>
+<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:xdr="http://schemas.openxmlformats.org/drawingml/2006/spreadsheetDrawing" xmlns:x14="http://schemas.microsoft.com/office/spreadsheetml/2009/9/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3">
+  <dimension ref="A1"/>
+  <sheetFormatPr defaultRowHeight="15.0" baseColWidth="10"/>
   <sheetData>
-    <row r="1" spans="1:11" x14ac:dyDescent="0.25">
+    <row r="1">
       <c r="A1" t="s">
         <v>0</v>
       </c>
@@ -1565,7 +1553,7 @@
         <v>10</v>
       </c>
     </row>
-    <row r="2" spans="1:11" x14ac:dyDescent="0.25">
+    <row r="2">
       <c r="A2" t="s">
         <v>73</v>
       </c>
@@ -1578,16 +1566,16 @@
       <c r="D2" t="s">
         <v>76</v>
       </c>
-      <c r="E2">
-        <v>0</v>
-      </c>
-      <c r="F2" s="1">
+      <c r="E2" t="n">
+        <v>0</v>
+      </c>
+      <c r="F2" s="1" t="n">
         <v>45600</v>
       </c>
-      <c r="G2" s="1">
+      <c r="G2" s="1" t="n">
         <v>45709</v>
       </c>
-      <c r="H2">
+      <c r="H2" t="n">
         <v>110</v>
       </c>
       <c r="I2" t="s">
@@ -1600,7 +1588,7 @@
         <v>44</v>
       </c>
     </row>
-    <row r="3" spans="1:11" x14ac:dyDescent="0.25">
+    <row r="3">
       <c r="A3" t="s">
         <v>73</v>
       </c>
@@ -1613,16 +1601,16 @@
       <c r="D3" t="s">
         <v>79</v>
       </c>
-      <c r="E3">
-        <v>0</v>
-      </c>
-      <c r="F3" s="1">
+      <c r="E3" t="n">
+        <v>0</v>
+      </c>
+      <c r="F3" s="1" t="n">
         <v>45601</v>
       </c>
-      <c r="G3" s="1">
+      <c r="G3" s="1" t="n">
         <v>45776</v>
       </c>
-      <c r="H3">
+      <c r="H3" t="n">
         <v>176</v>
       </c>
       <c r="I3" t="s">
@@ -1635,7 +1623,7 @@
         <v>61</v>
       </c>
     </row>
-    <row r="4" spans="1:11" x14ac:dyDescent="0.25">
+    <row r="4">
       <c r="A4" t="s">
         <v>73</v>
       </c>
@@ -1648,16 +1636,16 @@
       <c r="D4" t="s">
         <v>50</v>
       </c>
-      <c r="E4">
-        <v>0</v>
-      </c>
-      <c r="F4" s="1">
+      <c r="E4" t="n">
+        <v>0</v>
+      </c>
+      <c r="F4" s="1" t="n">
         <v>45601</v>
       </c>
-      <c r="G4" s="1">
+      <c r="G4" s="1" t="n">
         <v>45672</v>
       </c>
-      <c r="H4">
+      <c r="H4" t="n">
         <v>72</v>
       </c>
       <c r="I4" t="s">
@@ -1670,7 +1658,7 @@
         <v>38</v>
       </c>
     </row>
-    <row r="5" spans="1:11" x14ac:dyDescent="0.25">
+    <row r="5">
       <c r="A5" t="s">
         <v>73</v>
       </c>
@@ -1683,16 +1671,16 @@
       <c r="D5" t="s">
         <v>71</v>
       </c>
-      <c r="E5">
-        <v>0</v>
-      </c>
-      <c r="F5" s="1">
+      <c r="E5" t="n">
+        <v>0</v>
+      </c>
+      <c r="F5" s="1" t="n">
         <v>45602</v>
       </c>
-      <c r="G5" s="1">
+      <c r="G5" s="1" t="n">
         <v>45618</v>
       </c>
-      <c r="H5">
+      <c r="H5" t="n">
         <v>17</v>
       </c>
       <c r="I5" t="s">
@@ -1705,7 +1693,7 @@
         <v>16</v>
       </c>
     </row>
-    <row r="6" spans="1:11" x14ac:dyDescent="0.25">
+    <row r="6">
       <c r="A6" t="s">
         <v>73</v>
       </c>
@@ -1718,16 +1706,16 @@
       <c r="D6" t="s">
         <v>59</v>
       </c>
-      <c r="E6">
-        <v>0</v>
-      </c>
-      <c r="F6" s="1">
+      <c r="E6" t="n">
+        <v>0</v>
+      </c>
+      <c r="F6" s="1" t="n">
         <v>45608</v>
       </c>
-      <c r="G6" s="1">
+      <c r="G6" s="1" t="n">
         <v>45769</v>
       </c>
-      <c r="H6">
+      <c r="H6" t="n">
         <v>162</v>
       </c>
       <c r="I6" t="s">
@@ -1740,7 +1728,7 @@
         <v>47</v>
       </c>
     </row>
-    <row r="7" spans="1:11" x14ac:dyDescent="0.25">
+    <row r="7">
       <c r="A7" t="s">
         <v>73</v>
       </c>
@@ -1753,16 +1741,16 @@
       <c r="D7" t="s">
         <v>59</v>
       </c>
-      <c r="E7">
-        <v>0</v>
-      </c>
-      <c r="F7" s="1">
+      <c r="E7" t="n">
+        <v>0</v>
+      </c>
+      <c r="F7" s="1" t="n">
         <v>45608</v>
       </c>
-      <c r="G7" s="1">
+      <c r="G7" s="1" t="n">
         <v>45737</v>
       </c>
-      <c r="H7">
+      <c r="H7" t="n">
         <v>130</v>
       </c>
       <c r="I7" t="s">
@@ -1775,7 +1763,7 @@
         <v>68</v>
       </c>
     </row>
-    <row r="8" spans="1:11" x14ac:dyDescent="0.25">
+    <row r="8">
       <c r="A8" t="s">
         <v>73</v>
       </c>
@@ -1788,16 +1776,16 @@
       <c r="D8" t="s">
         <v>71</v>
       </c>
-      <c r="E8">
-        <v>0</v>
-      </c>
-      <c r="F8" s="1">
+      <c r="E8" t="n">
+        <v>0</v>
+      </c>
+      <c r="F8" s="1" t="n">
         <v>45609</v>
       </c>
-      <c r="G8" s="1">
+      <c r="G8" s="1" t="n">
         <v>45637</v>
       </c>
-      <c r="H8">
+      <c r="H8" t="n">
         <v>29</v>
       </c>
       <c r="I8" t="s">
@@ -1812,16 +1800,16 @@
     </row>
   </sheetData>
   <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
-  <pageSetup paperSize="9" orientation="portrait" horizontalDpi="300" verticalDpi="300"/>
+  <pageSetup paperSize="9" orientation="portrait" horizontalDpi="300" verticalDpi="300" r:id="rId2"/>
 </worksheet>
 </file>
 
 <file path=xl/worksheets/sheet4.xml><?xml version="1.0" encoding="utf-8"?>
-<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{00000000-0001-0000-0300-000000000000}">
-  <dimension ref="A1:K9"/>
-  <sheetFormatPr defaultColWidth="11.42578125" defaultRowHeight="15" x14ac:dyDescent="0.25"/>
+<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:xdr="http://schemas.openxmlformats.org/drawingml/2006/spreadsheetDrawing" xmlns:x14="http://schemas.microsoft.com/office/spreadsheetml/2009/9/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3">
+  <dimension ref="A1"/>
+  <sheetFormatPr defaultRowHeight="15.0" baseColWidth="10"/>
   <sheetData>
-    <row r="1" spans="1:11" x14ac:dyDescent="0.25">
+    <row r="1">
       <c r="A1" t="s">
         <v>0</v>
       </c>
@@ -1856,7 +1844,7 @@
         <v>10</v>
       </c>
     </row>
-    <row r="2" spans="1:11" x14ac:dyDescent="0.25">
+    <row r="2">
       <c r="A2" t="s">
         <v>92</v>
       </c>
@@ -1869,16 +1857,16 @@
       <c r="D2" t="s">
         <v>32</v>
       </c>
-      <c r="E2">
-        <v>0</v>
-      </c>
-      <c r="F2" s="1">
+      <c r="E2" t="n">
+        <v>0</v>
+      </c>
+      <c r="F2" s="1" t="n">
         <v>45628</v>
       </c>
-      <c r="G2" s="1">
+      <c r="G2" s="1" t="n">
         <v>45749</v>
       </c>
-      <c r="H2">
+      <c r="H2" t="n">
         <v>122</v>
       </c>
       <c r="I2" t="s">
@@ -1891,7 +1879,7 @@
         <v>72</v>
       </c>
     </row>
-    <row r="3" spans="1:11" x14ac:dyDescent="0.25">
+    <row r="3">
       <c r="A3" t="s">
         <v>92</v>
       </c>
@@ -1904,16 +1892,16 @@
       <c r="D3" t="s">
         <v>19</v>
       </c>
-      <c r="E3">
-        <v>0</v>
-      </c>
-      <c r="F3" s="1">
+      <c r="E3" t="n">
+        <v>0</v>
+      </c>
+      <c r="F3" s="1" t="n">
         <v>45628</v>
       </c>
-      <c r="G3" s="1">
+      <c r="G3" s="1" t="n">
         <v>45742</v>
       </c>
-      <c r="H3">
+      <c r="H3" t="n">
         <v>115</v>
       </c>
       <c r="I3" t="s">
@@ -1926,7 +1914,7 @@
         <v>64</v>
       </c>
     </row>
-    <row r="4" spans="1:11" x14ac:dyDescent="0.25">
+    <row r="4">
       <c r="A4" t="s">
         <v>92</v>
       </c>
@@ -1939,16 +1927,16 @@
       <c r="D4" t="s">
         <v>79</v>
       </c>
-      <c r="E4">
-        <v>0</v>
-      </c>
-      <c r="F4" s="1">
+      <c r="E4" t="n">
+        <v>0</v>
+      </c>
+      <c r="F4" s="1" t="n">
         <v>45629</v>
       </c>
-      <c r="G4" s="1">
+      <c r="G4" s="1" t="n">
         <v>45709</v>
       </c>
-      <c r="H4">
+      <c r="H4" t="n">
         <v>81</v>
       </c>
       <c r="I4" t="s">
@@ -1961,7 +1949,7 @@
         <v>56</v>
       </c>
     </row>
-    <row r="5" spans="1:11" x14ac:dyDescent="0.25">
+    <row r="5">
       <c r="A5" t="s">
         <v>92</v>
       </c>
@@ -1974,13 +1962,17 @@
       <c r="D5" t="s">
         <v>103</v>
       </c>
-      <c r="E5">
+      <c r="E5" t="n">
         <v>1</v>
       </c>
       <c r="F5" s="1"/>
       <c r="G5" s="1"/>
-    </row>
-    <row r="6" spans="1:11" x14ac:dyDescent="0.25">
+      <c r="H5"/>
+      <c r="I5"/>
+      <c r="J5"/>
+      <c r="K5"/>
+    </row>
+    <row r="6">
       <c r="A6" t="s">
         <v>92</v>
       </c>
@@ -1993,16 +1985,16 @@
       <c r="D6" t="s">
         <v>106</v>
       </c>
-      <c r="E6">
-        <v>0</v>
-      </c>
-      <c r="F6" s="1">
+      <c r="E6" t="n">
+        <v>0</v>
+      </c>
+      <c r="F6" s="1" t="n">
         <v>45635</v>
       </c>
-      <c r="G6" s="1">
+      <c r="G6" s="1" t="n">
         <v>45799</v>
       </c>
-      <c r="H6">
+      <c r="H6" t="n">
         <v>165</v>
       </c>
       <c r="I6" t="s">
@@ -2015,7 +2007,7 @@
         <v>61</v>
       </c>
     </row>
-    <row r="7" spans="1:11" x14ac:dyDescent="0.25">
+    <row r="7">
       <c r="A7" t="s">
         <v>92</v>
       </c>
@@ -2028,16 +2020,16 @@
       <c r="D7" t="s">
         <v>67</v>
       </c>
-      <c r="E7">
-        <v>0</v>
-      </c>
-      <c r="F7" s="1">
+      <c r="E7" t="n">
+        <v>0</v>
+      </c>
+      <c r="F7" s="1" t="n">
         <v>45635</v>
       </c>
-      <c r="G7" s="1">
+      <c r="G7" s="1" t="n">
         <v>45777</v>
       </c>
-      <c r="H7">
+      <c r="H7" t="n">
         <v>143</v>
       </c>
       <c r="I7" t="s">
@@ -2050,7 +2042,7 @@
         <v>47</v>
       </c>
     </row>
-    <row r="8" spans="1:11" x14ac:dyDescent="0.25">
+    <row r="8">
       <c r="A8" t="s">
         <v>92</v>
       </c>
@@ -2063,16 +2055,16 @@
       <c r="D8" t="s">
         <v>79</v>
       </c>
-      <c r="E8">
-        <v>0</v>
-      </c>
-      <c r="F8" s="1">
+      <c r="E8" t="n">
+        <v>0</v>
+      </c>
+      <c r="F8" s="1" t="n">
         <v>45636</v>
       </c>
-      <c r="G8" s="1">
+      <c r="G8" s="1" t="n">
         <v>45806</v>
       </c>
-      <c r="H8">
+      <c r="H8" t="n">
         <v>171</v>
       </c>
       <c r="I8" t="s">
@@ -2085,7 +2077,7 @@
         <v>38</v>
       </c>
     </row>
-    <row r="9" spans="1:11" x14ac:dyDescent="0.25">
+    <row r="9">
       <c r="A9" t="s">
         <v>92</v>
       </c>
@@ -2098,16 +2090,16 @@
       <c r="D9" t="s">
         <v>50</v>
       </c>
-      <c r="E9">
-        <v>0</v>
-      </c>
-      <c r="F9" s="1">
+      <c r="E9" t="n">
+        <v>0</v>
+      </c>
+      <c r="F9" s="1" t="n">
         <v>45637</v>
       </c>
-      <c r="G9" s="1">
+      <c r="G9" s="1" t="n">
         <v>45714</v>
       </c>
-      <c r="H9">
+      <c r="H9" t="n">
         <v>78</v>
       </c>
       <c r="I9" t="s">
@@ -2122,16 +2114,16 @@
     </row>
   </sheetData>
   <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
-  <pageSetup paperSize="9" orientation="portrait" horizontalDpi="300" verticalDpi="300"/>
+  <pageSetup paperSize="9" orientation="portrait" horizontalDpi="300" verticalDpi="300" r:id="rId2"/>
 </worksheet>
 </file>
 
 <file path=xl/worksheets/sheet5.xml><?xml version="1.0" encoding="utf-8"?>
-<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{00000000-0001-0000-0400-000000000000}">
-  <dimension ref="A1:K11"/>
-  <sheetFormatPr defaultColWidth="11.42578125" defaultRowHeight="15" x14ac:dyDescent="0.25"/>
+<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:xdr="http://schemas.openxmlformats.org/drawingml/2006/spreadsheetDrawing" xmlns:x14="http://schemas.microsoft.com/office/spreadsheetml/2009/9/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3">
+  <dimension ref="A1"/>
+  <sheetFormatPr defaultRowHeight="15.0" baseColWidth="10"/>
   <sheetData>
-    <row r="1" spans="1:11" x14ac:dyDescent="0.25">
+    <row r="1">
       <c r="A1" t="s">
         <v>0</v>
       </c>
@@ -2166,7 +2158,7 @@
         <v>10</v>
       </c>
     </row>
-    <row r="2" spans="1:11" x14ac:dyDescent="0.25">
+    <row r="2">
       <c r="A2" t="s">
         <v>114</v>
       </c>
@@ -2179,13 +2171,17 @@
       <c r="D2" t="s">
         <v>32</v>
       </c>
-      <c r="E2">
+      <c r="E2" t="n">
         <v>0</v>
       </c>
       <c r="F2" s="1"/>
       <c r="G2" s="1"/>
-    </row>
-    <row r="3" spans="1:11" x14ac:dyDescent="0.25">
+      <c r="H2"/>
+      <c r="I2"/>
+      <c r="J2"/>
+      <c r="K2"/>
+    </row>
+    <row r="3">
       <c r="A3" t="s">
         <v>114</v>
       </c>
@@ -2198,13 +2194,17 @@
       <c r="D3" t="s">
         <v>14</v>
       </c>
-      <c r="E3">
+      <c r="E3" t="n">
         <v>0</v>
       </c>
       <c r="F3" s="1"/>
       <c r="G3" s="1"/>
-    </row>
-    <row r="4" spans="1:11" x14ac:dyDescent="0.25">
+      <c r="H3"/>
+      <c r="I3"/>
+      <c r="J3"/>
+      <c r="K3"/>
+    </row>
+    <row r="4">
       <c r="A4" t="s">
         <v>114</v>
       </c>
@@ -2217,16 +2217,16 @@
       <c r="D4" t="s">
         <v>76</v>
       </c>
-      <c r="E4">
-        <v>0</v>
-      </c>
-      <c r="F4" s="1">
+      <c r="E4" t="n">
+        <v>0</v>
+      </c>
+      <c r="F4" s="1" t="n">
         <v>45671</v>
       </c>
-      <c r="G4" s="1">
+      <c r="G4" s="1" t="n">
         <v>45737</v>
       </c>
-      <c r="H4">
+      <c r="H4" t="n">
         <v>67</v>
       </c>
       <c r="I4" t="s">
@@ -2239,7 +2239,7 @@
         <v>51</v>
       </c>
     </row>
-    <row r="5" spans="1:11" x14ac:dyDescent="0.25">
+    <row r="5">
       <c r="A5" t="s">
         <v>114</v>
       </c>
@@ -2252,16 +2252,16 @@
       <c r="D5" t="s">
         <v>19</v>
       </c>
-      <c r="E5">
-        <v>0</v>
-      </c>
-      <c r="F5" s="1">
+      <c r="E5" t="n">
+        <v>0</v>
+      </c>
+      <c r="F5" s="1" t="n">
         <v>45671</v>
       </c>
-      <c r="G5" s="1">
+      <c r="G5" s="1" t="n">
         <v>45714</v>
       </c>
-      <c r="H5">
+      <c r="H5" t="n">
         <v>44</v>
       </c>
       <c r="I5" t="s">
@@ -2274,7 +2274,7 @@
         <v>72</v>
       </c>
     </row>
-    <row r="6" spans="1:11" x14ac:dyDescent="0.25">
+    <row r="6">
       <c r="A6" t="s">
         <v>114</v>
       </c>
@@ -2287,13 +2287,17 @@
       <c r="D6" t="s">
         <v>32</v>
       </c>
-      <c r="E6">
+      <c r="E6" t="n">
         <v>0</v>
       </c>
       <c r="F6" s="1"/>
       <c r="G6" s="1"/>
-    </row>
-    <row r="7" spans="1:11" x14ac:dyDescent="0.25">
+      <c r="H6"/>
+      <c r="I6"/>
+      <c r="J6"/>
+      <c r="K6"/>
+    </row>
+    <row r="7">
       <c r="A7" t="s">
         <v>114</v>
       </c>
@@ -2306,13 +2310,17 @@
       <c r="D7" t="s">
         <v>32</v>
       </c>
-      <c r="E7">
+      <c r="E7" t="n">
         <v>0</v>
       </c>
       <c r="F7" s="1"/>
       <c r="G7" s="1"/>
-    </row>
-    <row r="8" spans="1:11" x14ac:dyDescent="0.25">
+      <c r="H7"/>
+      <c r="I7"/>
+      <c r="J7"/>
+      <c r="K7"/>
+    </row>
+    <row r="8">
       <c r="A8" t="s">
         <v>114</v>
       </c>
@@ -2325,13 +2333,17 @@
       <c r="D8" t="s">
         <v>71</v>
       </c>
-      <c r="E8">
+      <c r="E8" t="n">
         <v>0</v>
       </c>
       <c r="F8" s="1"/>
       <c r="G8" s="1"/>
-    </row>
-    <row r="9" spans="1:11" x14ac:dyDescent="0.25">
+      <c r="H8"/>
+      <c r="I8"/>
+      <c r="J8"/>
+      <c r="K8"/>
+    </row>
+    <row r="9">
       <c r="A9" t="s">
         <v>114</v>
       </c>
@@ -2344,16 +2356,16 @@
       <c r="D9" t="s">
         <v>32</v>
       </c>
-      <c r="E9">
-        <v>0</v>
-      </c>
-      <c r="F9" s="1">
+      <c r="E9" t="n">
+        <v>0</v>
+      </c>
+      <c r="F9" s="1" t="n">
         <v>45679</v>
       </c>
-      <c r="G9" s="1">
+      <c r="G9" s="1" t="n">
         <v>45792</v>
       </c>
-      <c r="H9">
+      <c r="H9" t="n">
         <v>114</v>
       </c>
       <c r="I9" t="s">
@@ -2366,7 +2378,7 @@
         <v>44</v>
       </c>
     </row>
-    <row r="10" spans="1:11" x14ac:dyDescent="0.25">
+    <row r="10">
       <c r="A10" t="s">
         <v>114</v>
       </c>
@@ -2379,16 +2391,16 @@
       <c r="D10" t="s">
         <v>59</v>
       </c>
-      <c r="E10">
-        <v>0</v>
-      </c>
-      <c r="F10" s="1">
+      <c r="E10" t="n">
+        <v>0</v>
+      </c>
+      <c r="F10" s="1" t="n">
         <v>45679</v>
       </c>
-      <c r="G10" s="1">
+      <c r="G10" s="1" t="n">
         <v>45764</v>
       </c>
-      <c r="H10">
+      <c r="H10" t="n">
         <v>86</v>
       </c>
       <c r="I10" t="s">
@@ -2401,7 +2413,7 @@
         <v>56</v>
       </c>
     </row>
-    <row r="11" spans="1:11" x14ac:dyDescent="0.25">
+    <row r="11">
       <c r="A11" t="s">
         <v>114</v>
       </c>
@@ -2414,16 +2426,16 @@
       <c r="D11" t="s">
         <v>79</v>
       </c>
-      <c r="E11">
+      <c r="E11" t="n">
         <v>1</v>
       </c>
-      <c r="F11" s="1">
+      <c r="F11" s="1" t="n">
         <v>45667</v>
       </c>
-      <c r="G11" s="1">
+      <c r="G11" s="1" t="n">
         <v>45674</v>
       </c>
-      <c r="H11">
+      <c r="H11" t="n">
         <v>8</v>
       </c>
       <c r="I11" t="s">
@@ -2438,16 +2450,16 @@
     </row>
   </sheetData>
   <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
-  <pageSetup paperSize="9" orientation="portrait" horizontalDpi="300" verticalDpi="300"/>
+  <pageSetup paperSize="9" orientation="portrait" horizontalDpi="300" verticalDpi="300" r:id="rId2"/>
 </worksheet>
 </file>
 
 <file path=xl/worksheets/sheet6.xml><?xml version="1.0" encoding="utf-8"?>
-<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{00000000-0001-0000-0500-000000000000}">
-  <dimension ref="A1:K9"/>
-  <sheetFormatPr defaultColWidth="11.42578125" defaultRowHeight="15" x14ac:dyDescent="0.25"/>
+<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:xdr="http://schemas.openxmlformats.org/drawingml/2006/spreadsheetDrawing" xmlns:x14="http://schemas.microsoft.com/office/spreadsheetml/2009/9/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3">
+  <dimension ref="A1"/>
+  <sheetFormatPr defaultRowHeight="15.0" baseColWidth="10"/>
   <sheetData>
-    <row r="1" spans="1:11" x14ac:dyDescent="0.25">
+    <row r="1">
       <c r="A1" t="s">
         <v>0</v>
       </c>
@@ -2482,7 +2494,7 @@
         <v>10</v>
       </c>
     </row>
-    <row r="2" spans="1:11" x14ac:dyDescent="0.25">
+    <row r="2">
       <c r="A2" t="s">
         <v>135</v>
       </c>
@@ -2495,13 +2507,17 @@
       <c r="D2" t="s">
         <v>32</v>
       </c>
-      <c r="E2">
+      <c r="E2" t="n">
         <v>0</v>
       </c>
       <c r="F2" s="1"/>
       <c r="G2" s="1"/>
-    </row>
-    <row r="3" spans="1:11" x14ac:dyDescent="0.25">
+      <c r="H2"/>
+      <c r="I2"/>
+      <c r="J2"/>
+      <c r="K2"/>
+    </row>
+    <row r="3">
       <c r="A3" t="s">
         <v>135</v>
       </c>
@@ -2514,13 +2530,17 @@
       <c r="D3" t="s">
         <v>103</v>
       </c>
-      <c r="E3">
+      <c r="E3" t="n">
         <v>0</v>
       </c>
       <c r="F3" s="1"/>
       <c r="G3" s="1"/>
-    </row>
-    <row r="4" spans="1:11" x14ac:dyDescent="0.25">
+      <c r="H3"/>
+      <c r="I3"/>
+      <c r="J3"/>
+      <c r="K3"/>
+    </row>
+    <row r="4">
       <c r="A4" t="s">
         <v>135</v>
       </c>
@@ -2533,13 +2553,17 @@
       <c r="D4" t="s">
         <v>103</v>
       </c>
-      <c r="E4">
+      <c r="E4" t="n">
         <v>0</v>
       </c>
       <c r="F4" s="1"/>
       <c r="G4" s="1"/>
-    </row>
-    <row r="5" spans="1:11" x14ac:dyDescent="0.25">
+      <c r="H4"/>
+      <c r="I4"/>
+      <c r="J4"/>
+      <c r="K4"/>
+    </row>
+    <row r="5">
       <c r="A5" t="s">
         <v>135</v>
       </c>
@@ -2552,16 +2576,16 @@
       <c r="D5" t="s">
         <v>103</v>
       </c>
-      <c r="E5">
-        <v>0</v>
-      </c>
-      <c r="F5" s="1">
+      <c r="E5" t="n">
+        <v>0</v>
+      </c>
+      <c r="F5" s="1" t="n">
         <v>45714</v>
       </c>
-      <c r="G5" s="1">
+      <c r="G5" s="1" t="n">
         <v>45813</v>
       </c>
-      <c r="H5">
+      <c r="H5" t="n">
         <v>100</v>
       </c>
       <c r="I5" t="s">
@@ -2574,7 +2598,7 @@
         <v>64</v>
       </c>
     </row>
-    <row r="6" spans="1:11" x14ac:dyDescent="0.25">
+    <row r="6">
       <c r="A6" t="s">
         <v>135</v>
       </c>
@@ -2587,16 +2611,16 @@
       <c r="D6" t="s">
         <v>71</v>
       </c>
-      <c r="E6">
-        <v>0</v>
-      </c>
-      <c r="F6" s="1">
+      <c r="E6" t="n">
+        <v>0</v>
+      </c>
+      <c r="F6" s="1" t="n">
         <v>45719</v>
       </c>
-      <c r="G6" s="1">
+      <c r="G6" s="1" t="n">
         <v>45813</v>
       </c>
-      <c r="H6">
+      <c r="H6" t="n">
         <v>95</v>
       </c>
       <c r="I6" t="s">
@@ -2609,7 +2633,7 @@
         <v>72</v>
       </c>
     </row>
-    <row r="7" spans="1:11" x14ac:dyDescent="0.25">
+    <row r="7">
       <c r="A7" t="s">
         <v>135</v>
       </c>
@@ -2622,16 +2646,16 @@
       <c r="D7" t="s">
         <v>59</v>
       </c>
-      <c r="E7">
-        <v>0</v>
-      </c>
-      <c r="F7" s="1">
+      <c r="E7" t="n">
+        <v>0</v>
+      </c>
+      <c r="F7" s="1" t="n">
         <v>45719</v>
       </c>
-      <c r="G7" s="1">
+      <c r="G7" s="1" t="n">
         <v>45813</v>
       </c>
-      <c r="H7">
+      <c r="H7" t="n">
         <v>95</v>
       </c>
       <c r="I7" t="s">
@@ -2644,7 +2668,7 @@
         <v>68</v>
       </c>
     </row>
-    <row r="8" spans="1:11" x14ac:dyDescent="0.25">
+    <row r="8">
       <c r="A8" t="s">
         <v>135</v>
       </c>
@@ -2657,16 +2681,16 @@
       <c r="D8" t="s">
         <v>150</v>
       </c>
-      <c r="E8">
-        <v>0</v>
-      </c>
-      <c r="F8" s="1">
+      <c r="E8" t="n">
+        <v>0</v>
+      </c>
+      <c r="F8" s="1" t="n">
         <v>45720</v>
       </c>
-      <c r="G8" s="1">
+      <c r="G8" s="1" t="n">
         <v>45813</v>
       </c>
-      <c r="H8">
+      <c r="H8" t="n">
         <v>94</v>
       </c>
       <c r="I8" t="s">
@@ -2679,7 +2703,7 @@
         <v>44</v>
       </c>
     </row>
-    <row r="9" spans="1:11" x14ac:dyDescent="0.25">
+    <row r="9">
       <c r="A9" t="s">
         <v>135</v>
       </c>
@@ -2692,24 +2716,28 @@
       <c r="D9" t="s">
         <v>32</v>
       </c>
-      <c r="E9">
+      <c r="E9" t="n">
         <v>0</v>
       </c>
       <c r="F9" s="1"/>
       <c r="G9" s="1"/>
+      <c r="H9"/>
+      <c r="I9"/>
+      <c r="J9"/>
+      <c r="K9"/>
     </row>
   </sheetData>
   <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
-  <pageSetup paperSize="9" orientation="portrait" horizontalDpi="300" verticalDpi="300"/>
+  <pageSetup paperSize="9" orientation="portrait" horizontalDpi="300" verticalDpi="300" r:id="rId2"/>
 </worksheet>
 </file>
 
 <file path=xl/worksheets/sheet7.xml><?xml version="1.0" encoding="utf-8"?>
-<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{00000000-0001-0000-0600-000000000000}">
-  <dimension ref="A1:K10"/>
-  <sheetFormatPr defaultColWidth="11.42578125" defaultRowHeight="15" x14ac:dyDescent="0.25"/>
+<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:xdr="http://schemas.openxmlformats.org/drawingml/2006/spreadsheetDrawing" xmlns:x14="http://schemas.microsoft.com/office/spreadsheetml/2009/9/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3">
+  <dimension ref="A1"/>
+  <sheetFormatPr defaultRowHeight="15.0" baseColWidth="10"/>
   <sheetData>
-    <row r="1" spans="1:11" x14ac:dyDescent="0.25">
+    <row r="1">
       <c r="A1" t="s">
         <v>0</v>
       </c>
@@ -2744,7 +2772,7 @@
         <v>10</v>
       </c>
     </row>
-    <row r="2" spans="1:11" x14ac:dyDescent="0.25">
+    <row r="2">
       <c r="A2" t="s">
         <v>153</v>
       </c>
@@ -2757,13 +2785,17 @@
       <c r="D2" t="s">
         <v>156</v>
       </c>
-      <c r="E2">
+      <c r="E2" t="n">
         <v>0</v>
       </c>
       <c r="F2" s="1"/>
       <c r="G2" s="1"/>
-    </row>
-    <row r="3" spans="1:11" x14ac:dyDescent="0.25">
+      <c r="H2"/>
+      <c r="I2"/>
+      <c r="J2"/>
+      <c r="K2"/>
+    </row>
+    <row r="3">
       <c r="A3" t="s">
         <v>153</v>
       </c>
@@ -2776,13 +2808,17 @@
       <c r="D3" t="s">
         <v>50</v>
       </c>
-      <c r="E3">
+      <c r="E3" t="n">
         <v>0</v>
       </c>
       <c r="F3" s="1"/>
       <c r="G3" s="1"/>
-    </row>
-    <row r="4" spans="1:11" x14ac:dyDescent="0.25">
+      <c r="H3"/>
+      <c r="I3"/>
+      <c r="J3"/>
+      <c r="K3"/>
+    </row>
+    <row r="4">
       <c r="A4" t="s">
         <v>153</v>
       </c>
@@ -2795,13 +2831,17 @@
       <c r="D4" t="s">
         <v>32</v>
       </c>
-      <c r="E4">
+      <c r="E4" t="n">
         <v>0</v>
       </c>
       <c r="F4" s="1"/>
       <c r="G4" s="1"/>
-    </row>
-    <row r="5" spans="1:11" x14ac:dyDescent="0.25">
+      <c r="H4"/>
+      <c r="I4"/>
+      <c r="J4"/>
+      <c r="K4"/>
+    </row>
+    <row r="5">
       <c r="A5" t="s">
         <v>153</v>
       </c>
@@ -2814,13 +2854,17 @@
       <c r="D5" t="s">
         <v>19</v>
       </c>
-      <c r="E5">
+      <c r="E5" t="n">
         <v>0</v>
       </c>
       <c r="F5" s="1"/>
       <c r="G5" s="1"/>
-    </row>
-    <row r="6" spans="1:11" x14ac:dyDescent="0.25">
+      <c r="H5"/>
+      <c r="I5"/>
+      <c r="J5"/>
+      <c r="K5"/>
+    </row>
+    <row r="6">
       <c r="A6" t="s">
         <v>153</v>
       </c>
@@ -2833,13 +2877,17 @@
       <c r="D6" t="s">
         <v>32</v>
       </c>
-      <c r="E6">
+      <c r="E6" t="n">
         <v>0</v>
       </c>
       <c r="F6" s="1"/>
       <c r="G6" s="1"/>
-    </row>
-    <row r="7" spans="1:11" x14ac:dyDescent="0.25">
+      <c r="H6"/>
+      <c r="I6"/>
+      <c r="J6"/>
+      <c r="K6"/>
+    </row>
+    <row r="7">
       <c r="A7" t="s">
         <v>153</v>
       </c>
@@ -2852,16 +2900,16 @@
       <c r="D7" t="s">
         <v>167</v>
       </c>
-      <c r="E7">
-        <v>0</v>
-      </c>
-      <c r="F7" s="1">
+      <c r="E7" t="n">
+        <v>0</v>
+      </c>
+      <c r="F7" s="1" t="n">
         <v>45747</v>
       </c>
-      <c r="G7" s="1">
+      <c r="G7" s="1" t="n">
         <v>45813</v>
       </c>
-      <c r="H7">
+      <c r="H7" t="n">
         <v>67</v>
       </c>
       <c r="I7" t="s">
@@ -2874,7 +2922,7 @@
         <v>56</v>
       </c>
     </row>
-    <row r="8" spans="1:11" x14ac:dyDescent="0.25">
+    <row r="8">
       <c r="A8" t="s">
         <v>153</v>
       </c>
@@ -2887,13 +2935,29 @@
       <c r="D8" t="s">
         <v>32</v>
       </c>
-      <c r="E8">
-        <v>0</v>
-      </c>
-      <c r="F8" s="1"/>
-      <c r="G8" s="1"/>
-    </row>
-    <row r="9" spans="1:11" x14ac:dyDescent="0.25">
+      <c r="E8" t="n">
+        <v>0</v>
+      </c>
+      <c r="F8" s="1" t="n">
+        <v>45747</v>
+      </c>
+      <c r="G8" s="1" t="n">
+        <v>45820</v>
+      </c>
+      <c r="H8" t="n">
+        <v>74</v>
+      </c>
+      <c r="I8" t="s">
+        <v>42</v>
+      </c>
+      <c r="J8" t="s">
+        <v>43</v>
+      </c>
+      <c r="K8" t="s">
+        <v>64</v>
+      </c>
+    </row>
+    <row r="9">
       <c r="A9" t="s">
         <v>153</v>
       </c>
@@ -2906,13 +2970,17 @@
       <c r="D9" t="s">
         <v>59</v>
       </c>
-      <c r="E9">
+      <c r="E9" t="n">
         <v>0</v>
       </c>
       <c r="F9" s="1"/>
       <c r="G9" s="1"/>
-    </row>
-    <row r="10" spans="1:11" x14ac:dyDescent="0.25">
+      <c r="H9"/>
+      <c r="I9"/>
+      <c r="J9"/>
+      <c r="K9"/>
+    </row>
+    <row r="10">
       <c r="A10" t="s">
         <v>153</v>
       </c>
@@ -2925,24 +2993,28 @@
       <c r="D10" t="s">
         <v>50</v>
       </c>
-      <c r="E10">
+      <c r="E10" t="n">
         <v>0</v>
       </c>
       <c r="F10" s="1"/>
       <c r="G10" s="1"/>
+      <c r="H10"/>
+      <c r="I10"/>
+      <c r="J10"/>
+      <c r="K10"/>
     </row>
   </sheetData>
   <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
-  <pageSetup paperSize="9" orientation="portrait" horizontalDpi="300" verticalDpi="300"/>
+  <pageSetup paperSize="9" orientation="portrait" horizontalDpi="300" verticalDpi="300" r:id="rId2"/>
 </worksheet>
 </file>
 
 <file path=xl/worksheets/sheet8.xml><?xml version="1.0" encoding="utf-8"?>
-<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{00000000-0001-0000-0700-000000000000}">
-  <dimension ref="A1:K11"/>
-  <sheetFormatPr defaultColWidth="11.42578125" defaultRowHeight="15" x14ac:dyDescent="0.25"/>
+<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:xdr="http://schemas.openxmlformats.org/drawingml/2006/spreadsheetDrawing" xmlns:x14="http://schemas.microsoft.com/office/spreadsheetml/2009/9/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3">
+  <dimension ref="A1"/>
+  <sheetFormatPr defaultRowHeight="15.0" baseColWidth="10"/>
   <sheetData>
-    <row r="1" spans="1:11" x14ac:dyDescent="0.25">
+    <row r="1">
       <c r="A1" t="s">
         <v>0</v>
       </c>
@@ -2977,7 +3049,7 @@
         <v>10</v>
       </c>
     </row>
-    <row r="2" spans="1:11" x14ac:dyDescent="0.25">
+    <row r="2">
       <c r="A2" t="s">
         <v>174</v>
       </c>
@@ -2990,13 +3062,17 @@
       <c r="D2" t="s">
         <v>32</v>
       </c>
-      <c r="E2">
+      <c r="E2" t="n">
         <v>0</v>
       </c>
       <c r="F2" s="1"/>
       <c r="G2" s="1"/>
-    </row>
-    <row r="3" spans="1:11" x14ac:dyDescent="0.25">
+      <c r="H2"/>
+      <c r="I2"/>
+      <c r="J2"/>
+      <c r="K2"/>
+    </row>
+    <row r="3">
       <c r="A3" t="s">
         <v>174</v>
       </c>
@@ -3009,13 +3085,29 @@
       <c r="D3" t="s">
         <v>50</v>
       </c>
-      <c r="E3">
-        <v>0</v>
-      </c>
-      <c r="F3" s="1"/>
-      <c r="G3" s="1"/>
-    </row>
-    <row r="4" spans="1:11" x14ac:dyDescent="0.25">
+      <c r="E3" t="n">
+        <v>0</v>
+      </c>
+      <c r="F3" s="1" t="n">
+        <v>45768</v>
+      </c>
+      <c r="G3" s="1" t="n">
+        <v>45820</v>
+      </c>
+      <c r="H3" t="n">
+        <v>53</v>
+      </c>
+      <c r="I3" t="s">
+        <v>37</v>
+      </c>
+      <c r="J3" t="s">
+        <v>98</v>
+      </c>
+      <c r="K3" t="s">
+        <v>56</v>
+      </c>
+    </row>
+    <row r="4">
       <c r="A4" t="s">
         <v>174</v>
       </c>
@@ -3028,13 +3120,17 @@
       <c r="D4" t="s">
         <v>50</v>
       </c>
-      <c r="E4">
+      <c r="E4" t="n">
         <v>0</v>
       </c>
       <c r="F4" s="1"/>
       <c r="G4" s="1"/>
-    </row>
-    <row r="5" spans="1:11" x14ac:dyDescent="0.25">
+      <c r="H4"/>
+      <c r="I4"/>
+      <c r="J4"/>
+      <c r="K4"/>
+    </row>
+    <row r="5">
       <c r="A5" t="s">
         <v>174</v>
       </c>
@@ -3047,13 +3143,29 @@
       <c r="D5" t="s">
         <v>106</v>
       </c>
-      <c r="E5">
-        <v>0</v>
-      </c>
-      <c r="F5" s="1"/>
-      <c r="G5" s="1"/>
-    </row>
-    <row r="6" spans="1:11" x14ac:dyDescent="0.25">
+      <c r="E5" t="n">
+        <v>0</v>
+      </c>
+      <c r="F5" s="1" t="n">
+        <v>45769</v>
+      </c>
+      <c r="G5" s="1" t="n">
+        <v>45820</v>
+      </c>
+      <c r="H5" t="n">
+        <v>52</v>
+      </c>
+      <c r="I5" t="s">
+        <v>37</v>
+      </c>
+      <c r="J5" t="s">
+        <v>98</v>
+      </c>
+      <c r="K5" t="s">
+        <v>61</v>
+      </c>
+    </row>
+    <row r="6">
       <c r="A6" t="s">
         <v>174</v>
       </c>
@@ -3066,13 +3178,17 @@
       <c r="D6" t="s">
         <v>79</v>
       </c>
-      <c r="E6">
+      <c r="E6" t="n">
         <v>0</v>
       </c>
       <c r="F6" s="1"/>
       <c r="G6" s="1"/>
-    </row>
-    <row r="7" spans="1:11" x14ac:dyDescent="0.25">
+      <c r="H6"/>
+      <c r="I6"/>
+      <c r="J6"/>
+      <c r="K6"/>
+    </row>
+    <row r="7">
       <c r="A7" t="s">
         <v>174</v>
       </c>
@@ -3085,13 +3201,29 @@
       <c r="D7" t="s">
         <v>41</v>
       </c>
-      <c r="E7">
-        <v>0</v>
-      </c>
-      <c r="F7" s="1"/>
-      <c r="G7" s="1"/>
-    </row>
-    <row r="8" spans="1:11" x14ac:dyDescent="0.25">
+      <c r="E7" t="n">
+        <v>0</v>
+      </c>
+      <c r="F7" s="1" t="n">
+        <v>45775</v>
+      </c>
+      <c r="G7" s="1" t="n">
+        <v>45820</v>
+      </c>
+      <c r="H7" t="n">
+        <v>46</v>
+      </c>
+      <c r="I7" t="s">
+        <v>15</v>
+      </c>
+      <c r="J7" t="s">
+        <v>43</v>
+      </c>
+      <c r="K7" t="s">
+        <v>51</v>
+      </c>
+    </row>
+    <row r="8">
       <c r="A8" t="s">
         <v>174</v>
       </c>
@@ -3104,13 +3236,29 @@
       <c r="D8" t="s">
         <v>67</v>
       </c>
-      <c r="E8">
-        <v>0</v>
-      </c>
-      <c r="F8" s="1"/>
-      <c r="G8" s="1"/>
-    </row>
-    <row r="9" spans="1:11" x14ac:dyDescent="0.25">
+      <c r="E8" t="n">
+        <v>0</v>
+      </c>
+      <c r="F8" s="1" t="n">
+        <v>45775</v>
+      </c>
+      <c r="G8" s="1" t="n">
+        <v>45820</v>
+      </c>
+      <c r="H8" t="n">
+        <v>46</v>
+      </c>
+      <c r="I8" t="s">
+        <v>37</v>
+      </c>
+      <c r="J8" t="s">
+        <v>43</v>
+      </c>
+      <c r="K8" t="s">
+        <v>68</v>
+      </c>
+    </row>
+    <row r="9">
       <c r="A9" t="s">
         <v>174</v>
       </c>
@@ -3123,13 +3271,29 @@
       <c r="D9" t="s">
         <v>14</v>
       </c>
-      <c r="E9">
-        <v>0</v>
-      </c>
-      <c r="F9" s="1"/>
-      <c r="G9" s="1"/>
-    </row>
-    <row r="10" spans="1:11" x14ac:dyDescent="0.25">
+      <c r="E9" t="n">
+        <v>0</v>
+      </c>
+      <c r="F9" s="1" t="n">
+        <v>45776</v>
+      </c>
+      <c r="G9" s="1" t="n">
+        <v>45820</v>
+      </c>
+      <c r="H9" t="n">
+        <v>45</v>
+      </c>
+      <c r="I9" t="s">
+        <v>15</v>
+      </c>
+      <c r="J9" t="s">
+        <v>43</v>
+      </c>
+      <c r="K9" t="s">
+        <v>47</v>
+      </c>
+    </row>
+    <row r="10">
       <c r="A10" t="s">
         <v>174</v>
       </c>
@@ -3142,16 +3306,16 @@
       <c r="D10" t="s">
         <v>71</v>
       </c>
-      <c r="E10">
-        <v>0</v>
-      </c>
-      <c r="F10" s="1">
+      <c r="E10" t="n">
+        <v>0</v>
+      </c>
+      <c r="F10" s="1" t="n">
         <v>45776</v>
       </c>
-      <c r="G10" s="1">
+      <c r="G10" s="1" t="n">
         <v>45813</v>
       </c>
-      <c r="H10">
+      <c r="H10" t="n">
         <v>38</v>
       </c>
       <c r="I10" t="s">
@@ -3164,7 +3328,7 @@
         <v>16</v>
       </c>
     </row>
-    <row r="11" spans="1:11" x14ac:dyDescent="0.25">
+    <row r="11">
       <c r="A11" t="s">
         <v>174</v>
       </c>
@@ -3177,16 +3341,16 @@
       <c r="D11" t="s">
         <v>195</v>
       </c>
-      <c r="E11">
+      <c r="E11" t="n">
         <v>1</v>
       </c>
-      <c r="F11" s="1">
+      <c r="F11" s="1" t="n">
         <v>45777</v>
       </c>
-      <c r="G11" s="1">
+      <c r="G11" s="1" t="n">
         <v>45799</v>
       </c>
-      <c r="H11">
+      <c r="H11" t="n">
         <v>23</v>
       </c>
       <c r="I11" t="s">
@@ -3201,16 +3365,16 @@
     </row>
   </sheetData>
   <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
-  <pageSetup paperSize="9" orientation="portrait" horizontalDpi="300" verticalDpi="300"/>
+  <pageSetup paperSize="9" orientation="portrait" horizontalDpi="300" verticalDpi="300" r:id="rId2"/>
 </worksheet>
 </file>
 
 <file path=xl/worksheets/sheet9.xml><?xml version="1.0" encoding="utf-8"?>
-<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{00000000-0001-0000-0800-000000000000}">
-  <dimension ref="A1:K2"/>
-  <sheetFormatPr defaultColWidth="11.42578125" defaultRowHeight="15" x14ac:dyDescent="0.25"/>
+<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:xdr="http://schemas.openxmlformats.org/drawingml/2006/spreadsheetDrawing" xmlns:x14="http://schemas.microsoft.com/office/spreadsheetml/2009/9/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3">
+  <dimension ref="A1"/>
+  <sheetFormatPr defaultRowHeight="15.0" baseColWidth="10"/>
   <sheetData>
-    <row r="1" spans="1:11" x14ac:dyDescent="0.25">
+    <row r="1">
       <c r="A1" t="s">
         <v>0</v>
       </c>
@@ -3245,7 +3409,7 @@
         <v>10</v>
       </c>
     </row>
-    <row r="2" spans="1:11" x14ac:dyDescent="0.25">
+    <row r="2">
       <c r="A2" t="s">
         <v>197</v>
       </c>
@@ -3258,14 +3422,18 @@
       <c r="D2" t="s">
         <v>50</v>
       </c>
-      <c r="E2">
+      <c r="E2" t="n">
         <v>1</v>
       </c>
       <c r="F2" s="1"/>
       <c r="G2" s="1"/>
+      <c r="H2"/>
+      <c r="I2"/>
+      <c r="J2"/>
+      <c r="K2"/>
     </row>
   </sheetData>
   <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
-  <pageSetup paperSize="9" orientation="portrait" horizontalDpi="300" verticalDpi="300"/>
+  <pageSetup paperSize="9" orientation="portrait" horizontalDpi="300" verticalDpi="300" r:id="rId2"/>
 </worksheet>
 </file>
--- a/Stat Reviews/OT24_StatReview/scotusblog_replication/data/term_index.xlsx
+++ b/Stat Reviews/OT24_StatReview/scotusblog_replication/data/term_index.xlsx
@@ -20,7 +20,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="200" uniqueCount="200">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="202" uniqueCount="202">
   <si>
     <t xml:space="preserve">sitting</t>
   </si>
@@ -109,7 +109,7 @@
     <t xml:space="preserve">DCDC</t>
   </si>
   <si>
-    <t xml:space="preserve">(5-4)*</t>
+    <t xml:space="preserve">(6-3)*</t>
   </si>
   <si>
     <t xml:space="preserve">24A1007</t>
@@ -379,6 +379,9 @@
     <t xml:space="preserve">Stanley</t>
   </si>
   <si>
+    <t xml:space="preserve">(8-1)*</t>
+  </si>
+  <si>
     <t xml:space="preserve">23-1095</t>
   </si>
   <si>
@@ -440,6 +443,9 @@
   </si>
   <si>
     <t xml:space="preserve">Esteras</t>
+  </si>
+  <si>
+    <t xml:space="preserve">(7-2)*</t>
   </si>
   <si>
     <t xml:space="preserve">23-1324</t>
@@ -1965,12 +1971,24 @@
       <c r="E5" t="n">
         <v>1</v>
       </c>
-      <c r="F5" s="1"/>
-      <c r="G5" s="1"/>
-      <c r="H5"/>
-      <c r="I5"/>
-      <c r="J5"/>
-      <c r="K5"/>
+      <c r="F5" s="1" t="n">
+        <v>45630</v>
+      </c>
+      <c r="G5" s="1" t="n">
+        <v>45826</v>
+      </c>
+      <c r="H5" t="n">
+        <v>197</v>
+      </c>
+      <c r="I5" t="s">
+        <v>42</v>
+      </c>
+      <c r="J5" t="s">
+        <v>87</v>
+      </c>
+      <c r="K5" t="s">
+        <v>51</v>
+      </c>
     </row>
     <row r="6">
       <c r="A6" t="s">
@@ -2197,22 +2215,34 @@
       <c r="E3" t="n">
         <v>0</v>
       </c>
-      <c r="F3" s="1"/>
-      <c r="G3" s="1"/>
-      <c r="H3"/>
-      <c r="I3"/>
-      <c r="J3"/>
-      <c r="K3"/>
+      <c r="F3" s="1" t="n">
+        <v>45670</v>
+      </c>
+      <c r="G3" s="1" t="n">
+        <v>45828</v>
+      </c>
+      <c r="H3" t="n">
+        <v>159</v>
+      </c>
+      <c r="I3" t="s">
+        <v>42</v>
+      </c>
+      <c r="J3" t="s">
+        <v>119</v>
+      </c>
+      <c r="K3" t="s">
+        <v>47</v>
+      </c>
     </row>
     <row r="4">
       <c r="A4" t="s">
         <v>114</v>
       </c>
       <c r="B4" t="s">
-        <v>119</v>
+        <v>120</v>
       </c>
       <c r="C4" t="s">
-        <v>120</v>
+        <v>121</v>
       </c>
       <c r="D4" t="s">
         <v>76</v>
@@ -2244,10 +2274,10 @@
         <v>114</v>
       </c>
       <c r="B5" t="s">
-        <v>121</v>
+        <v>122</v>
       </c>
       <c r="C5" t="s">
-        <v>122</v>
+        <v>123</v>
       </c>
       <c r="D5" t="s">
         <v>19</v>
@@ -2279,10 +2309,10 @@
         <v>114</v>
       </c>
       <c r="B6" t="s">
-        <v>123</v>
+        <v>124</v>
       </c>
       <c r="C6" t="s">
-        <v>124</v>
+        <v>125</v>
       </c>
       <c r="D6" t="s">
         <v>32</v>
@@ -2302,10 +2332,10 @@
         <v>114</v>
       </c>
       <c r="B7" t="s">
-        <v>125</v>
+        <v>126</v>
       </c>
       <c r="C7" t="s">
-        <v>126</v>
+        <v>127</v>
       </c>
       <c r="D7" t="s">
         <v>32</v>
@@ -2313,22 +2343,34 @@
       <c r="E7" t="n">
         <v>0</v>
       </c>
-      <c r="F7" s="1"/>
-      <c r="G7" s="1"/>
-      <c r="H7"/>
-      <c r="I7"/>
-      <c r="J7"/>
-      <c r="K7"/>
+      <c r="F7" s="1" t="n">
+        <v>45678</v>
+      </c>
+      <c r="G7" s="1" t="n">
+        <v>45828</v>
+      </c>
+      <c r="H7" t="n">
+        <v>151</v>
+      </c>
+      <c r="I7" t="s">
+        <v>60</v>
+      </c>
+      <c r="J7" t="s">
+        <v>20</v>
+      </c>
+      <c r="K7" t="s">
+        <v>61</v>
+      </c>
     </row>
     <row r="8">
       <c r="A8" t="s">
         <v>114</v>
       </c>
       <c r="B8" t="s">
-        <v>127</v>
+        <v>128</v>
       </c>
       <c r="C8" t="s">
-        <v>128</v>
+        <v>129</v>
       </c>
       <c r="D8" t="s">
         <v>71</v>
@@ -2336,22 +2378,34 @@
       <c r="E8" t="n">
         <v>0</v>
       </c>
-      <c r="F8" s="1"/>
-      <c r="G8" s="1"/>
-      <c r="H8"/>
-      <c r="I8"/>
-      <c r="J8"/>
-      <c r="K8"/>
+      <c r="F8" s="1" t="n">
+        <v>45678</v>
+      </c>
+      <c r="G8" s="1" t="n">
+        <v>45828</v>
+      </c>
+      <c r="H8" t="n">
+        <v>151</v>
+      </c>
+      <c r="I8" t="s">
+        <v>37</v>
+      </c>
+      <c r="J8" t="s">
+        <v>87</v>
+      </c>
+      <c r="K8" t="s">
+        <v>38</v>
+      </c>
     </row>
     <row r="9">
       <c r="A9" t="s">
         <v>114</v>
       </c>
       <c r="B9" t="s">
-        <v>129</v>
+        <v>130</v>
       </c>
       <c r="C9" t="s">
-        <v>130</v>
+        <v>131</v>
       </c>
       <c r="D9" t="s">
         <v>32</v>
@@ -2383,10 +2437,10 @@
         <v>114</v>
       </c>
       <c r="B10" t="s">
-        <v>131</v>
+        <v>132</v>
       </c>
       <c r="C10" t="s">
-        <v>132</v>
+        <v>133</v>
       </c>
       <c r="D10" t="s">
         <v>59</v>
@@ -2418,10 +2472,10 @@
         <v>114</v>
       </c>
       <c r="B11" t="s">
-        <v>133</v>
+        <v>134</v>
       </c>
       <c r="C11" t="s">
-        <v>134</v>
+        <v>135</v>
       </c>
       <c r="D11" t="s">
         <v>79</v>
@@ -2496,13 +2550,13 @@
     </row>
     <row r="2">
       <c r="A2" t="s">
-        <v>135</v>
+        <v>136</v>
       </c>
       <c r="B2" t="s">
-        <v>136</v>
+        <v>137</v>
       </c>
       <c r="C2" t="s">
-        <v>137</v>
+        <v>138</v>
       </c>
       <c r="D2" t="s">
         <v>32</v>
@@ -2519,13 +2573,13 @@
     </row>
     <row r="3">
       <c r="A3" t="s">
-        <v>135</v>
+        <v>136</v>
       </c>
       <c r="B3" t="s">
-        <v>138</v>
+        <v>139</v>
       </c>
       <c r="C3" t="s">
-        <v>139</v>
+        <v>140</v>
       </c>
       <c r="D3" t="s">
         <v>103</v>
@@ -2533,22 +2587,34 @@
       <c r="E3" t="n">
         <v>0</v>
       </c>
-      <c r="F3" s="1"/>
-      <c r="G3" s="1"/>
-      <c r="H3"/>
-      <c r="I3"/>
-      <c r="J3"/>
-      <c r="K3"/>
+      <c r="F3" s="1" t="n">
+        <v>45713</v>
+      </c>
+      <c r="G3" s="1" t="n">
+        <v>45828</v>
+      </c>
+      <c r="H3" t="n">
+        <v>116</v>
+      </c>
+      <c r="I3" t="s">
+        <v>15</v>
+      </c>
+      <c r="J3" t="s">
+        <v>141</v>
+      </c>
+      <c r="K3" t="s">
+        <v>61</v>
+      </c>
     </row>
     <row r="4">
       <c r="A4" t="s">
-        <v>135</v>
+        <v>136</v>
       </c>
       <c r="B4" t="s">
-        <v>140</v>
+        <v>142</v>
       </c>
       <c r="C4" t="s">
-        <v>141</v>
+        <v>143</v>
       </c>
       <c r="D4" t="s">
         <v>103</v>
@@ -2556,22 +2622,34 @@
       <c r="E4" t="n">
         <v>0</v>
       </c>
-      <c r="F4" s="1"/>
-      <c r="G4" s="1"/>
-      <c r="H4"/>
-      <c r="I4"/>
-      <c r="J4"/>
-      <c r="K4"/>
+      <c r="F4" s="1" t="n">
+        <v>45713</v>
+      </c>
+      <c r="G4" s="1" t="n">
+        <v>45826</v>
+      </c>
+      <c r="H4" t="n">
+        <v>114</v>
+      </c>
+      <c r="I4" t="s">
+        <v>42</v>
+      </c>
+      <c r="J4" t="s">
+        <v>25</v>
+      </c>
+      <c r="K4" t="s">
+        <v>51</v>
+      </c>
     </row>
     <row r="5">
       <c r="A5" t="s">
-        <v>135</v>
+        <v>136</v>
       </c>
       <c r="B5" t="s">
-        <v>142</v>
+        <v>144</v>
       </c>
       <c r="C5" t="s">
-        <v>143</v>
+        <v>145</v>
       </c>
       <c r="D5" t="s">
         <v>103</v>
@@ -2600,13 +2678,13 @@
     </row>
     <row r="6">
       <c r="A6" t="s">
-        <v>135</v>
+        <v>136</v>
       </c>
       <c r="B6" t="s">
-        <v>144</v>
+        <v>146</v>
       </c>
       <c r="C6" t="s">
-        <v>145</v>
+        <v>147</v>
       </c>
       <c r="D6" t="s">
         <v>71</v>
@@ -2635,13 +2713,13 @@
     </row>
     <row r="7">
       <c r="A7" t="s">
-        <v>135</v>
+        <v>136</v>
       </c>
       <c r="B7" t="s">
-        <v>146</v>
+        <v>148</v>
       </c>
       <c r="C7" t="s">
-        <v>147</v>
+        <v>149</v>
       </c>
       <c r="D7" t="s">
         <v>59</v>
@@ -2670,16 +2748,16 @@
     </row>
     <row r="8">
       <c r="A8" t="s">
-        <v>135</v>
+        <v>136</v>
       </c>
       <c r="B8" t="s">
-        <v>148</v>
+        <v>150</v>
       </c>
       <c r="C8" t="s">
-        <v>149</v>
+        <v>151</v>
       </c>
       <c r="D8" t="s">
-        <v>150</v>
+        <v>152</v>
       </c>
       <c r="E8" t="n">
         <v>0</v>
@@ -2705,13 +2783,13 @@
     </row>
     <row r="9">
       <c r="A9" t="s">
-        <v>135</v>
+        <v>136</v>
       </c>
       <c r="B9" t="s">
-        <v>151</v>
+        <v>153</v>
       </c>
       <c r="C9" t="s">
-        <v>152</v>
+        <v>154</v>
       </c>
       <c r="D9" t="s">
         <v>32</v>
@@ -2719,12 +2797,24 @@
       <c r="E9" t="n">
         <v>0</v>
       </c>
-      <c r="F9" s="1"/>
-      <c r="G9" s="1"/>
-      <c r="H9"/>
-      <c r="I9"/>
-      <c r="J9"/>
-      <c r="K9"/>
+      <c r="F9" s="1" t="n">
+        <v>45721</v>
+      </c>
+      <c r="G9" s="1" t="n">
+        <v>45826</v>
+      </c>
+      <c r="H9" t="n">
+        <v>106</v>
+      </c>
+      <c r="I9" t="s">
+        <v>37</v>
+      </c>
+      <c r="J9" t="s">
+        <v>87</v>
+      </c>
+      <c r="K9" t="s">
+        <v>38</v>
+      </c>
     </row>
   </sheetData>
   <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
@@ -2774,16 +2864,16 @@
     </row>
     <row r="2">
       <c r="A2" t="s">
-        <v>153</v>
+        <v>155</v>
       </c>
       <c r="B2" t="s">
-        <v>154</v>
+        <v>156</v>
       </c>
       <c r="C2" t="s">
-        <v>155</v>
+        <v>157</v>
       </c>
       <c r="D2" t="s">
-        <v>156</v>
+        <v>158</v>
       </c>
       <c r="E2" t="n">
         <v>0</v>
@@ -2797,13 +2887,13 @@
     </row>
     <row r="3">
       <c r="A3" t="s">
-        <v>153</v>
+        <v>155</v>
       </c>
       <c r="B3" t="s">
-        <v>157</v>
+        <v>159</v>
       </c>
       <c r="C3" t="s">
-        <v>158</v>
+        <v>160</v>
       </c>
       <c r="D3" t="s">
         <v>50</v>
@@ -2820,13 +2910,13 @@
     </row>
     <row r="4">
       <c r="A4" t="s">
-        <v>153</v>
+        <v>155</v>
       </c>
       <c r="B4" t="s">
-        <v>159</v>
+        <v>161</v>
       </c>
       <c r="C4" t="s">
-        <v>160</v>
+        <v>162</v>
       </c>
       <c r="D4" t="s">
         <v>32</v>
@@ -2834,22 +2924,34 @@
       <c r="E4" t="n">
         <v>0</v>
       </c>
-      <c r="F4" s="1"/>
-      <c r="G4" s="1"/>
-      <c r="H4"/>
-      <c r="I4"/>
-      <c r="J4"/>
-      <c r="K4"/>
+      <c r="F4" s="1" t="n">
+        <v>45741</v>
+      </c>
+      <c r="G4" s="1" t="n">
+        <v>45826</v>
+      </c>
+      <c r="H4" t="n">
+        <v>86</v>
+      </c>
+      <c r="I4" t="s">
+        <v>15</v>
+      </c>
+      <c r="J4" t="s">
+        <v>20</v>
+      </c>
+      <c r="K4" t="s">
+        <v>68</v>
+      </c>
     </row>
     <row r="5">
       <c r="A5" t="s">
-        <v>153</v>
+        <v>155</v>
       </c>
       <c r="B5" t="s">
-        <v>161</v>
+        <v>163</v>
       </c>
       <c r="C5" t="s">
-        <v>162</v>
+        <v>164</v>
       </c>
       <c r="D5" t="s">
         <v>19</v>
@@ -2857,22 +2959,34 @@
       <c r="E5" t="n">
         <v>0</v>
       </c>
-      <c r="F5" s="1"/>
-      <c r="G5" s="1"/>
-      <c r="H5"/>
-      <c r="I5"/>
-      <c r="J5"/>
-      <c r="K5"/>
+      <c r="F5" s="1" t="n">
+        <v>45741</v>
+      </c>
+      <c r="G5" s="1" t="n">
+        <v>45826</v>
+      </c>
+      <c r="H5" t="n">
+        <v>86</v>
+      </c>
+      <c r="I5" t="s">
+        <v>37</v>
+      </c>
+      <c r="J5" t="s">
+        <v>111</v>
+      </c>
+      <c r="K5" t="s">
+        <v>68</v>
+      </c>
     </row>
     <row r="6">
       <c r="A6" t="s">
-        <v>153</v>
+        <v>155</v>
       </c>
       <c r="B6" t="s">
-        <v>163</v>
+        <v>165</v>
       </c>
       <c r="C6" t="s">
-        <v>164</v>
+        <v>166</v>
       </c>
       <c r="D6" t="s">
         <v>32</v>
@@ -2889,16 +3003,16 @@
     </row>
     <row r="7">
       <c r="A7" t="s">
-        <v>153</v>
+        <v>155</v>
       </c>
       <c r="B7" t="s">
-        <v>165</v>
+        <v>167</v>
       </c>
       <c r="C7" t="s">
-        <v>166</v>
+        <v>168</v>
       </c>
       <c r="D7" t="s">
-        <v>167</v>
+        <v>169</v>
       </c>
       <c r="E7" t="n">
         <v>0</v>
@@ -2924,13 +3038,13 @@
     </row>
     <row r="8">
       <c r="A8" t="s">
-        <v>153</v>
+        <v>155</v>
       </c>
       <c r="B8" t="s">
-        <v>168</v>
+        <v>170</v>
       </c>
       <c r="C8" t="s">
-        <v>169</v>
+        <v>171</v>
       </c>
       <c r="D8" t="s">
         <v>32</v>
@@ -2959,13 +3073,13 @@
     </row>
     <row r="9">
       <c r="A9" t="s">
-        <v>153</v>
+        <v>155</v>
       </c>
       <c r="B9" t="s">
-        <v>170</v>
+        <v>172</v>
       </c>
       <c r="C9" t="s">
-        <v>171</v>
+        <v>173</v>
       </c>
       <c r="D9" t="s">
         <v>59</v>
@@ -2973,22 +3087,34 @@
       <c r="E9" t="n">
         <v>0</v>
       </c>
-      <c r="F9" s="1"/>
-      <c r="G9" s="1"/>
-      <c r="H9"/>
-      <c r="I9"/>
-      <c r="J9"/>
-      <c r="K9"/>
+      <c r="F9" s="1" t="n">
+        <v>45748</v>
+      </c>
+      <c r="G9" s="1" t="n">
+        <v>45828</v>
+      </c>
+      <c r="H9" t="n">
+        <v>81</v>
+      </c>
+      <c r="I9" t="s">
+        <v>37</v>
+      </c>
+      <c r="J9" t="s">
+        <v>43</v>
+      </c>
+      <c r="K9" t="s">
+        <v>51</v>
+      </c>
     </row>
     <row r="10">
       <c r="A10" t="s">
-        <v>153</v>
+        <v>155</v>
       </c>
       <c r="B10" t="s">
-        <v>172</v>
+        <v>174</v>
       </c>
       <c r="C10" t="s">
-        <v>173</v>
+        <v>175</v>
       </c>
       <c r="D10" t="s">
         <v>50</v>
@@ -3051,13 +3177,13 @@
     </row>
     <row r="2">
       <c r="A2" t="s">
-        <v>174</v>
+        <v>176</v>
       </c>
       <c r="B2" t="s">
-        <v>175</v>
+        <v>177</v>
       </c>
       <c r="C2" t="s">
-        <v>176</v>
+        <v>178</v>
       </c>
       <c r="D2" t="s">
         <v>32</v>
@@ -3074,13 +3200,13 @@
     </row>
     <row r="3">
       <c r="A3" t="s">
-        <v>174</v>
+        <v>176</v>
       </c>
       <c r="B3" t="s">
-        <v>177</v>
+        <v>179</v>
       </c>
       <c r="C3" t="s">
-        <v>178</v>
+        <v>180</v>
       </c>
       <c r="D3" t="s">
         <v>50</v>
@@ -3109,13 +3235,13 @@
     </row>
     <row r="4">
       <c r="A4" t="s">
-        <v>174</v>
+        <v>176</v>
       </c>
       <c r="B4" t="s">
-        <v>179</v>
+        <v>181</v>
       </c>
       <c r="C4" t="s">
-        <v>180</v>
+        <v>182</v>
       </c>
       <c r="D4" t="s">
         <v>50</v>
@@ -3132,13 +3258,13 @@
     </row>
     <row r="5">
       <c r="A5" t="s">
-        <v>174</v>
+        <v>176</v>
       </c>
       <c r="B5" t="s">
-        <v>181</v>
+        <v>183</v>
       </c>
       <c r="C5" t="s">
-        <v>182</v>
+        <v>184</v>
       </c>
       <c r="D5" t="s">
         <v>106</v>
@@ -3167,13 +3293,13 @@
     </row>
     <row r="6">
       <c r="A6" t="s">
-        <v>174</v>
+        <v>176</v>
       </c>
       <c r="B6" t="s">
-        <v>183</v>
+        <v>185</v>
       </c>
       <c r="C6" t="s">
-        <v>184</v>
+        <v>186</v>
       </c>
       <c r="D6" t="s">
         <v>79</v>
@@ -3181,22 +3307,34 @@
       <c r="E6" t="n">
         <v>0</v>
       </c>
-      <c r="F6" s="1"/>
-      <c r="G6" s="1"/>
-      <c r="H6"/>
-      <c r="I6"/>
-      <c r="J6"/>
-      <c r="K6"/>
+      <c r="F6" s="1" t="n">
+        <v>45770</v>
+      </c>
+      <c r="G6" s="1" t="n">
+        <v>45828</v>
+      </c>
+      <c r="H6" t="n">
+        <v>59</v>
+      </c>
+      <c r="I6" t="s">
+        <v>37</v>
+      </c>
+      <c r="J6" t="s">
+        <v>20</v>
+      </c>
+      <c r="K6" t="s">
+        <v>38</v>
+      </c>
     </row>
     <row r="7">
       <c r="A7" t="s">
-        <v>174</v>
+        <v>176</v>
       </c>
       <c r="B7" t="s">
-        <v>185</v>
+        <v>187</v>
       </c>
       <c r="C7" t="s">
-        <v>186</v>
+        <v>188</v>
       </c>
       <c r="D7" t="s">
         <v>41</v>
@@ -3225,13 +3363,13 @@
     </row>
     <row r="8">
       <c r="A8" t="s">
-        <v>174</v>
+        <v>176</v>
       </c>
       <c r="B8" t="s">
-        <v>187</v>
+        <v>189</v>
       </c>
       <c r="C8" t="s">
-        <v>188</v>
+        <v>190</v>
       </c>
       <c r="D8" t="s">
         <v>67</v>
@@ -3260,13 +3398,13 @@
     </row>
     <row r="9">
       <c r="A9" t="s">
-        <v>174</v>
+        <v>176</v>
       </c>
       <c r="B9" t="s">
-        <v>189</v>
+        <v>191</v>
       </c>
       <c r="C9" t="s">
-        <v>190</v>
+        <v>192</v>
       </c>
       <c r="D9" t="s">
         <v>14</v>
@@ -3295,13 +3433,13 @@
     </row>
     <row r="10">
       <c r="A10" t="s">
-        <v>174</v>
+        <v>176</v>
       </c>
       <c r="B10" t="s">
-        <v>191</v>
+        <v>193</v>
       </c>
       <c r="C10" t="s">
-        <v>192</v>
+        <v>194</v>
       </c>
       <c r="D10" t="s">
         <v>71</v>
@@ -3330,16 +3468,16 @@
     </row>
     <row r="11">
       <c r="A11" t="s">
-        <v>174</v>
+        <v>176</v>
       </c>
       <c r="B11" t="s">
-        <v>193</v>
+        <v>195</v>
       </c>
       <c r="C11" t="s">
-        <v>194</v>
+        <v>196</v>
       </c>
       <c r="D11" t="s">
-        <v>195</v>
+        <v>197</v>
       </c>
       <c r="E11" t="n">
         <v>1</v>
@@ -3357,7 +3495,7 @@
         <v>42</v>
       </c>
       <c r="J11" t="s">
-        <v>196</v>
+        <v>198</v>
       </c>
       <c r="K11" t="s">
         <v>16</v>
@@ -3411,13 +3549,13 @@
     </row>
     <row r="2">
       <c r="A2" t="s">
-        <v>197</v>
+        <v>199</v>
       </c>
       <c r="B2" t="s">
-        <v>198</v>
+        <v>200</v>
       </c>
       <c r="C2" t="s">
-        <v>199</v>
+        <v>201</v>
       </c>
       <c r="D2" t="s">
         <v>50</v>

--- a/Stat Reviews/OT24_StatReview/scotusblog_replication/data/term_index.xlsx
+++ b/Stat Reviews/OT24_StatReview/scotusblog_replication/data/term_index.xlsx
@@ -3460,7 +3460,7 @@
         <v>84</v>
       </c>
       <c r="J10" t="s">
-        <v>43</v>
+        <v>98</v>
       </c>
       <c r="K10" t="s">
         <v>16</v>

--- a/Stat Reviews/OT24_StatReview/scotusblog_replication/data/term_index.xlsx
+++ b/Stat Reviews/OT24_StatReview/scotusblog_replication/data/term_index.xlsx
@@ -20,7 +20,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="202" uniqueCount="202">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="203" uniqueCount="203">
   <si>
     <t xml:space="preserve">sitting</t>
   </si>
@@ -109,7 +109,10 @@
     <t xml:space="preserve">DCDC</t>
   </si>
   <si>
-    <t xml:space="preserve">(6-3)*</t>
+    <t xml:space="preserve">Vacate</t>
+  </si>
+  <si>
+    <t xml:space="preserve">(5-4)*</t>
   </si>
   <si>
     <t xml:space="preserve">24A1007</t>
@@ -127,7 +130,7 @@
     <t xml:space="preserve">23-191</t>
   </si>
   <si>
-    <t xml:space="preserve">Willaims</t>
+    <t xml:space="preserve">Williams</t>
   </si>
   <si>
     <t xml:space="preserve">SCAL</t>
@@ -187,7 +190,7 @@
     <t xml:space="preserve">CCAOK</t>
   </si>
   <si>
-    <t xml:space="preserve">(6-2)</t>
+    <t xml:space="preserve">(5-3)</t>
   </si>
   <si>
     <t xml:space="preserve">Sotomayor</t>
@@ -211,7 +214,7 @@
     <t xml:space="preserve">23-583</t>
   </si>
   <si>
-    <t xml:space="preserve">Bouarafa</t>
+    <t xml:space="preserve">Bouarfa</t>
   </si>
   <si>
     <t xml:space="preserve">Jackson</t>
@@ -283,61 +286,61 @@
     <t xml:space="preserve">Velazquez</t>
   </si>
   <si>
+    <t xml:space="preserve">23-825</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Delligatti</t>
+  </si>
+  <si>
+    <t xml:space="preserve">23-970</t>
+  </si>
+  <si>
+    <t xml:space="preserve">NVIDIA</t>
+  </si>
+  <si>
+    <t xml:space="preserve">December</t>
+  </si>
+  <si>
+    <t xml:space="preserve">23-1038</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Wages and White Lion </t>
+  </si>
+  <si>
+    <t xml:space="preserve">23-824</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Miller</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Reverse</t>
+  </si>
+  <si>
+    <t xml:space="preserve">(8-1)</t>
+  </si>
+  <si>
+    <t xml:space="preserve">23-867</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Hungary</t>
+  </si>
+  <si>
+    <t xml:space="preserve">23-477</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Skrmetti</t>
+  </si>
+  <si>
+    <t xml:space="preserve">CA6</t>
+  </si>
+  <si>
     <t xml:space="preserve">(6-3)</t>
   </si>
   <si>
-    <t xml:space="preserve">23-825</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Delligatti</t>
-  </si>
-  <si>
-    <t xml:space="preserve">23-970</t>
-  </si>
-  <si>
-    <t xml:space="preserve">NVIDIA</t>
-  </si>
-  <si>
-    <t xml:space="preserve">December</t>
-  </si>
-  <si>
-    <t xml:space="preserve">23-1038</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Wages and White Lion </t>
-  </si>
-  <si>
-    <t xml:space="preserve">23-824</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Miller</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Reverse</t>
-  </si>
-  <si>
-    <t xml:space="preserve">(8-1)</t>
-  </si>
-  <si>
-    <t xml:space="preserve">23-867</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Hungary</t>
-  </si>
-  <si>
-    <t xml:space="preserve">23-477</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Skrmetti</t>
-  </si>
-  <si>
-    <t xml:space="preserve">CA6</t>
-  </si>
-  <si>
     <t xml:space="preserve">23-909</t>
   </si>
   <si>
-    <t xml:space="preserve">Kouisisis</t>
+    <t xml:space="preserve">Kousisis</t>
   </si>
   <si>
     <t xml:space="preserve">CA3</t>
@@ -1112,10 +1115,10 @@
       </c>
       <c r="H5"/>
       <c r="I5" t="s">
-        <v>24</v>
+        <v>29</v>
       </c>
       <c r="J5" t="s">
-        <v>29</v>
+        <v>30</v>
       </c>
       <c r="K5" t="s">
         <v>16</v>
@@ -1126,13 +1129,13 @@
         <v>11</v>
       </c>
       <c r="B6" t="s">
-        <v>30</v>
+        <v>31</v>
       </c>
       <c r="C6" t="s">
-        <v>31</v>
+        <v>32</v>
       </c>
       <c r="D6" t="s">
-        <v>32</v>
+        <v>33</v>
       </c>
       <c r="E6" t="n">
         <v>0</v>
@@ -1200,16 +1203,16 @@
     </row>
     <row r="2">
       <c r="A2" t="s">
-        <v>33</v>
+        <v>34</v>
       </c>
       <c r="B2" t="s">
-        <v>34</v>
+        <v>35</v>
       </c>
       <c r="C2" t="s">
-        <v>35</v>
+        <v>36</v>
       </c>
       <c r="D2" t="s">
-        <v>36</v>
+        <v>37</v>
       </c>
       <c r="E2" t="n">
         <v>0</v>
@@ -1224,27 +1227,27 @@
         <v>138</v>
       </c>
       <c r="I2" t="s">
-        <v>37</v>
+        <v>38</v>
       </c>
       <c r="J2" t="s">
         <v>25</v>
       </c>
       <c r="K2" t="s">
-        <v>38</v>
+        <v>39</v>
       </c>
     </row>
     <row r="3">
       <c r="A3" t="s">
-        <v>33</v>
+        <v>34</v>
       </c>
       <c r="B3" t="s">
-        <v>39</v>
+        <v>40</v>
       </c>
       <c r="C3" t="s">
-        <v>40</v>
+        <v>41</v>
       </c>
       <c r="D3" t="s">
-        <v>41</v>
+        <v>42</v>
       </c>
       <c r="E3" t="n">
         <v>0</v>
@@ -1259,27 +1262,27 @@
         <v>101</v>
       </c>
       <c r="I3" t="s">
-        <v>42</v>
+        <v>43</v>
       </c>
       <c r="J3" t="s">
-        <v>43</v>
+        <v>44</v>
       </c>
       <c r="K3" t="s">
-        <v>44</v>
+        <v>45</v>
       </c>
     </row>
     <row r="4">
       <c r="A4" t="s">
+        <v>34</v>
+      </c>
+      <c r="B4" t="s">
+        <v>46</v>
+      </c>
+      <c r="C4" t="s">
+        <v>47</v>
+      </c>
+      <c r="D4" t="s">
         <v>33</v>
-      </c>
-      <c r="B4" t="s">
-        <v>45</v>
-      </c>
-      <c r="C4" t="s">
-        <v>46</v>
-      </c>
-      <c r="D4" t="s">
-        <v>32</v>
       </c>
       <c r="E4" t="n">
         <v>0</v>
@@ -1294,27 +1297,27 @@
         <v>170</v>
       </c>
       <c r="I4" t="s">
-        <v>37</v>
+        <v>38</v>
       </c>
       <c r="J4" t="s">
         <v>20</v>
       </c>
       <c r="K4" t="s">
-        <v>47</v>
+        <v>48</v>
       </c>
     </row>
     <row r="5">
       <c r="A5" t="s">
-        <v>33</v>
+        <v>34</v>
       </c>
       <c r="B5" t="s">
-        <v>48</v>
+        <v>49</v>
       </c>
       <c r="C5" t="s">
-        <v>49</v>
+        <v>50</v>
       </c>
       <c r="D5" t="s">
-        <v>50</v>
+        <v>51</v>
       </c>
       <c r="E5" t="n">
         <v>0</v>
@@ -1329,27 +1332,27 @@
         <v>141</v>
       </c>
       <c r="I5" t="s">
-        <v>37</v>
+        <v>38</v>
       </c>
       <c r="J5" t="s">
         <v>20</v>
       </c>
       <c r="K5" t="s">
-        <v>51</v>
+        <v>52</v>
       </c>
     </row>
     <row r="6">
       <c r="A6" t="s">
-        <v>33</v>
+        <v>34</v>
       </c>
       <c r="B6" t="s">
-        <v>52</v>
+        <v>53</v>
       </c>
       <c r="C6" t="s">
-        <v>53</v>
+        <v>54</v>
       </c>
       <c r="D6" t="s">
-        <v>54</v>
+        <v>55</v>
       </c>
       <c r="E6" t="n">
         <v>1</v>
@@ -1364,27 +1367,27 @@
         <v>140</v>
       </c>
       <c r="I6" t="s">
-        <v>37</v>
+        <v>38</v>
       </c>
       <c r="J6" t="s">
-        <v>55</v>
+        <v>56</v>
       </c>
       <c r="K6" t="s">
-        <v>56</v>
+        <v>57</v>
       </c>
     </row>
     <row r="7">
       <c r="A7" t="s">
-        <v>33</v>
+        <v>34</v>
       </c>
       <c r="B7" t="s">
-        <v>57</v>
+        <v>58</v>
       </c>
       <c r="C7" t="s">
-        <v>58</v>
+        <v>59</v>
       </c>
       <c r="D7" t="s">
-        <v>59</v>
+        <v>60</v>
       </c>
       <c r="E7" t="n">
         <v>0</v>
@@ -1399,24 +1402,24 @@
         <v>170</v>
       </c>
       <c r="I7" t="s">
-        <v>60</v>
+        <v>61</v>
       </c>
       <c r="J7" t="s">
         <v>25</v>
       </c>
       <c r="K7" t="s">
-        <v>61</v>
+        <v>62</v>
       </c>
     </row>
     <row r="8">
       <c r="A8" t="s">
-        <v>33</v>
+        <v>34</v>
       </c>
       <c r="B8" t="s">
-        <v>62</v>
+        <v>63</v>
       </c>
       <c r="C8" t="s">
-        <v>63</v>
+        <v>64</v>
       </c>
       <c r="D8" t="s">
         <v>14</v>
@@ -1434,27 +1437,27 @@
         <v>57</v>
       </c>
       <c r="I8" t="s">
-        <v>42</v>
+        <v>43</v>
       </c>
       <c r="J8" t="s">
-        <v>43</v>
+        <v>44</v>
       </c>
       <c r="K8" t="s">
-        <v>64</v>
+        <v>65</v>
       </c>
     </row>
     <row r="9">
       <c r="A9" t="s">
-        <v>33</v>
+        <v>34</v>
       </c>
       <c r="B9" t="s">
-        <v>65</v>
+        <v>66</v>
       </c>
       <c r="C9" t="s">
-        <v>66</v>
+        <v>67</v>
       </c>
       <c r="D9" t="s">
-        <v>67</v>
+        <v>68</v>
       </c>
       <c r="E9" t="n">
         <v>0</v>
@@ -1469,27 +1472,27 @@
         <v>141</v>
       </c>
       <c r="I9" t="s">
-        <v>42</v>
+        <v>43</v>
       </c>
       <c r="J9" t="s">
         <v>20</v>
       </c>
       <c r="K9" t="s">
-        <v>68</v>
+        <v>69</v>
       </c>
     </row>
     <row r="10">
       <c r="A10" t="s">
-        <v>33</v>
+        <v>34</v>
       </c>
       <c r="B10" t="s">
-        <v>69</v>
+        <v>70</v>
       </c>
       <c r="C10" t="s">
-        <v>70</v>
+        <v>71</v>
       </c>
       <c r="D10" t="s">
-        <v>71</v>
+        <v>72</v>
       </c>
       <c r="E10" t="n">
         <v>0</v>
@@ -1504,13 +1507,13 @@
         <v>140</v>
       </c>
       <c r="I10" t="s">
-        <v>37</v>
+        <v>38</v>
       </c>
       <c r="J10" t="s">
-        <v>43</v>
+        <v>25</v>
       </c>
       <c r="K10" t="s">
-        <v>72</v>
+        <v>73</v>
       </c>
     </row>
   </sheetData>
@@ -1561,16 +1564,16 @@
     </row>
     <row r="2">
       <c r="A2" t="s">
-        <v>73</v>
+        <v>74</v>
       </c>
       <c r="B2" t="s">
-        <v>74</v>
+        <v>75</v>
       </c>
       <c r="C2" t="s">
-        <v>75</v>
+        <v>76</v>
       </c>
       <c r="D2" t="s">
-        <v>76</v>
+        <v>77</v>
       </c>
       <c r="E2" t="n">
         <v>0</v>
@@ -1585,27 +1588,27 @@
         <v>110</v>
       </c>
       <c r="I2" t="s">
-        <v>60</v>
+        <v>61</v>
       </c>
       <c r="J2" t="s">
-        <v>43</v>
+        <v>44</v>
       </c>
       <c r="K2" t="s">
-        <v>44</v>
+        <v>45</v>
       </c>
     </row>
     <row r="3">
       <c r="A3" t="s">
-        <v>73</v>
+        <v>74</v>
       </c>
       <c r="B3" t="s">
-        <v>77</v>
+        <v>78</v>
       </c>
       <c r="C3" t="s">
-        <v>78</v>
+        <v>79</v>
       </c>
       <c r="D3" t="s">
-        <v>79</v>
+        <v>80</v>
       </c>
       <c r="E3" t="n">
         <v>0</v>
@@ -1620,27 +1623,27 @@
         <v>176</v>
       </c>
       <c r="I3" t="s">
-        <v>42</v>
+        <v>43</v>
       </c>
       <c r="J3" t="s">
         <v>20</v>
       </c>
       <c r="K3" t="s">
-        <v>61</v>
+        <v>62</v>
       </c>
     </row>
     <row r="4">
       <c r="A4" t="s">
-        <v>73</v>
+        <v>74</v>
       </c>
       <c r="B4" t="s">
-        <v>80</v>
+        <v>81</v>
       </c>
       <c r="C4" t="s">
-        <v>81</v>
+        <v>82</v>
       </c>
       <c r="D4" t="s">
-        <v>50</v>
+        <v>51</v>
       </c>
       <c r="E4" t="n">
         <v>0</v>
@@ -1655,27 +1658,27 @@
         <v>72</v>
       </c>
       <c r="I4" t="s">
-        <v>37</v>
+        <v>38</v>
       </c>
       <c r="J4" t="s">
-        <v>43</v>
+        <v>44</v>
       </c>
       <c r="K4" t="s">
-        <v>38</v>
+        <v>39</v>
       </c>
     </row>
     <row r="5">
       <c r="A5" t="s">
-        <v>73</v>
+        <v>74</v>
       </c>
       <c r="B5" t="s">
-        <v>82</v>
+        <v>83</v>
       </c>
       <c r="C5" t="s">
-        <v>83</v>
+        <v>84</v>
       </c>
       <c r="D5" t="s">
-        <v>71</v>
+        <v>72</v>
       </c>
       <c r="E5" t="n">
         <v>0</v>
@@ -1690,7 +1693,7 @@
         <v>17</v>
       </c>
       <c r="I5" t="s">
-        <v>84</v>
+        <v>85</v>
       </c>
       <c r="J5" t="s">
         <v>16</v>
@@ -1701,16 +1704,16 @@
     </row>
     <row r="6">
       <c r="A6" t="s">
-        <v>73</v>
+        <v>74</v>
       </c>
       <c r="B6" t="s">
-        <v>85</v>
+        <v>86</v>
       </c>
       <c r="C6" t="s">
-        <v>86</v>
+        <v>87</v>
       </c>
       <c r="D6" t="s">
-        <v>59</v>
+        <v>19</v>
       </c>
       <c r="E6" t="n">
         <v>0</v>
@@ -1725,18 +1728,18 @@
         <v>162</v>
       </c>
       <c r="I6" t="s">
-        <v>37</v>
+        <v>38</v>
       </c>
       <c r="J6" t="s">
-        <v>87</v>
+        <v>25</v>
       </c>
       <c r="K6" t="s">
-        <v>47</v>
+        <v>48</v>
       </c>
     </row>
     <row r="7">
       <c r="A7" t="s">
-        <v>73</v>
+        <v>74</v>
       </c>
       <c r="B7" t="s">
         <v>88</v>
@@ -1745,7 +1748,7 @@
         <v>89</v>
       </c>
       <c r="D7" t="s">
-        <v>59</v>
+        <v>60</v>
       </c>
       <c r="E7" t="n">
         <v>0</v>
@@ -1760,18 +1763,18 @@
         <v>130</v>
       </c>
       <c r="I7" t="s">
-        <v>42</v>
+        <v>43</v>
       </c>
       <c r="J7" t="s">
         <v>20</v>
       </c>
       <c r="K7" t="s">
-        <v>68</v>
+        <v>69</v>
       </c>
     </row>
     <row r="8">
       <c r="A8" t="s">
-        <v>73</v>
+        <v>74</v>
       </c>
       <c r="B8" t="s">
         <v>90</v>
@@ -1780,7 +1783,7 @@
         <v>91</v>
       </c>
       <c r="D8" t="s">
-        <v>71</v>
+        <v>72</v>
       </c>
       <c r="E8" t="n">
         <v>0</v>
@@ -1795,7 +1798,7 @@
         <v>29</v>
       </c>
       <c r="I8" t="s">
-        <v>84</v>
+        <v>85</v>
       </c>
       <c r="J8" t="s">
         <v>16</v>
@@ -1861,7 +1864,7 @@
         <v>94</v>
       </c>
       <c r="D2" t="s">
-        <v>32</v>
+        <v>33</v>
       </c>
       <c r="E2" t="n">
         <v>0</v>
@@ -1879,10 +1882,10 @@
         <v>15</v>
       </c>
       <c r="J2" t="s">
-        <v>43</v>
+        <v>44</v>
       </c>
       <c r="K2" t="s">
-        <v>72</v>
+        <v>73</v>
       </c>
     </row>
     <row r="3">
@@ -1917,7 +1920,7 @@
         <v>98</v>
       </c>
       <c r="K3" t="s">
-        <v>64</v>
+        <v>65</v>
       </c>
     </row>
     <row r="4">
@@ -1931,7 +1934,7 @@
         <v>100</v>
       </c>
       <c r="D4" t="s">
-        <v>79</v>
+        <v>80</v>
       </c>
       <c r="E4" t="n">
         <v>0</v>
@@ -1949,10 +1952,10 @@
         <v>15</v>
       </c>
       <c r="J4" t="s">
-        <v>43</v>
+        <v>44</v>
       </c>
       <c r="K4" t="s">
-        <v>56</v>
+        <v>57</v>
       </c>
     </row>
     <row r="5">
@@ -1981,13 +1984,13 @@
         <v>197</v>
       </c>
       <c r="I5" t="s">
-        <v>42</v>
+        <v>43</v>
       </c>
       <c r="J5" t="s">
-        <v>87</v>
+        <v>104</v>
       </c>
       <c r="K5" t="s">
-        <v>51</v>
+        <v>52</v>
       </c>
     </row>
     <row r="6">
@@ -1995,13 +1998,13 @@
         <v>92</v>
       </c>
       <c r="B6" t="s">
-        <v>104</v>
+        <v>105</v>
       </c>
       <c r="C6" t="s">
-        <v>105</v>
+        <v>106</v>
       </c>
       <c r="D6" t="s">
-        <v>106</v>
+        <v>107</v>
       </c>
       <c r="E6" t="n">
         <v>0</v>
@@ -2016,13 +2019,13 @@
         <v>165</v>
       </c>
       <c r="I6" t="s">
-        <v>42</v>
+        <v>43</v>
       </c>
       <c r="J6" t="s">
-        <v>43</v>
+        <v>44</v>
       </c>
       <c r="K6" t="s">
-        <v>61</v>
+        <v>62</v>
       </c>
     </row>
     <row r="7">
@@ -2030,13 +2033,13 @@
         <v>92</v>
       </c>
       <c r="B7" t="s">
-        <v>107</v>
+        <v>108</v>
       </c>
       <c r="C7" t="s">
-        <v>108</v>
+        <v>109</v>
       </c>
       <c r="D7" t="s">
-        <v>67</v>
+        <v>68</v>
       </c>
       <c r="E7" t="n">
         <v>0</v>
@@ -2051,13 +2054,13 @@
         <v>143</v>
       </c>
       <c r="I7" t="s">
-        <v>37</v>
+        <v>38</v>
       </c>
       <c r="J7" t="s">
         <v>25</v>
       </c>
       <c r="K7" t="s">
-        <v>47</v>
+        <v>48</v>
       </c>
     </row>
     <row r="8">
@@ -2065,13 +2068,13 @@
         <v>92</v>
       </c>
       <c r="B8" t="s">
-        <v>109</v>
+        <v>110</v>
       </c>
       <c r="C8" t="s">
-        <v>110</v>
+        <v>111</v>
       </c>
       <c r="D8" t="s">
-        <v>79</v>
+        <v>80</v>
       </c>
       <c r="E8" t="n">
         <v>0</v>
@@ -2086,13 +2089,13 @@
         <v>171</v>
       </c>
       <c r="I8" t="s">
-        <v>37</v>
+        <v>38</v>
       </c>
       <c r="J8" t="s">
-        <v>111</v>
+        <v>112</v>
       </c>
       <c r="K8" t="s">
-        <v>38</v>
+        <v>39</v>
       </c>
     </row>
     <row r="9">
@@ -2100,13 +2103,13 @@
         <v>92</v>
       </c>
       <c r="B9" t="s">
-        <v>112</v>
+        <v>113</v>
       </c>
       <c r="C9" t="s">
-        <v>113</v>
+        <v>114</v>
       </c>
       <c r="D9" t="s">
-        <v>50</v>
+        <v>51</v>
       </c>
       <c r="E9" t="n">
         <v>0</v>
@@ -2124,10 +2127,10 @@
         <v>15</v>
       </c>
       <c r="J9" t="s">
-        <v>43</v>
+        <v>44</v>
       </c>
       <c r="K9" t="s">
-        <v>44</v>
+        <v>45</v>
       </c>
     </row>
   </sheetData>
@@ -2178,16 +2181,16 @@
     </row>
     <row r="2">
       <c r="A2" t="s">
-        <v>114</v>
+        <v>115</v>
       </c>
       <c r="B2" t="s">
-        <v>115</v>
+        <v>116</v>
       </c>
       <c r="C2" t="s">
-        <v>116</v>
+        <v>117</v>
       </c>
       <c r="D2" t="s">
-        <v>32</v>
+        <v>33</v>
       </c>
       <c r="E2" t="n">
         <v>0</v>
@@ -2201,13 +2204,13 @@
     </row>
     <row r="3">
       <c r="A3" t="s">
-        <v>114</v>
+        <v>115</v>
       </c>
       <c r="B3" t="s">
-        <v>117</v>
+        <v>118</v>
       </c>
       <c r="C3" t="s">
-        <v>118</v>
+        <v>119</v>
       </c>
       <c r="D3" t="s">
         <v>14</v>
@@ -2225,27 +2228,27 @@
         <v>159</v>
       </c>
       <c r="I3" t="s">
-        <v>42</v>
+        <v>43</v>
       </c>
       <c r="J3" t="s">
-        <v>119</v>
+        <v>120</v>
       </c>
       <c r="K3" t="s">
-        <v>47</v>
+        <v>48</v>
       </c>
     </row>
     <row r="4">
       <c r="A4" t="s">
-        <v>114</v>
+        <v>115</v>
       </c>
       <c r="B4" t="s">
-        <v>120</v>
+        <v>121</v>
       </c>
       <c r="C4" t="s">
-        <v>121</v>
+        <v>122</v>
       </c>
       <c r="D4" t="s">
-        <v>76</v>
+        <v>77</v>
       </c>
       <c r="E4" t="n">
         <v>0</v>
@@ -2263,21 +2266,21 @@
         <v>15</v>
       </c>
       <c r="J4" t="s">
-        <v>43</v>
+        <v>44</v>
       </c>
       <c r="K4" t="s">
-        <v>51</v>
+        <v>52</v>
       </c>
     </row>
     <row r="5">
       <c r="A5" t="s">
-        <v>114</v>
+        <v>115</v>
       </c>
       <c r="B5" t="s">
-        <v>122</v>
+        <v>123</v>
       </c>
       <c r="C5" t="s">
-        <v>123</v>
+        <v>124</v>
       </c>
       <c r="D5" t="s">
         <v>19</v>
@@ -2295,27 +2298,27 @@
         <v>44</v>
       </c>
       <c r="I5" t="s">
-        <v>37</v>
+        <v>38</v>
       </c>
       <c r="J5" t="s">
-        <v>43</v>
+        <v>44</v>
       </c>
       <c r="K5" t="s">
-        <v>72</v>
+        <v>73</v>
       </c>
     </row>
     <row r="6">
       <c r="A6" t="s">
-        <v>114</v>
+        <v>115</v>
       </c>
       <c r="B6" t="s">
-        <v>124</v>
+        <v>125</v>
       </c>
       <c r="C6" t="s">
-        <v>125</v>
+        <v>126</v>
       </c>
       <c r="D6" t="s">
-        <v>32</v>
+        <v>33</v>
       </c>
       <c r="E6" t="n">
         <v>0</v>
@@ -2329,16 +2332,16 @@
     </row>
     <row r="7">
       <c r="A7" t="s">
-        <v>114</v>
+        <v>115</v>
       </c>
       <c r="B7" t="s">
-        <v>126</v>
+        <v>127</v>
       </c>
       <c r="C7" t="s">
-        <v>127</v>
+        <v>128</v>
       </c>
       <c r="D7" t="s">
-        <v>32</v>
+        <v>33</v>
       </c>
       <c r="E7" t="n">
         <v>0</v>
@@ -2353,27 +2356,27 @@
         <v>151</v>
       </c>
       <c r="I7" t="s">
-        <v>60</v>
+        <v>61</v>
       </c>
       <c r="J7" t="s">
         <v>20</v>
       </c>
       <c r="K7" t="s">
-        <v>61</v>
+        <v>62</v>
       </c>
     </row>
     <row r="8">
       <c r="A8" t="s">
-        <v>114</v>
+        <v>115</v>
       </c>
       <c r="B8" t="s">
-        <v>128</v>
+        <v>129</v>
       </c>
       <c r="C8" t="s">
-        <v>129</v>
+        <v>130</v>
       </c>
       <c r="D8" t="s">
-        <v>71</v>
+        <v>72</v>
       </c>
       <c r="E8" t="n">
         <v>0</v>
@@ -2388,27 +2391,27 @@
         <v>151</v>
       </c>
       <c r="I8" t="s">
-        <v>37</v>
+        <v>38</v>
       </c>
       <c r="J8" t="s">
-        <v>87</v>
+        <v>104</v>
       </c>
       <c r="K8" t="s">
-        <v>38</v>
+        <v>39</v>
       </c>
     </row>
     <row r="9">
       <c r="A9" t="s">
-        <v>114</v>
+        <v>115</v>
       </c>
       <c r="B9" t="s">
-        <v>130</v>
+        <v>131</v>
       </c>
       <c r="C9" t="s">
-        <v>131</v>
+        <v>132</v>
       </c>
       <c r="D9" t="s">
-        <v>32</v>
+        <v>33</v>
       </c>
       <c r="E9" t="n">
         <v>0</v>
@@ -2426,24 +2429,24 @@
         <v>15</v>
       </c>
       <c r="J9" t="s">
-        <v>43</v>
+        <v>44</v>
       </c>
       <c r="K9" t="s">
-        <v>44</v>
+        <v>45</v>
       </c>
     </row>
     <row r="10">
       <c r="A10" t="s">
-        <v>114</v>
+        <v>115</v>
       </c>
       <c r="B10" t="s">
-        <v>132</v>
+        <v>133</v>
       </c>
       <c r="C10" t="s">
-        <v>133</v>
+        <v>134</v>
       </c>
       <c r="D10" t="s">
-        <v>59</v>
+        <v>60</v>
       </c>
       <c r="E10" t="n">
         <v>0</v>
@@ -2458,27 +2461,27 @@
         <v>86</v>
       </c>
       <c r="I10" t="s">
-        <v>37</v>
+        <v>38</v>
       </c>
       <c r="J10" t="s">
-        <v>43</v>
+        <v>44</v>
       </c>
       <c r="K10" t="s">
-        <v>56</v>
+        <v>57</v>
       </c>
     </row>
     <row r="11">
       <c r="A11" t="s">
-        <v>114</v>
+        <v>115</v>
       </c>
       <c r="B11" t="s">
-        <v>134</v>
+        <v>135</v>
       </c>
       <c r="C11" t="s">
-        <v>135</v>
+        <v>136</v>
       </c>
       <c r="D11" t="s">
-        <v>79</v>
+        <v>80</v>
       </c>
       <c r="E11" t="n">
         <v>1</v>
@@ -2493,10 +2496,10 @@
         <v>8</v>
       </c>
       <c r="I11" t="s">
-        <v>42</v>
+        <v>43</v>
       </c>
       <c r="J11" t="s">
-        <v>43</v>
+        <v>44</v>
       </c>
       <c r="K11" t="s">
         <v>16</v>
@@ -2550,16 +2553,16 @@
     </row>
     <row r="2">
       <c r="A2" t="s">
-        <v>136</v>
+        <v>137</v>
       </c>
       <c r="B2" t="s">
-        <v>137</v>
+        <v>138</v>
       </c>
       <c r="C2" t="s">
-        <v>138</v>
+        <v>139</v>
       </c>
       <c r="D2" t="s">
-        <v>32</v>
+        <v>33</v>
       </c>
       <c r="E2" t="n">
         <v>0</v>
@@ -2573,13 +2576,13 @@
     </row>
     <row r="3">
       <c r="A3" t="s">
-        <v>136</v>
+        <v>137</v>
       </c>
       <c r="B3" t="s">
-        <v>139</v>
+        <v>140</v>
       </c>
       <c r="C3" t="s">
-        <v>140</v>
+        <v>141</v>
       </c>
       <c r="D3" t="s">
         <v>103</v>
@@ -2600,21 +2603,21 @@
         <v>15</v>
       </c>
       <c r="J3" t="s">
-        <v>141</v>
+        <v>142</v>
       </c>
       <c r="K3" t="s">
-        <v>61</v>
+        <v>62</v>
       </c>
     </row>
     <row r="4">
       <c r="A4" t="s">
-        <v>136</v>
+        <v>137</v>
       </c>
       <c r="B4" t="s">
-        <v>142</v>
+        <v>143</v>
       </c>
       <c r="C4" t="s">
-        <v>143</v>
+        <v>144</v>
       </c>
       <c r="D4" t="s">
         <v>103</v>
@@ -2632,24 +2635,24 @@
         <v>114</v>
       </c>
       <c r="I4" t="s">
-        <v>42</v>
+        <v>43</v>
       </c>
       <c r="J4" t="s">
         <v>25</v>
       </c>
       <c r="K4" t="s">
-        <v>51</v>
+        <v>52</v>
       </c>
     </row>
     <row r="5">
       <c r="A5" t="s">
-        <v>136</v>
+        <v>137</v>
       </c>
       <c r="B5" t="s">
-        <v>144</v>
+        <v>145</v>
       </c>
       <c r="C5" t="s">
-        <v>145</v>
+        <v>146</v>
       </c>
       <c r="D5" t="s">
         <v>103</v>
@@ -2670,24 +2673,24 @@
         <v>15</v>
       </c>
       <c r="J5" t="s">
-        <v>43</v>
+        <v>44</v>
       </c>
       <c r="K5" t="s">
-        <v>64</v>
+        <v>65</v>
       </c>
     </row>
     <row r="6">
       <c r="A6" t="s">
-        <v>136</v>
+        <v>137</v>
       </c>
       <c r="B6" t="s">
-        <v>146</v>
+        <v>147</v>
       </c>
       <c r="C6" t="s">
-        <v>147</v>
+        <v>148</v>
       </c>
       <c r="D6" t="s">
-        <v>71</v>
+        <v>72</v>
       </c>
       <c r="E6" t="n">
         <v>0</v>
@@ -2702,27 +2705,27 @@
         <v>95</v>
       </c>
       <c r="I6" t="s">
-        <v>37</v>
+        <v>38</v>
       </c>
       <c r="J6" t="s">
-        <v>43</v>
+        <v>44</v>
       </c>
       <c r="K6" t="s">
-        <v>72</v>
+        <v>73</v>
       </c>
     </row>
     <row r="7">
       <c r="A7" t="s">
-        <v>136</v>
+        <v>137</v>
       </c>
       <c r="B7" t="s">
-        <v>148</v>
+        <v>149</v>
       </c>
       <c r="C7" t="s">
-        <v>149</v>
+        <v>150</v>
       </c>
       <c r="D7" t="s">
-        <v>59</v>
+        <v>60</v>
       </c>
       <c r="E7" t="n">
         <v>0</v>
@@ -2737,27 +2740,27 @@
         <v>95</v>
       </c>
       <c r="I7" t="s">
-        <v>37</v>
+        <v>38</v>
       </c>
       <c r="J7" t="s">
-        <v>43</v>
+        <v>44</v>
       </c>
       <c r="K7" t="s">
-        <v>68</v>
+        <v>69</v>
       </c>
     </row>
     <row r="8">
       <c r="A8" t="s">
-        <v>136</v>
+        <v>137</v>
       </c>
       <c r="B8" t="s">
-        <v>150</v>
+        <v>151</v>
       </c>
       <c r="C8" t="s">
-        <v>151</v>
+        <v>152</v>
       </c>
       <c r="D8" t="s">
-        <v>152</v>
+        <v>153</v>
       </c>
       <c r="E8" t="n">
         <v>0</v>
@@ -2772,27 +2775,27 @@
         <v>94</v>
       </c>
       <c r="I8" t="s">
-        <v>37</v>
+        <v>38</v>
       </c>
       <c r="J8" t="s">
-        <v>43</v>
+        <v>44</v>
       </c>
       <c r="K8" t="s">
-        <v>44</v>
+        <v>45</v>
       </c>
     </row>
     <row r="9">
       <c r="A9" t="s">
-        <v>136</v>
+        <v>137</v>
       </c>
       <c r="B9" t="s">
-        <v>153</v>
+        <v>154</v>
       </c>
       <c r="C9" t="s">
-        <v>154</v>
+        <v>155</v>
       </c>
       <c r="D9" t="s">
-        <v>32</v>
+        <v>33</v>
       </c>
       <c r="E9" t="n">
         <v>0</v>
@@ -2807,13 +2810,13 @@
         <v>106</v>
       </c>
       <c r="I9" t="s">
-        <v>37</v>
+        <v>38</v>
       </c>
       <c r="J9" t="s">
-        <v>87</v>
+        <v>104</v>
       </c>
       <c r="K9" t="s">
-        <v>38</v>
+        <v>39</v>
       </c>
     </row>
   </sheetData>
@@ -2864,16 +2867,16 @@
     </row>
     <row r="2">
       <c r="A2" t="s">
-        <v>155</v>
+        <v>156</v>
       </c>
       <c r="B2" t="s">
-        <v>156</v>
+        <v>157</v>
       </c>
       <c r="C2" t="s">
-        <v>157</v>
+        <v>158</v>
       </c>
       <c r="D2" t="s">
-        <v>158</v>
+        <v>159</v>
       </c>
       <c r="E2" t="n">
         <v>0</v>
@@ -2887,16 +2890,16 @@
     </row>
     <row r="3">
       <c r="A3" t="s">
-        <v>155</v>
+        <v>156</v>
       </c>
       <c r="B3" t="s">
-        <v>159</v>
+        <v>160</v>
       </c>
       <c r="C3" t="s">
-        <v>160</v>
+        <v>161</v>
       </c>
       <c r="D3" t="s">
-        <v>50</v>
+        <v>51</v>
       </c>
       <c r="E3" t="n">
         <v>0</v>
@@ -2910,16 +2913,16 @@
     </row>
     <row r="4">
       <c r="A4" t="s">
-        <v>155</v>
+        <v>156</v>
       </c>
       <c r="B4" t="s">
-        <v>161</v>
+        <v>162</v>
       </c>
       <c r="C4" t="s">
-        <v>162</v>
+        <v>163</v>
       </c>
       <c r="D4" t="s">
-        <v>32</v>
+        <v>33</v>
       </c>
       <c r="E4" t="n">
         <v>0</v>
@@ -2940,18 +2943,18 @@
         <v>20</v>
       </c>
       <c r="K4" t="s">
-        <v>68</v>
+        <v>69</v>
       </c>
     </row>
     <row r="5">
       <c r="A5" t="s">
-        <v>155</v>
+        <v>156</v>
       </c>
       <c r="B5" t="s">
-        <v>163</v>
+        <v>164</v>
       </c>
       <c r="C5" t="s">
-        <v>164</v>
+        <v>165</v>
       </c>
       <c r="D5" t="s">
         <v>19</v>
@@ -2969,27 +2972,27 @@
         <v>86</v>
       </c>
       <c r="I5" t="s">
-        <v>37</v>
+        <v>38</v>
       </c>
       <c r="J5" t="s">
-        <v>111</v>
+        <v>112</v>
       </c>
       <c r="K5" t="s">
-        <v>68</v>
+        <v>69</v>
       </c>
     </row>
     <row r="6">
       <c r="A6" t="s">
-        <v>155</v>
+        <v>156</v>
       </c>
       <c r="B6" t="s">
-        <v>165</v>
+        <v>166</v>
       </c>
       <c r="C6" t="s">
-        <v>166</v>
+        <v>167</v>
       </c>
       <c r="D6" t="s">
-        <v>32</v>
+        <v>33</v>
       </c>
       <c r="E6" t="n">
         <v>0</v>
@@ -3003,16 +3006,16 @@
     </row>
     <row r="7">
       <c r="A7" t="s">
-        <v>155</v>
+        <v>156</v>
       </c>
       <c r="B7" t="s">
-        <v>167</v>
+        <v>168</v>
       </c>
       <c r="C7" t="s">
-        <v>168</v>
+        <v>169</v>
       </c>
       <c r="D7" t="s">
-        <v>169</v>
+        <v>170</v>
       </c>
       <c r="E7" t="n">
         <v>0</v>
@@ -3027,27 +3030,27 @@
         <v>67</v>
       </c>
       <c r="I7" t="s">
-        <v>37</v>
+        <v>38</v>
       </c>
       <c r="J7" t="s">
-        <v>43</v>
+        <v>44</v>
       </c>
       <c r="K7" t="s">
-        <v>56</v>
+        <v>57</v>
       </c>
     </row>
     <row r="8">
       <c r="A8" t="s">
-        <v>155</v>
+        <v>156</v>
       </c>
       <c r="B8" t="s">
-        <v>170</v>
+        <v>171</v>
       </c>
       <c r="C8" t="s">
-        <v>171</v>
+        <v>172</v>
       </c>
       <c r="D8" t="s">
-        <v>32</v>
+        <v>33</v>
       </c>
       <c r="E8" t="n">
         <v>0</v>
@@ -3062,27 +3065,27 @@
         <v>74</v>
       </c>
       <c r="I8" t="s">
-        <v>42</v>
+        <v>43</v>
       </c>
       <c r="J8" t="s">
-        <v>43</v>
+        <v>44</v>
       </c>
       <c r="K8" t="s">
-        <v>64</v>
+        <v>65</v>
       </c>
     </row>
     <row r="9">
       <c r="A9" t="s">
-        <v>155</v>
+        <v>156</v>
       </c>
       <c r="B9" t="s">
-        <v>172</v>
+        <v>173</v>
       </c>
       <c r="C9" t="s">
-        <v>173</v>
+        <v>174</v>
       </c>
       <c r="D9" t="s">
-        <v>59</v>
+        <v>60</v>
       </c>
       <c r="E9" t="n">
         <v>0</v>
@@ -3097,27 +3100,27 @@
         <v>81</v>
       </c>
       <c r="I9" t="s">
-        <v>37</v>
+        <v>38</v>
       </c>
       <c r="J9" t="s">
-        <v>43</v>
+        <v>44</v>
       </c>
       <c r="K9" t="s">
-        <v>51</v>
+        <v>52</v>
       </c>
     </row>
     <row r="10">
       <c r="A10" t="s">
-        <v>155</v>
+        <v>156</v>
       </c>
       <c r="B10" t="s">
-        <v>174</v>
+        <v>175</v>
       </c>
       <c r="C10" t="s">
-        <v>175</v>
+        <v>176</v>
       </c>
       <c r="D10" t="s">
-        <v>50</v>
+        <v>51</v>
       </c>
       <c r="E10" t="n">
         <v>0</v>
@@ -3177,16 +3180,16 @@
     </row>
     <row r="2">
       <c r="A2" t="s">
-        <v>176</v>
+        <v>177</v>
       </c>
       <c r="B2" t="s">
-        <v>177</v>
+        <v>178</v>
       </c>
       <c r="C2" t="s">
-        <v>178</v>
+        <v>179</v>
       </c>
       <c r="D2" t="s">
-        <v>32</v>
+        <v>33</v>
       </c>
       <c r="E2" t="n">
         <v>0</v>
@@ -3200,16 +3203,16 @@
     </row>
     <row r="3">
       <c r="A3" t="s">
-        <v>176</v>
+        <v>177</v>
       </c>
       <c r="B3" t="s">
-        <v>179</v>
+        <v>180</v>
       </c>
       <c r="C3" t="s">
-        <v>180</v>
+        <v>181</v>
       </c>
       <c r="D3" t="s">
-        <v>50</v>
+        <v>51</v>
       </c>
       <c r="E3" t="n">
         <v>0</v>
@@ -3224,27 +3227,27 @@
         <v>53</v>
       </c>
       <c r="I3" t="s">
-        <v>37</v>
+        <v>38</v>
       </c>
       <c r="J3" t="s">
         <v>98</v>
       </c>
       <c r="K3" t="s">
-        <v>56</v>
+        <v>57</v>
       </c>
     </row>
     <row r="4">
       <c r="A4" t="s">
-        <v>176</v>
+        <v>177</v>
       </c>
       <c r="B4" t="s">
-        <v>181</v>
+        <v>182</v>
       </c>
       <c r="C4" t="s">
-        <v>182</v>
+        <v>183</v>
       </c>
       <c r="D4" t="s">
-        <v>50</v>
+        <v>51</v>
       </c>
       <c r="E4" t="n">
         <v>0</v>
@@ -3258,16 +3261,16 @@
     </row>
     <row r="5">
       <c r="A5" t="s">
-        <v>176</v>
+        <v>177</v>
       </c>
       <c r="B5" t="s">
-        <v>183</v>
+        <v>184</v>
       </c>
       <c r="C5" t="s">
-        <v>184</v>
+        <v>185</v>
       </c>
       <c r="D5" t="s">
-        <v>106</v>
+        <v>107</v>
       </c>
       <c r="E5" t="n">
         <v>0</v>
@@ -3282,27 +3285,27 @@
         <v>52</v>
       </c>
       <c r="I5" t="s">
-        <v>37</v>
+        <v>38</v>
       </c>
       <c r="J5" t="s">
         <v>98</v>
       </c>
       <c r="K5" t="s">
-        <v>61</v>
+        <v>62</v>
       </c>
     </row>
     <row r="6">
       <c r="A6" t="s">
-        <v>176</v>
+        <v>177</v>
       </c>
       <c r="B6" t="s">
-        <v>185</v>
+        <v>186</v>
       </c>
       <c r="C6" t="s">
-        <v>186</v>
+        <v>187</v>
       </c>
       <c r="D6" t="s">
-        <v>79</v>
+        <v>80</v>
       </c>
       <c r="E6" t="n">
         <v>0</v>
@@ -3317,27 +3320,27 @@
         <v>59</v>
       </c>
       <c r="I6" t="s">
-        <v>37</v>
+        <v>38</v>
       </c>
       <c r="J6" t="s">
         <v>20</v>
       </c>
       <c r="K6" t="s">
-        <v>38</v>
+        <v>39</v>
       </c>
     </row>
     <row r="7">
       <c r="A7" t="s">
-        <v>176</v>
+        <v>177</v>
       </c>
       <c r="B7" t="s">
-        <v>187</v>
+        <v>188</v>
       </c>
       <c r="C7" t="s">
-        <v>188</v>
+        <v>189</v>
       </c>
       <c r="D7" t="s">
-        <v>41</v>
+        <v>42</v>
       </c>
       <c r="E7" t="n">
         <v>0</v>
@@ -3355,24 +3358,24 @@
         <v>15</v>
       </c>
       <c r="J7" t="s">
-        <v>43</v>
+        <v>44</v>
       </c>
       <c r="K7" t="s">
-        <v>51</v>
+        <v>52</v>
       </c>
     </row>
     <row r="8">
       <c r="A8" t="s">
-        <v>176</v>
+        <v>177</v>
       </c>
       <c r="B8" t="s">
-        <v>189</v>
+        <v>190</v>
       </c>
       <c r="C8" t="s">
-        <v>190</v>
+        <v>191</v>
       </c>
       <c r="D8" t="s">
-        <v>67</v>
+        <v>68</v>
       </c>
       <c r="E8" t="n">
         <v>0</v>
@@ -3387,24 +3390,24 @@
         <v>46</v>
       </c>
       <c r="I8" t="s">
-        <v>37</v>
+        <v>38</v>
       </c>
       <c r="J8" t="s">
-        <v>43</v>
+        <v>44</v>
       </c>
       <c r="K8" t="s">
-        <v>68</v>
+        <v>69</v>
       </c>
     </row>
     <row r="9">
       <c r="A9" t="s">
-        <v>176</v>
+        <v>177</v>
       </c>
       <c r="B9" t="s">
-        <v>191</v>
+        <v>192</v>
       </c>
       <c r="C9" t="s">
-        <v>192</v>
+        <v>193</v>
       </c>
       <c r="D9" t="s">
         <v>14</v>
@@ -3425,24 +3428,24 @@
         <v>15</v>
       </c>
       <c r="J9" t="s">
-        <v>43</v>
+        <v>44</v>
       </c>
       <c r="K9" t="s">
-        <v>47</v>
+        <v>48</v>
       </c>
     </row>
     <row r="10">
       <c r="A10" t="s">
-        <v>176</v>
+        <v>177</v>
       </c>
       <c r="B10" t="s">
-        <v>193</v>
+        <v>194</v>
       </c>
       <c r="C10" t="s">
-        <v>194</v>
+        <v>195</v>
       </c>
       <c r="D10" t="s">
-        <v>71</v>
+        <v>72</v>
       </c>
       <c r="E10" t="n">
         <v>0</v>
@@ -3457,7 +3460,7 @@
         <v>38</v>
       </c>
       <c r="I10" t="s">
-        <v>84</v>
+        <v>85</v>
       </c>
       <c r="J10" t="s">
         <v>98</v>
@@ -3468,16 +3471,16 @@
     </row>
     <row r="11">
       <c r="A11" t="s">
-        <v>176</v>
+        <v>177</v>
       </c>
       <c r="B11" t="s">
-        <v>195</v>
+        <v>196</v>
       </c>
       <c r="C11" t="s">
-        <v>196</v>
+        <v>197</v>
       </c>
       <c r="D11" t="s">
-        <v>197</v>
+        <v>198</v>
       </c>
       <c r="E11" t="n">
         <v>1</v>
@@ -3492,10 +3495,10 @@
         <v>23</v>
       </c>
       <c r="I11" t="s">
-        <v>42</v>
+        <v>43</v>
       </c>
       <c r="J11" t="s">
-        <v>198</v>
+        <v>199</v>
       </c>
       <c r="K11" t="s">
         <v>16</v>
@@ -3549,16 +3552,16 @@
     </row>
     <row r="2">
       <c r="A2" t="s">
-        <v>199</v>
+        <v>200</v>
       </c>
       <c r="B2" t="s">
-        <v>200</v>
+        <v>201</v>
       </c>
       <c r="C2" t="s">
-        <v>201</v>
+        <v>202</v>
       </c>
       <c r="D2" t="s">
-        <v>50</v>
+        <v>51</v>
       </c>
       <c r="E2" t="n">
         <v>1</v>

--- a/Stat Reviews/OT24_StatReview/scotusblog_replication/data/term_index.xlsx
+++ b/Stat Reviews/OT24_StatReview/scotusblog_replication/data/term_index.xlsx
@@ -1146,7 +1146,7 @@
       </c>
       <c r="H6"/>
       <c r="I6" t="s">
-        <v>24</v>
+        <v>29</v>
       </c>
       <c r="J6" t="s">
         <v>20</v>
@@ -2195,12 +2195,24 @@
       <c r="E2" t="n">
         <v>0</v>
       </c>
-      <c r="F2" s="1"/>
-      <c r="G2" s="1"/>
-      <c r="H2"/>
-      <c r="I2"/>
-      <c r="J2"/>
-      <c r="K2"/>
+      <c r="F2" s="1" t="n">
+        <v>45670</v>
+      </c>
+      <c r="G2" s="1" t="n">
+        <v>45834</v>
+      </c>
+      <c r="H2" t="n">
+        <v>165</v>
+      </c>
+      <c r="I2" t="s">
+        <v>38</v>
+      </c>
+      <c r="J2" t="s">
+        <v>25</v>
+      </c>
+      <c r="K2" t="s">
+        <v>65</v>
+      </c>
     </row>
     <row r="3">
       <c r="A3" t="s">
@@ -2567,12 +2579,24 @@
       <c r="E2" t="n">
         <v>0</v>
       </c>
-      <c r="F2" s="1"/>
-      <c r="G2" s="1"/>
-      <c r="H2"/>
-      <c r="I2"/>
-      <c r="J2"/>
-      <c r="K2"/>
+      <c r="F2" s="1" t="n">
+        <v>45712</v>
+      </c>
+      <c r="G2" s="1" t="n">
+        <v>45834</v>
+      </c>
+      <c r="H2" t="n">
+        <v>123</v>
+      </c>
+      <c r="I2" t="s">
+        <v>38</v>
+      </c>
+      <c r="J2" t="s">
+        <v>104</v>
+      </c>
+      <c r="K2" t="s">
+        <v>57</v>
+      </c>
     </row>
     <row r="3">
       <c r="A3" t="s">
@@ -2904,12 +2928,24 @@
       <c r="E3" t="n">
         <v>0</v>
       </c>
-      <c r="F3" s="1"/>
-      <c r="G3" s="1"/>
-      <c r="H3"/>
-      <c r="I3"/>
-      <c r="J3"/>
-      <c r="K3"/>
+      <c r="F3" s="1" t="n">
+        <v>45740</v>
+      </c>
+      <c r="G3" s="1" t="n">
+        <v>45834</v>
+      </c>
+      <c r="H3" t="n">
+        <v>95</v>
+      </c>
+      <c r="I3" t="s">
+        <v>15</v>
+      </c>
+      <c r="J3" t="s">
+        <v>25</v>
+      </c>
+      <c r="K3" t="s">
+        <v>73</v>
+      </c>
     </row>
     <row r="4">
       <c r="A4" t="s">
@@ -3125,12 +3161,24 @@
       <c r="E10" t="n">
         <v>0</v>
       </c>
-      <c r="F10" s="1"/>
-      <c r="G10" s="1"/>
-      <c r="H10"/>
-      <c r="I10"/>
-      <c r="J10"/>
-      <c r="K10"/>
+      <c r="F10" s="1" t="n">
+        <v>45749</v>
+      </c>
+      <c r="G10" s="1" t="n">
+        <v>45834</v>
+      </c>
+      <c r="H10" t="n">
+        <v>86</v>
+      </c>
+      <c r="I10" t="s">
+        <v>38</v>
+      </c>
+      <c r="J10" t="s">
+        <v>104</v>
+      </c>
+      <c r="K10" t="s">
+        <v>48</v>
+      </c>
     </row>
   </sheetData>
   <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>

--- a/Stat Reviews/OT24_StatReview/scotusblog_replication/data/term_index.xlsx
+++ b/Stat Reviews/OT24_StatReview/scotusblog_replication/data/term_index.xlsx
@@ -1,634 +1,645 @@
 
 <file path=xl/workbook.xml><?xml version="1.0" encoding="utf-8"?>
 <workbook xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x15="http://schemas.microsoft.com/office/spreadsheetml/2010/11/main" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr6="http://schemas.microsoft.com/office/spreadsheetml/2016/revision6" xmlns:xr10="http://schemas.microsoft.com/office/spreadsheetml/2016/revision10" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" mc:Ignorable="x15 xr xr6 xr10 xr2">
-  <workbookPr date1904="false"/>
+  <fileVersion appName="xl" lastEdited="7" lowestEdited="7" rupBuild="28827"/>
+  <workbookPr/>
+  <mc:AlternateContent xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006">
+    <mc:Choice Requires="x15">
+      <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\Users\jaketruscott\Github\scotuswatch\Stat Reviews\OT24_StatReview\scotusblog_replication\data\"/>
+    </mc:Choice>
+  </mc:AlternateContent>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{A8276E09-40AF-4186-939A-95F7E6928968}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
-    <workbookView xWindow="0" yWindow="0" windowWidth="13125" windowHeight="6105" firstSheet="0" activeTab="0"/>
+    <workbookView xWindow="28680" yWindow="-120" windowWidth="29040" windowHeight="15720" activeTab="6" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
   <sheets>
-    <sheet name="No_Argument" sheetId="1" state="visible" r:id="rId1"/>
-    <sheet name="October" sheetId="2" state="visible" r:id="rId2"/>
-    <sheet name="November" sheetId="3" state="visible" r:id="rId3"/>
-    <sheet name="December" sheetId="4" state="visible" r:id="rId4"/>
-    <sheet name="January" sheetId="5" state="visible" r:id="rId5"/>
-    <sheet name="February" sheetId="6" state="visible" r:id="rId6"/>
-    <sheet name="March" sheetId="7" state="visible" r:id="rId7"/>
-    <sheet name="April" sheetId="8" state="visible" r:id="rId8"/>
-    <sheet name="May" sheetId="9" state="visible" r:id="rId9"/>
+    <sheet name="No_Argument" sheetId="1" r:id="rId1"/>
+    <sheet name="October" sheetId="2" r:id="rId2"/>
+    <sheet name="November" sheetId="3" r:id="rId3"/>
+    <sheet name="December" sheetId="4" r:id="rId4"/>
+    <sheet name="January" sheetId="5" r:id="rId5"/>
+    <sheet name="February" sheetId="6" r:id="rId6"/>
+    <sheet name="March" sheetId="7" r:id="rId7"/>
+    <sheet name="April" sheetId="8" r:id="rId8"/>
+    <sheet name="May" sheetId="9" r:id="rId9"/>
   </sheets>
+  <calcPr calcId="0"/>
 </workbook>
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="203" uniqueCount="203">
-  <si>
-    <t xml:space="preserve">sitting</t>
-  </si>
-  <si>
-    <t xml:space="preserve">docket</t>
-  </si>
-  <si>
-    <t xml:space="preserve">short_hand</t>
-  </si>
-  <si>
-    <t xml:space="preserve">lower_court</t>
-  </si>
-  <si>
-    <t xml:space="preserve">major_case</t>
-  </si>
-  <si>
-    <t xml:space="preserve">date_argued</t>
-  </si>
-  <si>
-    <t xml:space="preserve">date_decided</t>
-  </si>
-  <si>
-    <t xml:space="preserve">days_elapsed</t>
-  </si>
-  <si>
-    <t xml:space="preserve">decision</t>
-  </si>
-  <si>
-    <t xml:space="preserve">coalition</t>
-  </si>
-  <si>
-    <t xml:space="preserve">author</t>
-  </si>
-  <si>
-    <t xml:space="preserve">No Argument</t>
-  </si>
-  <si>
-    <t xml:space="preserve">23-167</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Hamm</t>
-  </si>
-  <si>
-    <t xml:space="preserve">CA11</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Vacate and Remand</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Per Curiam</t>
-  </si>
-  <si>
-    <t xml:space="preserve">23-6573</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Andrew</t>
-  </si>
-  <si>
-    <t xml:space="preserve">CA10</t>
-  </si>
-  <si>
-    <t xml:space="preserve">(7-2)</t>
-  </si>
-  <si>
-    <t xml:space="preserve">24A910</t>
-  </si>
-  <si>
-    <t xml:space="preserve">DOE v. CA</t>
-  </si>
-  <si>
-    <t xml:space="preserve">DCMA</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Granted</t>
-  </si>
-  <si>
-    <t xml:space="preserve">(5-4)</t>
-  </si>
-  <si>
-    <t xml:space="preserve">24A931</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Trump v. J.G.G.</t>
-  </si>
-  <si>
-    <t xml:space="preserve">DCDC</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Vacate</t>
-  </si>
-  <si>
-    <t xml:space="preserve">(5-4)*</t>
-  </si>
-  <si>
-    <t xml:space="preserve">24A1007</t>
-  </si>
-  <si>
-    <t xml:space="preserve">A.A.R.P v. Trump</t>
-  </si>
-  <si>
-    <t xml:space="preserve">CA5</t>
-  </si>
-  <si>
-    <t xml:space="preserve">October</t>
-  </si>
-  <si>
-    <t xml:space="preserve">23-191</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Williams</t>
-  </si>
-  <si>
-    <t xml:space="preserve">SCAL</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Reverse and Remand</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Kavanaugh</t>
-  </si>
-  <si>
-    <t xml:space="preserve">23-677</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Royal Canin</t>
-  </si>
-  <si>
-    <t xml:space="preserve">CA8</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Affirm</t>
-  </si>
-  <si>
-    <t xml:space="preserve">(9-0)</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Kagan</t>
-  </si>
-  <si>
-    <t xml:space="preserve">23-852</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Vanderstok</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Gorsuch</t>
-  </si>
-  <si>
-    <t xml:space="preserve">23-621</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Lackey</t>
-  </si>
-  <si>
-    <t xml:space="preserve">CA4</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Roberts</t>
-  </si>
-  <si>
-    <t xml:space="preserve">22-7466</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Glossip</t>
-  </si>
-  <si>
-    <t xml:space="preserve">CCAOK</t>
-  </si>
-  <si>
-    <t xml:space="preserve">(5-3)</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Sotomayor</t>
-  </si>
-  <si>
-    <t xml:space="preserve">23-365</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Medical Marijuana</t>
-  </si>
-  <si>
-    <t xml:space="preserve">CA2</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Affirm and Remand</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Barrett</t>
-  </si>
-  <si>
-    <t xml:space="preserve">23-583</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Bouarfa</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Jackson</t>
-  </si>
-  <si>
-    <t xml:space="preserve">23-713</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Bufkin</t>
-  </si>
-  <si>
-    <t xml:space="preserve">CAFED</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Thomas</t>
-  </si>
-  <si>
-    <t xml:space="preserve">23-753</t>
-  </si>
-  <si>
-    <t xml:space="preserve">SF v. EPA</t>
-  </si>
-  <si>
-    <t xml:space="preserve">CA9</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Alito</t>
-  </si>
-  <si>
-    <t xml:space="preserve">November</t>
-  </si>
-  <si>
-    <t xml:space="preserve">23-1127</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Wisconsin Bell</t>
-  </si>
-  <si>
-    <t xml:space="preserve">CA7</t>
-  </si>
-  <si>
-    <t xml:space="preserve">23-715</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Advocate Christ Medical</t>
-  </si>
-  <si>
-    <t xml:space="preserve">CADC</t>
-  </si>
-  <si>
-    <t xml:space="preserve">23-217</t>
-  </si>
-  <si>
-    <t xml:space="preserve">E.M.D. Sales</t>
-  </si>
-  <si>
-    <t xml:space="preserve">23-980</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Facebook</t>
-  </si>
-  <si>
-    <t xml:space="preserve">DIG</t>
-  </si>
-  <si>
-    <t xml:space="preserve">23-929</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Velazquez</t>
-  </si>
-  <si>
-    <t xml:space="preserve">23-825</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Delligatti</t>
-  </si>
-  <si>
-    <t xml:space="preserve">23-970</t>
-  </si>
-  <si>
-    <t xml:space="preserve">NVIDIA</t>
-  </si>
-  <si>
-    <t xml:space="preserve">December</t>
-  </si>
-  <si>
-    <t xml:space="preserve">23-1038</t>
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="565" uniqueCount="204">
+  <si>
+    <t>sitting</t>
+  </si>
+  <si>
+    <t>docket</t>
+  </si>
+  <si>
+    <t>short_hand</t>
+  </si>
+  <si>
+    <t>lower_court</t>
+  </si>
+  <si>
+    <t>major_case</t>
+  </si>
+  <si>
+    <t>date_argued</t>
+  </si>
+  <si>
+    <t>date_decided</t>
+  </si>
+  <si>
+    <t>days_elapsed</t>
+  </si>
+  <si>
+    <t>decision</t>
+  </si>
+  <si>
+    <t>coalition</t>
+  </si>
+  <si>
+    <t>author</t>
+  </si>
+  <si>
+    <t>No Argument</t>
+  </si>
+  <si>
+    <t>23-167</t>
+  </si>
+  <si>
+    <t>Hamm</t>
+  </si>
+  <si>
+    <t>CA11</t>
+  </si>
+  <si>
+    <t>Vacate and Remand</t>
+  </si>
+  <si>
+    <t>Per Curiam</t>
+  </si>
+  <si>
+    <t>23-6573</t>
+  </si>
+  <si>
+    <t>Andrew</t>
+  </si>
+  <si>
+    <t>CA10</t>
+  </si>
+  <si>
+    <t>(7-2)</t>
+  </si>
+  <si>
+    <t>24A910</t>
+  </si>
+  <si>
+    <t>DOE v. CA</t>
+  </si>
+  <si>
+    <t>DCMA</t>
+  </si>
+  <si>
+    <t>Granted</t>
+  </si>
+  <si>
+    <t>(5-4)</t>
+  </si>
+  <si>
+    <t>24A931</t>
+  </si>
+  <si>
+    <t>Trump v. J.G.G.</t>
+  </si>
+  <si>
+    <t>DCDC</t>
+  </si>
+  <si>
+    <t>Vacate</t>
+  </si>
+  <si>
+    <t>(5-4)*</t>
+  </si>
+  <si>
+    <t>24A1007</t>
+  </si>
+  <si>
+    <t>A.A.R.P v. Trump</t>
+  </si>
+  <si>
+    <t>CA5</t>
+  </si>
+  <si>
+    <t>October</t>
+  </si>
+  <si>
+    <t>23-191</t>
+  </si>
+  <si>
+    <t>Williams</t>
+  </si>
+  <si>
+    <t>SCAL</t>
+  </si>
+  <si>
+    <t>Reverse and Remand</t>
+  </si>
+  <si>
+    <t>Kavanaugh</t>
+  </si>
+  <si>
+    <t>23-677</t>
+  </si>
+  <si>
+    <t>Royal Canin</t>
+  </si>
+  <si>
+    <t>CA8</t>
+  </si>
+  <si>
+    <t>Affirm</t>
+  </si>
+  <si>
+    <t>(9-0)</t>
+  </si>
+  <si>
+    <t>Kagan</t>
+  </si>
+  <si>
+    <t>23-852</t>
+  </si>
+  <si>
+    <t>Vanderstok</t>
+  </si>
+  <si>
+    <t>Gorsuch</t>
+  </si>
+  <si>
+    <t>23-621</t>
+  </si>
+  <si>
+    <t>Lackey</t>
+  </si>
+  <si>
+    <t>CA4</t>
+  </si>
+  <si>
+    <t>Roberts</t>
+  </si>
+  <si>
+    <t>22-7466</t>
+  </si>
+  <si>
+    <t>Glossip</t>
+  </si>
+  <si>
+    <t>CCAOK</t>
+  </si>
+  <si>
+    <t>(5-3)</t>
+  </si>
+  <si>
+    <t>Sotomayor</t>
+  </si>
+  <si>
+    <t>23-365</t>
+  </si>
+  <si>
+    <t>Medical Marijuana</t>
+  </si>
+  <si>
+    <t>CA2</t>
+  </si>
+  <si>
+    <t>Affirm and Remand</t>
+  </si>
+  <si>
+    <t>Barrett</t>
+  </si>
+  <si>
+    <t>23-583</t>
+  </si>
+  <si>
+    <t>Bouarfa</t>
+  </si>
+  <si>
+    <t>Jackson</t>
+  </si>
+  <si>
+    <t>23-713</t>
+  </si>
+  <si>
+    <t>Bufkin</t>
+  </si>
+  <si>
+    <t>CAFED</t>
+  </si>
+  <si>
+    <t>Thomas</t>
+  </si>
+  <si>
+    <t>23-753</t>
+  </si>
+  <si>
+    <t>SF v. EPA</t>
+  </si>
+  <si>
+    <t>CA9</t>
+  </si>
+  <si>
+    <t>Alito</t>
+  </si>
+  <si>
+    <t>November</t>
+  </si>
+  <si>
+    <t>23-1127</t>
+  </si>
+  <si>
+    <t>Wisconsin Bell</t>
+  </si>
+  <si>
+    <t>CA7</t>
+  </si>
+  <si>
+    <t>23-715</t>
+  </si>
+  <si>
+    <t>Advocate Christ Medical</t>
+  </si>
+  <si>
+    <t>CADC</t>
+  </si>
+  <si>
+    <t>23-217</t>
+  </si>
+  <si>
+    <t>E.M.D. Sales</t>
+  </si>
+  <si>
+    <t>23-980</t>
+  </si>
+  <si>
+    <t>Facebook</t>
+  </si>
+  <si>
+    <t>DIG</t>
+  </si>
+  <si>
+    <t>23-929</t>
+  </si>
+  <si>
+    <t>Velazquez</t>
+  </si>
+  <si>
+    <t>23-825</t>
+  </si>
+  <si>
+    <t>Delligatti</t>
+  </si>
+  <si>
+    <t>23-970</t>
+  </si>
+  <si>
+    <t>NVIDIA</t>
+  </si>
+  <si>
+    <t>December</t>
+  </si>
+  <si>
+    <t>23-1038</t>
   </si>
   <si>
     <t xml:space="preserve">Wages and White Lion </t>
   </si>
   <si>
-    <t xml:space="preserve">23-824</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Miller</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Reverse</t>
-  </si>
-  <si>
-    <t xml:space="preserve">(8-1)</t>
-  </si>
-  <si>
-    <t xml:space="preserve">23-867</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Hungary</t>
-  </si>
-  <si>
-    <t xml:space="preserve">23-477</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Skrmetti</t>
-  </si>
-  <si>
-    <t xml:space="preserve">CA6</t>
-  </si>
-  <si>
-    <t xml:space="preserve">(6-3)</t>
-  </si>
-  <si>
-    <t xml:space="preserve">23-909</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Kousisis</t>
-  </si>
-  <si>
-    <t xml:space="preserve">CA3</t>
-  </si>
-  <si>
-    <t xml:space="preserve">23-861</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Feliciano</t>
-  </si>
-  <si>
-    <t xml:space="preserve">23-975</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Seven County</t>
-  </si>
-  <si>
-    <t xml:space="preserve">(8-0)</t>
-  </si>
-  <si>
-    <t xml:space="preserve">23-900</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Dewberry</t>
-  </si>
-  <si>
-    <t xml:space="preserve">January</t>
-  </si>
-  <si>
-    <t xml:space="preserve">23-1002</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Hewitt</t>
-  </si>
-  <si>
-    <t xml:space="preserve">23-997</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Stanley</t>
-  </si>
-  <si>
-    <t xml:space="preserve">(8-1)*</t>
-  </si>
-  <si>
-    <t xml:space="preserve">23-1095</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Thompson</t>
-  </si>
-  <si>
-    <t xml:space="preserve">23-971</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Waetzig</t>
-  </si>
-  <si>
-    <t xml:space="preserve">23-1122</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Free Speech</t>
-  </si>
-  <si>
-    <t xml:space="preserve">23-1187</t>
+    <t>23-824</t>
+  </si>
+  <si>
+    <t>Miller</t>
+  </si>
+  <si>
+    <t>Reverse</t>
+  </si>
+  <si>
+    <t>(8-1)</t>
+  </si>
+  <si>
+    <t>23-867</t>
+  </si>
+  <si>
+    <t>Hungary</t>
+  </si>
+  <si>
+    <t>23-477</t>
+  </si>
+  <si>
+    <t>Skrmetti</t>
+  </si>
+  <si>
+    <t>CA6</t>
+  </si>
+  <si>
+    <t>(6-3)</t>
+  </si>
+  <si>
+    <t>23-909</t>
+  </si>
+  <si>
+    <t>Kousisis</t>
+  </si>
+  <si>
+    <t>CA3</t>
+  </si>
+  <si>
+    <t>23-861</t>
+  </si>
+  <si>
+    <t>Feliciano</t>
+  </si>
+  <si>
+    <t>23-975</t>
+  </si>
+  <si>
+    <t>Seven County</t>
+  </si>
+  <si>
+    <t>(8-0)</t>
+  </si>
+  <si>
+    <t>23-900</t>
+  </si>
+  <si>
+    <t>Dewberry</t>
+  </si>
+  <si>
+    <t>January</t>
+  </si>
+  <si>
+    <t>23-1002</t>
+  </si>
+  <si>
+    <t>Hewitt</t>
+  </si>
+  <si>
+    <t>23-997</t>
+  </si>
+  <si>
+    <t>Stanley</t>
+  </si>
+  <si>
+    <t>(8-1)*</t>
+  </si>
+  <si>
+    <t>23-1095</t>
+  </si>
+  <si>
+    <t>Thompson</t>
+  </si>
+  <si>
+    <t>23-971</t>
+  </si>
+  <si>
+    <t>Waetzig</t>
+  </si>
+  <si>
+    <t>23-1122</t>
+  </si>
+  <si>
+    <t>Free Speech</t>
+  </si>
+  <si>
+    <t>Affirmed</t>
+  </si>
+  <si>
+    <t>23-1187</t>
   </si>
   <si>
     <t xml:space="preserve"> R.J. Reynolds </t>
   </si>
   <si>
-    <t xml:space="preserve">23-1226</t>
-  </si>
-  <si>
-    <t xml:space="preserve">McLaughlin</t>
-  </si>
-  <si>
-    <t xml:space="preserve">23-1239</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Barnes</t>
-  </si>
-  <si>
-    <t xml:space="preserve">23-1007</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Cunningham</t>
-  </si>
-  <si>
-    <t xml:space="preserve">24-656</t>
-  </si>
-  <si>
-    <t xml:space="preserve">TikTok</t>
-  </si>
-  <si>
-    <t xml:space="preserve">February</t>
-  </si>
-  <si>
-    <t xml:space="preserve">23-7809</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Guitierrez</t>
-  </si>
-  <si>
-    <t xml:space="preserve">23-7483</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Esteras</t>
-  </si>
-  <si>
-    <t xml:space="preserve">(7-2)*</t>
-  </si>
-  <si>
-    <t xml:space="preserve">23-1324</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Perttu</t>
-  </si>
-  <si>
-    <t xml:space="preserve">23-1039</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Ames</t>
-  </si>
-  <si>
-    <t xml:space="preserve">23-1201</t>
-  </si>
-  <si>
-    <t xml:space="preserve">CC/Devas</t>
-  </si>
-  <si>
-    <t xml:space="preserve">23-1259</t>
-  </si>
-  <si>
-    <t xml:space="preserve">BLOM Bank</t>
-  </si>
-  <si>
-    <t xml:space="preserve">23-1141</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Smith and Wesson</t>
-  </si>
-  <si>
-    <t xml:space="preserve">CA1</t>
-  </si>
-  <si>
-    <t xml:space="preserve">23-1300</t>
-  </si>
-  <si>
-    <t xml:space="preserve">NRC</t>
-  </si>
-  <si>
-    <t xml:space="preserve">March</t>
-  </si>
-  <si>
-    <t xml:space="preserve">24-109</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Lousiana</t>
-  </si>
-  <si>
-    <t xml:space="preserve">WDLA</t>
-  </si>
-  <si>
-    <t xml:space="preserve">23-1270</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Riley</t>
-  </si>
-  <si>
-    <t xml:space="preserve">23-1229</t>
+    <t>23-1226</t>
+  </si>
+  <si>
+    <t>McLaughlin</t>
+  </si>
+  <si>
+    <t>23-1239</t>
+  </si>
+  <si>
+    <t>Barnes</t>
+  </si>
+  <si>
+    <t>23-1007</t>
+  </si>
+  <si>
+    <t>Cunningham</t>
+  </si>
+  <si>
+    <t>24-656</t>
+  </si>
+  <si>
+    <t>TikTok</t>
+  </si>
+  <si>
+    <t>February</t>
+  </si>
+  <si>
+    <t>23-7809</t>
+  </si>
+  <si>
+    <t>Guitierrez</t>
+  </si>
+  <si>
+    <t>23-7483</t>
+  </si>
+  <si>
+    <t>Esteras</t>
+  </si>
+  <si>
+    <t>(7-2)*</t>
+  </si>
+  <si>
+    <t>23-1324</t>
+  </si>
+  <si>
+    <t>Perttu</t>
+  </si>
+  <si>
+    <t>23-1039</t>
+  </si>
+  <si>
+    <t>Ames</t>
+  </si>
+  <si>
+    <t>23-1201</t>
+  </si>
+  <si>
+    <t>CC/Devas</t>
+  </si>
+  <si>
+    <t>23-1259</t>
+  </si>
+  <si>
+    <t>BLOM Bank</t>
+  </si>
+  <si>
+    <t>23-1141</t>
+  </si>
+  <si>
+    <t>Smith and Wesson</t>
+  </si>
+  <si>
+    <t>CA1</t>
+  </si>
+  <si>
+    <t>23-1300</t>
+  </si>
+  <si>
+    <t>NRC</t>
+  </si>
+  <si>
+    <t>March</t>
+  </si>
+  <si>
+    <t>24-109</t>
+  </si>
+  <si>
+    <t>Lousiana</t>
+  </si>
+  <si>
+    <t>WDLA</t>
+  </si>
+  <si>
+    <t>23-1270</t>
+  </si>
+  <si>
+    <t>Riley</t>
+  </si>
+  <si>
+    <t>23-1229</t>
   </si>
   <si>
     <t xml:space="preserve">Calumet </t>
   </si>
   <si>
-    <t xml:space="preserve">23-1067</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Oklahoma</t>
-  </si>
-  <si>
-    <t xml:space="preserve">24-354</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Consumers' Research</t>
-  </si>
-  <si>
-    <t xml:space="preserve">24-154</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Catholic Charities</t>
-  </si>
-  <si>
-    <t xml:space="preserve">SCWI</t>
-  </si>
-  <si>
-    <t xml:space="preserve">23-1345</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Rivers</t>
-  </si>
-  <si>
-    <t xml:space="preserve">24-20</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Fuld</t>
-  </si>
-  <si>
-    <t xml:space="preserve">23-1275</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Medina</t>
-  </si>
-  <si>
-    <t xml:space="preserve">April</t>
-  </si>
-  <si>
-    <t xml:space="preserve">24-316</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Kennedy</t>
-  </si>
-  <si>
-    <t xml:space="preserve">24-275</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Parrish</t>
-  </si>
-  <si>
-    <t xml:space="preserve">24-297</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Mahmoud</t>
-  </si>
-  <si>
-    <t xml:space="preserve">24-416</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Zuch</t>
-  </si>
-  <si>
-    <t xml:space="preserve">24-7</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Diamond</t>
-  </si>
-  <si>
-    <t xml:space="preserve">24-249</t>
-  </si>
-  <si>
-    <t xml:space="preserve">A.J.T.</t>
-  </si>
-  <si>
-    <t xml:space="preserve">24-320</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Soto</t>
-  </si>
-  <si>
-    <t xml:space="preserve">24-362</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Martin</t>
-  </si>
-  <si>
-    <t xml:space="preserve">24-304</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Laboratory Corp.</t>
-  </si>
-  <si>
-    <t xml:space="preserve">24-394</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Drummond</t>
-  </si>
-  <si>
-    <t xml:space="preserve">SCOK</t>
-  </si>
-  <si>
-    <t xml:space="preserve">(4-4)*</t>
-  </si>
-  <si>
-    <t xml:space="preserve">May</t>
-  </si>
-  <si>
-    <t xml:space="preserve">24A884</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Trump v. CASA</t>
+    <t>23-1067</t>
+  </si>
+  <si>
+    <t>Oklahoma</t>
+  </si>
+  <si>
+    <t>24-354</t>
+  </si>
+  <si>
+    <t>Consumers' Research</t>
+  </si>
+  <si>
+    <t>24-154</t>
+  </si>
+  <si>
+    <t>Catholic Charities</t>
+  </si>
+  <si>
+    <t>SCWI</t>
+  </si>
+  <si>
+    <t>23-1345</t>
+  </si>
+  <si>
+    <t>Rivers</t>
+  </si>
+  <si>
+    <t>24-20</t>
+  </si>
+  <si>
+    <t>Fuld</t>
+  </si>
+  <si>
+    <t>23-1275</t>
+  </si>
+  <si>
+    <t>Medina</t>
+  </si>
+  <si>
+    <t>April</t>
+  </si>
+  <si>
+    <t>24-316</t>
+  </si>
+  <si>
+    <t>Kennedy</t>
+  </si>
+  <si>
+    <t>24-275</t>
+  </si>
+  <si>
+    <t>Parrish</t>
+  </si>
+  <si>
+    <t>24-297</t>
+  </si>
+  <si>
+    <t>Mahmoud</t>
+  </si>
+  <si>
+    <t>24-416</t>
+  </si>
+  <si>
+    <t>Zuch</t>
+  </si>
+  <si>
+    <t>24-7</t>
+  </si>
+  <si>
+    <t>Diamond</t>
+  </si>
+  <si>
+    <t>24-249</t>
+  </si>
+  <si>
+    <t>A.J.T.</t>
+  </si>
+  <si>
+    <t>24-320</t>
+  </si>
+  <si>
+    <t>Soto</t>
+  </si>
+  <si>
+    <t>24-362</t>
+  </si>
+  <si>
+    <t>Martin</t>
+  </si>
+  <si>
+    <t>24-304</t>
+  </si>
+  <si>
+    <t>Laboratory Corp.</t>
+  </si>
+  <si>
+    <t>24-394</t>
+  </si>
+  <si>
+    <t>Drummond</t>
+  </si>
+  <si>
+    <t>SCOK</t>
+  </si>
+  <si>
+    <t>(4-4)*</t>
+  </si>
+  <si>
+    <t>May</t>
+  </si>
+  <si>
+    <t>24A884</t>
+  </si>
+  <si>
+    <t>Trump v. CASA</t>
   </si>
 </sst>
 </file>
@@ -636,9 +647,9 @@
 <file path=xl/styles.xml><?xml version="1.0" encoding="utf-8"?>
 <styleSheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:x16r2="http://schemas.microsoft.com/office/spreadsheetml/2015/02/main" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" mc:Ignorable="x14ac x16r2 xr">
   <numFmts count="1">
-    <numFmt numFmtId="165" formatCode="mm/dd/yyyy"/>
+    <numFmt numFmtId="164" formatCode="mm/dd/yyyy"/>
   </numFmts>
-  <fonts count="2">
+  <fonts count="2" x14ac:knownFonts="1">
     <font>
       <sz val="11"/>
       <color rgb="FF000000"/>
@@ -674,12 +685,21 @@
   </cellStyleXfs>
   <cellXfs count="2">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0"/>
-    <xf numFmtId="165" fontId="1" fillId="0" borderId="0" xfId="0" applyFont="1" applyNumberFormat="1"/>
+    <xf numFmtId="164" fontId="1" fillId="0" borderId="0" xfId="0" applyNumberFormat="1" applyFont="1"/>
   </cellXfs>
   <cellStyles count="1">
     <cellStyle name="Normal" xfId="0" builtinId="0"/>
   </cellStyles>
   <dxfs count="0"/>
+  <tableStyles count="0" defaultTableStyle="TableStyleMedium2" defaultPivotStyle="PivotStyleLight16"/>
+  <extLst>
+    <ext xmlns:x14="http://schemas.microsoft.com/office/spreadsheetml/2009/9/main" uri="{EB79DEF2-80B8-43e5-95BD-54CBDDF9020C}">
+      <x14:slicerStyles defaultSlicerStyle="SlicerStyleLight1"/>
+    </ext>
+    <ext xmlns:x15="http://schemas.microsoft.com/office/spreadsheetml/2010/11/main" uri="{9260A510-F301-46a8-8635-F512D64BE5F5}">
+      <x15:timelineStyles defaultTimelineStyle="TimeSlicerStyleLight1"/>
+    </ext>
+  </extLst>
 </styleSheet>
 </file>
 
@@ -961,11 +981,11 @@
 </file>
 
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
-<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:xdr="http://schemas.openxmlformats.org/drawingml/2006/spreadsheetDrawing" xmlns:x14="http://schemas.microsoft.com/office/spreadsheetml/2009/9/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3">
-  <dimension ref="A1"/>
-  <sheetFormatPr defaultRowHeight="15.0" baseColWidth="10"/>
+<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{00000000-0001-0000-0000-000000000000}">
+  <dimension ref="A1:K6"/>
+  <sheetFormatPr defaultColWidth="11.42578125" defaultRowHeight="15" x14ac:dyDescent="0.25"/>
   <sheetData>
-    <row r="1">
+    <row r="1" spans="1:11" x14ac:dyDescent="0.25">
       <c r="A1" t="s">
         <v>0</v>
       </c>
@@ -1000,7 +1020,7 @@
         <v>10</v>
       </c>
     </row>
-    <row r="2">
+    <row r="2" spans="1:11" x14ac:dyDescent="0.25">
       <c r="A2" t="s">
         <v>11</v>
       </c>
@@ -1013,14 +1033,13 @@
       <c r="D2" t="s">
         <v>14</v>
       </c>
-      <c r="E2" t="n">
+      <c r="E2">
         <v>0</v>
       </c>
       <c r="F2" s="1"/>
-      <c r="G2" s="1" t="n">
+      <c r="G2" s="1">
         <v>45600</v>
       </c>
-      <c r="H2"/>
       <c r="I2" t="s">
         <v>15</v>
       </c>
@@ -1031,7 +1050,7 @@
         <v>16</v>
       </c>
     </row>
-    <row r="3">
+    <row r="3" spans="1:11" x14ac:dyDescent="0.25">
       <c r="A3" t="s">
         <v>11</v>
       </c>
@@ -1044,14 +1063,13 @@
       <c r="D3" t="s">
         <v>19</v>
       </c>
-      <c r="E3" t="n">
+      <c r="E3">
         <v>0</v>
       </c>
       <c r="F3" s="1"/>
-      <c r="G3" s="1" t="n">
+      <c r="G3" s="1">
         <v>45678</v>
       </c>
-      <c r="H3"/>
       <c r="I3" t="s">
         <v>15</v>
       </c>
@@ -1062,7 +1080,7 @@
         <v>16</v>
       </c>
     </row>
-    <row r="4">
+    <row r="4" spans="1:11" x14ac:dyDescent="0.25">
       <c r="A4" t="s">
         <v>11</v>
       </c>
@@ -1075,14 +1093,13 @@
       <c r="D4" t="s">
         <v>23</v>
       </c>
-      <c r="E4" t="n">
+      <c r="E4">
         <v>0</v>
       </c>
       <c r="F4" s="1"/>
-      <c r="G4" s="1" t="n">
+      <c r="G4" s="1">
         <v>45751</v>
       </c>
-      <c r="H4"/>
       <c r="I4" t="s">
         <v>24</v>
       </c>
@@ -1093,7 +1110,7 @@
         <v>16</v>
       </c>
     </row>
-    <row r="5">
+    <row r="5" spans="1:11" x14ac:dyDescent="0.25">
       <c r="A5" t="s">
         <v>11</v>
       </c>
@@ -1106,14 +1123,13 @@
       <c r="D5" t="s">
         <v>28</v>
       </c>
-      <c r="E5" t="n">
+      <c r="E5">
         <v>0</v>
       </c>
       <c r="F5" s="1"/>
-      <c r="G5" s="1" t="n">
+      <c r="G5" s="1">
         <v>45754</v>
       </c>
-      <c r="H5"/>
       <c r="I5" t="s">
         <v>29</v>
       </c>
@@ -1124,7 +1140,7 @@
         <v>16</v>
       </c>
     </row>
-    <row r="6">
+    <row r="6" spans="1:11" x14ac:dyDescent="0.25">
       <c r="A6" t="s">
         <v>11</v>
       </c>
@@ -1137,14 +1153,13 @@
       <c r="D6" t="s">
         <v>33</v>
       </c>
-      <c r="E6" t="n">
+      <c r="E6">
         <v>0</v>
       </c>
       <c r="F6" s="1"/>
-      <c r="G6" s="1" t="n">
+      <c r="G6" s="1">
         <v>45793</v>
       </c>
-      <c r="H6"/>
       <c r="I6" t="s">
         <v>29</v>
       </c>
@@ -1157,16 +1172,16 @@
     </row>
   </sheetData>
   <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
-  <pageSetup paperSize="9" orientation="portrait" horizontalDpi="300" verticalDpi="300" r:id="rId2"/>
+  <pageSetup paperSize="9" orientation="portrait" horizontalDpi="300" verticalDpi="300"/>
 </worksheet>
 </file>
 
 <file path=xl/worksheets/sheet2.xml><?xml version="1.0" encoding="utf-8"?>
-<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:xdr="http://schemas.openxmlformats.org/drawingml/2006/spreadsheetDrawing" xmlns:x14="http://schemas.microsoft.com/office/spreadsheetml/2009/9/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3">
-  <dimension ref="A1"/>
-  <sheetFormatPr defaultRowHeight="15.0" baseColWidth="10"/>
+<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{00000000-0001-0000-0100-000000000000}">
+  <dimension ref="A1:K10"/>
+  <sheetFormatPr defaultColWidth="11.42578125" defaultRowHeight="15" x14ac:dyDescent="0.25"/>
   <sheetData>
-    <row r="1">
+    <row r="1" spans="1:11" x14ac:dyDescent="0.25">
       <c r="A1" t="s">
         <v>0</v>
       </c>
@@ -1201,7 +1216,7 @@
         <v>10</v>
       </c>
     </row>
-    <row r="2">
+    <row r="2" spans="1:11" x14ac:dyDescent="0.25">
       <c r="A2" t="s">
         <v>34</v>
       </c>
@@ -1214,16 +1229,16 @@
       <c r="D2" t="s">
         <v>37</v>
       </c>
-      <c r="E2" t="n">
-        <v>0</v>
-      </c>
-      <c r="F2" s="1" t="n">
+      <c r="E2">
+        <v>0</v>
+      </c>
+      <c r="F2" s="1">
         <v>45572</v>
       </c>
-      <c r="G2" s="1" t="n">
+      <c r="G2" s="1">
         <v>45709</v>
       </c>
-      <c r="H2" t="n">
+      <c r="H2">
         <v>138</v>
       </c>
       <c r="I2" t="s">
@@ -1236,7 +1251,7 @@
         <v>39</v>
       </c>
     </row>
-    <row r="3">
+    <row r="3" spans="1:11" x14ac:dyDescent="0.25">
       <c r="A3" t="s">
         <v>34</v>
       </c>
@@ -1249,16 +1264,16 @@
       <c r="D3" t="s">
         <v>42</v>
       </c>
-      <c r="E3" t="n">
-        <v>0</v>
-      </c>
-      <c r="F3" s="1" t="n">
+      <c r="E3">
+        <v>0</v>
+      </c>
+      <c r="F3" s="1">
         <v>45572</v>
       </c>
-      <c r="G3" s="1" t="n">
+      <c r="G3" s="1">
         <v>45672</v>
       </c>
-      <c r="H3" t="n">
+      <c r="H3">
         <v>101</v>
       </c>
       <c r="I3" t="s">
@@ -1271,7 +1286,7 @@
         <v>45</v>
       </c>
     </row>
-    <row r="4">
+    <row r="4" spans="1:11" x14ac:dyDescent="0.25">
       <c r="A4" t="s">
         <v>34</v>
       </c>
@@ -1284,16 +1299,16 @@
       <c r="D4" t="s">
         <v>33</v>
       </c>
-      <c r="E4" t="n">
-        <v>0</v>
-      </c>
-      <c r="F4" s="1" t="n">
+      <c r="E4">
+        <v>0</v>
+      </c>
+      <c r="F4" s="1">
         <v>45573</v>
       </c>
-      <c r="G4" s="1" t="n">
+      <c r="G4" s="1">
         <v>45742</v>
       </c>
-      <c r="H4" t="n">
+      <c r="H4">
         <v>170</v>
       </c>
       <c r="I4" t="s">
@@ -1306,7 +1321,7 @@
         <v>48</v>
       </c>
     </row>
-    <row r="5">
+    <row r="5" spans="1:11" x14ac:dyDescent="0.25">
       <c r="A5" t="s">
         <v>34</v>
       </c>
@@ -1319,16 +1334,16 @@
       <c r="D5" t="s">
         <v>51</v>
       </c>
-      <c r="E5" t="n">
-        <v>0</v>
-      </c>
-      <c r="F5" s="1" t="n">
+      <c r="E5">
+        <v>0</v>
+      </c>
+      <c r="F5" s="1">
         <v>45573</v>
       </c>
-      <c r="G5" s="1" t="n">
+      <c r="G5" s="1">
         <v>45713</v>
       </c>
-      <c r="H5" t="n">
+      <c r="H5">
         <v>141</v>
       </c>
       <c r="I5" t="s">
@@ -1341,7 +1356,7 @@
         <v>52</v>
       </c>
     </row>
-    <row r="6">
+    <row r="6" spans="1:11" x14ac:dyDescent="0.25">
       <c r="A6" t="s">
         <v>34</v>
       </c>
@@ -1354,16 +1369,16 @@
       <c r="D6" t="s">
         <v>55</v>
       </c>
-      <c r="E6" t="n">
+      <c r="E6">
         <v>1</v>
       </c>
-      <c r="F6" s="1" t="n">
+      <c r="F6" s="1">
         <v>45574</v>
       </c>
-      <c r="G6" s="1" t="n">
+      <c r="G6" s="1">
         <v>45713</v>
       </c>
-      <c r="H6" t="n">
+      <c r="H6">
         <v>140</v>
       </c>
       <c r="I6" t="s">
@@ -1376,7 +1391,7 @@
         <v>57</v>
       </c>
     </row>
-    <row r="7">
+    <row r="7" spans="1:11" x14ac:dyDescent="0.25">
       <c r="A7" t="s">
         <v>34</v>
       </c>
@@ -1389,16 +1404,16 @@
       <c r="D7" t="s">
         <v>60</v>
       </c>
-      <c r="E7" t="n">
-        <v>0</v>
-      </c>
-      <c r="F7" s="1" t="n">
+      <c r="E7">
+        <v>0</v>
+      </c>
+      <c r="F7" s="1">
         <v>45580</v>
       </c>
-      <c r="G7" s="1" t="n">
+      <c r="G7" s="1">
         <v>45749</v>
       </c>
-      <c r="H7" t="n">
+      <c r="H7">
         <v>170</v>
       </c>
       <c r="I7" t="s">
@@ -1411,7 +1426,7 @@
         <v>62</v>
       </c>
     </row>
-    <row r="8">
+    <row r="8" spans="1:11" x14ac:dyDescent="0.25">
       <c r="A8" t="s">
         <v>34</v>
       </c>
@@ -1424,16 +1439,16 @@
       <c r="D8" t="s">
         <v>14</v>
       </c>
-      <c r="E8" t="n">
-        <v>0</v>
-      </c>
-      <c r="F8" s="1" t="n">
+      <c r="E8">
+        <v>0</v>
+      </c>
+      <c r="F8" s="1">
         <v>45580</v>
       </c>
-      <c r="G8" s="1" t="n">
+      <c r="G8" s="1">
         <v>45636</v>
       </c>
-      <c r="H8" t="n">
+      <c r="H8">
         <v>57</v>
       </c>
       <c r="I8" t="s">
@@ -1446,7 +1461,7 @@
         <v>65</v>
       </c>
     </row>
-    <row r="9">
+    <row r="9" spans="1:11" x14ac:dyDescent="0.25">
       <c r="A9" t="s">
         <v>34</v>
       </c>
@@ -1459,16 +1474,16 @@
       <c r="D9" t="s">
         <v>68</v>
       </c>
-      <c r="E9" t="n">
-        <v>0</v>
-      </c>
-      <c r="F9" s="1" t="n">
+      <c r="E9">
+        <v>0</v>
+      </c>
+      <c r="F9" s="1">
         <v>45581</v>
       </c>
-      <c r="G9" s="1" t="n">
+      <c r="G9" s="1">
         <v>45721</v>
       </c>
-      <c r="H9" t="n">
+      <c r="H9">
         <v>141</v>
       </c>
       <c r="I9" t="s">
@@ -1481,7 +1496,7 @@
         <v>69</v>
       </c>
     </row>
-    <row r="10">
+    <row r="10" spans="1:11" x14ac:dyDescent="0.25">
       <c r="A10" t="s">
         <v>34</v>
       </c>
@@ -1494,16 +1509,16 @@
       <c r="D10" t="s">
         <v>72</v>
       </c>
-      <c r="E10" t="n">
-        <v>0</v>
-      </c>
-      <c r="F10" s="1" t="n">
+      <c r="E10">
+        <v>0</v>
+      </c>
+      <c r="F10" s="1">
         <v>45581</v>
       </c>
-      <c r="G10" s="1" t="n">
+      <c r="G10" s="1">
         <v>45720</v>
       </c>
-      <c r="H10" t="n">
+      <c r="H10">
         <v>140</v>
       </c>
       <c r="I10" t="s">
@@ -1518,16 +1533,16 @@
     </row>
   </sheetData>
   <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
-  <pageSetup paperSize="9" orientation="portrait" horizontalDpi="300" verticalDpi="300" r:id="rId2"/>
+  <pageSetup paperSize="9" orientation="portrait" horizontalDpi="300" verticalDpi="300"/>
 </worksheet>
 </file>
 
 <file path=xl/worksheets/sheet3.xml><?xml version="1.0" encoding="utf-8"?>
-<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:xdr="http://schemas.openxmlformats.org/drawingml/2006/spreadsheetDrawing" xmlns:x14="http://schemas.microsoft.com/office/spreadsheetml/2009/9/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3">
-  <dimension ref="A1"/>
-  <sheetFormatPr defaultRowHeight="15.0" baseColWidth="10"/>
+<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{00000000-0001-0000-0200-000000000000}">
+  <dimension ref="A1:K8"/>
+  <sheetFormatPr defaultColWidth="11.42578125" defaultRowHeight="15" x14ac:dyDescent="0.25"/>
   <sheetData>
-    <row r="1">
+    <row r="1" spans="1:11" x14ac:dyDescent="0.25">
       <c r="A1" t="s">
         <v>0</v>
       </c>
@@ -1562,7 +1577,7 @@
         <v>10</v>
       </c>
     </row>
-    <row r="2">
+    <row r="2" spans="1:11" x14ac:dyDescent="0.25">
       <c r="A2" t="s">
         <v>74</v>
       </c>
@@ -1575,16 +1590,16 @@
       <c r="D2" t="s">
         <v>77</v>
       </c>
-      <c r="E2" t="n">
-        <v>0</v>
-      </c>
-      <c r="F2" s="1" t="n">
+      <c r="E2">
+        <v>0</v>
+      </c>
+      <c r="F2" s="1">
         <v>45600</v>
       </c>
-      <c r="G2" s="1" t="n">
+      <c r="G2" s="1">
         <v>45709</v>
       </c>
-      <c r="H2" t="n">
+      <c r="H2">
         <v>110</v>
       </c>
       <c r="I2" t="s">
@@ -1597,7 +1612,7 @@
         <v>45</v>
       </c>
     </row>
-    <row r="3">
+    <row r="3" spans="1:11" x14ac:dyDescent="0.25">
       <c r="A3" t="s">
         <v>74</v>
       </c>
@@ -1610,16 +1625,16 @@
       <c r="D3" t="s">
         <v>80</v>
       </c>
-      <c r="E3" t="n">
-        <v>0</v>
-      </c>
-      <c r="F3" s="1" t="n">
+      <c r="E3">
+        <v>0</v>
+      </c>
+      <c r="F3" s="1">
         <v>45601</v>
       </c>
-      <c r="G3" s="1" t="n">
+      <c r="G3" s="1">
         <v>45776</v>
       </c>
-      <c r="H3" t="n">
+      <c r="H3">
         <v>176</v>
       </c>
       <c r="I3" t="s">
@@ -1632,7 +1647,7 @@
         <v>62</v>
       </c>
     </row>
-    <row r="4">
+    <row r="4" spans="1:11" x14ac:dyDescent="0.25">
       <c r="A4" t="s">
         <v>74</v>
       </c>
@@ -1645,16 +1660,16 @@
       <c r="D4" t="s">
         <v>51</v>
       </c>
-      <c r="E4" t="n">
-        <v>0</v>
-      </c>
-      <c r="F4" s="1" t="n">
+      <c r="E4">
+        <v>0</v>
+      </c>
+      <c r="F4" s="1">
         <v>45601</v>
       </c>
-      <c r="G4" s="1" t="n">
+      <c r="G4" s="1">
         <v>45672</v>
       </c>
-      <c r="H4" t="n">
+      <c r="H4">
         <v>72</v>
       </c>
       <c r="I4" t="s">
@@ -1667,7 +1682,7 @@
         <v>39</v>
       </c>
     </row>
-    <row r="5">
+    <row r="5" spans="1:11" x14ac:dyDescent="0.25">
       <c r="A5" t="s">
         <v>74</v>
       </c>
@@ -1680,16 +1695,16 @@
       <c r="D5" t="s">
         <v>72</v>
       </c>
-      <c r="E5" t="n">
-        <v>0</v>
-      </c>
-      <c r="F5" s="1" t="n">
+      <c r="E5">
+        <v>0</v>
+      </c>
+      <c r="F5" s="1">
         <v>45602</v>
       </c>
-      <c r="G5" s="1" t="n">
+      <c r="G5" s="1">
         <v>45618</v>
       </c>
-      <c r="H5" t="n">
+      <c r="H5">
         <v>17</v>
       </c>
       <c r="I5" t="s">
@@ -1702,7 +1717,7 @@
         <v>16</v>
       </c>
     </row>
-    <row r="6">
+    <row r="6" spans="1:11" x14ac:dyDescent="0.25">
       <c r="A6" t="s">
         <v>74</v>
       </c>
@@ -1715,16 +1730,16 @@
       <c r="D6" t="s">
         <v>19</v>
       </c>
-      <c r="E6" t="n">
-        <v>0</v>
-      </c>
-      <c r="F6" s="1" t="n">
+      <c r="E6">
+        <v>0</v>
+      </c>
+      <c r="F6" s="1">
         <v>45608</v>
       </c>
-      <c r="G6" s="1" t="n">
+      <c r="G6" s="1">
         <v>45769</v>
       </c>
-      <c r="H6" t="n">
+      <c r="H6">
         <v>162</v>
       </c>
       <c r="I6" t="s">
@@ -1737,7 +1752,7 @@
         <v>48</v>
       </c>
     </row>
-    <row r="7">
+    <row r="7" spans="1:11" x14ac:dyDescent="0.25">
       <c r="A7" t="s">
         <v>74</v>
       </c>
@@ -1750,16 +1765,16 @@
       <c r="D7" t="s">
         <v>60</v>
       </c>
-      <c r="E7" t="n">
-        <v>0</v>
-      </c>
-      <c r="F7" s="1" t="n">
+      <c r="E7">
+        <v>0</v>
+      </c>
+      <c r="F7" s="1">
         <v>45608</v>
       </c>
-      <c r="G7" s="1" t="n">
+      <c r="G7" s="1">
         <v>45737</v>
       </c>
-      <c r="H7" t="n">
+      <c r="H7">
         <v>130</v>
       </c>
       <c r="I7" t="s">
@@ -1772,7 +1787,7 @@
         <v>69</v>
       </c>
     </row>
-    <row r="8">
+    <row r="8" spans="1:11" x14ac:dyDescent="0.25">
       <c r="A8" t="s">
         <v>74</v>
       </c>
@@ -1785,16 +1800,16 @@
       <c r="D8" t="s">
         <v>72</v>
       </c>
-      <c r="E8" t="n">
-        <v>0</v>
-      </c>
-      <c r="F8" s="1" t="n">
+      <c r="E8">
+        <v>0</v>
+      </c>
+      <c r="F8" s="1">
         <v>45609</v>
       </c>
-      <c r="G8" s="1" t="n">
+      <c r="G8" s="1">
         <v>45637</v>
       </c>
-      <c r="H8" t="n">
+      <c r="H8">
         <v>29</v>
       </c>
       <c r="I8" t="s">
@@ -1809,16 +1824,16 @@
     </row>
   </sheetData>
   <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
-  <pageSetup paperSize="9" orientation="portrait" horizontalDpi="300" verticalDpi="300" r:id="rId2"/>
+  <pageSetup paperSize="9" orientation="portrait" horizontalDpi="300" verticalDpi="300"/>
 </worksheet>
 </file>
 
 <file path=xl/worksheets/sheet4.xml><?xml version="1.0" encoding="utf-8"?>
-<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:xdr="http://schemas.openxmlformats.org/drawingml/2006/spreadsheetDrawing" xmlns:x14="http://schemas.microsoft.com/office/spreadsheetml/2009/9/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3">
-  <dimension ref="A1"/>
-  <sheetFormatPr defaultRowHeight="15.0" baseColWidth="10"/>
+<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{00000000-0001-0000-0300-000000000000}">
+  <dimension ref="A1:K9"/>
+  <sheetFormatPr defaultColWidth="11.42578125" defaultRowHeight="15" x14ac:dyDescent="0.25"/>
   <sheetData>
-    <row r="1">
+    <row r="1" spans="1:11" x14ac:dyDescent="0.25">
       <c r="A1" t="s">
         <v>0</v>
       </c>
@@ -1853,7 +1868,7 @@
         <v>10</v>
       </c>
     </row>
-    <row r="2">
+    <row r="2" spans="1:11" x14ac:dyDescent="0.25">
       <c r="A2" t="s">
         <v>92</v>
       </c>
@@ -1866,16 +1881,16 @@
       <c r="D2" t="s">
         <v>33</v>
       </c>
-      <c r="E2" t="n">
-        <v>0</v>
-      </c>
-      <c r="F2" s="1" t="n">
+      <c r="E2">
+        <v>0</v>
+      </c>
+      <c r="F2" s="1">
         <v>45628</v>
       </c>
-      <c r="G2" s="1" t="n">
+      <c r="G2" s="1">
         <v>45749</v>
       </c>
-      <c r="H2" t="n">
+      <c r="H2">
         <v>122</v>
       </c>
       <c r="I2" t="s">
@@ -1888,7 +1903,7 @@
         <v>73</v>
       </c>
     </row>
-    <row r="3">
+    <row r="3" spans="1:11" x14ac:dyDescent="0.25">
       <c r="A3" t="s">
         <v>92</v>
       </c>
@@ -1901,16 +1916,16 @@
       <c r="D3" t="s">
         <v>19</v>
       </c>
-      <c r="E3" t="n">
-        <v>0</v>
-      </c>
-      <c r="F3" s="1" t="n">
+      <c r="E3">
+        <v>0</v>
+      </c>
+      <c r="F3" s="1">
         <v>45628</v>
       </c>
-      <c r="G3" s="1" t="n">
+      <c r="G3" s="1">
         <v>45742</v>
       </c>
-      <c r="H3" t="n">
+      <c r="H3">
         <v>115</v>
       </c>
       <c r="I3" t="s">
@@ -1923,7 +1938,7 @@
         <v>65</v>
       </c>
     </row>
-    <row r="4">
+    <row r="4" spans="1:11" x14ac:dyDescent="0.25">
       <c r="A4" t="s">
         <v>92</v>
       </c>
@@ -1936,16 +1951,16 @@
       <c r="D4" t="s">
         <v>80</v>
       </c>
-      <c r="E4" t="n">
-        <v>0</v>
-      </c>
-      <c r="F4" s="1" t="n">
+      <c r="E4">
+        <v>0</v>
+      </c>
+      <c r="F4" s="1">
         <v>45629</v>
       </c>
-      <c r="G4" s="1" t="n">
+      <c r="G4" s="1">
         <v>45709</v>
       </c>
-      <c r="H4" t="n">
+      <c r="H4">
         <v>81</v>
       </c>
       <c r="I4" t="s">
@@ -1958,7 +1973,7 @@
         <v>57</v>
       </c>
     </row>
-    <row r="5">
+    <row r="5" spans="1:11" x14ac:dyDescent="0.25">
       <c r="A5" t="s">
         <v>92</v>
       </c>
@@ -1971,16 +1986,16 @@
       <c r="D5" t="s">
         <v>103</v>
       </c>
-      <c r="E5" t="n">
+      <c r="E5">
         <v>1</v>
       </c>
-      <c r="F5" s="1" t="n">
+      <c r="F5" s="1">
         <v>45630</v>
       </c>
-      <c r="G5" s="1" t="n">
+      <c r="G5" s="1">
         <v>45826</v>
       </c>
-      <c r="H5" t="n">
+      <c r="H5">
         <v>197</v>
       </c>
       <c r="I5" t="s">
@@ -1993,7 +2008,7 @@
         <v>52</v>
       </c>
     </row>
-    <row r="6">
+    <row r="6" spans="1:11" x14ac:dyDescent="0.25">
       <c r="A6" t="s">
         <v>92</v>
       </c>
@@ -2006,16 +2021,16 @@
       <c r="D6" t="s">
         <v>107</v>
       </c>
-      <c r="E6" t="n">
-        <v>0</v>
-      </c>
-      <c r="F6" s="1" t="n">
+      <c r="E6">
+        <v>0</v>
+      </c>
+      <c r="F6" s="1">
         <v>45635</v>
       </c>
-      <c r="G6" s="1" t="n">
+      <c r="G6" s="1">
         <v>45799</v>
       </c>
-      <c r="H6" t="n">
+      <c r="H6">
         <v>165</v>
       </c>
       <c r="I6" t="s">
@@ -2028,7 +2043,7 @@
         <v>62</v>
       </c>
     </row>
-    <row r="7">
+    <row r="7" spans="1:11" x14ac:dyDescent="0.25">
       <c r="A7" t="s">
         <v>92</v>
       </c>
@@ -2041,16 +2056,16 @@
       <c r="D7" t="s">
         <v>68</v>
       </c>
-      <c r="E7" t="n">
-        <v>0</v>
-      </c>
-      <c r="F7" s="1" t="n">
+      <c r="E7">
+        <v>0</v>
+      </c>
+      <c r="F7" s="1">
         <v>45635</v>
       </c>
-      <c r="G7" s="1" t="n">
+      <c r="G7" s="1">
         <v>45777</v>
       </c>
-      <c r="H7" t="n">
+      <c r="H7">
         <v>143</v>
       </c>
       <c r="I7" t="s">
@@ -2063,7 +2078,7 @@
         <v>48</v>
       </c>
     </row>
-    <row r="8">
+    <row r="8" spans="1:11" x14ac:dyDescent="0.25">
       <c r="A8" t="s">
         <v>92</v>
       </c>
@@ -2076,16 +2091,16 @@
       <c r="D8" t="s">
         <v>80</v>
       </c>
-      <c r="E8" t="n">
-        <v>0</v>
-      </c>
-      <c r="F8" s="1" t="n">
+      <c r="E8">
+        <v>0</v>
+      </c>
+      <c r="F8" s="1">
         <v>45636</v>
       </c>
-      <c r="G8" s="1" t="n">
+      <c r="G8" s="1">
         <v>45806</v>
       </c>
-      <c r="H8" t="n">
+      <c r="H8">
         <v>171</v>
       </c>
       <c r="I8" t="s">
@@ -2098,7 +2113,7 @@
         <v>39</v>
       </c>
     </row>
-    <row r="9">
+    <row r="9" spans="1:11" x14ac:dyDescent="0.25">
       <c r="A9" t="s">
         <v>92</v>
       </c>
@@ -2111,16 +2126,16 @@
       <c r="D9" t="s">
         <v>51</v>
       </c>
-      <c r="E9" t="n">
-        <v>0</v>
-      </c>
-      <c r="F9" s="1" t="n">
+      <c r="E9">
+        <v>0</v>
+      </c>
+      <c r="F9" s="1">
         <v>45637</v>
       </c>
-      <c r="G9" s="1" t="n">
+      <c r="G9" s="1">
         <v>45714</v>
       </c>
-      <c r="H9" t="n">
+      <c r="H9">
         <v>78</v>
       </c>
       <c r="I9" t="s">
@@ -2135,16 +2150,16 @@
     </row>
   </sheetData>
   <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
-  <pageSetup paperSize="9" orientation="portrait" horizontalDpi="300" verticalDpi="300" r:id="rId2"/>
+  <pageSetup paperSize="9" orientation="portrait" horizontalDpi="300" verticalDpi="300"/>
 </worksheet>
 </file>
 
 <file path=xl/worksheets/sheet5.xml><?xml version="1.0" encoding="utf-8"?>
-<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:xdr="http://schemas.openxmlformats.org/drawingml/2006/spreadsheetDrawing" xmlns:x14="http://schemas.microsoft.com/office/spreadsheetml/2009/9/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3">
-  <dimension ref="A1"/>
-  <sheetFormatPr defaultRowHeight="15.0" baseColWidth="10"/>
+<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{00000000-0001-0000-0400-000000000000}">
+  <dimension ref="A1:K11"/>
+  <sheetFormatPr defaultColWidth="11.42578125" defaultRowHeight="15" x14ac:dyDescent="0.25"/>
   <sheetData>
-    <row r="1">
+    <row r="1" spans="1:11" x14ac:dyDescent="0.25">
       <c r="A1" t="s">
         <v>0</v>
       </c>
@@ -2179,7 +2194,7 @@
         <v>10</v>
       </c>
     </row>
-    <row r="2">
+    <row r="2" spans="1:11" x14ac:dyDescent="0.25">
       <c r="A2" t="s">
         <v>115</v>
       </c>
@@ -2192,16 +2207,16 @@
       <c r="D2" t="s">
         <v>33</v>
       </c>
-      <c r="E2" t="n">
-        <v>0</v>
-      </c>
-      <c r="F2" s="1" t="n">
+      <c r="E2">
+        <v>0</v>
+      </c>
+      <c r="F2" s="1">
         <v>45670</v>
       </c>
-      <c r="G2" s="1" t="n">
+      <c r="G2" s="1">
         <v>45834</v>
       </c>
-      <c r="H2" t="n">
+      <c r="H2">
         <v>165</v>
       </c>
       <c r="I2" t="s">
@@ -2214,7 +2229,7 @@
         <v>65</v>
       </c>
     </row>
-    <row r="3">
+    <row r="3" spans="1:11" x14ac:dyDescent="0.25">
       <c r="A3" t="s">
         <v>115</v>
       </c>
@@ -2227,16 +2242,16 @@
       <c r="D3" t="s">
         <v>14</v>
       </c>
-      <c r="E3" t="n">
-        <v>0</v>
-      </c>
-      <c r="F3" s="1" t="n">
+      <c r="E3">
+        <v>0</v>
+      </c>
+      <c r="F3" s="1">
         <v>45670</v>
       </c>
-      <c r="G3" s="1" t="n">
+      <c r="G3" s="1">
         <v>45828</v>
       </c>
-      <c r="H3" t="n">
+      <c r="H3">
         <v>159</v>
       </c>
       <c r="I3" t="s">
@@ -2249,7 +2264,7 @@
         <v>48</v>
       </c>
     </row>
-    <row r="4">
+    <row r="4" spans="1:11" x14ac:dyDescent="0.25">
       <c r="A4" t="s">
         <v>115</v>
       </c>
@@ -2262,16 +2277,16 @@
       <c r="D4" t="s">
         <v>77</v>
       </c>
-      <c r="E4" t="n">
-        <v>0</v>
-      </c>
-      <c r="F4" s="1" t="n">
+      <c r="E4">
+        <v>0</v>
+      </c>
+      <c r="F4" s="1">
         <v>45671</v>
       </c>
-      <c r="G4" s="1" t="n">
+      <c r="G4" s="1">
         <v>45737</v>
       </c>
-      <c r="H4" t="n">
+      <c r="H4">
         <v>67</v>
       </c>
       <c r="I4" t="s">
@@ -2284,7 +2299,7 @@
         <v>52</v>
       </c>
     </row>
-    <row r="5">
+    <row r="5" spans="1:11" x14ac:dyDescent="0.25">
       <c r="A5" t="s">
         <v>115</v>
       </c>
@@ -2297,16 +2312,16 @@
       <c r="D5" t="s">
         <v>19</v>
       </c>
-      <c r="E5" t="n">
-        <v>0</v>
-      </c>
-      <c r="F5" s="1" t="n">
+      <c r="E5">
+        <v>0</v>
+      </c>
+      <c r="F5" s="1">
         <v>45671</v>
       </c>
-      <c r="G5" s="1" t="n">
+      <c r="G5" s="1">
         <v>45714</v>
       </c>
-      <c r="H5" t="n">
+      <c r="H5">
         <v>44</v>
       </c>
       <c r="I5" t="s">
@@ -2319,7 +2334,7 @@
         <v>73</v>
       </c>
     </row>
-    <row r="6">
+    <row r="6" spans="1:11" x14ac:dyDescent="0.25">
       <c r="A6" t="s">
         <v>115</v>
       </c>
@@ -2332,39 +2347,51 @@
       <c r="D6" t="s">
         <v>33</v>
       </c>
-      <c r="E6" t="n">
-        <v>0</v>
-      </c>
-      <c r="F6" s="1"/>
-      <c r="G6" s="1"/>
-      <c r="H6"/>
-      <c r="I6"/>
-      <c r="J6"/>
-      <c r="K6"/>
-    </row>
-    <row r="7">
+      <c r="E6">
+        <v>0</v>
+      </c>
+      <c r="F6" s="1">
+        <v>45672</v>
+      </c>
+      <c r="G6" s="1">
+        <v>45835</v>
+      </c>
+      <c r="H6">
+        <v>164</v>
+      </c>
+      <c r="I6" t="s">
+        <v>127</v>
+      </c>
+      <c r="J6" t="s">
+        <v>104</v>
+      </c>
+      <c r="K6" t="s">
+        <v>69</v>
+      </c>
+    </row>
+    <row r="7" spans="1:11" x14ac:dyDescent="0.25">
       <c r="A7" t="s">
         <v>115</v>
       </c>
       <c r="B7" t="s">
-        <v>127</v>
+        <v>128</v>
       </c>
       <c r="C7" t="s">
-        <v>128</v>
+        <v>129</v>
       </c>
       <c r="D7" t="s">
         <v>33</v>
       </c>
-      <c r="E7" t="n">
-        <v>0</v>
-      </c>
-      <c r="F7" s="1" t="n">
+      <c r="E7">
+        <v>0</v>
+      </c>
+      <c r="F7" s="1">
         <v>45678</v>
       </c>
-      <c r="G7" s="1" t="n">
+      <c r="G7" s="1">
         <v>45828</v>
       </c>
-      <c r="H7" t="n">
+      <c r="H7">
         <v>151</v>
       </c>
       <c r="I7" t="s">
@@ -2377,29 +2404,29 @@
         <v>62</v>
       </c>
     </row>
-    <row r="8">
+    <row r="8" spans="1:11" x14ac:dyDescent="0.25">
       <c r="A8" t="s">
         <v>115</v>
       </c>
       <c r="B8" t="s">
-        <v>129</v>
+        <v>130</v>
       </c>
       <c r="C8" t="s">
-        <v>130</v>
+        <v>131</v>
       </c>
       <c r="D8" t="s">
         <v>72</v>
       </c>
-      <c r="E8" t="n">
-        <v>0</v>
-      </c>
-      <c r="F8" s="1" t="n">
+      <c r="E8">
+        <v>0</v>
+      </c>
+      <c r="F8" s="1">
         <v>45678</v>
       </c>
-      <c r="G8" s="1" t="n">
+      <c r="G8" s="1">
         <v>45828</v>
       </c>
-      <c r="H8" t="n">
+      <c r="H8">
         <v>151</v>
       </c>
       <c r="I8" t="s">
@@ -2412,29 +2439,29 @@
         <v>39</v>
       </c>
     </row>
-    <row r="9">
+    <row r="9" spans="1:11" x14ac:dyDescent="0.25">
       <c r="A9" t="s">
         <v>115</v>
       </c>
       <c r="B9" t="s">
-        <v>131</v>
+        <v>132</v>
       </c>
       <c r="C9" t="s">
-        <v>132</v>
+        <v>133</v>
       </c>
       <c r="D9" t="s">
         <v>33</v>
       </c>
-      <c r="E9" t="n">
-        <v>0</v>
-      </c>
-      <c r="F9" s="1" t="n">
+      <c r="E9">
+        <v>0</v>
+      </c>
+      <c r="F9" s="1">
         <v>45679</v>
       </c>
-      <c r="G9" s="1" t="n">
+      <c r="G9" s="1">
         <v>45792</v>
       </c>
-      <c r="H9" t="n">
+      <c r="H9">
         <v>114</v>
       </c>
       <c r="I9" t="s">
@@ -2447,29 +2474,29 @@
         <v>45</v>
       </c>
     </row>
-    <row r="10">
+    <row r="10" spans="1:11" x14ac:dyDescent="0.25">
       <c r="A10" t="s">
         <v>115</v>
       </c>
       <c r="B10" t="s">
-        <v>133</v>
+        <v>134</v>
       </c>
       <c r="C10" t="s">
-        <v>134</v>
+        <v>135</v>
       </c>
       <c r="D10" t="s">
         <v>60</v>
       </c>
-      <c r="E10" t="n">
-        <v>0</v>
-      </c>
-      <c r="F10" s="1" t="n">
+      <c r="E10">
+        <v>0</v>
+      </c>
+      <c r="F10" s="1">
         <v>45679</v>
       </c>
-      <c r="G10" s="1" t="n">
+      <c r="G10" s="1">
         <v>45764</v>
       </c>
-      <c r="H10" t="n">
+      <c r="H10">
         <v>86</v>
       </c>
       <c r="I10" t="s">
@@ -2482,29 +2509,29 @@
         <v>57</v>
       </c>
     </row>
-    <row r="11">
+    <row r="11" spans="1:11" x14ac:dyDescent="0.25">
       <c r="A11" t="s">
         <v>115</v>
       </c>
       <c r="B11" t="s">
-        <v>135</v>
+        <v>136</v>
       </c>
       <c r="C11" t="s">
-        <v>136</v>
+        <v>137</v>
       </c>
       <c r="D11" t="s">
         <v>80</v>
       </c>
-      <c r="E11" t="n">
+      <c r="E11">
         <v>1</v>
       </c>
-      <c r="F11" s="1" t="n">
+      <c r="F11" s="1">
         <v>45667</v>
       </c>
-      <c r="G11" s="1" t="n">
+      <c r="G11" s="1">
         <v>45674</v>
       </c>
-      <c r="H11" t="n">
+      <c r="H11">
         <v>8</v>
       </c>
       <c r="I11" t="s">
@@ -2519,16 +2546,16 @@
     </row>
   </sheetData>
   <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
-  <pageSetup paperSize="9" orientation="portrait" horizontalDpi="300" verticalDpi="300" r:id="rId2"/>
+  <pageSetup paperSize="9" orientation="portrait" horizontalDpi="300" verticalDpi="300"/>
 </worksheet>
 </file>
 
 <file path=xl/worksheets/sheet6.xml><?xml version="1.0" encoding="utf-8"?>
-<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:xdr="http://schemas.openxmlformats.org/drawingml/2006/spreadsheetDrawing" xmlns:x14="http://schemas.microsoft.com/office/spreadsheetml/2009/9/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3">
-  <dimension ref="A1"/>
-  <sheetFormatPr defaultRowHeight="15.0" baseColWidth="10"/>
+<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{00000000-0001-0000-0500-000000000000}">
+  <dimension ref="A1:K9"/>
+  <sheetFormatPr defaultColWidth="11.42578125" defaultRowHeight="15" x14ac:dyDescent="0.25"/>
   <sheetData>
-    <row r="1">
+    <row r="1" spans="1:11" x14ac:dyDescent="0.25">
       <c r="A1" t="s">
         <v>0</v>
       </c>
@@ -2563,29 +2590,29 @@
         <v>10</v>
       </c>
     </row>
-    <row r="2">
+    <row r="2" spans="1:11" x14ac:dyDescent="0.25">
       <c r="A2" t="s">
-        <v>137</v>
+        <v>138</v>
       </c>
       <c r="B2" t="s">
-        <v>138</v>
+        <v>139</v>
       </c>
       <c r="C2" t="s">
-        <v>139</v>
+        <v>140</v>
       </c>
       <c r="D2" t="s">
         <v>33</v>
       </c>
-      <c r="E2" t="n">
-        <v>0</v>
-      </c>
-      <c r="F2" s="1" t="n">
+      <c r="E2">
+        <v>0</v>
+      </c>
+      <c r="F2" s="1">
         <v>45712</v>
       </c>
-      <c r="G2" s="1" t="n">
+      <c r="G2" s="1">
         <v>45834</v>
       </c>
-      <c r="H2" t="n">
+      <c r="H2">
         <v>123</v>
       </c>
       <c r="I2" t="s">
@@ -2598,64 +2625,64 @@
         <v>57</v>
       </c>
     </row>
-    <row r="3">
+    <row r="3" spans="1:11" x14ac:dyDescent="0.25">
       <c r="A3" t="s">
-        <v>137</v>
+        <v>138</v>
       </c>
       <c r="B3" t="s">
-        <v>140</v>
+        <v>141</v>
       </c>
       <c r="C3" t="s">
-        <v>141</v>
+        <v>142</v>
       </c>
       <c r="D3" t="s">
         <v>103</v>
       </c>
-      <c r="E3" t="n">
-        <v>0</v>
-      </c>
-      <c r="F3" s="1" t="n">
+      <c r="E3">
+        <v>0</v>
+      </c>
+      <c r="F3" s="1">
         <v>45713</v>
       </c>
-      <c r="G3" s="1" t="n">
+      <c r="G3" s="1">
         <v>45828</v>
       </c>
-      <c r="H3" t="n">
+      <c r="H3">
         <v>116</v>
       </c>
       <c r="I3" t="s">
         <v>15</v>
       </c>
       <c r="J3" t="s">
-        <v>142</v>
+        <v>143</v>
       </c>
       <c r="K3" t="s">
         <v>62</v>
       </c>
     </row>
-    <row r="4">
+    <row r="4" spans="1:11" x14ac:dyDescent="0.25">
       <c r="A4" t="s">
-        <v>137</v>
+        <v>138</v>
       </c>
       <c r="B4" t="s">
-        <v>143</v>
+        <v>144</v>
       </c>
       <c r="C4" t="s">
-        <v>144</v>
+        <v>145</v>
       </c>
       <c r="D4" t="s">
         <v>103</v>
       </c>
-      <c r="E4" t="n">
-        <v>0</v>
-      </c>
-      <c r="F4" s="1" t="n">
+      <c r="E4">
+        <v>0</v>
+      </c>
+      <c r="F4" s="1">
         <v>45713</v>
       </c>
-      <c r="G4" s="1" t="n">
+      <c r="G4" s="1">
         <v>45826</v>
       </c>
-      <c r="H4" t="n">
+      <c r="H4">
         <v>114</v>
       </c>
       <c r="I4" t="s">
@@ -2668,29 +2695,29 @@
         <v>52</v>
       </c>
     </row>
-    <row r="5">
+    <row r="5" spans="1:11" x14ac:dyDescent="0.25">
       <c r="A5" t="s">
-        <v>137</v>
+        <v>138</v>
       </c>
       <c r="B5" t="s">
-        <v>145</v>
+        <v>146</v>
       </c>
       <c r="C5" t="s">
-        <v>146</v>
+        <v>147</v>
       </c>
       <c r="D5" t="s">
         <v>103</v>
       </c>
-      <c r="E5" t="n">
-        <v>0</v>
-      </c>
-      <c r="F5" s="1" t="n">
+      <c r="E5">
+        <v>0</v>
+      </c>
+      <c r="F5" s="1">
         <v>45714</v>
       </c>
-      <c r="G5" s="1" t="n">
+      <c r="G5" s="1">
         <v>45813</v>
       </c>
-      <c r="H5" t="n">
+      <c r="H5">
         <v>100</v>
       </c>
       <c r="I5" t="s">
@@ -2703,29 +2730,29 @@
         <v>65</v>
       </c>
     </row>
-    <row r="6">
+    <row r="6" spans="1:11" x14ac:dyDescent="0.25">
       <c r="A6" t="s">
-        <v>137</v>
+        <v>138</v>
       </c>
       <c r="B6" t="s">
-        <v>147</v>
+        <v>148</v>
       </c>
       <c r="C6" t="s">
-        <v>148</v>
+        <v>149</v>
       </c>
       <c r="D6" t="s">
         <v>72</v>
       </c>
-      <c r="E6" t="n">
-        <v>0</v>
-      </c>
-      <c r="F6" s="1" t="n">
+      <c r="E6">
+        <v>0</v>
+      </c>
+      <c r="F6" s="1">
         <v>45719</v>
       </c>
-      <c r="G6" s="1" t="n">
+      <c r="G6" s="1">
         <v>45813</v>
       </c>
-      <c r="H6" t="n">
+      <c r="H6">
         <v>95</v>
       </c>
       <c r="I6" t="s">
@@ -2738,29 +2765,29 @@
         <v>73</v>
       </c>
     </row>
-    <row r="7">
+    <row r="7" spans="1:11" x14ac:dyDescent="0.25">
       <c r="A7" t="s">
-        <v>137</v>
+        <v>138</v>
       </c>
       <c r="B7" t="s">
-        <v>149</v>
+        <v>150</v>
       </c>
       <c r="C7" t="s">
-        <v>150</v>
+        <v>151</v>
       </c>
       <c r="D7" t="s">
         <v>60</v>
       </c>
-      <c r="E7" t="n">
-        <v>0</v>
-      </c>
-      <c r="F7" s="1" t="n">
+      <c r="E7">
+        <v>0</v>
+      </c>
+      <c r="F7" s="1">
         <v>45719</v>
       </c>
-      <c r="G7" s="1" t="n">
+      <c r="G7" s="1">
         <v>45813</v>
       </c>
-      <c r="H7" t="n">
+      <c r="H7">
         <v>95</v>
       </c>
       <c r="I7" t="s">
@@ -2773,29 +2800,29 @@
         <v>69</v>
       </c>
     </row>
-    <row r="8">
+    <row r="8" spans="1:11" x14ac:dyDescent="0.25">
       <c r="A8" t="s">
-        <v>137</v>
+        <v>138</v>
       </c>
       <c r="B8" t="s">
-        <v>151</v>
+        <v>152</v>
       </c>
       <c r="C8" t="s">
-        <v>152</v>
+        <v>153</v>
       </c>
       <c r="D8" t="s">
-        <v>153</v>
-      </c>
-      <c r="E8" t="n">
-        <v>0</v>
-      </c>
-      <c r="F8" s="1" t="n">
+        <v>154</v>
+      </c>
+      <c r="E8">
+        <v>0</v>
+      </c>
+      <c r="F8" s="1">
         <v>45720</v>
       </c>
-      <c r="G8" s="1" t="n">
+      <c r="G8" s="1">
         <v>45813</v>
       </c>
-      <c r="H8" t="n">
+      <c r="H8">
         <v>94</v>
       </c>
       <c r="I8" t="s">
@@ -2808,29 +2835,29 @@
         <v>45</v>
       </c>
     </row>
-    <row r="9">
+    <row r="9" spans="1:11" x14ac:dyDescent="0.25">
       <c r="A9" t="s">
-        <v>137</v>
+        <v>138</v>
       </c>
       <c r="B9" t="s">
-        <v>154</v>
+        <v>155</v>
       </c>
       <c r="C9" t="s">
-        <v>155</v>
+        <v>156</v>
       </c>
       <c r="D9" t="s">
         <v>33</v>
       </c>
-      <c r="E9" t="n">
-        <v>0</v>
-      </c>
-      <c r="F9" s="1" t="n">
+      <c r="E9">
+        <v>0</v>
+      </c>
+      <c r="F9" s="1">
         <v>45721</v>
       </c>
-      <c r="G9" s="1" t="n">
+      <c r="G9" s="1">
         <v>45826</v>
       </c>
-      <c r="H9" t="n">
+      <c r="H9">
         <v>106</v>
       </c>
       <c r="I9" t="s">
@@ -2845,16 +2872,16 @@
     </row>
   </sheetData>
   <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
-  <pageSetup paperSize="9" orientation="portrait" horizontalDpi="300" verticalDpi="300" r:id="rId2"/>
+  <pageSetup paperSize="9" orientation="portrait" horizontalDpi="300" verticalDpi="300"/>
 </worksheet>
 </file>
 
 <file path=xl/worksheets/sheet7.xml><?xml version="1.0" encoding="utf-8"?>
-<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:xdr="http://schemas.openxmlformats.org/drawingml/2006/spreadsheetDrawing" xmlns:x14="http://schemas.microsoft.com/office/spreadsheetml/2009/9/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3">
-  <dimension ref="A1"/>
-  <sheetFormatPr defaultRowHeight="15.0" baseColWidth="10"/>
+<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{00000000-0001-0000-0600-000000000000}">
+  <dimension ref="A1:K10"/>
+  <sheetFormatPr defaultColWidth="11.42578125" defaultRowHeight="15" x14ac:dyDescent="0.25"/>
   <sheetData>
-    <row r="1">
+    <row r="1" spans="1:11" x14ac:dyDescent="0.25">
       <c r="A1" t="s">
         <v>0</v>
       </c>
@@ -2889,52 +2916,48 @@
         <v>10</v>
       </c>
     </row>
-    <row r="2">
+    <row r="2" spans="1:11" x14ac:dyDescent="0.25">
       <c r="A2" t="s">
-        <v>156</v>
+        <v>157</v>
       </c>
       <c r="B2" t="s">
-        <v>157</v>
+        <v>158</v>
       </c>
       <c r="C2" t="s">
-        <v>158</v>
+        <v>159</v>
       </c>
       <c r="D2" t="s">
-        <v>159</v>
-      </c>
-      <c r="E2" t="n">
+        <v>160</v>
+      </c>
+      <c r="E2">
         <v>0</v>
       </c>
       <c r="F2" s="1"/>
       <c r="G2" s="1"/>
-      <c r="H2"/>
-      <c r="I2"/>
-      <c r="J2"/>
-      <c r="K2"/>
-    </row>
-    <row r="3">
+    </row>
+    <row r="3" spans="1:11" x14ac:dyDescent="0.25">
       <c r="A3" t="s">
-        <v>156</v>
+        <v>157</v>
       </c>
       <c r="B3" t="s">
-        <v>160</v>
+        <v>161</v>
       </c>
       <c r="C3" t="s">
-        <v>161</v>
+        <v>162</v>
       </c>
       <c r="D3" t="s">
         <v>51</v>
       </c>
-      <c r="E3" t="n">
-        <v>0</v>
-      </c>
-      <c r="F3" s="1" t="n">
+      <c r="E3">
+        <v>0</v>
+      </c>
+      <c r="F3" s="1">
         <v>45740</v>
       </c>
-      <c r="G3" s="1" t="n">
+      <c r="G3" s="1">
         <v>45834</v>
       </c>
-      <c r="H3" t="n">
+      <c r="H3">
         <v>95</v>
       </c>
       <c r="I3" t="s">
@@ -2947,29 +2970,29 @@
         <v>73</v>
       </c>
     </row>
-    <row r="4">
+    <row r="4" spans="1:11" x14ac:dyDescent="0.25">
       <c r="A4" t="s">
-        <v>156</v>
+        <v>157</v>
       </c>
       <c r="B4" t="s">
-        <v>162</v>
+        <v>163</v>
       </c>
       <c r="C4" t="s">
-        <v>163</v>
+        <v>164</v>
       </c>
       <c r="D4" t="s">
         <v>33</v>
       </c>
-      <c r="E4" t="n">
-        <v>0</v>
-      </c>
-      <c r="F4" s="1" t="n">
+      <c r="E4">
+        <v>0</v>
+      </c>
+      <c r="F4" s="1">
         <v>45741</v>
       </c>
-      <c r="G4" s="1" t="n">
+      <c r="G4" s="1">
         <v>45826</v>
       </c>
-      <c r="H4" t="n">
+      <c r="H4">
         <v>86</v>
       </c>
       <c r="I4" t="s">
@@ -2982,29 +3005,29 @@
         <v>69</v>
       </c>
     </row>
-    <row r="5">
+    <row r="5" spans="1:11" x14ac:dyDescent="0.25">
       <c r="A5" t="s">
-        <v>156</v>
+        <v>157</v>
       </c>
       <c r="B5" t="s">
-        <v>164</v>
+        <v>165</v>
       </c>
       <c r="C5" t="s">
-        <v>165</v>
+        <v>166</v>
       </c>
       <c r="D5" t="s">
         <v>19</v>
       </c>
-      <c r="E5" t="n">
-        <v>0</v>
-      </c>
-      <c r="F5" s="1" t="n">
+      <c r="E5">
+        <v>0</v>
+      </c>
+      <c r="F5" s="1">
         <v>45741</v>
       </c>
-      <c r="G5" s="1" t="n">
+      <c r="G5" s="1">
         <v>45826</v>
       </c>
-      <c r="H5" t="n">
+      <c r="H5">
         <v>86</v>
       </c>
       <c r="I5" t="s">
@@ -3017,52 +3040,64 @@
         <v>69</v>
       </c>
     </row>
-    <row r="6">
+    <row r="6" spans="1:11" x14ac:dyDescent="0.25">
       <c r="A6" t="s">
-        <v>156</v>
+        <v>157</v>
       </c>
       <c r="B6" t="s">
-        <v>166</v>
+        <v>167</v>
       </c>
       <c r="C6" t="s">
-        <v>167</v>
+        <v>168</v>
       </c>
       <c r="D6" t="s">
         <v>33</v>
       </c>
-      <c r="E6" t="n">
-        <v>0</v>
-      </c>
-      <c r="F6" s="1"/>
-      <c r="G6" s="1"/>
-      <c r="H6"/>
-      <c r="I6"/>
-      <c r="J6"/>
-      <c r="K6"/>
-    </row>
-    <row r="7">
+      <c r="E6">
+        <v>0</v>
+      </c>
+      <c r="F6" s="1">
+        <v>45742</v>
+      </c>
+      <c r="G6" s="1">
+        <v>45835</v>
+      </c>
+      <c r="H6">
+        <v>94</v>
+      </c>
+      <c r="I6" t="s">
+        <v>38</v>
+      </c>
+      <c r="J6" t="s">
+        <v>104</v>
+      </c>
+      <c r="K6" t="s">
+        <v>45</v>
+      </c>
+    </row>
+    <row r="7" spans="1:11" x14ac:dyDescent="0.25">
       <c r="A7" t="s">
-        <v>156</v>
+        <v>157</v>
       </c>
       <c r="B7" t="s">
-        <v>168</v>
+        <v>169</v>
       </c>
       <c r="C7" t="s">
-        <v>169</v>
+        <v>170</v>
       </c>
       <c r="D7" t="s">
-        <v>170</v>
-      </c>
-      <c r="E7" t="n">
-        <v>0</v>
-      </c>
-      <c r="F7" s="1" t="n">
+        <v>171</v>
+      </c>
+      <c r="E7">
+        <v>0</v>
+      </c>
+      <c r="F7" s="1">
         <v>45747</v>
       </c>
-      <c r="G7" s="1" t="n">
+      <c r="G7" s="1">
         <v>45813</v>
       </c>
-      <c r="H7" t="n">
+      <c r="H7">
         <v>67</v>
       </c>
       <c r="I7" t="s">
@@ -3075,29 +3110,29 @@
         <v>57</v>
       </c>
     </row>
-    <row r="8">
+    <row r="8" spans="1:11" x14ac:dyDescent="0.25">
       <c r="A8" t="s">
-        <v>156</v>
+        <v>157</v>
       </c>
       <c r="B8" t="s">
-        <v>171</v>
+        <v>172</v>
       </c>
       <c r="C8" t="s">
-        <v>172</v>
+        <v>173</v>
       </c>
       <c r="D8" t="s">
         <v>33</v>
       </c>
-      <c r="E8" t="n">
-        <v>0</v>
-      </c>
-      <c r="F8" s="1" t="n">
+      <c r="E8">
+        <v>0</v>
+      </c>
+      <c r="F8" s="1">
         <v>45747</v>
       </c>
-      <c r="G8" s="1" t="n">
+      <c r="G8" s="1">
         <v>45820</v>
       </c>
-      <c r="H8" t="n">
+      <c r="H8">
         <v>74</v>
       </c>
       <c r="I8" t="s">
@@ -3110,29 +3145,29 @@
         <v>65</v>
       </c>
     </row>
-    <row r="9">
+    <row r="9" spans="1:11" x14ac:dyDescent="0.25">
       <c r="A9" t="s">
-        <v>156</v>
+        <v>157</v>
       </c>
       <c r="B9" t="s">
-        <v>173</v>
+        <v>174</v>
       </c>
       <c r="C9" t="s">
-        <v>174</v>
+        <v>175</v>
       </c>
       <c r="D9" t="s">
         <v>60</v>
       </c>
-      <c r="E9" t="n">
-        <v>0</v>
-      </c>
-      <c r="F9" s="1" t="n">
+      <c r="E9">
+        <v>0</v>
+      </c>
+      <c r="F9" s="1">
         <v>45748</v>
       </c>
-      <c r="G9" s="1" t="n">
+      <c r="G9" s="1">
         <v>45828</v>
       </c>
-      <c r="H9" t="n">
+      <c r="H9">
         <v>81</v>
       </c>
       <c r="I9" t="s">
@@ -3145,29 +3180,29 @@
         <v>52</v>
       </c>
     </row>
-    <row r="10">
+    <row r="10" spans="1:11" x14ac:dyDescent="0.25">
       <c r="A10" t="s">
-        <v>156</v>
+        <v>157</v>
       </c>
       <c r="B10" t="s">
-        <v>175</v>
+        <v>176</v>
       </c>
       <c r="C10" t="s">
-        <v>176</v>
+        <v>177</v>
       </c>
       <c r="D10" t="s">
         <v>51</v>
       </c>
-      <c r="E10" t="n">
-        <v>0</v>
-      </c>
-      <c r="F10" s="1" t="n">
+      <c r="E10">
+        <v>0</v>
+      </c>
+      <c r="F10" s="1">
         <v>45749</v>
       </c>
-      <c r="G10" s="1" t="n">
+      <c r="G10" s="1">
         <v>45834</v>
       </c>
-      <c r="H10" t="n">
+      <c r="H10">
         <v>86</v>
       </c>
       <c r="I10" t="s">
@@ -3182,16 +3217,16 @@
     </row>
   </sheetData>
   <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
-  <pageSetup paperSize="9" orientation="portrait" horizontalDpi="300" verticalDpi="300" r:id="rId2"/>
+  <pageSetup paperSize="9" orientation="portrait" horizontalDpi="300" verticalDpi="300"/>
 </worksheet>
 </file>
 
 <file path=xl/worksheets/sheet8.xml><?xml version="1.0" encoding="utf-8"?>
-<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:xdr="http://schemas.openxmlformats.org/drawingml/2006/spreadsheetDrawing" xmlns:x14="http://schemas.microsoft.com/office/spreadsheetml/2009/9/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3">
-  <dimension ref="A1"/>
-  <sheetFormatPr defaultRowHeight="15.0" baseColWidth="10"/>
+<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{00000000-0001-0000-0700-000000000000}">
+  <dimension ref="A1:K11"/>
+  <sheetFormatPr defaultColWidth="11.42578125" defaultRowHeight="15" x14ac:dyDescent="0.25"/>
   <sheetData>
-    <row r="1">
+    <row r="1" spans="1:11" x14ac:dyDescent="0.25">
       <c r="A1" t="s">
         <v>0</v>
       </c>
@@ -3226,52 +3261,64 @@
         <v>10</v>
       </c>
     </row>
-    <row r="2">
+    <row r="2" spans="1:11" x14ac:dyDescent="0.25">
       <c r="A2" t="s">
-        <v>177</v>
+        <v>178</v>
       </c>
       <c r="B2" t="s">
-        <v>178</v>
+        <v>179</v>
       </c>
       <c r="C2" t="s">
-        <v>179</v>
+        <v>180</v>
       </c>
       <c r="D2" t="s">
         <v>33</v>
       </c>
-      <c r="E2" t="n">
-        <v>0</v>
-      </c>
-      <c r="F2" s="1"/>
-      <c r="G2" s="1"/>
-      <c r="H2"/>
-      <c r="I2"/>
-      <c r="J2"/>
-      <c r="K2"/>
-    </row>
-    <row r="3">
+      <c r="E2">
+        <v>0</v>
+      </c>
+      <c r="F2" s="1">
+        <v>45768</v>
+      </c>
+      <c r="G2" s="1">
+        <v>45835</v>
+      </c>
+      <c r="H2">
+        <v>68</v>
+      </c>
+      <c r="I2" t="s">
+        <v>38</v>
+      </c>
+      <c r="J2" t="s">
+        <v>104</v>
+      </c>
+      <c r="K2" t="s">
+        <v>39</v>
+      </c>
+    </row>
+    <row r="3" spans="1:11" x14ac:dyDescent="0.25">
       <c r="A3" t="s">
-        <v>177</v>
+        <v>178</v>
       </c>
       <c r="B3" t="s">
-        <v>180</v>
+        <v>181</v>
       </c>
       <c r="C3" t="s">
-        <v>181</v>
+        <v>182</v>
       </c>
       <c r="D3" t="s">
         <v>51</v>
       </c>
-      <c r="E3" t="n">
-        <v>0</v>
-      </c>
-      <c r="F3" s="1" t="n">
+      <c r="E3">
+        <v>0</v>
+      </c>
+      <c r="F3" s="1">
         <v>45768</v>
       </c>
-      <c r="G3" s="1" t="n">
+      <c r="G3" s="1">
         <v>45820</v>
       </c>
-      <c r="H3" t="n">
+      <c r="H3">
         <v>53</v>
       </c>
       <c r="I3" t="s">
@@ -3284,52 +3331,64 @@
         <v>57</v>
       </c>
     </row>
-    <row r="4">
+    <row r="4" spans="1:11" x14ac:dyDescent="0.25">
       <c r="A4" t="s">
-        <v>177</v>
+        <v>178</v>
       </c>
       <c r="B4" t="s">
-        <v>182</v>
+        <v>183</v>
       </c>
       <c r="C4" t="s">
-        <v>183</v>
+        <v>184</v>
       </c>
       <c r="D4" t="s">
         <v>51</v>
       </c>
-      <c r="E4" t="n">
-        <v>0</v>
-      </c>
-      <c r="F4" s="1"/>
-      <c r="G4" s="1"/>
-      <c r="H4"/>
-      <c r="I4"/>
-      <c r="J4"/>
-      <c r="K4"/>
-    </row>
-    <row r="5">
+      <c r="E4">
+        <v>0</v>
+      </c>
+      <c r="F4" s="1">
+        <v>45769</v>
+      </c>
+      <c r="G4" s="1">
+        <v>45835</v>
+      </c>
+      <c r="H4">
+        <v>67</v>
+      </c>
+      <c r="I4" t="s">
+        <v>38</v>
+      </c>
+      <c r="J4" t="s">
+        <v>104</v>
+      </c>
+      <c r="K4" t="s">
+        <v>73</v>
+      </c>
+    </row>
+    <row r="5" spans="1:11" x14ac:dyDescent="0.25">
       <c r="A5" t="s">
-        <v>177</v>
+        <v>178</v>
       </c>
       <c r="B5" t="s">
-        <v>184</v>
+        <v>185</v>
       </c>
       <c r="C5" t="s">
-        <v>185</v>
+        <v>186</v>
       </c>
       <c r="D5" t="s">
         <v>107</v>
       </c>
-      <c r="E5" t="n">
-        <v>0</v>
-      </c>
-      <c r="F5" s="1" t="n">
+      <c r="E5">
+        <v>0</v>
+      </c>
+      <c r="F5" s="1">
         <v>45769</v>
       </c>
-      <c r="G5" s="1" t="n">
+      <c r="G5" s="1">
         <v>45820</v>
       </c>
-      <c r="H5" t="n">
+      <c r="H5">
         <v>52</v>
       </c>
       <c r="I5" t="s">
@@ -3342,29 +3401,29 @@
         <v>62</v>
       </c>
     </row>
-    <row r="6">
+    <row r="6" spans="1:11" x14ac:dyDescent="0.25">
       <c r="A6" t="s">
-        <v>177</v>
+        <v>178</v>
       </c>
       <c r="B6" t="s">
-        <v>186</v>
+        <v>187</v>
       </c>
       <c r="C6" t="s">
-        <v>187</v>
+        <v>188</v>
       </c>
       <c r="D6" t="s">
         <v>80</v>
       </c>
-      <c r="E6" t="n">
-        <v>0</v>
-      </c>
-      <c r="F6" s="1" t="n">
+      <c r="E6">
+        <v>0</v>
+      </c>
+      <c r="F6" s="1">
         <v>45770</v>
       </c>
-      <c r="G6" s="1" t="n">
+      <c r="G6" s="1">
         <v>45828</v>
       </c>
-      <c r="H6" t="n">
+      <c r="H6">
         <v>59</v>
       </c>
       <c r="I6" t="s">
@@ -3377,29 +3436,29 @@
         <v>39</v>
       </c>
     </row>
-    <row r="7">
+    <row r="7" spans="1:11" x14ac:dyDescent="0.25">
       <c r="A7" t="s">
-        <v>177</v>
+        <v>178</v>
       </c>
       <c r="B7" t="s">
-        <v>188</v>
+        <v>189</v>
       </c>
       <c r="C7" t="s">
-        <v>189</v>
+        <v>190</v>
       </c>
       <c r="D7" t="s">
         <v>42</v>
       </c>
-      <c r="E7" t="n">
-        <v>0</v>
-      </c>
-      <c r="F7" s="1" t="n">
+      <c r="E7">
+        <v>0</v>
+      </c>
+      <c r="F7" s="1">
         <v>45775</v>
       </c>
-      <c r="G7" s="1" t="n">
+      <c r="G7" s="1">
         <v>45820</v>
       </c>
-      <c r="H7" t="n">
+      <c r="H7">
         <v>46</v>
       </c>
       <c r="I7" t="s">
@@ -3412,29 +3471,29 @@
         <v>52</v>
       </c>
     </row>
-    <row r="8">
+    <row r="8" spans="1:11" x14ac:dyDescent="0.25">
       <c r="A8" t="s">
-        <v>177</v>
+        <v>178</v>
       </c>
       <c r="B8" t="s">
-        <v>190</v>
+        <v>191</v>
       </c>
       <c r="C8" t="s">
-        <v>191</v>
+        <v>192</v>
       </c>
       <c r="D8" t="s">
         <v>68</v>
       </c>
-      <c r="E8" t="n">
-        <v>0</v>
-      </c>
-      <c r="F8" s="1" t="n">
+      <c r="E8">
+        <v>0</v>
+      </c>
+      <c r="F8" s="1">
         <v>45775</v>
       </c>
-      <c r="G8" s="1" t="n">
+      <c r="G8" s="1">
         <v>45820</v>
       </c>
-      <c r="H8" t="n">
+      <c r="H8">
         <v>46</v>
       </c>
       <c r="I8" t="s">
@@ -3447,29 +3506,29 @@
         <v>69</v>
       </c>
     </row>
-    <row r="9">
+    <row r="9" spans="1:11" x14ac:dyDescent="0.25">
       <c r="A9" t="s">
-        <v>177</v>
+        <v>178</v>
       </c>
       <c r="B9" t="s">
-        <v>192</v>
+        <v>193</v>
       </c>
       <c r="C9" t="s">
-        <v>193</v>
+        <v>194</v>
       </c>
       <c r="D9" t="s">
         <v>14</v>
       </c>
-      <c r="E9" t="n">
-        <v>0</v>
-      </c>
-      <c r="F9" s="1" t="n">
+      <c r="E9">
+        <v>0</v>
+      </c>
+      <c r="F9" s="1">
         <v>45776</v>
       </c>
-      <c r="G9" s="1" t="n">
+      <c r="G9" s="1">
         <v>45820</v>
       </c>
-      <c r="H9" t="n">
+      <c r="H9">
         <v>45</v>
       </c>
       <c r="I9" t="s">
@@ -3482,29 +3541,29 @@
         <v>48</v>
       </c>
     </row>
-    <row r="10">
+    <row r="10" spans="1:11" x14ac:dyDescent="0.25">
       <c r="A10" t="s">
-        <v>177</v>
+        <v>178</v>
       </c>
       <c r="B10" t="s">
-        <v>194</v>
+        <v>195</v>
       </c>
       <c r="C10" t="s">
-        <v>195</v>
+        <v>196</v>
       </c>
       <c r="D10" t="s">
         <v>72</v>
       </c>
-      <c r="E10" t="n">
-        <v>0</v>
-      </c>
-      <c r="F10" s="1" t="n">
+      <c r="E10">
+        <v>0</v>
+      </c>
+      <c r="F10" s="1">
         <v>45776</v>
       </c>
-      <c r="G10" s="1" t="n">
+      <c r="G10" s="1">
         <v>45813</v>
       </c>
-      <c r="H10" t="n">
+      <c r="H10">
         <v>38</v>
       </c>
       <c r="I10" t="s">
@@ -3517,36 +3576,36 @@
         <v>16</v>
       </c>
     </row>
-    <row r="11">
+    <row r="11" spans="1:11" x14ac:dyDescent="0.25">
       <c r="A11" t="s">
-        <v>177</v>
+        <v>178</v>
       </c>
       <c r="B11" t="s">
-        <v>196</v>
+        <v>197</v>
       </c>
       <c r="C11" t="s">
-        <v>197</v>
+        <v>198</v>
       </c>
       <c r="D11" t="s">
-        <v>198</v>
-      </c>
-      <c r="E11" t="n">
+        <v>199</v>
+      </c>
+      <c r="E11">
         <v>1</v>
       </c>
-      <c r="F11" s="1" t="n">
+      <c r="F11" s="1">
         <v>45777</v>
       </c>
-      <c r="G11" s="1" t="n">
+      <c r="G11" s="1">
         <v>45799</v>
       </c>
-      <c r="H11" t="n">
+      <c r="H11">
         <v>23</v>
       </c>
       <c r="I11" t="s">
         <v>43</v>
       </c>
       <c r="J11" t="s">
-        <v>199</v>
+        <v>200</v>
       </c>
       <c r="K11" t="s">
         <v>16</v>
@@ -3554,16 +3613,16 @@
     </row>
   </sheetData>
   <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
-  <pageSetup paperSize="9" orientation="portrait" horizontalDpi="300" verticalDpi="300" r:id="rId2"/>
+  <pageSetup paperSize="9" orientation="portrait" horizontalDpi="300" verticalDpi="300"/>
 </worksheet>
 </file>
 
 <file path=xl/worksheets/sheet9.xml><?xml version="1.0" encoding="utf-8"?>
-<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:xdr="http://schemas.openxmlformats.org/drawingml/2006/spreadsheetDrawing" xmlns:x14="http://schemas.microsoft.com/office/spreadsheetml/2009/9/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3">
-  <dimension ref="A1"/>
-  <sheetFormatPr defaultRowHeight="15.0" baseColWidth="10"/>
+<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{00000000-0001-0000-0800-000000000000}">
+  <dimension ref="A1:K2"/>
+  <sheetFormatPr defaultColWidth="11.42578125" defaultRowHeight="15" x14ac:dyDescent="0.25"/>
   <sheetData>
-    <row r="1">
+    <row r="1" spans="1:11" x14ac:dyDescent="0.25">
       <c r="A1" t="s">
         <v>0</v>
       </c>
@@ -3598,31 +3657,43 @@
         <v>10</v>
       </c>
     </row>
-    <row r="2">
+    <row r="2" spans="1:11" x14ac:dyDescent="0.25">
       <c r="A2" t="s">
-        <v>200</v>
+        <v>201</v>
       </c>
       <c r="B2" t="s">
-        <v>201</v>
+        <v>202</v>
       </c>
       <c r="C2" t="s">
-        <v>202</v>
+        <v>203</v>
       </c>
       <c r="D2" t="s">
         <v>51</v>
       </c>
-      <c r="E2" t="n">
+      <c r="E2">
         <v>1</v>
       </c>
-      <c r="F2" s="1"/>
-      <c r="G2" s="1"/>
-      <c r="H2"/>
-      <c r="I2"/>
-      <c r="J2"/>
-      <c r="K2"/>
+      <c r="F2" s="1">
+        <v>45792</v>
+      </c>
+      <c r="G2" s="1">
+        <v>45835</v>
+      </c>
+      <c r="H2">
+        <v>44</v>
+      </c>
+      <c r="I2" t="s">
+        <v>29</v>
+      </c>
+      <c r="J2" t="s">
+        <v>104</v>
+      </c>
+      <c r="K2" t="s">
+        <v>62</v>
+      </c>
     </row>
   </sheetData>
   <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
-  <pageSetup paperSize="9" orientation="portrait" horizontalDpi="300" verticalDpi="300" r:id="rId2"/>
+  <pageSetup paperSize="9" orientation="portrait" horizontalDpi="300" verticalDpi="300"/>
 </worksheet>
 </file>
--- a/Stat Reviews/OT24_StatReview/scotusblog_replication/data/term_index.xlsx
+++ b/Stat Reviews/OT24_StatReview/scotusblog_replication/data/term_index.xlsx
@@ -1,645 +1,637 @@
 
 <file path=xl/workbook.xml><?xml version="1.0" encoding="utf-8"?>
 <workbook xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x15="http://schemas.microsoft.com/office/spreadsheetml/2010/11/main" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr6="http://schemas.microsoft.com/office/spreadsheetml/2016/revision6" xmlns:xr10="http://schemas.microsoft.com/office/spreadsheetml/2016/revision10" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" mc:Ignorable="x15 xr xr6 xr10 xr2">
-  <fileVersion appName="xl" lastEdited="7" lowestEdited="7" rupBuild="28827"/>
-  <workbookPr/>
-  <mc:AlternateContent xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006">
-    <mc:Choice Requires="x15">
-      <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\Users\jaketruscott\Github\scotuswatch\Stat Reviews\OT24_StatReview\scotusblog_replication\data\"/>
-    </mc:Choice>
-  </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{A8276E09-40AF-4186-939A-95F7E6928968}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <workbookPr date1904="false"/>
   <bookViews>
-    <workbookView xWindow="28680" yWindow="-120" windowWidth="29040" windowHeight="15720" activeTab="6" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
+    <workbookView xWindow="0" yWindow="0" windowWidth="13125" windowHeight="6105" firstSheet="0" activeTab="0"/>
   </bookViews>
   <sheets>
-    <sheet name="No_Argument" sheetId="1" r:id="rId1"/>
-    <sheet name="October" sheetId="2" r:id="rId2"/>
-    <sheet name="November" sheetId="3" r:id="rId3"/>
-    <sheet name="December" sheetId="4" r:id="rId4"/>
-    <sheet name="January" sheetId="5" r:id="rId5"/>
-    <sheet name="February" sheetId="6" r:id="rId6"/>
-    <sheet name="March" sheetId="7" r:id="rId7"/>
-    <sheet name="April" sheetId="8" r:id="rId8"/>
-    <sheet name="May" sheetId="9" r:id="rId9"/>
+    <sheet name="No_Argument" sheetId="1" state="visible" r:id="rId1"/>
+    <sheet name="October" sheetId="2" state="visible" r:id="rId2"/>
+    <sheet name="November" sheetId="3" state="visible" r:id="rId3"/>
+    <sheet name="December" sheetId="4" state="visible" r:id="rId4"/>
+    <sheet name="January" sheetId="5" state="visible" r:id="rId5"/>
+    <sheet name="February" sheetId="6" state="visible" r:id="rId6"/>
+    <sheet name="March" sheetId="7" state="visible" r:id="rId7"/>
+    <sheet name="April" sheetId="8" state="visible" r:id="rId8"/>
+    <sheet name="May" sheetId="9" state="visible" r:id="rId9"/>
   </sheets>
-  <calcPr calcId="0"/>
 </workbook>
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="565" uniqueCount="204">
-  <si>
-    <t>sitting</t>
-  </si>
-  <si>
-    <t>docket</t>
-  </si>
-  <si>
-    <t>short_hand</t>
-  </si>
-  <si>
-    <t>lower_court</t>
-  </si>
-  <si>
-    <t>major_case</t>
-  </si>
-  <si>
-    <t>date_argued</t>
-  </si>
-  <si>
-    <t>date_decided</t>
-  </si>
-  <si>
-    <t>days_elapsed</t>
-  </si>
-  <si>
-    <t>decision</t>
-  </si>
-  <si>
-    <t>coalition</t>
-  </si>
-  <si>
-    <t>author</t>
-  </si>
-  <si>
-    <t>No Argument</t>
-  </si>
-  <si>
-    <t>23-167</t>
-  </si>
-  <si>
-    <t>Hamm</t>
-  </si>
-  <si>
-    <t>CA11</t>
-  </si>
-  <si>
-    <t>Vacate and Remand</t>
-  </si>
-  <si>
-    <t>Per Curiam</t>
-  </si>
-  <si>
-    <t>23-6573</t>
-  </si>
-  <si>
-    <t>Andrew</t>
-  </si>
-  <si>
-    <t>CA10</t>
-  </si>
-  <si>
-    <t>(7-2)</t>
-  </si>
-  <si>
-    <t>24A910</t>
-  </si>
-  <si>
-    <t>DOE v. CA</t>
-  </si>
-  <si>
-    <t>DCMA</t>
-  </si>
-  <si>
-    <t>Granted</t>
-  </si>
-  <si>
-    <t>(5-4)</t>
-  </si>
-  <si>
-    <t>24A931</t>
-  </si>
-  <si>
-    <t>Trump v. J.G.G.</t>
-  </si>
-  <si>
-    <t>DCDC</t>
-  </si>
-  <si>
-    <t>Vacate</t>
-  </si>
-  <si>
-    <t>(5-4)*</t>
-  </si>
-  <si>
-    <t>24A1007</t>
-  </si>
-  <si>
-    <t>A.A.R.P v. Trump</t>
-  </si>
-  <si>
-    <t>CA5</t>
-  </si>
-  <si>
-    <t>October</t>
-  </si>
-  <si>
-    <t>23-191</t>
-  </si>
-  <si>
-    <t>Williams</t>
-  </si>
-  <si>
-    <t>SCAL</t>
-  </si>
-  <si>
-    <t>Reverse and Remand</t>
-  </si>
-  <si>
-    <t>Kavanaugh</t>
-  </si>
-  <si>
-    <t>23-677</t>
-  </si>
-  <si>
-    <t>Royal Canin</t>
-  </si>
-  <si>
-    <t>CA8</t>
-  </si>
-  <si>
-    <t>Affirm</t>
-  </si>
-  <si>
-    <t>(9-0)</t>
-  </si>
-  <si>
-    <t>Kagan</t>
-  </si>
-  <si>
-    <t>23-852</t>
-  </si>
-  <si>
-    <t>Vanderstok</t>
-  </si>
-  <si>
-    <t>Gorsuch</t>
-  </si>
-  <si>
-    <t>23-621</t>
-  </si>
-  <si>
-    <t>Lackey</t>
-  </si>
-  <si>
-    <t>CA4</t>
-  </si>
-  <si>
-    <t>Roberts</t>
-  </si>
-  <si>
-    <t>22-7466</t>
-  </si>
-  <si>
-    <t>Glossip</t>
-  </si>
-  <si>
-    <t>CCAOK</t>
-  </si>
-  <si>
-    <t>(5-3)</t>
-  </si>
-  <si>
-    <t>Sotomayor</t>
-  </si>
-  <si>
-    <t>23-365</t>
-  </si>
-  <si>
-    <t>Medical Marijuana</t>
-  </si>
-  <si>
-    <t>CA2</t>
-  </si>
-  <si>
-    <t>Affirm and Remand</t>
-  </si>
-  <si>
-    <t>Barrett</t>
-  </si>
-  <si>
-    <t>23-583</t>
-  </si>
-  <si>
-    <t>Bouarfa</t>
-  </si>
-  <si>
-    <t>Jackson</t>
-  </si>
-  <si>
-    <t>23-713</t>
-  </si>
-  <si>
-    <t>Bufkin</t>
-  </si>
-  <si>
-    <t>CAFED</t>
-  </si>
-  <si>
-    <t>Thomas</t>
-  </si>
-  <si>
-    <t>23-753</t>
-  </si>
-  <si>
-    <t>SF v. EPA</t>
-  </si>
-  <si>
-    <t>CA9</t>
-  </si>
-  <si>
-    <t>Alito</t>
-  </si>
-  <si>
-    <t>November</t>
-  </si>
-  <si>
-    <t>23-1127</t>
-  </si>
-  <si>
-    <t>Wisconsin Bell</t>
-  </si>
-  <si>
-    <t>CA7</t>
-  </si>
-  <si>
-    <t>23-715</t>
-  </si>
-  <si>
-    <t>Advocate Christ Medical</t>
-  </si>
-  <si>
-    <t>CADC</t>
-  </si>
-  <si>
-    <t>23-217</t>
-  </si>
-  <si>
-    <t>E.M.D. Sales</t>
-  </si>
-  <si>
-    <t>23-980</t>
-  </si>
-  <si>
-    <t>Facebook</t>
-  </si>
-  <si>
-    <t>DIG</t>
-  </si>
-  <si>
-    <t>23-929</t>
-  </si>
-  <si>
-    <t>Velazquez</t>
-  </si>
-  <si>
-    <t>23-825</t>
-  </si>
-  <si>
-    <t>Delligatti</t>
-  </si>
-  <si>
-    <t>23-970</t>
-  </si>
-  <si>
-    <t>NVIDIA</t>
-  </si>
-  <si>
-    <t>December</t>
-  </si>
-  <si>
-    <t>23-1038</t>
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="204" uniqueCount="204">
+  <si>
+    <t xml:space="preserve">sitting</t>
+  </si>
+  <si>
+    <t xml:space="preserve">docket</t>
+  </si>
+  <si>
+    <t xml:space="preserve">short_hand</t>
+  </si>
+  <si>
+    <t xml:space="preserve">lower_court</t>
+  </si>
+  <si>
+    <t xml:space="preserve">major_case</t>
+  </si>
+  <si>
+    <t xml:space="preserve">date_argued</t>
+  </si>
+  <si>
+    <t xml:space="preserve">date_decided</t>
+  </si>
+  <si>
+    <t xml:space="preserve">days_elapsed</t>
+  </si>
+  <si>
+    <t xml:space="preserve">decision</t>
+  </si>
+  <si>
+    <t xml:space="preserve">coalition</t>
+  </si>
+  <si>
+    <t xml:space="preserve">author</t>
+  </si>
+  <si>
+    <t xml:space="preserve">No Argument</t>
+  </si>
+  <si>
+    <t xml:space="preserve">23-167</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Hamm</t>
+  </si>
+  <si>
+    <t xml:space="preserve">CA11</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Vacate and Remand</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Per Curiam</t>
+  </si>
+  <si>
+    <t xml:space="preserve">23-6573</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Andrew</t>
+  </si>
+  <si>
+    <t xml:space="preserve">CA10</t>
+  </si>
+  <si>
+    <t xml:space="preserve">(7-2)</t>
+  </si>
+  <si>
+    <t xml:space="preserve">24A910</t>
+  </si>
+  <si>
+    <t xml:space="preserve">DOE v. CA</t>
+  </si>
+  <si>
+    <t xml:space="preserve">DCMA</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Granted</t>
+  </si>
+  <si>
+    <t xml:space="preserve">(5-4)</t>
+  </si>
+  <si>
+    <t xml:space="preserve">24A931</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Trump v. J.G.G.</t>
+  </si>
+  <si>
+    <t xml:space="preserve">DCDC</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Vacate</t>
+  </si>
+  <si>
+    <t xml:space="preserve">(5-4)*</t>
+  </si>
+  <si>
+    <t xml:space="preserve">24A1007</t>
+  </si>
+  <si>
+    <t xml:space="preserve">A.A.R.P v. Trump</t>
+  </si>
+  <si>
+    <t xml:space="preserve">CA5</t>
+  </si>
+  <si>
+    <t xml:space="preserve">October</t>
+  </si>
+  <si>
+    <t xml:space="preserve">23-191</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Williams</t>
+  </si>
+  <si>
+    <t xml:space="preserve">SCAL</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Reverse and Remand</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Kavanaugh</t>
+  </si>
+  <si>
+    <t xml:space="preserve">23-677</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Royal Canin</t>
+  </si>
+  <si>
+    <t xml:space="preserve">CA8</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Affirm</t>
+  </si>
+  <si>
+    <t xml:space="preserve">(9-0)</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Kagan</t>
+  </si>
+  <si>
+    <t xml:space="preserve">23-852</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Vanderstok</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Gorsuch</t>
+  </si>
+  <si>
+    <t xml:space="preserve">23-621</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Lackey</t>
+  </si>
+  <si>
+    <t xml:space="preserve">CA4</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Roberts</t>
+  </si>
+  <si>
+    <t xml:space="preserve">22-7466</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Glossip</t>
+  </si>
+  <si>
+    <t xml:space="preserve">CCAOK</t>
+  </si>
+  <si>
+    <t xml:space="preserve">(5-3)</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Sotomayor</t>
+  </si>
+  <si>
+    <t xml:space="preserve">23-365</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Medical Marijuana</t>
+  </si>
+  <si>
+    <t xml:space="preserve">CA2</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Affirm and Remand</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Barrett</t>
+  </si>
+  <si>
+    <t xml:space="preserve">23-583</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Bouarfa</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Jackson</t>
+  </si>
+  <si>
+    <t xml:space="preserve">23-713</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Bufkin</t>
+  </si>
+  <si>
+    <t xml:space="preserve">CAFED</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Thomas</t>
+  </si>
+  <si>
+    <t xml:space="preserve">23-753</t>
+  </si>
+  <si>
+    <t xml:space="preserve">SF v. EPA</t>
+  </si>
+  <si>
+    <t xml:space="preserve">CA9</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Alito</t>
+  </si>
+  <si>
+    <t xml:space="preserve">November</t>
+  </si>
+  <si>
+    <t xml:space="preserve">23-1127</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Wisconsin Bell</t>
+  </si>
+  <si>
+    <t xml:space="preserve">CA7</t>
+  </si>
+  <si>
+    <t xml:space="preserve">23-715</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Advocate Christ Medical</t>
+  </si>
+  <si>
+    <t xml:space="preserve">CADC</t>
+  </si>
+  <si>
+    <t xml:space="preserve">23-217</t>
+  </si>
+  <si>
+    <t xml:space="preserve">E.M.D. Sales</t>
+  </si>
+  <si>
+    <t xml:space="preserve">23-980</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Facebook</t>
+  </si>
+  <si>
+    <t xml:space="preserve">DIG</t>
+  </si>
+  <si>
+    <t xml:space="preserve">23-929</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Velazquez</t>
+  </si>
+  <si>
+    <t xml:space="preserve">23-825</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Delligatti</t>
+  </si>
+  <si>
+    <t xml:space="preserve">23-970</t>
+  </si>
+  <si>
+    <t xml:space="preserve">NVIDIA</t>
+  </si>
+  <si>
+    <t xml:space="preserve">December</t>
+  </si>
+  <si>
+    <t xml:space="preserve">23-1038</t>
   </si>
   <si>
     <t xml:space="preserve">Wages and White Lion </t>
   </si>
   <si>
-    <t>23-824</t>
-  </si>
-  <si>
-    <t>Miller</t>
-  </si>
-  <si>
-    <t>Reverse</t>
-  </si>
-  <si>
-    <t>(8-1)</t>
-  </si>
-  <si>
-    <t>23-867</t>
-  </si>
-  <si>
-    <t>Hungary</t>
-  </si>
-  <si>
-    <t>23-477</t>
-  </si>
-  <si>
-    <t>Skrmetti</t>
-  </si>
-  <si>
-    <t>CA6</t>
-  </si>
-  <si>
-    <t>(6-3)</t>
-  </si>
-  <si>
-    <t>23-909</t>
-  </si>
-  <si>
-    <t>Kousisis</t>
-  </si>
-  <si>
-    <t>CA3</t>
-  </si>
-  <si>
-    <t>23-861</t>
-  </si>
-  <si>
-    <t>Feliciano</t>
-  </si>
-  <si>
-    <t>23-975</t>
-  </si>
-  <si>
-    <t>Seven County</t>
-  </si>
-  <si>
-    <t>(8-0)</t>
-  </si>
-  <si>
-    <t>23-900</t>
-  </si>
-  <si>
-    <t>Dewberry</t>
-  </si>
-  <si>
-    <t>January</t>
-  </si>
-  <si>
-    <t>23-1002</t>
-  </si>
-  <si>
-    <t>Hewitt</t>
-  </si>
-  <si>
-    <t>23-997</t>
-  </si>
-  <si>
-    <t>Stanley</t>
-  </si>
-  <si>
-    <t>(8-1)*</t>
-  </si>
-  <si>
-    <t>23-1095</t>
-  </si>
-  <si>
-    <t>Thompson</t>
-  </si>
-  <si>
-    <t>23-971</t>
-  </si>
-  <si>
-    <t>Waetzig</t>
-  </si>
-  <si>
-    <t>23-1122</t>
-  </si>
-  <si>
-    <t>Free Speech</t>
-  </si>
-  <si>
-    <t>Affirmed</t>
-  </si>
-  <si>
-    <t>23-1187</t>
+    <t xml:space="preserve">23-824</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Miller</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Reverse</t>
+  </si>
+  <si>
+    <t xml:space="preserve">(8-1)</t>
+  </si>
+  <si>
+    <t xml:space="preserve">23-867</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Hungary</t>
+  </si>
+  <si>
+    <t xml:space="preserve">23-477</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Skrmetti</t>
+  </si>
+  <si>
+    <t xml:space="preserve">CA6</t>
+  </si>
+  <si>
+    <t xml:space="preserve">(6-3)</t>
+  </si>
+  <si>
+    <t xml:space="preserve">23-909</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Kousisis</t>
+  </si>
+  <si>
+    <t xml:space="preserve">CA3</t>
+  </si>
+  <si>
+    <t xml:space="preserve">23-861</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Feliciano</t>
+  </si>
+  <si>
+    <t xml:space="preserve">23-975</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Seven County</t>
+  </si>
+  <si>
+    <t xml:space="preserve">(8-0)</t>
+  </si>
+  <si>
+    <t xml:space="preserve">23-900</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Dewberry</t>
+  </si>
+  <si>
+    <t xml:space="preserve">January</t>
+  </si>
+  <si>
+    <t xml:space="preserve">23-1002</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Hewitt</t>
+  </si>
+  <si>
+    <t xml:space="preserve">23-997</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Stanley</t>
+  </si>
+  <si>
+    <t xml:space="preserve">(8-1)*</t>
+  </si>
+  <si>
+    <t xml:space="preserve">23-1095</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Thompson</t>
+  </si>
+  <si>
+    <t xml:space="preserve">23-971</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Waetzig</t>
+  </si>
+  <si>
+    <t xml:space="preserve">23-1122</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Free Speech</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Affirmed</t>
+  </si>
+  <si>
+    <t xml:space="preserve">23-1187</t>
   </si>
   <si>
     <t xml:space="preserve"> R.J. Reynolds </t>
   </si>
   <si>
-    <t>23-1226</t>
-  </si>
-  <si>
-    <t>McLaughlin</t>
-  </si>
-  <si>
-    <t>23-1239</t>
-  </si>
-  <si>
-    <t>Barnes</t>
-  </si>
-  <si>
-    <t>23-1007</t>
-  </si>
-  <si>
-    <t>Cunningham</t>
-  </si>
-  <si>
-    <t>24-656</t>
-  </si>
-  <si>
-    <t>TikTok</t>
-  </si>
-  <si>
-    <t>February</t>
-  </si>
-  <si>
-    <t>23-7809</t>
-  </si>
-  <si>
-    <t>Guitierrez</t>
-  </si>
-  <si>
-    <t>23-7483</t>
-  </si>
-  <si>
-    <t>Esteras</t>
-  </si>
-  <si>
-    <t>(7-2)*</t>
-  </si>
-  <si>
-    <t>23-1324</t>
-  </si>
-  <si>
-    <t>Perttu</t>
-  </si>
-  <si>
-    <t>23-1039</t>
-  </si>
-  <si>
-    <t>Ames</t>
-  </si>
-  <si>
-    <t>23-1201</t>
-  </si>
-  <si>
-    <t>CC/Devas</t>
-  </si>
-  <si>
-    <t>23-1259</t>
-  </si>
-  <si>
-    <t>BLOM Bank</t>
-  </si>
-  <si>
-    <t>23-1141</t>
-  </si>
-  <si>
-    <t>Smith and Wesson</t>
-  </si>
-  <si>
-    <t>CA1</t>
-  </si>
-  <si>
-    <t>23-1300</t>
-  </si>
-  <si>
-    <t>NRC</t>
-  </si>
-  <si>
-    <t>March</t>
-  </si>
-  <si>
-    <t>24-109</t>
-  </si>
-  <si>
-    <t>Lousiana</t>
-  </si>
-  <si>
-    <t>WDLA</t>
-  </si>
-  <si>
-    <t>23-1270</t>
-  </si>
-  <si>
-    <t>Riley</t>
-  </si>
-  <si>
-    <t>23-1229</t>
+    <t xml:space="preserve">23-1226</t>
+  </si>
+  <si>
+    <t xml:space="preserve">McLaughlin</t>
+  </si>
+  <si>
+    <t xml:space="preserve">23-1239</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Barnes</t>
+  </si>
+  <si>
+    <t xml:space="preserve">23-1007</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Cunningham</t>
+  </si>
+  <si>
+    <t xml:space="preserve">24-656</t>
+  </si>
+  <si>
+    <t xml:space="preserve">TikTok</t>
+  </si>
+  <si>
+    <t xml:space="preserve">February</t>
+  </si>
+  <si>
+    <t xml:space="preserve">23-7809</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Guitierrez</t>
+  </si>
+  <si>
+    <t xml:space="preserve">23-7483</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Esteras</t>
+  </si>
+  <si>
+    <t xml:space="preserve">(7-2)*</t>
+  </si>
+  <si>
+    <t xml:space="preserve">23-1324</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Perttu</t>
+  </si>
+  <si>
+    <t xml:space="preserve">23-1039</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Ames</t>
+  </si>
+  <si>
+    <t xml:space="preserve">23-1201</t>
+  </si>
+  <si>
+    <t xml:space="preserve">CC/Devas</t>
+  </si>
+  <si>
+    <t xml:space="preserve">23-1259</t>
+  </si>
+  <si>
+    <t xml:space="preserve">BLOM Bank</t>
+  </si>
+  <si>
+    <t xml:space="preserve">23-1141</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Smith and Wesson</t>
+  </si>
+  <si>
+    <t xml:space="preserve">CA1</t>
+  </si>
+  <si>
+    <t xml:space="preserve">23-1300</t>
+  </si>
+  <si>
+    <t xml:space="preserve">NRC</t>
+  </si>
+  <si>
+    <t xml:space="preserve">March</t>
+  </si>
+  <si>
+    <t xml:space="preserve">24-109</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Lousiana</t>
+  </si>
+  <si>
+    <t xml:space="preserve">WDLA</t>
+  </si>
+  <si>
+    <t xml:space="preserve">23-1270</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Riley</t>
+  </si>
+  <si>
+    <t xml:space="preserve">23-1229</t>
   </si>
   <si>
     <t xml:space="preserve">Calumet </t>
   </si>
   <si>
-    <t>23-1067</t>
-  </si>
-  <si>
-    <t>Oklahoma</t>
-  </si>
-  <si>
-    <t>24-354</t>
-  </si>
-  <si>
-    <t>Consumers' Research</t>
-  </si>
-  <si>
-    <t>24-154</t>
-  </si>
-  <si>
-    <t>Catholic Charities</t>
-  </si>
-  <si>
-    <t>SCWI</t>
-  </si>
-  <si>
-    <t>23-1345</t>
-  </si>
-  <si>
-    <t>Rivers</t>
-  </si>
-  <si>
-    <t>24-20</t>
-  </si>
-  <si>
-    <t>Fuld</t>
-  </si>
-  <si>
-    <t>23-1275</t>
-  </si>
-  <si>
-    <t>Medina</t>
-  </si>
-  <si>
-    <t>April</t>
-  </si>
-  <si>
-    <t>24-316</t>
-  </si>
-  <si>
-    <t>Kennedy</t>
-  </si>
-  <si>
-    <t>24-275</t>
-  </si>
-  <si>
-    <t>Parrish</t>
-  </si>
-  <si>
-    <t>24-297</t>
-  </si>
-  <si>
-    <t>Mahmoud</t>
-  </si>
-  <si>
-    <t>24-416</t>
-  </si>
-  <si>
-    <t>Zuch</t>
-  </si>
-  <si>
-    <t>24-7</t>
-  </si>
-  <si>
-    <t>Diamond</t>
-  </si>
-  <si>
-    <t>24-249</t>
-  </si>
-  <si>
-    <t>A.J.T.</t>
-  </si>
-  <si>
-    <t>24-320</t>
-  </si>
-  <si>
-    <t>Soto</t>
-  </si>
-  <si>
-    <t>24-362</t>
-  </si>
-  <si>
-    <t>Martin</t>
-  </si>
-  <si>
-    <t>24-304</t>
-  </si>
-  <si>
-    <t>Laboratory Corp.</t>
-  </si>
-  <si>
-    <t>24-394</t>
-  </si>
-  <si>
-    <t>Drummond</t>
-  </si>
-  <si>
-    <t>SCOK</t>
-  </si>
-  <si>
-    <t>(4-4)*</t>
-  </si>
-  <si>
-    <t>May</t>
-  </si>
-  <si>
-    <t>24A884</t>
-  </si>
-  <si>
-    <t>Trump v. CASA</t>
+    <t xml:space="preserve">23-1067</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Oklahoma</t>
+  </si>
+  <si>
+    <t xml:space="preserve">24-354</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Consumers' Research</t>
+  </si>
+  <si>
+    <t xml:space="preserve">24-154</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Catholic Charities</t>
+  </si>
+  <si>
+    <t xml:space="preserve">SCWI</t>
+  </si>
+  <si>
+    <t xml:space="preserve">23-1345</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Rivers</t>
+  </si>
+  <si>
+    <t xml:space="preserve">24-20</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Fuld</t>
+  </si>
+  <si>
+    <t xml:space="preserve">23-1275</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Medina</t>
+  </si>
+  <si>
+    <t xml:space="preserve">April</t>
+  </si>
+  <si>
+    <t xml:space="preserve">24-316</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Kennedy</t>
+  </si>
+  <si>
+    <t xml:space="preserve">24-275</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Parrish</t>
+  </si>
+  <si>
+    <t xml:space="preserve">24-297</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Mahmoud</t>
+  </si>
+  <si>
+    <t xml:space="preserve">24-416</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Zuch</t>
+  </si>
+  <si>
+    <t xml:space="preserve">24-7</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Diamond</t>
+  </si>
+  <si>
+    <t xml:space="preserve">24-249</t>
+  </si>
+  <si>
+    <t xml:space="preserve">A.J.T.</t>
+  </si>
+  <si>
+    <t xml:space="preserve">24-320</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Soto</t>
+  </si>
+  <si>
+    <t xml:space="preserve">24-362</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Martin</t>
+  </si>
+  <si>
+    <t xml:space="preserve">24-304</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Laboratory Corp.</t>
+  </si>
+  <si>
+    <t xml:space="preserve">24-394</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Drummond</t>
+  </si>
+  <si>
+    <t xml:space="preserve">SCOK</t>
+  </si>
+  <si>
+    <t xml:space="preserve">(4-4)*</t>
+  </si>
+  <si>
+    <t xml:space="preserve">May</t>
+  </si>
+  <si>
+    <t xml:space="preserve">24A884</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Trump v. CASA</t>
   </si>
 </sst>
 </file>
@@ -647,9 +639,9 @@
 <file path=xl/styles.xml><?xml version="1.0" encoding="utf-8"?>
 <styleSheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:x16r2="http://schemas.microsoft.com/office/spreadsheetml/2015/02/main" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" mc:Ignorable="x14ac x16r2 xr">
   <numFmts count="1">
-    <numFmt numFmtId="164" formatCode="mm/dd/yyyy"/>
+    <numFmt numFmtId="165" formatCode="mm/dd/yyyy"/>
   </numFmts>
-  <fonts count="2" x14ac:knownFonts="1">
+  <fonts count="2">
     <font>
       <sz val="11"/>
       <color rgb="FF000000"/>
@@ -685,21 +677,12 @@
   </cellStyleXfs>
   <cellXfs count="2">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0"/>
-    <xf numFmtId="164" fontId="1" fillId="0" borderId="0" xfId="0" applyNumberFormat="1" applyFont="1"/>
+    <xf numFmtId="165" fontId="1" fillId="0" borderId="0" xfId="0" applyFont="1" applyNumberFormat="1"/>
   </cellXfs>
   <cellStyles count="1">
     <cellStyle name="Normal" xfId="0" builtinId="0"/>
   </cellStyles>
   <dxfs count="0"/>
-  <tableStyles count="0" defaultTableStyle="TableStyleMedium2" defaultPivotStyle="PivotStyleLight16"/>
-  <extLst>
-    <ext xmlns:x14="http://schemas.microsoft.com/office/spreadsheetml/2009/9/main" uri="{EB79DEF2-80B8-43e5-95BD-54CBDDF9020C}">
-      <x14:slicerStyles defaultSlicerStyle="SlicerStyleLight1"/>
-    </ext>
-    <ext xmlns:x15="http://schemas.microsoft.com/office/spreadsheetml/2010/11/main" uri="{9260A510-F301-46a8-8635-F512D64BE5F5}">
-      <x15:timelineStyles defaultTimelineStyle="TimeSlicerStyleLight1"/>
-    </ext>
-  </extLst>
 </styleSheet>
 </file>
 
@@ -981,11 +964,11 @@
 </file>
 
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
-<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{00000000-0001-0000-0000-000000000000}">
-  <dimension ref="A1:K6"/>
-  <sheetFormatPr defaultColWidth="11.42578125" defaultRowHeight="15" x14ac:dyDescent="0.25"/>
+<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:xdr="http://schemas.openxmlformats.org/drawingml/2006/spreadsheetDrawing" xmlns:x14="http://schemas.microsoft.com/office/spreadsheetml/2009/9/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3">
+  <dimension ref="A1"/>
+  <sheetFormatPr defaultRowHeight="15.0" baseColWidth="10"/>
   <sheetData>
-    <row r="1" spans="1:11" x14ac:dyDescent="0.25">
+    <row r="1">
       <c r="A1" t="s">
         <v>0</v>
       </c>
@@ -1020,7 +1003,7 @@
         <v>10</v>
       </c>
     </row>
-    <row r="2" spans="1:11" x14ac:dyDescent="0.25">
+    <row r="2">
       <c r="A2" t="s">
         <v>11</v>
       </c>
@@ -1033,13 +1016,14 @@
       <c r="D2" t="s">
         <v>14</v>
       </c>
-      <c r="E2">
+      <c r="E2" t="n">
         <v>0</v>
       </c>
       <c r="F2" s="1"/>
-      <c r="G2" s="1">
+      <c r="G2" s="1" t="n">
         <v>45600</v>
       </c>
+      <c r="H2"/>
       <c r="I2" t="s">
         <v>15</v>
       </c>
@@ -1050,7 +1034,7 @@
         <v>16</v>
       </c>
     </row>
-    <row r="3" spans="1:11" x14ac:dyDescent="0.25">
+    <row r="3">
       <c r="A3" t="s">
         <v>11</v>
       </c>
@@ -1063,13 +1047,14 @@
       <c r="D3" t="s">
         <v>19</v>
       </c>
-      <c r="E3">
+      <c r="E3" t="n">
         <v>0</v>
       </c>
       <c r="F3" s="1"/>
-      <c r="G3" s="1">
+      <c r="G3" s="1" t="n">
         <v>45678</v>
       </c>
+      <c r="H3"/>
       <c r="I3" t="s">
         <v>15</v>
       </c>
@@ -1080,7 +1065,7 @@
         <v>16</v>
       </c>
     </row>
-    <row r="4" spans="1:11" x14ac:dyDescent="0.25">
+    <row r="4">
       <c r="A4" t="s">
         <v>11</v>
       </c>
@@ -1093,13 +1078,14 @@
       <c r="D4" t="s">
         <v>23</v>
       </c>
-      <c r="E4">
+      <c r="E4" t="n">
         <v>0</v>
       </c>
       <c r="F4" s="1"/>
-      <c r="G4" s="1">
+      <c r="G4" s="1" t="n">
         <v>45751</v>
       </c>
+      <c r="H4"/>
       <c r="I4" t="s">
         <v>24</v>
       </c>
@@ -1110,7 +1096,7 @@
         <v>16</v>
       </c>
     </row>
-    <row r="5" spans="1:11" x14ac:dyDescent="0.25">
+    <row r="5">
       <c r="A5" t="s">
         <v>11</v>
       </c>
@@ -1123,13 +1109,14 @@
       <c r="D5" t="s">
         <v>28</v>
       </c>
-      <c r="E5">
+      <c r="E5" t="n">
         <v>0</v>
       </c>
       <c r="F5" s="1"/>
-      <c r="G5" s="1">
+      <c r="G5" s="1" t="n">
         <v>45754</v>
       </c>
+      <c r="H5"/>
       <c r="I5" t="s">
         <v>29</v>
       </c>
@@ -1140,7 +1127,7 @@
         <v>16</v>
       </c>
     </row>
-    <row r="6" spans="1:11" x14ac:dyDescent="0.25">
+    <row r="6">
       <c r="A6" t="s">
         <v>11</v>
       </c>
@@ -1153,13 +1140,14 @@
       <c r="D6" t="s">
         <v>33</v>
       </c>
-      <c r="E6">
+      <c r="E6" t="n">
         <v>0</v>
       </c>
       <c r="F6" s="1"/>
-      <c r="G6" s="1">
+      <c r="G6" s="1" t="n">
         <v>45793</v>
       </c>
+      <c r="H6"/>
       <c r="I6" t="s">
         <v>29</v>
       </c>
@@ -1172,16 +1160,16 @@
     </row>
   </sheetData>
   <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
-  <pageSetup paperSize="9" orientation="portrait" horizontalDpi="300" verticalDpi="300"/>
+  <pageSetup paperSize="9" orientation="portrait" horizontalDpi="300" verticalDpi="300" r:id="rId2"/>
 </worksheet>
 </file>
 
 <file path=xl/worksheets/sheet2.xml><?xml version="1.0" encoding="utf-8"?>
-<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{00000000-0001-0000-0100-000000000000}">
-  <dimension ref="A1:K10"/>
-  <sheetFormatPr defaultColWidth="11.42578125" defaultRowHeight="15" x14ac:dyDescent="0.25"/>
+<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:xdr="http://schemas.openxmlformats.org/drawingml/2006/spreadsheetDrawing" xmlns:x14="http://schemas.microsoft.com/office/spreadsheetml/2009/9/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3">
+  <dimension ref="A1"/>
+  <sheetFormatPr defaultRowHeight="15.0" baseColWidth="10"/>
   <sheetData>
-    <row r="1" spans="1:11" x14ac:dyDescent="0.25">
+    <row r="1">
       <c r="A1" t="s">
         <v>0</v>
       </c>
@@ -1216,7 +1204,7 @@
         <v>10</v>
       </c>
     </row>
-    <row r="2" spans="1:11" x14ac:dyDescent="0.25">
+    <row r="2">
       <c r="A2" t="s">
         <v>34</v>
       </c>
@@ -1229,16 +1217,16 @@
       <c r="D2" t="s">
         <v>37</v>
       </c>
-      <c r="E2">
-        <v>0</v>
-      </c>
-      <c r="F2" s="1">
+      <c r="E2" t="n">
+        <v>0</v>
+      </c>
+      <c r="F2" s="1" t="n">
         <v>45572</v>
       </c>
-      <c r="G2" s="1">
+      <c r="G2" s="1" t="n">
         <v>45709</v>
       </c>
-      <c r="H2">
+      <c r="H2" t="n">
         <v>138</v>
       </c>
       <c r="I2" t="s">
@@ -1251,7 +1239,7 @@
         <v>39</v>
       </c>
     </row>
-    <row r="3" spans="1:11" x14ac:dyDescent="0.25">
+    <row r="3">
       <c r="A3" t="s">
         <v>34</v>
       </c>
@@ -1264,16 +1252,16 @@
       <c r="D3" t="s">
         <v>42</v>
       </c>
-      <c r="E3">
-        <v>0</v>
-      </c>
-      <c r="F3" s="1">
+      <c r="E3" t="n">
+        <v>0</v>
+      </c>
+      <c r="F3" s="1" t="n">
         <v>45572</v>
       </c>
-      <c r="G3" s="1">
+      <c r="G3" s="1" t="n">
         <v>45672</v>
       </c>
-      <c r="H3">
+      <c r="H3" t="n">
         <v>101</v>
       </c>
       <c r="I3" t="s">
@@ -1286,7 +1274,7 @@
         <v>45</v>
       </c>
     </row>
-    <row r="4" spans="1:11" x14ac:dyDescent="0.25">
+    <row r="4">
       <c r="A4" t="s">
         <v>34</v>
       </c>
@@ -1299,16 +1287,16 @@
       <c r="D4" t="s">
         <v>33</v>
       </c>
-      <c r="E4">
-        <v>0</v>
-      </c>
-      <c r="F4" s="1">
+      <c r="E4" t="n">
+        <v>0</v>
+      </c>
+      <c r="F4" s="1" t="n">
         <v>45573</v>
       </c>
-      <c r="G4" s="1">
+      <c r="G4" s="1" t="n">
         <v>45742</v>
       </c>
-      <c r="H4">
+      <c r="H4" t="n">
         <v>170</v>
       </c>
       <c r="I4" t="s">
@@ -1321,7 +1309,7 @@
         <v>48</v>
       </c>
     </row>
-    <row r="5" spans="1:11" x14ac:dyDescent="0.25">
+    <row r="5">
       <c r="A5" t="s">
         <v>34</v>
       </c>
@@ -1334,16 +1322,16 @@
       <c r="D5" t="s">
         <v>51</v>
       </c>
-      <c r="E5">
-        <v>0</v>
-      </c>
-      <c r="F5" s="1">
+      <c r="E5" t="n">
+        <v>0</v>
+      </c>
+      <c r="F5" s="1" t="n">
         <v>45573</v>
       </c>
-      <c r="G5" s="1">
+      <c r="G5" s="1" t="n">
         <v>45713</v>
       </c>
-      <c r="H5">
+      <c r="H5" t="n">
         <v>141</v>
       </c>
       <c r="I5" t="s">
@@ -1356,7 +1344,7 @@
         <v>52</v>
       </c>
     </row>
-    <row r="6" spans="1:11" x14ac:dyDescent="0.25">
+    <row r="6">
       <c r="A6" t="s">
         <v>34</v>
       </c>
@@ -1369,16 +1357,16 @@
       <c r="D6" t="s">
         <v>55</v>
       </c>
-      <c r="E6">
+      <c r="E6" t="n">
         <v>1</v>
       </c>
-      <c r="F6" s="1">
+      <c r="F6" s="1" t="n">
         <v>45574</v>
       </c>
-      <c r="G6" s="1">
+      <c r="G6" s="1" t="n">
         <v>45713</v>
       </c>
-      <c r="H6">
+      <c r="H6" t="n">
         <v>140</v>
       </c>
       <c r="I6" t="s">
@@ -1391,7 +1379,7 @@
         <v>57</v>
       </c>
     </row>
-    <row r="7" spans="1:11" x14ac:dyDescent="0.25">
+    <row r="7">
       <c r="A7" t="s">
         <v>34</v>
       </c>
@@ -1404,16 +1392,16 @@
       <c r="D7" t="s">
         <v>60</v>
       </c>
-      <c r="E7">
-        <v>0</v>
-      </c>
-      <c r="F7" s="1">
+      <c r="E7" t="n">
+        <v>0</v>
+      </c>
+      <c r="F7" s="1" t="n">
         <v>45580</v>
       </c>
-      <c r="G7" s="1">
+      <c r="G7" s="1" t="n">
         <v>45749</v>
       </c>
-      <c r="H7">
+      <c r="H7" t="n">
         <v>170</v>
       </c>
       <c r="I7" t="s">
@@ -1426,7 +1414,7 @@
         <v>62</v>
       </c>
     </row>
-    <row r="8" spans="1:11" x14ac:dyDescent="0.25">
+    <row r="8">
       <c r="A8" t="s">
         <v>34</v>
       </c>
@@ -1439,16 +1427,16 @@
       <c r="D8" t="s">
         <v>14</v>
       </c>
-      <c r="E8">
-        <v>0</v>
-      </c>
-      <c r="F8" s="1">
+      <c r="E8" t="n">
+        <v>0</v>
+      </c>
+      <c r="F8" s="1" t="n">
         <v>45580</v>
       </c>
-      <c r="G8" s="1">
+      <c r="G8" s="1" t="n">
         <v>45636</v>
       </c>
-      <c r="H8">
+      <c r="H8" t="n">
         <v>57</v>
       </c>
       <c r="I8" t="s">
@@ -1461,7 +1449,7 @@
         <v>65</v>
       </c>
     </row>
-    <row r="9" spans="1:11" x14ac:dyDescent="0.25">
+    <row r="9">
       <c r="A9" t="s">
         <v>34</v>
       </c>
@@ -1474,16 +1462,16 @@
       <c r="D9" t="s">
         <v>68</v>
       </c>
-      <c r="E9">
-        <v>0</v>
-      </c>
-      <c r="F9" s="1">
+      <c r="E9" t="n">
+        <v>0</v>
+      </c>
+      <c r="F9" s="1" t="n">
         <v>45581</v>
       </c>
-      <c r="G9" s="1">
+      <c r="G9" s="1" t="n">
         <v>45721</v>
       </c>
-      <c r="H9">
+      <c r="H9" t="n">
         <v>141</v>
       </c>
       <c r="I9" t="s">
@@ -1496,7 +1484,7 @@
         <v>69</v>
       </c>
     </row>
-    <row r="10" spans="1:11" x14ac:dyDescent="0.25">
+    <row r="10">
       <c r="A10" t="s">
         <v>34</v>
       </c>
@@ -1509,16 +1497,16 @@
       <c r="D10" t="s">
         <v>72</v>
       </c>
-      <c r="E10">
-        <v>0</v>
-      </c>
-      <c r="F10" s="1">
+      <c r="E10" t="n">
+        <v>0</v>
+      </c>
+      <c r="F10" s="1" t="n">
         <v>45581</v>
       </c>
-      <c r="G10" s="1">
+      <c r="G10" s="1" t="n">
         <v>45720</v>
       </c>
-      <c r="H10">
+      <c r="H10" t="n">
         <v>140</v>
       </c>
       <c r="I10" t="s">
@@ -1533,16 +1521,16 @@
     </row>
   </sheetData>
   <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
-  <pageSetup paperSize="9" orientation="portrait" horizontalDpi="300" verticalDpi="300"/>
+  <pageSetup paperSize="9" orientation="portrait" horizontalDpi="300" verticalDpi="300" r:id="rId2"/>
 </worksheet>
 </file>
 
 <file path=xl/worksheets/sheet3.xml><?xml version="1.0" encoding="utf-8"?>
-<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{00000000-0001-0000-0200-000000000000}">
-  <dimension ref="A1:K8"/>
-  <sheetFormatPr defaultColWidth="11.42578125" defaultRowHeight="15" x14ac:dyDescent="0.25"/>
+<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:xdr="http://schemas.openxmlformats.org/drawingml/2006/spreadsheetDrawing" xmlns:x14="http://schemas.microsoft.com/office/spreadsheetml/2009/9/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3">
+  <dimension ref="A1"/>
+  <sheetFormatPr defaultRowHeight="15.0" baseColWidth="10"/>
   <sheetData>
-    <row r="1" spans="1:11" x14ac:dyDescent="0.25">
+    <row r="1">
       <c r="A1" t="s">
         <v>0</v>
       </c>
@@ -1577,7 +1565,7 @@
         <v>10</v>
       </c>
     </row>
-    <row r="2" spans="1:11" x14ac:dyDescent="0.25">
+    <row r="2">
       <c r="A2" t="s">
         <v>74</v>
       </c>
@@ -1590,16 +1578,16 @@
       <c r="D2" t="s">
         <v>77</v>
       </c>
-      <c r="E2">
-        <v>0</v>
-      </c>
-      <c r="F2" s="1">
+      <c r="E2" t="n">
+        <v>0</v>
+      </c>
+      <c r="F2" s="1" t="n">
         <v>45600</v>
       </c>
-      <c r="G2" s="1">
+      <c r="G2" s="1" t="n">
         <v>45709</v>
       </c>
-      <c r="H2">
+      <c r="H2" t="n">
         <v>110</v>
       </c>
       <c r="I2" t="s">
@@ -1612,7 +1600,7 @@
         <v>45</v>
       </c>
     </row>
-    <row r="3" spans="1:11" x14ac:dyDescent="0.25">
+    <row r="3">
       <c r="A3" t="s">
         <v>74</v>
       </c>
@@ -1625,16 +1613,16 @@
       <c r="D3" t="s">
         <v>80</v>
       </c>
-      <c r="E3">
-        <v>0</v>
-      </c>
-      <c r="F3" s="1">
+      <c r="E3" t="n">
+        <v>0</v>
+      </c>
+      <c r="F3" s="1" t="n">
         <v>45601</v>
       </c>
-      <c r="G3" s="1">
+      <c r="G3" s="1" t="n">
         <v>45776</v>
       </c>
-      <c r="H3">
+      <c r="H3" t="n">
         <v>176</v>
       </c>
       <c r="I3" t="s">
@@ -1647,7 +1635,7 @@
         <v>62</v>
       </c>
     </row>
-    <row r="4" spans="1:11" x14ac:dyDescent="0.25">
+    <row r="4">
       <c r="A4" t="s">
         <v>74</v>
       </c>
@@ -1660,16 +1648,16 @@
       <c r="D4" t="s">
         <v>51</v>
       </c>
-      <c r="E4">
-        <v>0</v>
-      </c>
-      <c r="F4" s="1">
+      <c r="E4" t="n">
+        <v>0</v>
+      </c>
+      <c r="F4" s="1" t="n">
         <v>45601</v>
       </c>
-      <c r="G4" s="1">
+      <c r="G4" s="1" t="n">
         <v>45672</v>
       </c>
-      <c r="H4">
+      <c r="H4" t="n">
         <v>72</v>
       </c>
       <c r="I4" t="s">
@@ -1682,7 +1670,7 @@
         <v>39</v>
       </c>
     </row>
-    <row r="5" spans="1:11" x14ac:dyDescent="0.25">
+    <row r="5">
       <c r="A5" t="s">
         <v>74</v>
       </c>
@@ -1695,16 +1683,16 @@
       <c r="D5" t="s">
         <v>72</v>
       </c>
-      <c r="E5">
-        <v>0</v>
-      </c>
-      <c r="F5" s="1">
+      <c r="E5" t="n">
+        <v>0</v>
+      </c>
+      <c r="F5" s="1" t="n">
         <v>45602</v>
       </c>
-      <c r="G5" s="1">
+      <c r="G5" s="1" t="n">
         <v>45618</v>
       </c>
-      <c r="H5">
+      <c r="H5" t="n">
         <v>17</v>
       </c>
       <c r="I5" t="s">
@@ -1717,7 +1705,7 @@
         <v>16</v>
       </c>
     </row>
-    <row r="6" spans="1:11" x14ac:dyDescent="0.25">
+    <row r="6">
       <c r="A6" t="s">
         <v>74</v>
       </c>
@@ -1730,16 +1718,16 @@
       <c r="D6" t="s">
         <v>19</v>
       </c>
-      <c r="E6">
-        <v>0</v>
-      </c>
-      <c r="F6" s="1">
+      <c r="E6" t="n">
+        <v>0</v>
+      </c>
+      <c r="F6" s="1" t="n">
         <v>45608</v>
       </c>
-      <c r="G6" s="1">
+      <c r="G6" s="1" t="n">
         <v>45769</v>
       </c>
-      <c r="H6">
+      <c r="H6" t="n">
         <v>162</v>
       </c>
       <c r="I6" t="s">
@@ -1752,7 +1740,7 @@
         <v>48</v>
       </c>
     </row>
-    <row r="7" spans="1:11" x14ac:dyDescent="0.25">
+    <row r="7">
       <c r="A7" t="s">
         <v>74</v>
       </c>
@@ -1765,16 +1753,16 @@
       <c r="D7" t="s">
         <v>60</v>
       </c>
-      <c r="E7">
-        <v>0</v>
-      </c>
-      <c r="F7" s="1">
+      <c r="E7" t="n">
+        <v>0</v>
+      </c>
+      <c r="F7" s="1" t="n">
         <v>45608</v>
       </c>
-      <c r="G7" s="1">
+      <c r="G7" s="1" t="n">
         <v>45737</v>
       </c>
-      <c r="H7">
+      <c r="H7" t="n">
         <v>130</v>
       </c>
       <c r="I7" t="s">
@@ -1787,7 +1775,7 @@
         <v>69</v>
       </c>
     </row>
-    <row r="8" spans="1:11" x14ac:dyDescent="0.25">
+    <row r="8">
       <c r="A8" t="s">
         <v>74</v>
       </c>
@@ -1800,16 +1788,16 @@
       <c r="D8" t="s">
         <v>72</v>
       </c>
-      <c r="E8">
-        <v>0</v>
-      </c>
-      <c r="F8" s="1">
+      <c r="E8" t="n">
+        <v>0</v>
+      </c>
+      <c r="F8" s="1" t="n">
         <v>45609</v>
       </c>
-      <c r="G8" s="1">
+      <c r="G8" s="1" t="n">
         <v>45637</v>
       </c>
-      <c r="H8">
+      <c r="H8" t="n">
         <v>29</v>
       </c>
       <c r="I8" t="s">
@@ -1824,16 +1812,16 @@
     </row>
   </sheetData>
   <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
-  <pageSetup paperSize="9" orientation="portrait" horizontalDpi="300" verticalDpi="300"/>
+  <pageSetup paperSize="9" orientation="portrait" horizontalDpi="300" verticalDpi="300" r:id="rId2"/>
 </worksheet>
 </file>
 
 <file path=xl/worksheets/sheet4.xml><?xml version="1.0" encoding="utf-8"?>
-<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{00000000-0001-0000-0300-000000000000}">
-  <dimension ref="A1:K9"/>
-  <sheetFormatPr defaultColWidth="11.42578125" defaultRowHeight="15" x14ac:dyDescent="0.25"/>
+<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:xdr="http://schemas.openxmlformats.org/drawingml/2006/spreadsheetDrawing" xmlns:x14="http://schemas.microsoft.com/office/spreadsheetml/2009/9/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3">
+  <dimension ref="A1"/>
+  <sheetFormatPr defaultRowHeight="15.0" baseColWidth="10"/>
   <sheetData>
-    <row r="1" spans="1:11" x14ac:dyDescent="0.25">
+    <row r="1">
       <c r="A1" t="s">
         <v>0</v>
       </c>
@@ -1868,7 +1856,7 @@
         <v>10</v>
       </c>
     </row>
-    <row r="2" spans="1:11" x14ac:dyDescent="0.25">
+    <row r="2">
       <c r="A2" t="s">
         <v>92</v>
       </c>
@@ -1881,16 +1869,16 @@
       <c r="D2" t="s">
         <v>33</v>
       </c>
-      <c r="E2">
-        <v>0</v>
-      </c>
-      <c r="F2" s="1">
+      <c r="E2" t="n">
+        <v>0</v>
+      </c>
+      <c r="F2" s="1" t="n">
         <v>45628</v>
       </c>
-      <c r="G2" s="1">
+      <c r="G2" s="1" t="n">
         <v>45749</v>
       </c>
-      <c r="H2">
+      <c r="H2" t="n">
         <v>122</v>
       </c>
       <c r="I2" t="s">
@@ -1903,7 +1891,7 @@
         <v>73</v>
       </c>
     </row>
-    <row r="3" spans="1:11" x14ac:dyDescent="0.25">
+    <row r="3">
       <c r="A3" t="s">
         <v>92</v>
       </c>
@@ -1916,16 +1904,16 @@
       <c r="D3" t="s">
         <v>19</v>
       </c>
-      <c r="E3">
-        <v>0</v>
-      </c>
-      <c r="F3" s="1">
+      <c r="E3" t="n">
+        <v>0</v>
+      </c>
+      <c r="F3" s="1" t="n">
         <v>45628</v>
       </c>
-      <c r="G3" s="1">
+      <c r="G3" s="1" t="n">
         <v>45742</v>
       </c>
-      <c r="H3">
+      <c r="H3" t="n">
         <v>115</v>
       </c>
       <c r="I3" t="s">
@@ -1938,7 +1926,7 @@
         <v>65</v>
       </c>
     </row>
-    <row r="4" spans="1:11" x14ac:dyDescent="0.25">
+    <row r="4">
       <c r="A4" t="s">
         <v>92</v>
       </c>
@@ -1951,16 +1939,16 @@
       <c r="D4" t="s">
         <v>80</v>
       </c>
-      <c r="E4">
-        <v>0</v>
-      </c>
-      <c r="F4" s="1">
+      <c r="E4" t="n">
+        <v>0</v>
+      </c>
+      <c r="F4" s="1" t="n">
         <v>45629</v>
       </c>
-      <c r="G4" s="1">
+      <c r="G4" s="1" t="n">
         <v>45709</v>
       </c>
-      <c r="H4">
+      <c r="H4" t="n">
         <v>81</v>
       </c>
       <c r="I4" t="s">
@@ -1973,7 +1961,7 @@
         <v>57</v>
       </c>
     </row>
-    <row r="5" spans="1:11" x14ac:dyDescent="0.25">
+    <row r="5">
       <c r="A5" t="s">
         <v>92</v>
       </c>
@@ -1986,16 +1974,16 @@
       <c r="D5" t="s">
         <v>103</v>
       </c>
-      <c r="E5">
+      <c r="E5" t="n">
         <v>1</v>
       </c>
-      <c r="F5" s="1">
+      <c r="F5" s="1" t="n">
         <v>45630</v>
       </c>
-      <c r="G5" s="1">
+      <c r="G5" s="1" t="n">
         <v>45826</v>
       </c>
-      <c r="H5">
+      <c r="H5" t="n">
         <v>197</v>
       </c>
       <c r="I5" t="s">
@@ -2008,7 +1996,7 @@
         <v>52</v>
       </c>
     </row>
-    <row r="6" spans="1:11" x14ac:dyDescent="0.25">
+    <row r="6">
       <c r="A6" t="s">
         <v>92</v>
       </c>
@@ -2021,16 +2009,16 @@
       <c r="D6" t="s">
         <v>107</v>
       </c>
-      <c r="E6">
-        <v>0</v>
-      </c>
-      <c r="F6" s="1">
+      <c r="E6" t="n">
+        <v>0</v>
+      </c>
+      <c r="F6" s="1" t="n">
         <v>45635</v>
       </c>
-      <c r="G6" s="1">
+      <c r="G6" s="1" t="n">
         <v>45799</v>
       </c>
-      <c r="H6">
+      <c r="H6" t="n">
         <v>165</v>
       </c>
       <c r="I6" t="s">
@@ -2043,7 +2031,7 @@
         <v>62</v>
       </c>
     </row>
-    <row r="7" spans="1:11" x14ac:dyDescent="0.25">
+    <row r="7">
       <c r="A7" t="s">
         <v>92</v>
       </c>
@@ -2056,16 +2044,16 @@
       <c r="D7" t="s">
         <v>68</v>
       </c>
-      <c r="E7">
-        <v>0</v>
-      </c>
-      <c r="F7" s="1">
+      <c r="E7" t="n">
+        <v>0</v>
+      </c>
+      <c r="F7" s="1" t="n">
         <v>45635</v>
       </c>
-      <c r="G7" s="1">
+      <c r="G7" s="1" t="n">
         <v>45777</v>
       </c>
-      <c r="H7">
+      <c r="H7" t="n">
         <v>143</v>
       </c>
       <c r="I7" t="s">
@@ -2078,7 +2066,7 @@
         <v>48</v>
       </c>
     </row>
-    <row r="8" spans="1:11" x14ac:dyDescent="0.25">
+    <row r="8">
       <c r="A8" t="s">
         <v>92</v>
       </c>
@@ -2091,16 +2079,16 @@
       <c r="D8" t="s">
         <v>80</v>
       </c>
-      <c r="E8">
-        <v>0</v>
-      </c>
-      <c r="F8" s="1">
+      <c r="E8" t="n">
+        <v>0</v>
+      </c>
+      <c r="F8" s="1" t="n">
         <v>45636</v>
       </c>
-      <c r="G8" s="1">
+      <c r="G8" s="1" t="n">
         <v>45806</v>
       </c>
-      <c r="H8">
+      <c r="H8" t="n">
         <v>171</v>
       </c>
       <c r="I8" t="s">
@@ -2113,7 +2101,7 @@
         <v>39</v>
       </c>
     </row>
-    <row r="9" spans="1:11" x14ac:dyDescent="0.25">
+    <row r="9">
       <c r="A9" t="s">
         <v>92</v>
       </c>
@@ -2126,16 +2114,16 @@
       <c r="D9" t="s">
         <v>51</v>
       </c>
-      <c r="E9">
-        <v>0</v>
-      </c>
-      <c r="F9" s="1">
+      <c r="E9" t="n">
+        <v>0</v>
+      </c>
+      <c r="F9" s="1" t="n">
         <v>45637</v>
       </c>
-      <c r="G9" s="1">
+      <c r="G9" s="1" t="n">
         <v>45714</v>
       </c>
-      <c r="H9">
+      <c r="H9" t="n">
         <v>78</v>
       </c>
       <c r="I9" t="s">
@@ -2150,16 +2138,16 @@
     </row>
   </sheetData>
   <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
-  <pageSetup paperSize="9" orientation="portrait" horizontalDpi="300" verticalDpi="300"/>
+  <pageSetup paperSize="9" orientation="portrait" horizontalDpi="300" verticalDpi="300" r:id="rId2"/>
 </worksheet>
 </file>
 
 <file path=xl/worksheets/sheet5.xml><?xml version="1.0" encoding="utf-8"?>
-<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{00000000-0001-0000-0400-000000000000}">
-  <dimension ref="A1:K11"/>
-  <sheetFormatPr defaultColWidth="11.42578125" defaultRowHeight="15" x14ac:dyDescent="0.25"/>
+<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:xdr="http://schemas.openxmlformats.org/drawingml/2006/spreadsheetDrawing" xmlns:x14="http://schemas.microsoft.com/office/spreadsheetml/2009/9/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3">
+  <dimension ref="A1"/>
+  <sheetFormatPr defaultRowHeight="15.0" baseColWidth="10"/>
   <sheetData>
-    <row r="1" spans="1:11" x14ac:dyDescent="0.25">
+    <row r="1">
       <c r="A1" t="s">
         <v>0</v>
       </c>
@@ -2194,7 +2182,7 @@
         <v>10</v>
       </c>
     </row>
-    <row r="2" spans="1:11" x14ac:dyDescent="0.25">
+    <row r="2">
       <c r="A2" t="s">
         <v>115</v>
       </c>
@@ -2207,16 +2195,16 @@
       <c r="D2" t="s">
         <v>33</v>
       </c>
-      <c r="E2">
-        <v>0</v>
-      </c>
-      <c r="F2" s="1">
+      <c r="E2" t="n">
+        <v>0</v>
+      </c>
+      <c r="F2" s="1" t="n">
         <v>45670</v>
       </c>
-      <c r="G2" s="1">
+      <c r="G2" s="1" t="n">
         <v>45834</v>
       </c>
-      <c r="H2">
+      <c r="H2" t="n">
         <v>165</v>
       </c>
       <c r="I2" t="s">
@@ -2229,7 +2217,7 @@
         <v>65</v>
       </c>
     </row>
-    <row r="3" spans="1:11" x14ac:dyDescent="0.25">
+    <row r="3">
       <c r="A3" t="s">
         <v>115</v>
       </c>
@@ -2242,16 +2230,16 @@
       <c r="D3" t="s">
         <v>14</v>
       </c>
-      <c r="E3">
-        <v>0</v>
-      </c>
-      <c r="F3" s="1">
+      <c r="E3" t="n">
+        <v>0</v>
+      </c>
+      <c r="F3" s="1" t="n">
         <v>45670</v>
       </c>
-      <c r="G3" s="1">
+      <c r="G3" s="1" t="n">
         <v>45828</v>
       </c>
-      <c r="H3">
+      <c r="H3" t="n">
         <v>159</v>
       </c>
       <c r="I3" t="s">
@@ -2264,7 +2252,7 @@
         <v>48</v>
       </c>
     </row>
-    <row r="4" spans="1:11" x14ac:dyDescent="0.25">
+    <row r="4">
       <c r="A4" t="s">
         <v>115</v>
       </c>
@@ -2277,16 +2265,16 @@
       <c r="D4" t="s">
         <v>77</v>
       </c>
-      <c r="E4">
-        <v>0</v>
-      </c>
-      <c r="F4" s="1">
+      <c r="E4" t="n">
+        <v>0</v>
+      </c>
+      <c r="F4" s="1" t="n">
         <v>45671</v>
       </c>
-      <c r="G4" s="1">
+      <c r="G4" s="1" t="n">
         <v>45737</v>
       </c>
-      <c r="H4">
+      <c r="H4" t="n">
         <v>67</v>
       </c>
       <c r="I4" t="s">
@@ -2299,7 +2287,7 @@
         <v>52</v>
       </c>
     </row>
-    <row r="5" spans="1:11" x14ac:dyDescent="0.25">
+    <row r="5">
       <c r="A5" t="s">
         <v>115</v>
       </c>
@@ -2312,16 +2300,16 @@
       <c r="D5" t="s">
         <v>19</v>
       </c>
-      <c r="E5">
-        <v>0</v>
-      </c>
-      <c r="F5" s="1">
+      <c r="E5" t="n">
+        <v>0</v>
+      </c>
+      <c r="F5" s="1" t="n">
         <v>45671</v>
       </c>
-      <c r="G5" s="1">
+      <c r="G5" s="1" t="n">
         <v>45714</v>
       </c>
-      <c r="H5">
+      <c r="H5" t="n">
         <v>44</v>
       </c>
       <c r="I5" t="s">
@@ -2334,7 +2322,7 @@
         <v>73</v>
       </c>
     </row>
-    <row r="6" spans="1:11" x14ac:dyDescent="0.25">
+    <row r="6">
       <c r="A6" t="s">
         <v>115</v>
       </c>
@@ -2347,16 +2335,16 @@
       <c r="D6" t="s">
         <v>33</v>
       </c>
-      <c r="E6">
-        <v>0</v>
-      </c>
-      <c r="F6" s="1">
+      <c r="E6" t="n">
+        <v>0</v>
+      </c>
+      <c r="F6" s="1" t="n">
         <v>45672</v>
       </c>
-      <c r="G6" s="1">
+      <c r="G6" s="1" t="n">
         <v>45835</v>
       </c>
-      <c r="H6">
+      <c r="H6" t="n">
         <v>164</v>
       </c>
       <c r="I6" t="s">
@@ -2369,7 +2357,7 @@
         <v>69</v>
       </c>
     </row>
-    <row r="7" spans="1:11" x14ac:dyDescent="0.25">
+    <row r="7">
       <c r="A7" t="s">
         <v>115</v>
       </c>
@@ -2382,16 +2370,16 @@
       <c r="D7" t="s">
         <v>33</v>
       </c>
-      <c r="E7">
-        <v>0</v>
-      </c>
-      <c r="F7" s="1">
+      <c r="E7" t="n">
+        <v>0</v>
+      </c>
+      <c r="F7" s="1" t="n">
         <v>45678</v>
       </c>
-      <c r="G7" s="1">
+      <c r="G7" s="1" t="n">
         <v>45828</v>
       </c>
-      <c r="H7">
+      <c r="H7" t="n">
         <v>151</v>
       </c>
       <c r="I7" t="s">
@@ -2404,7 +2392,7 @@
         <v>62</v>
       </c>
     </row>
-    <row r="8" spans="1:11" x14ac:dyDescent="0.25">
+    <row r="8">
       <c r="A8" t="s">
         <v>115</v>
       </c>
@@ -2417,16 +2405,16 @@
       <c r="D8" t="s">
         <v>72</v>
       </c>
-      <c r="E8">
-        <v>0</v>
-      </c>
-      <c r="F8" s="1">
+      <c r="E8" t="n">
+        <v>0</v>
+      </c>
+      <c r="F8" s="1" t="n">
         <v>45678</v>
       </c>
-      <c r="G8" s="1">
+      <c r="G8" s="1" t="n">
         <v>45828</v>
       </c>
-      <c r="H8">
+      <c r="H8" t="n">
         <v>151</v>
       </c>
       <c r="I8" t="s">
@@ -2439,7 +2427,7 @@
         <v>39</v>
       </c>
     </row>
-    <row r="9" spans="1:11" x14ac:dyDescent="0.25">
+    <row r="9">
       <c r="A9" t="s">
         <v>115</v>
       </c>
@@ -2452,16 +2440,16 @@
       <c r="D9" t="s">
         <v>33</v>
       </c>
-      <c r="E9">
-        <v>0</v>
-      </c>
-      <c r="F9" s="1">
+      <c r="E9" t="n">
+        <v>0</v>
+      </c>
+      <c r="F9" s="1" t="n">
         <v>45679</v>
       </c>
-      <c r="G9" s="1">
+      <c r="G9" s="1" t="n">
         <v>45792</v>
       </c>
-      <c r="H9">
+      <c r="H9" t="n">
         <v>114</v>
       </c>
       <c r="I9" t="s">
@@ -2474,7 +2462,7 @@
         <v>45</v>
       </c>
     </row>
-    <row r="10" spans="1:11" x14ac:dyDescent="0.25">
+    <row r="10">
       <c r="A10" t="s">
         <v>115</v>
       </c>
@@ -2487,16 +2475,16 @@
       <c r="D10" t="s">
         <v>60</v>
       </c>
-      <c r="E10">
-        <v>0</v>
-      </c>
-      <c r="F10" s="1">
+      <c r="E10" t="n">
+        <v>0</v>
+      </c>
+      <c r="F10" s="1" t="n">
         <v>45679</v>
       </c>
-      <c r="G10" s="1">
+      <c r="G10" s="1" t="n">
         <v>45764</v>
       </c>
-      <c r="H10">
+      <c r="H10" t="n">
         <v>86</v>
       </c>
       <c r="I10" t="s">
@@ -2509,7 +2497,7 @@
         <v>57</v>
       </c>
     </row>
-    <row r="11" spans="1:11" x14ac:dyDescent="0.25">
+    <row r="11">
       <c r="A11" t="s">
         <v>115</v>
       </c>
@@ -2522,16 +2510,16 @@
       <c r="D11" t="s">
         <v>80</v>
       </c>
-      <c r="E11">
+      <c r="E11" t="n">
         <v>1</v>
       </c>
-      <c r="F11" s="1">
+      <c r="F11" s="1" t="n">
         <v>45667</v>
       </c>
-      <c r="G11" s="1">
+      <c r="G11" s="1" t="n">
         <v>45674</v>
       </c>
-      <c r="H11">
+      <c r="H11" t="n">
         <v>8</v>
       </c>
       <c r="I11" t="s">
@@ -2546,16 +2534,16 @@
     </row>
   </sheetData>
   <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
-  <pageSetup paperSize="9" orientation="portrait" horizontalDpi="300" verticalDpi="300"/>
+  <pageSetup paperSize="9" orientation="portrait" horizontalDpi="300" verticalDpi="300" r:id="rId2"/>
 </worksheet>
 </file>
 
 <file path=xl/worksheets/sheet6.xml><?xml version="1.0" encoding="utf-8"?>
-<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{00000000-0001-0000-0500-000000000000}">
-  <dimension ref="A1:K9"/>
-  <sheetFormatPr defaultColWidth="11.42578125" defaultRowHeight="15" x14ac:dyDescent="0.25"/>
+<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:xdr="http://schemas.openxmlformats.org/drawingml/2006/spreadsheetDrawing" xmlns:x14="http://schemas.microsoft.com/office/spreadsheetml/2009/9/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3">
+  <dimension ref="A1"/>
+  <sheetFormatPr defaultRowHeight="15.0" baseColWidth="10"/>
   <sheetData>
-    <row r="1" spans="1:11" x14ac:dyDescent="0.25">
+    <row r="1">
       <c r="A1" t="s">
         <v>0</v>
       </c>
@@ -2590,7 +2578,7 @@
         <v>10</v>
       </c>
     </row>
-    <row r="2" spans="1:11" x14ac:dyDescent="0.25">
+    <row r="2">
       <c r="A2" t="s">
         <v>138</v>
       </c>
@@ -2603,16 +2591,16 @@
       <c r="D2" t="s">
         <v>33</v>
       </c>
-      <c r="E2">
-        <v>0</v>
-      </c>
-      <c r="F2" s="1">
+      <c r="E2" t="n">
+        <v>0</v>
+      </c>
+      <c r="F2" s="1" t="n">
         <v>45712</v>
       </c>
-      <c r="G2" s="1">
+      <c r="G2" s="1" t="n">
         <v>45834</v>
       </c>
-      <c r="H2">
+      <c r="H2" t="n">
         <v>123</v>
       </c>
       <c r="I2" t="s">
@@ -2625,7 +2613,7 @@
         <v>57</v>
       </c>
     </row>
-    <row r="3" spans="1:11" x14ac:dyDescent="0.25">
+    <row r="3">
       <c r="A3" t="s">
         <v>138</v>
       </c>
@@ -2638,16 +2626,16 @@
       <c r="D3" t="s">
         <v>103</v>
       </c>
-      <c r="E3">
-        <v>0</v>
-      </c>
-      <c r="F3" s="1">
+      <c r="E3" t="n">
+        <v>0</v>
+      </c>
+      <c r="F3" s="1" t="n">
         <v>45713</v>
       </c>
-      <c r="G3" s="1">
+      <c r="G3" s="1" t="n">
         <v>45828</v>
       </c>
-      <c r="H3">
+      <c r="H3" t="n">
         <v>116</v>
       </c>
       <c r="I3" t="s">
@@ -2660,7 +2648,7 @@
         <v>62</v>
       </c>
     </row>
-    <row r="4" spans="1:11" x14ac:dyDescent="0.25">
+    <row r="4">
       <c r="A4" t="s">
         <v>138</v>
       </c>
@@ -2673,16 +2661,16 @@
       <c r="D4" t="s">
         <v>103</v>
       </c>
-      <c r="E4">
-        <v>0</v>
-      </c>
-      <c r="F4" s="1">
+      <c r="E4" t="n">
+        <v>0</v>
+      </c>
+      <c r="F4" s="1" t="n">
         <v>45713</v>
       </c>
-      <c r="G4" s="1">
+      <c r="G4" s="1" t="n">
         <v>45826</v>
       </c>
-      <c r="H4">
+      <c r="H4" t="n">
         <v>114</v>
       </c>
       <c r="I4" t="s">
@@ -2695,7 +2683,7 @@
         <v>52</v>
       </c>
     </row>
-    <row r="5" spans="1:11" x14ac:dyDescent="0.25">
+    <row r="5">
       <c r="A5" t="s">
         <v>138</v>
       </c>
@@ -2708,16 +2696,16 @@
       <c r="D5" t="s">
         <v>103</v>
       </c>
-      <c r="E5">
-        <v>0</v>
-      </c>
-      <c r="F5" s="1">
+      <c r="E5" t="n">
+        <v>0</v>
+      </c>
+      <c r="F5" s="1" t="n">
         <v>45714</v>
       </c>
-      <c r="G5" s="1">
+      <c r="G5" s="1" t="n">
         <v>45813</v>
       </c>
-      <c r="H5">
+      <c r="H5" t="n">
         <v>100</v>
       </c>
       <c r="I5" t="s">
@@ -2730,7 +2718,7 @@
         <v>65</v>
       </c>
     </row>
-    <row r="6" spans="1:11" x14ac:dyDescent="0.25">
+    <row r="6">
       <c r="A6" t="s">
         <v>138</v>
       </c>
@@ -2743,16 +2731,16 @@
       <c r="D6" t="s">
         <v>72</v>
       </c>
-      <c r="E6">
-        <v>0</v>
-      </c>
-      <c r="F6" s="1">
+      <c r="E6" t="n">
+        <v>0</v>
+      </c>
+      <c r="F6" s="1" t="n">
         <v>45719</v>
       </c>
-      <c r="G6" s="1">
+      <c r="G6" s="1" t="n">
         <v>45813</v>
       </c>
-      <c r="H6">
+      <c r="H6" t="n">
         <v>95</v>
       </c>
       <c r="I6" t="s">
@@ -2765,7 +2753,7 @@
         <v>73</v>
       </c>
     </row>
-    <row r="7" spans="1:11" x14ac:dyDescent="0.25">
+    <row r="7">
       <c r="A7" t="s">
         <v>138</v>
       </c>
@@ -2778,16 +2766,16 @@
       <c r="D7" t="s">
         <v>60</v>
       </c>
-      <c r="E7">
-        <v>0</v>
-      </c>
-      <c r="F7" s="1">
+      <c r="E7" t="n">
+        <v>0</v>
+      </c>
+      <c r="F7" s="1" t="n">
         <v>45719</v>
       </c>
-      <c r="G7" s="1">
+      <c r="G7" s="1" t="n">
         <v>45813</v>
       </c>
-      <c r="H7">
+      <c r="H7" t="n">
         <v>95</v>
       </c>
       <c r="I7" t="s">
@@ -2800,7 +2788,7 @@
         <v>69</v>
       </c>
     </row>
-    <row r="8" spans="1:11" x14ac:dyDescent="0.25">
+    <row r="8">
       <c r="A8" t="s">
         <v>138</v>
       </c>
@@ -2813,16 +2801,16 @@
       <c r="D8" t="s">
         <v>154</v>
       </c>
-      <c r="E8">
-        <v>0</v>
-      </c>
-      <c r="F8" s="1">
+      <c r="E8" t="n">
+        <v>0</v>
+      </c>
+      <c r="F8" s="1" t="n">
         <v>45720</v>
       </c>
-      <c r="G8" s="1">
+      <c r="G8" s="1" t="n">
         <v>45813</v>
       </c>
-      <c r="H8">
+      <c r="H8" t="n">
         <v>94</v>
       </c>
       <c r="I8" t="s">
@@ -2835,7 +2823,7 @@
         <v>45</v>
       </c>
     </row>
-    <row r="9" spans="1:11" x14ac:dyDescent="0.25">
+    <row r="9">
       <c r="A9" t="s">
         <v>138</v>
       </c>
@@ -2848,16 +2836,16 @@
       <c r="D9" t="s">
         <v>33</v>
       </c>
-      <c r="E9">
-        <v>0</v>
-      </c>
-      <c r="F9" s="1">
+      <c r="E9" t="n">
+        <v>0</v>
+      </c>
+      <c r="F9" s="1" t="n">
         <v>45721</v>
       </c>
-      <c r="G9" s="1">
+      <c r="G9" s="1" t="n">
         <v>45826</v>
       </c>
-      <c r="H9">
+      <c r="H9" t="n">
         <v>106</v>
       </c>
       <c r="I9" t="s">
@@ -2872,16 +2860,16 @@
     </row>
   </sheetData>
   <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
-  <pageSetup paperSize="9" orientation="portrait" horizontalDpi="300" verticalDpi="300"/>
+  <pageSetup paperSize="9" orientation="portrait" horizontalDpi="300" verticalDpi="300" r:id="rId2"/>
 </worksheet>
 </file>
 
 <file path=xl/worksheets/sheet7.xml><?xml version="1.0" encoding="utf-8"?>
-<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{00000000-0001-0000-0600-000000000000}">
-  <dimension ref="A1:K10"/>
-  <sheetFormatPr defaultColWidth="11.42578125" defaultRowHeight="15" x14ac:dyDescent="0.25"/>
+<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:xdr="http://schemas.openxmlformats.org/drawingml/2006/spreadsheetDrawing" xmlns:x14="http://schemas.microsoft.com/office/spreadsheetml/2009/9/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3">
+  <dimension ref="A1"/>
+  <sheetFormatPr defaultRowHeight="15.0" baseColWidth="10"/>
   <sheetData>
-    <row r="1" spans="1:11" x14ac:dyDescent="0.25">
+    <row r="1">
       <c r="A1" t="s">
         <v>0</v>
       </c>
@@ -2916,7 +2904,7 @@
         <v>10</v>
       </c>
     </row>
-    <row r="2" spans="1:11" x14ac:dyDescent="0.25">
+    <row r="2">
       <c r="A2" t="s">
         <v>157</v>
       </c>
@@ -2929,13 +2917,17 @@
       <c r="D2" t="s">
         <v>160</v>
       </c>
-      <c r="E2">
+      <c r="E2" t="n">
         <v>0</v>
       </c>
       <c r="F2" s="1"/>
       <c r="G2" s="1"/>
-    </row>
-    <row r="3" spans="1:11" x14ac:dyDescent="0.25">
+      <c r="H2"/>
+      <c r="I2"/>
+      <c r="J2"/>
+      <c r="K2"/>
+    </row>
+    <row r="3">
       <c r="A3" t="s">
         <v>157</v>
       </c>
@@ -2948,16 +2940,16 @@
       <c r="D3" t="s">
         <v>51</v>
       </c>
-      <c r="E3">
-        <v>0</v>
-      </c>
-      <c r="F3" s="1">
+      <c r="E3" t="n">
+        <v>0</v>
+      </c>
+      <c r="F3" s="1" t="n">
         <v>45740</v>
       </c>
-      <c r="G3" s="1">
+      <c r="G3" s="1" t="n">
         <v>45834</v>
       </c>
-      <c r="H3">
+      <c r="H3" t="n">
         <v>95</v>
       </c>
       <c r="I3" t="s">
@@ -2970,7 +2962,7 @@
         <v>73</v>
       </c>
     </row>
-    <row r="4" spans="1:11" x14ac:dyDescent="0.25">
+    <row r="4">
       <c r="A4" t="s">
         <v>157</v>
       </c>
@@ -2983,16 +2975,16 @@
       <c r="D4" t="s">
         <v>33</v>
       </c>
-      <c r="E4">
-        <v>0</v>
-      </c>
-      <c r="F4" s="1">
+      <c r="E4" t="n">
+        <v>0</v>
+      </c>
+      <c r="F4" s="1" t="n">
         <v>45741</v>
       </c>
-      <c r="G4" s="1">
+      <c r="G4" s="1" t="n">
         <v>45826</v>
       </c>
-      <c r="H4">
+      <c r="H4" t="n">
         <v>86</v>
       </c>
       <c r="I4" t="s">
@@ -3005,7 +2997,7 @@
         <v>69</v>
       </c>
     </row>
-    <row r="5" spans="1:11" x14ac:dyDescent="0.25">
+    <row r="5">
       <c r="A5" t="s">
         <v>157</v>
       </c>
@@ -3018,16 +3010,16 @@
       <c r="D5" t="s">
         <v>19</v>
       </c>
-      <c r="E5">
-        <v>0</v>
-      </c>
-      <c r="F5" s="1">
+      <c r="E5" t="n">
+        <v>0</v>
+      </c>
+      <c r="F5" s="1" t="n">
         <v>45741</v>
       </c>
-      <c r="G5" s="1">
+      <c r="G5" s="1" t="n">
         <v>45826</v>
       </c>
-      <c r="H5">
+      <c r="H5" t="n">
         <v>86</v>
       </c>
       <c r="I5" t="s">
@@ -3040,7 +3032,7 @@
         <v>69</v>
       </c>
     </row>
-    <row r="6" spans="1:11" x14ac:dyDescent="0.25">
+    <row r="6">
       <c r="A6" t="s">
         <v>157</v>
       </c>
@@ -3053,16 +3045,16 @@
       <c r="D6" t="s">
         <v>33</v>
       </c>
-      <c r="E6">
-        <v>0</v>
-      </c>
-      <c r="F6" s="1">
+      <c r="E6" t="n">
+        <v>0</v>
+      </c>
+      <c r="F6" s="1" t="n">
         <v>45742</v>
       </c>
-      <c r="G6" s="1">
+      <c r="G6" s="1" t="n">
         <v>45835</v>
       </c>
-      <c r="H6">
+      <c r="H6" t="n">
         <v>94</v>
       </c>
       <c r="I6" t="s">
@@ -3075,7 +3067,7 @@
         <v>45</v>
       </c>
     </row>
-    <row r="7" spans="1:11" x14ac:dyDescent="0.25">
+    <row r="7">
       <c r="A7" t="s">
         <v>157</v>
       </c>
@@ -3088,16 +3080,16 @@
       <c r="D7" t="s">
         <v>171</v>
       </c>
-      <c r="E7">
-        <v>0</v>
-      </c>
-      <c r="F7" s="1">
+      <c r="E7" t="n">
+        <v>0</v>
+      </c>
+      <c r="F7" s="1" t="n">
         <v>45747</v>
       </c>
-      <c r="G7" s="1">
+      <c r="G7" s="1" t="n">
         <v>45813</v>
       </c>
-      <c r="H7">
+      <c r="H7" t="n">
         <v>67</v>
       </c>
       <c r="I7" t="s">
@@ -3110,7 +3102,7 @@
         <v>57</v>
       </c>
     </row>
-    <row r="8" spans="1:11" x14ac:dyDescent="0.25">
+    <row r="8">
       <c r="A8" t="s">
         <v>157</v>
       </c>
@@ -3123,16 +3115,16 @@
       <c r="D8" t="s">
         <v>33</v>
       </c>
-      <c r="E8">
-        <v>0</v>
-      </c>
-      <c r="F8" s="1">
+      <c r="E8" t="n">
+        <v>0</v>
+      </c>
+      <c r="F8" s="1" t="n">
         <v>45747</v>
       </c>
-      <c r="G8" s="1">
+      <c r="G8" s="1" t="n">
         <v>45820</v>
       </c>
-      <c r="H8">
+      <c r="H8" t="n">
         <v>74</v>
       </c>
       <c r="I8" t="s">
@@ -3145,7 +3137,7 @@
         <v>65</v>
       </c>
     </row>
-    <row r="9" spans="1:11" x14ac:dyDescent="0.25">
+    <row r="9">
       <c r="A9" t="s">
         <v>157</v>
       </c>
@@ -3158,16 +3150,16 @@
       <c r="D9" t="s">
         <v>60</v>
       </c>
-      <c r="E9">
-        <v>0</v>
-      </c>
-      <c r="F9" s="1">
+      <c r="E9" t="n">
+        <v>0</v>
+      </c>
+      <c r="F9" s="1" t="n">
         <v>45748</v>
       </c>
-      <c r="G9" s="1">
+      <c r="G9" s="1" t="n">
         <v>45828</v>
       </c>
-      <c r="H9">
+      <c r="H9" t="n">
         <v>81</v>
       </c>
       <c r="I9" t="s">
@@ -3180,7 +3172,7 @@
         <v>52</v>
       </c>
     </row>
-    <row r="10" spans="1:11" x14ac:dyDescent="0.25">
+    <row r="10">
       <c r="A10" t="s">
         <v>157</v>
       </c>
@@ -3193,16 +3185,16 @@
       <c r="D10" t="s">
         <v>51</v>
       </c>
-      <c r="E10">
-        <v>0</v>
-      </c>
-      <c r="F10" s="1">
+      <c r="E10" t="n">
+        <v>0</v>
+      </c>
+      <c r="F10" s="1" t="n">
         <v>45749</v>
       </c>
-      <c r="G10" s="1">
+      <c r="G10" s="1" t="n">
         <v>45834</v>
       </c>
-      <c r="H10">
+      <c r="H10" t="n">
         <v>86</v>
       </c>
       <c r="I10" t="s">
@@ -3217,16 +3209,16 @@
     </row>
   </sheetData>
   <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
-  <pageSetup paperSize="9" orientation="portrait" horizontalDpi="300" verticalDpi="300"/>
+  <pageSetup paperSize="9" orientation="portrait" horizontalDpi="300" verticalDpi="300" r:id="rId2"/>
 </worksheet>
 </file>
 
 <file path=xl/worksheets/sheet8.xml><?xml version="1.0" encoding="utf-8"?>
-<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{00000000-0001-0000-0700-000000000000}">
-  <dimension ref="A1:K11"/>
-  <sheetFormatPr defaultColWidth="11.42578125" defaultRowHeight="15" x14ac:dyDescent="0.25"/>
+<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:xdr="http://schemas.openxmlformats.org/drawingml/2006/spreadsheetDrawing" xmlns:x14="http://schemas.microsoft.com/office/spreadsheetml/2009/9/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3">
+  <dimension ref="A1"/>
+  <sheetFormatPr defaultRowHeight="15.0" baseColWidth="10"/>
   <sheetData>
-    <row r="1" spans="1:11" x14ac:dyDescent="0.25">
+    <row r="1">
       <c r="A1" t="s">
         <v>0</v>
       </c>
@@ -3261,7 +3253,7 @@
         <v>10</v>
       </c>
     </row>
-    <row r="2" spans="1:11" x14ac:dyDescent="0.25">
+    <row r="2">
       <c r="A2" t="s">
         <v>178</v>
       </c>
@@ -3274,16 +3266,16 @@
       <c r="D2" t="s">
         <v>33</v>
       </c>
-      <c r="E2">
-        <v>0</v>
-      </c>
-      <c r="F2" s="1">
+      <c r="E2" t="n">
+        <v>0</v>
+      </c>
+      <c r="F2" s="1" t="n">
         <v>45768</v>
       </c>
-      <c r="G2" s="1">
+      <c r="G2" s="1" t="n">
         <v>45835</v>
       </c>
-      <c r="H2">
+      <c r="H2" t="n">
         <v>68</v>
       </c>
       <c r="I2" t="s">
@@ -3296,7 +3288,7 @@
         <v>39</v>
       </c>
     </row>
-    <row r="3" spans="1:11" x14ac:dyDescent="0.25">
+    <row r="3">
       <c r="A3" t="s">
         <v>178</v>
       </c>
@@ -3309,16 +3301,16 @@
       <c r="D3" t="s">
         <v>51</v>
       </c>
-      <c r="E3">
-        <v>0</v>
-      </c>
-      <c r="F3" s="1">
+      <c r="E3" t="n">
+        <v>0</v>
+      </c>
+      <c r="F3" s="1" t="n">
         <v>45768</v>
       </c>
-      <c r="G3" s="1">
+      <c r="G3" s="1" t="n">
         <v>45820</v>
       </c>
-      <c r="H3">
+      <c r="H3" t="n">
         <v>53</v>
       </c>
       <c r="I3" t="s">
@@ -3331,7 +3323,7 @@
         <v>57</v>
       </c>
     </row>
-    <row r="4" spans="1:11" x14ac:dyDescent="0.25">
+    <row r="4">
       <c r="A4" t="s">
         <v>178</v>
       </c>
@@ -3344,16 +3336,16 @@
       <c r="D4" t="s">
         <v>51</v>
       </c>
-      <c r="E4">
-        <v>0</v>
-      </c>
-      <c r="F4" s="1">
+      <c r="E4" t="n">
+        <v>0</v>
+      </c>
+      <c r="F4" s="1" t="n">
         <v>45769</v>
       </c>
-      <c r="G4" s="1">
+      <c r="G4" s="1" t="n">
         <v>45835</v>
       </c>
-      <c r="H4">
+      <c r="H4" t="n">
         <v>67</v>
       </c>
       <c r="I4" t="s">
@@ -3366,7 +3358,7 @@
         <v>73</v>
       </c>
     </row>
-    <row r="5" spans="1:11" x14ac:dyDescent="0.25">
+    <row r="5">
       <c r="A5" t="s">
         <v>178</v>
       </c>
@@ -3379,16 +3371,16 @@
       <c r="D5" t="s">
         <v>107</v>
       </c>
-      <c r="E5">
-        <v>0</v>
-      </c>
-      <c r="F5" s="1">
+      <c r="E5" t="n">
+        <v>0</v>
+      </c>
+      <c r="F5" s="1" t="n">
         <v>45769</v>
       </c>
-      <c r="G5" s="1">
+      <c r="G5" s="1" t="n">
         <v>45820</v>
       </c>
-      <c r="H5">
+      <c r="H5" t="n">
         <v>52</v>
       </c>
       <c r="I5" t="s">
@@ -3401,7 +3393,7 @@
         <v>62</v>
       </c>
     </row>
-    <row r="6" spans="1:11" x14ac:dyDescent="0.25">
+    <row r="6">
       <c r="A6" t="s">
         <v>178</v>
       </c>
@@ -3414,16 +3406,16 @@
       <c r="D6" t="s">
         <v>80</v>
       </c>
-      <c r="E6">
-        <v>0</v>
-      </c>
-      <c r="F6" s="1">
+      <c r="E6" t="n">
+        <v>0</v>
+      </c>
+      <c r="F6" s="1" t="n">
         <v>45770</v>
       </c>
-      <c r="G6" s="1">
+      <c r="G6" s="1" t="n">
         <v>45828</v>
       </c>
-      <c r="H6">
+      <c r="H6" t="n">
         <v>59</v>
       </c>
       <c r="I6" t="s">
@@ -3436,7 +3428,7 @@
         <v>39</v>
       </c>
     </row>
-    <row r="7" spans="1:11" x14ac:dyDescent="0.25">
+    <row r="7">
       <c r="A7" t="s">
         <v>178</v>
       </c>
@@ -3449,16 +3441,16 @@
       <c r="D7" t="s">
         <v>42</v>
       </c>
-      <c r="E7">
-        <v>0</v>
-      </c>
-      <c r="F7" s="1">
+      <c r="E7" t="n">
+        <v>0</v>
+      </c>
+      <c r="F7" s="1" t="n">
         <v>45775</v>
       </c>
-      <c r="G7" s="1">
+      <c r="G7" s="1" t="n">
         <v>45820</v>
       </c>
-      <c r="H7">
+      <c r="H7" t="n">
         <v>46</v>
       </c>
       <c r="I7" t="s">
@@ -3471,7 +3463,7 @@
         <v>52</v>
       </c>
     </row>
-    <row r="8" spans="1:11" x14ac:dyDescent="0.25">
+    <row r="8">
       <c r="A8" t="s">
         <v>178</v>
       </c>
@@ -3484,16 +3476,16 @@
       <c r="D8" t="s">
         <v>68</v>
       </c>
-      <c r="E8">
-        <v>0</v>
-      </c>
-      <c r="F8" s="1">
+      <c r="E8" t="n">
+        <v>0</v>
+      </c>
+      <c r="F8" s="1" t="n">
         <v>45775</v>
       </c>
-      <c r="G8" s="1">
+      <c r="G8" s="1" t="n">
         <v>45820</v>
       </c>
-      <c r="H8">
+      <c r="H8" t="n">
         <v>46</v>
       </c>
       <c r="I8" t="s">
@@ -3506,7 +3498,7 @@
         <v>69</v>
       </c>
     </row>
-    <row r="9" spans="1:11" x14ac:dyDescent="0.25">
+    <row r="9">
       <c r="A9" t="s">
         <v>178</v>
       </c>
@@ -3519,16 +3511,16 @@
       <c r="D9" t="s">
         <v>14</v>
       </c>
-      <c r="E9">
-        <v>0</v>
-      </c>
-      <c r="F9" s="1">
+      <c r="E9" t="n">
+        <v>0</v>
+      </c>
+      <c r="F9" s="1" t="n">
         <v>45776</v>
       </c>
-      <c r="G9" s="1">
+      <c r="G9" s="1" t="n">
         <v>45820</v>
       </c>
-      <c r="H9">
+      <c r="H9" t="n">
         <v>45</v>
       </c>
       <c r="I9" t="s">
@@ -3541,7 +3533,7 @@
         <v>48</v>
       </c>
     </row>
-    <row r="10" spans="1:11" x14ac:dyDescent="0.25">
+    <row r="10">
       <c r="A10" t="s">
         <v>178</v>
       </c>
@@ -3554,16 +3546,16 @@
       <c r="D10" t="s">
         <v>72</v>
       </c>
-      <c r="E10">
-        <v>0</v>
-      </c>
-      <c r="F10" s="1">
+      <c r="E10" t="n">
+        <v>0</v>
+      </c>
+      <c r="F10" s="1" t="n">
         <v>45776</v>
       </c>
-      <c r="G10" s="1">
+      <c r="G10" s="1" t="n">
         <v>45813</v>
       </c>
-      <c r="H10">
+      <c r="H10" t="n">
         <v>38</v>
       </c>
       <c r="I10" t="s">
@@ -3576,7 +3568,7 @@
         <v>16</v>
       </c>
     </row>
-    <row r="11" spans="1:11" x14ac:dyDescent="0.25">
+    <row r="11">
       <c r="A11" t="s">
         <v>178</v>
       </c>
@@ -3589,16 +3581,16 @@
       <c r="D11" t="s">
         <v>199</v>
       </c>
-      <c r="E11">
+      <c r="E11" t="n">
         <v>1</v>
       </c>
-      <c r="F11" s="1">
+      <c r="F11" s="1" t="n">
         <v>45777</v>
       </c>
-      <c r="G11" s="1">
+      <c r="G11" s="1" t="n">
         <v>45799</v>
       </c>
-      <c r="H11">
+      <c r="H11" t="n">
         <v>23</v>
       </c>
       <c r="I11" t="s">
@@ -3613,16 +3605,16 @@
     </row>
   </sheetData>
   <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
-  <pageSetup paperSize="9" orientation="portrait" horizontalDpi="300" verticalDpi="300"/>
+  <pageSetup paperSize="9" orientation="portrait" horizontalDpi="300" verticalDpi="300" r:id="rId2"/>
 </worksheet>
 </file>
 
 <file path=xl/worksheets/sheet9.xml><?xml version="1.0" encoding="utf-8"?>
-<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{00000000-0001-0000-0800-000000000000}">
-  <dimension ref="A1:K2"/>
-  <sheetFormatPr defaultColWidth="11.42578125" defaultRowHeight="15" x14ac:dyDescent="0.25"/>
+<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:xdr="http://schemas.openxmlformats.org/drawingml/2006/spreadsheetDrawing" xmlns:x14="http://schemas.microsoft.com/office/spreadsheetml/2009/9/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3">
+  <dimension ref="A1"/>
+  <sheetFormatPr defaultRowHeight="15.0" baseColWidth="10"/>
   <sheetData>
-    <row r="1" spans="1:11" x14ac:dyDescent="0.25">
+    <row r="1">
       <c r="A1" t="s">
         <v>0</v>
       </c>
@@ -3657,7 +3649,7 @@
         <v>10</v>
       </c>
     </row>
-    <row r="2" spans="1:11" x14ac:dyDescent="0.25">
+    <row r="2">
       <c r="A2" t="s">
         <v>201</v>
       </c>
@@ -3670,16 +3662,16 @@
       <c r="D2" t="s">
         <v>51</v>
       </c>
-      <c r="E2">
+      <c r="E2" t="n">
         <v>1</v>
       </c>
-      <c r="F2" s="1">
+      <c r="F2" s="1" t="n">
         <v>45792</v>
       </c>
-      <c r="G2" s="1">
+      <c r="G2" s="1" t="n">
         <v>45835</v>
       </c>
-      <c r="H2">
+      <c r="H2" t="n">
         <v>44</v>
       </c>
       <c r="I2" t="s">
@@ -3694,6 +3686,6 @@
     </row>
   </sheetData>
   <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
-  <pageSetup paperSize="9" orientation="portrait" horizontalDpi="300" verticalDpi="300"/>
+  <pageSetup paperSize="9" orientation="portrait" horizontalDpi="300" verticalDpi="300" r:id="rId2"/>
 </worksheet>
 </file>